--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Le moteur" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Le coût variable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Intégration &amp; contrôles" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +23,13 @@
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00&quot; €&quot;"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.0&quot; h&quot;"/>
-    <numFmt numFmtId="171" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="172" formatCode="#,##0&quot; h&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; h&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0&quot; h&quot;"/>
+    <numFmt numFmtId="172" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,8 +142,9 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00262626"/>
-      <sz val="12"/>
+      <i val="1"/>
+      <color rgb="006B7075"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -153,8 +155,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C41822"/>
-      <sz val="8"/>
+      <color rgb="00262626"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -164,12 +166,84 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="005F8A17"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B26B00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B26B00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C41822"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C41822"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C41822"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00007AC3"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B7075"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B7075"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005F8A17"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00007AC3"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00262626"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00007AC3"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -211,8 +285,13 @@
         <fgColor rgb="00FDF3E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0EDE4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -284,6 +363,14 @@
       <top style="thin">
         <color rgb="00007AC3"/>
       </top>
+      <bottom style="thin">
+        <color rgb="00007AC3"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00007AC3"/>
+      </top>
     </border>
     <border>
       <bottom style="thin">
@@ -294,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -373,6 +460,9 @@
     <xf numFmtId="167" fontId="17" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="17" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -385,6 +475,9 @@
     <xf numFmtId="167" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -394,7 +487,7 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -403,16 +496,16 @@
     <xf numFmtId="3" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="17" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -424,16 +517,34 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -442,10 +553,7 @@
     <xf numFmtId="165" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -454,7 +562,7 @@
     <xf numFmtId="3" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,19 +571,25 @@
     <xf numFmtId="165" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,25 +598,110 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -510,6 +709,27 @@
         <color rgb="00C41822"/>
         <sz val="8"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="005F8A17"/>
+        <sz val="8"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00C41822"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F6C9CC"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -873,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.4" customWidth="1" min="1" max="1"/>
@@ -894,6 +1114,8 @@
     <col width="11.5" customWidth="1" min="16" max="16"/>
     <col width="11.5" customWidth="1" min="17" max="17"/>
     <col width="11.5" customWidth="1" min="18" max="18"/>
+    <col width="11.5" customWidth="1" min="19" max="19"/>
+    <col width="11.5" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -919,6 +1141,8 @@
       <c r="P1" s="1" t="n"/>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -943,6 +1167,8 @@
       <c r="P2" s="1" t="n"/>
       <c r="Q2" s="1" t="n"/>
       <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
+      <c r="T2" s="1" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -963,6 +1189,8 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="n"/>
@@ -993,6 +1221,8 @@
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="n"/>
       <c r="R4" s="7" t="n"/>
+      <c r="S4" s="7" t="n"/>
+      <c r="T4" s="7" t="n"/>
     </row>
     <row r="5" ht="8" customHeight="1">
       <c r="A5" s="5" t="n"/>
@@ -1013,6 +1243,8 @@
       <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
       <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="n"/>
@@ -1036,6 +1268,8 @@
       <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="n"/>
       <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
     </row>
     <row r="7" ht="8" customHeight="1">
       <c r="A7" s="5" t="n"/>
@@ -1056,6 +1290,8 @@
       <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="n"/>
       <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
     </row>
     <row r="8" ht="3" customHeight="1">
       <c r="A8" s="5" t="n"/>
@@ -1076,6 +1312,8 @@
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
     </row>
     <row r="9" ht="12" customHeight="1">
       <c r="A9" s="5" t="n"/>
@@ -1116,6 +1354,8 @@
       <c r="P9" s="13" t="n"/>
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="n"/>
@@ -1151,6 +1391,8 @@
       <c r="P10" s="13" t="n"/>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="5" t="n"/>
@@ -1191,6 +1433,8 @@
       <c r="P11" s="19" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
     </row>
     <row r="12" ht="8" customHeight="1">
       <c r="A12" s="5" t="n"/>
@@ -1211,6 +1455,8 @@
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="5" t="n"/>
@@ -1234,6 +1480,8 @@
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
+      <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="n"/>
@@ -1258,6 +1506,8 @@
       <c r="P14" s="19" t="n"/>
       <c r="Q14" s="19" t="n"/>
       <c r="R14" s="19" t="n"/>
+      <c r="S14" s="19" t="n"/>
+      <c r="T14" s="19" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1">
       <c r="A15" s="5" t="n"/>
@@ -1278,6 +1528,8 @@
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1298,6 +1550,8 @@
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="n"/>
@@ -1322,12 +1576,14 @@
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Ces dix-sept colonnes sortent de la base. Elles sont additives : on peut les sommer, les filtrer, les remonter à la marque — rien n'y est un ratio.</t>
+          <t>Ces dix-neuf colonnes sortent de la base. Elles sont additives : on peut les sommer, les filtrer, les remonter à la marque — rien n'y est un ratio.</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -1346,6 +1602,8 @@
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="5" t="n"/>
@@ -1426,12 +1684,22 @@
       </c>
       <c r="Q19" s="26" t="inlineStr">
         <is>
+          <t>Heures d'enseignement 2026</t>
+        </is>
+      </c>
+      <c r="R19" s="26" t="inlineStr">
+        <is>
           <t>Consommables 604+6063</t>
         </is>
       </c>
-      <c r="R19" s="26" t="inlineStr">
+      <c r="S19" s="26" t="inlineStr">
         <is>
           <t>Vacataires 621</t>
+        </is>
+      </c>
+      <c r="T19" s="26" t="inlineStr">
+        <is>
+          <t>Enseignants permanents 6411</t>
         </is>
       </c>
     </row>
@@ -1486,11 +1754,17 @@
       <c r="P20" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" s="30" t="n">
+      <c r="Q20" s="32" t="n">
+        <v>2880</v>
+      </c>
+      <c r="R20" s="30" t="n">
         <v>43535</v>
       </c>
-      <c r="R20" s="30" t="n">
+      <c r="S20" s="30" t="n">
         <v>72438</v>
+      </c>
+      <c r="T20" s="30" t="n">
+        <v>136087.43</v>
       </c>
     </row>
     <row r="21">
@@ -1540,11 +1814,17 @@
       <c r="P21" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" s="30" t="n">
+      <c r="Q21" s="32" t="n">
+        <v>2880</v>
+      </c>
+      <c r="R21" s="30" t="n">
         <v>53954</v>
       </c>
-      <c r="R21" s="30" t="n">
+      <c r="S21" s="30" t="n">
         <v>72438</v>
+      </c>
+      <c r="T21" s="30" t="n">
+        <v>168182.73</v>
       </c>
     </row>
     <row r="22">
@@ -1594,11 +1874,17 @@
       <c r="P22" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" s="30" t="n">
+      <c r="Q22" s="32" t="n">
+        <v>2880</v>
+      </c>
+      <c r="R22" s="30" t="n">
         <v>43535</v>
       </c>
-      <c r="R22" s="30" t="n">
+      <c r="S22" s="30" t="n">
         <v>72438</v>
+      </c>
+      <c r="T22" s="30" t="n">
+        <v>136168.63</v>
       </c>
     </row>
     <row r="23">
@@ -1652,11 +1938,17 @@
       <c r="P23" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="Q23" s="30" t="n">
+      <c r="Q23" s="32" t="n">
+        <v>4800</v>
+      </c>
+      <c r="R23" s="30" t="n">
         <v>90791</v>
       </c>
-      <c r="R23" s="30" t="n">
+      <c r="S23" s="30" t="n">
         <v>120729</v>
+      </c>
+      <c r="T23" s="30" t="n">
+        <v>284669.17</v>
       </c>
     </row>
     <row r="24">
@@ -1706,11 +1998,17 @@
       <c r="P24" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="Q24" s="30" t="n">
+      <c r="Q24" s="32" t="n">
+        <v>7200</v>
+      </c>
+      <c r="R24" s="30" t="n">
         <v>131722</v>
       </c>
-      <c r="R24" s="30" t="n">
+      <c r="S24" s="30" t="n">
         <v>181094</v>
+      </c>
+      <c r="T24" s="30" t="n">
+        <v>488050.48</v>
       </c>
     </row>
     <row r="25">
@@ -1760,11 +2058,17 @@
       <c r="P25" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" s="30" t="n">
+      <c r="Q25" s="32" t="n">
+        <v>4800</v>
+      </c>
+      <c r="R25" s="30" t="n">
         <v>85954</v>
       </c>
-      <c r="R25" s="30" t="n">
+      <c r="S25" s="30" t="n">
         <v>120729</v>
+      </c>
+      <c r="T25" s="30" t="n">
+        <v>267683.87</v>
       </c>
     </row>
     <row r="26">
@@ -1818,11 +2122,17 @@
       <c r="P26" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="30" t="n">
+      <c r="Q26" s="32" t="n">
+        <v>4800</v>
+      </c>
+      <c r="R26" s="30" t="n">
         <v>92652</v>
       </c>
-      <c r="R26" s="30" t="n">
+      <c r="S26" s="30" t="n">
         <v>120729</v>
+      </c>
+      <c r="T26" s="30" t="n">
+        <v>280337.09</v>
       </c>
     </row>
     <row r="27">
@@ -1872,11 +2182,17 @@
       <c r="P27" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="Q27" s="30" t="n">
+      <c r="Q27" s="32" t="n">
+        <v>6240</v>
+      </c>
+      <c r="R27" s="30" t="n">
         <v>120559</v>
       </c>
-      <c r="R27" s="30" t="n">
+      <c r="S27" s="30" t="n">
         <v>156948</v>
+      </c>
+      <c r="T27" s="30" t="n">
+        <v>400192.8</v>
       </c>
     </row>
     <row r="28">
@@ -1926,11 +2242,17 @@
       <c r="P28" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="Q28" s="30" t="n">
+      <c r="Q28" s="32" t="n">
+        <v>5640</v>
+      </c>
+      <c r="R28" s="30" t="n">
         <v>109396</v>
       </c>
-      <c r="R28" s="30" t="n">
+      <c r="S28" s="30" t="n">
         <v>144875</v>
+      </c>
+      <c r="T28" s="30" t="n">
+        <v>344252.4</v>
       </c>
     </row>
     <row r="29">
@@ -1980,11 +2302,17 @@
       <c r="P29" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="Q29" s="30" t="n">
+      <c r="Q29" s="32" t="n">
+        <v>7200</v>
+      </c>
+      <c r="R29" s="30" t="n">
         <v>142140</v>
       </c>
-      <c r="R29" s="30" t="n">
+      <c r="S29" s="30" t="n">
         <v>181094</v>
+      </c>
+      <c r="T29" s="30" t="n">
+        <v>502062.96</v>
       </c>
     </row>
     <row r="30">
@@ -2038,11 +2366,17 @@
       <c r="P30" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="30" t="n">
+      <c r="Q30" s="32" t="n">
+        <v>5680</v>
+      </c>
+      <c r="R30" s="30" t="n">
         <v>52838</v>
       </c>
-      <c r="R30" s="30" t="n">
+      <c r="S30" s="30" t="n">
         <v>96583</v>
+      </c>
+      <c r="T30" s="30" t="n">
+        <v>182756.35</v>
       </c>
     </row>
     <row r="31">
@@ -2092,11 +2426,17 @@
       <c r="P31" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="Q31" s="30" t="n">
+      <c r="Q31" s="32" t="n">
+        <v>5680</v>
+      </c>
+      <c r="R31" s="30" t="n">
         <v>67722</v>
       </c>
-      <c r="R31" s="30" t="n">
+      <c r="S31" s="30" t="n">
         <v>96583</v>
+      </c>
+      <c r="T31" s="30" t="n">
+        <v>241308.7</v>
       </c>
     </row>
     <row r="32">
@@ -2150,11 +2490,17 @@
       <c r="P32" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q32" s="30" t="n">
+      <c r="Q32" s="32" t="n">
+        <v>2880</v>
+      </c>
+      <c r="R32" s="30" t="n">
         <v>43535</v>
       </c>
-      <c r="R32" s="30" t="n">
+      <c r="S32" s="30" t="n">
         <v>72438</v>
+      </c>
+      <c r="T32" s="30" t="n">
+        <v>185947.72</v>
       </c>
     </row>
     <row r="33">
@@ -2204,84 +2550,98 @@
       <c r="P33" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="Q33" s="30" t="n">
+      <c r="Q33" s="32" t="n">
+        <v>2880</v>
+      </c>
+      <c r="R33" s="30" t="n">
         <v>51349</v>
       </c>
-      <c r="R33" s="30" t="n">
+      <c r="S33" s="30" t="n">
         <v>72438</v>
+      </c>
+      <c r="T33" s="30" t="n">
+        <v>223369.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>GROUPE</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>14 campus</t>
         </is>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <f>SUM(D20:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <f>SUM(E20:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <f>SUM(F20:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <f>SUM(G20:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <f>SUM(H20:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="35">
         <f>SUM(I20:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="35" t="inlineStr">
+      <c r="J34" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <f>SUM(K20:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <f>SUM(L20:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <f>SUM(M20:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="34">
         <f>SUM(N20:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <f>SUM(O20:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="34">
         <f>SUM(P20:P33)</f>
         <v/>
       </c>
-      <c r="Q34" s="34">
+      <c r="Q34" s="37">
         <f>SUM(Q20:Q33)</f>
         <v/>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="35">
         <f>SUM(R20:R33)</f>
+        <v/>
+      </c>
+      <c r="S34" s="35">
+        <f>SUM(S20:S33)</f>
+        <v/>
+      </c>
+      <c r="T34" s="35">
+        <f>SUM(T20:T33)</f>
         <v/>
       </c>
     </row>
@@ -2304,6 +2664,8 @@
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
       <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -2324,6 +2686,8 @@
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
       <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -2344,6 +2708,8 @@
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
       <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -2364,6 +2730,8 @@
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
       <c r="R38" s="5" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -2384,6 +2752,8 @@
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n"/>
       <c r="R39" s="5" t="n"/>
+      <c r="S39" s="5" t="n"/>
+      <c r="T39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -2404,10 +2774,12 @@
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="n"/>
       <c r="R40" s="5" t="n"/>
+      <c r="S40" s="5" t="n"/>
+      <c r="T40" s="5" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>②  CE QUE LE MASQUE CALCULE  ·  chaque formule pointe une cellule du tableau ①</t>
         </is>
@@ -2428,6 +2800,8 @@
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="n"/>
       <c r="R41" s="5" t="n"/>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="5" t="n"/>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="5" t="n"/>
@@ -2452,6 +2826,8 @@
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="n"/>
       <c r="R42" s="5" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="5" t="n"/>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="5" t="n"/>
@@ -2520,55 +2896,57 @@
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n"/>
       <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory</t>
         </is>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="40">
         <f>C20</f>
         <v/>
       </c>
-      <c r="D44" s="39">
+      <c r="D44" s="41">
         <f>IFERROR(L20/K20,0)</f>
         <v/>
       </c>
-      <c r="E44" s="40">
+      <c r="E44" s="42">
         <f>IFERROR(M20/L20,0)</f>
         <v/>
       </c>
-      <c r="F44" s="40">
-        <f>IFERROR(Q20/N20,0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="41">
+      <c r="F44" s="42">
+        <f>IFERROR(R20/N20,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="43">
         <f>O20-N20</f>
         <v/>
       </c>
-      <c r="H44" s="40">
+      <c r="H44" s="42">
         <f>I20*$F$4</f>
         <v/>
       </c>
-      <c r="I44" s="42">
+      <c r="I44" s="44">
         <f>F20*((1+$F$4)^J20-1)*D44</f>
         <v/>
       </c>
-      <c r="J44" s="40">
+      <c r="J44" s="42">
         <f>I44*E44</f>
         <v/>
       </c>
-      <c r="K44" s="40">
-        <f>IF(I44&lt;=G44,F44,F44+R20/O20)</f>
-        <v/>
-      </c>
-      <c r="L44" s="40">
+      <c r="K44" s="42">
+        <f>IF(I44&lt;=G44,F44,F44+S20/O20)</f>
+        <v/>
+      </c>
+      <c r="L44" s="42">
         <f>J44-H44-I44*K44</f>
         <v/>
       </c>
-      <c r="M44" s="40">
+      <c r="M44" s="42">
         <f>IFERROR(H44/I44,0)</f>
         <v/>
       </c>
@@ -2577,51 +2955,53 @@
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="n"/>
       <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n"/>
+      <c r="T44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="37" t="inlineStr"/>
-      <c r="C45" s="38">
+      <c r="B45" s="39" t="inlineStr"/>
+      <c r="C45" s="40">
         <f>C21</f>
         <v/>
       </c>
-      <c r="D45" s="39">
+      <c r="D45" s="41">
         <f>IFERROR(L21/K21,0)</f>
         <v/>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="42">
         <f>IFERROR(M21/L21,0)</f>
         <v/>
       </c>
-      <c r="F45" s="40">
-        <f>IFERROR(Q21/N21,0)</f>
-        <v/>
-      </c>
-      <c r="G45" s="41">
+      <c r="F45" s="42">
+        <f>IFERROR(R21/N21,0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="43">
         <f>O21-N21</f>
         <v/>
       </c>
-      <c r="H45" s="40">
+      <c r="H45" s="42">
         <f>I21*$F$4</f>
         <v/>
       </c>
-      <c r="I45" s="42">
+      <c r="I45" s="44">
         <f>F21*((1+$F$4)^J21-1)*D45</f>
         <v/>
       </c>
-      <c r="J45" s="40">
+      <c r="J45" s="42">
         <f>I45*E45</f>
         <v/>
       </c>
-      <c r="K45" s="40">
-        <f>IF(I45&lt;=G45,F45,F45+R21/O21)</f>
-        <v/>
-      </c>
-      <c r="L45" s="40">
+      <c r="K45" s="42">
+        <f>IF(I45&lt;=G45,F45,F45+S21/O21)</f>
+        <v/>
+      </c>
+      <c r="L45" s="42">
         <f>J45-H45-I45*K45</f>
         <v/>
       </c>
-      <c r="M45" s="40">
+      <c r="M45" s="42">
         <f>IFERROR(H45/I45,0)</f>
         <v/>
       </c>
@@ -2630,51 +3010,53 @@
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
       <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="37" t="inlineStr"/>
-      <c r="C46" s="38">
+      <c r="B46" s="39" t="inlineStr"/>
+      <c r="C46" s="40">
         <f>C22</f>
         <v/>
       </c>
-      <c r="D46" s="39">
+      <c r="D46" s="41">
         <f>IFERROR(L22/K22,0)</f>
         <v/>
       </c>
-      <c r="E46" s="40">
+      <c r="E46" s="42">
         <f>IFERROR(M22/L22,0)</f>
         <v/>
       </c>
-      <c r="F46" s="40">
-        <f>IFERROR(Q22/N22,0)</f>
-        <v/>
-      </c>
-      <c r="G46" s="41">
+      <c r="F46" s="42">
+        <f>IFERROR(R22/N22,0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="43">
         <f>O22-N22</f>
         <v/>
       </c>
-      <c r="H46" s="40">
+      <c r="H46" s="42">
         <f>I22*$F$4</f>
         <v/>
       </c>
-      <c r="I46" s="42">
+      <c r="I46" s="44">
         <f>F22*((1+$F$4)^J22-1)*D46</f>
         <v/>
       </c>
-      <c r="J46" s="40">
+      <c r="J46" s="42">
         <f>I46*E46</f>
         <v/>
       </c>
-      <c r="K46" s="40">
-        <f>IF(I46&lt;=G46,F46,F46+R22/O22)</f>
-        <v/>
-      </c>
-      <c r="L46" s="40">
+      <c r="K46" s="42">
+        <f>IF(I46&lt;=G46,F46,F46+S22/O22)</f>
+        <v/>
+      </c>
+      <c r="L46" s="42">
         <f>J46-H46-I46*K46</f>
         <v/>
       </c>
-      <c r="M46" s="40">
+      <c r="M46" s="42">
         <f>IFERROR(H46/I46,0)</f>
         <v/>
       </c>
@@ -2683,55 +3065,57 @@
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n"/>
       <c r="R46" s="5" t="n"/>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>ISCOM</t>
         </is>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="40">
         <f>C23</f>
         <v/>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="41">
         <f>IFERROR(L23/K23,0)</f>
         <v/>
       </c>
-      <c r="E47" s="40">
+      <c r="E47" s="42">
         <f>IFERROR(M23/L23,0)</f>
         <v/>
       </c>
-      <c r="F47" s="40">
-        <f>IFERROR(Q23/N23,0)</f>
-        <v/>
-      </c>
-      <c r="G47" s="41">
+      <c r="F47" s="42">
+        <f>IFERROR(R23/N23,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="43">
         <f>O23-N23</f>
         <v/>
       </c>
-      <c r="H47" s="40">
+      <c r="H47" s="42">
         <f>I23*$F$4</f>
         <v/>
       </c>
-      <c r="I47" s="42">
+      <c r="I47" s="44">
         <f>F23*((1+$F$4)^J23-1)*D47</f>
         <v/>
       </c>
-      <c r="J47" s="40">
+      <c r="J47" s="42">
         <f>I47*E47</f>
         <v/>
       </c>
-      <c r="K47" s="40">
-        <f>IF(I47&lt;=G47,F47,F47+R23/O23)</f>
-        <v/>
-      </c>
-      <c r="L47" s="40">
+      <c r="K47" s="42">
+        <f>IF(I47&lt;=G47,F47,F47+S23/O23)</f>
+        <v/>
+      </c>
+      <c r="L47" s="42">
         <f>J47-H47-I47*K47</f>
         <v/>
       </c>
-      <c r="M47" s="40">
+      <c r="M47" s="42">
         <f>IFERROR(H47/I47,0)</f>
         <v/>
       </c>
@@ -2740,51 +3124,53 @@
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n"/>
       <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="37" t="inlineStr"/>
-      <c r="C48" s="38">
+      <c r="B48" s="39" t="inlineStr"/>
+      <c r="C48" s="40">
         <f>C24</f>
         <v/>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="41">
         <f>IFERROR(L24/K24,0)</f>
         <v/>
       </c>
-      <c r="E48" s="40">
+      <c r="E48" s="42">
         <f>IFERROR(M24/L24,0)</f>
         <v/>
       </c>
-      <c r="F48" s="40">
-        <f>IFERROR(Q24/N24,0)</f>
-        <v/>
-      </c>
-      <c r="G48" s="41">
+      <c r="F48" s="42">
+        <f>IFERROR(R24/N24,0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="43">
         <f>O24-N24</f>
         <v/>
       </c>
-      <c r="H48" s="40">
+      <c r="H48" s="42">
         <f>I24*$F$4</f>
         <v/>
       </c>
-      <c r="I48" s="42">
+      <c r="I48" s="44">
         <f>F24*((1+$F$4)^J24-1)*D48</f>
         <v/>
       </c>
-      <c r="J48" s="40">
+      <c r="J48" s="42">
         <f>I48*E48</f>
         <v/>
       </c>
-      <c r="K48" s="40">
-        <f>IF(I48&lt;=G48,F48,F48+R24/O24)</f>
-        <v/>
-      </c>
-      <c r="L48" s="40">
+      <c r="K48" s="42">
+        <f>IF(I48&lt;=G48,F48,F48+S24/O24)</f>
+        <v/>
+      </c>
+      <c r="L48" s="42">
         <f>J48-H48-I48*K48</f>
         <v/>
       </c>
-      <c r="M48" s="40">
+      <c r="M48" s="42">
         <f>IFERROR(H48/I48,0)</f>
         <v/>
       </c>
@@ -2793,51 +3179,53 @@
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="n"/>
       <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="37" t="inlineStr"/>
-      <c r="C49" s="38">
+      <c r="B49" s="39" t="inlineStr"/>
+      <c r="C49" s="40">
         <f>C25</f>
         <v/>
       </c>
-      <c r="D49" s="39">
+      <c r="D49" s="41">
         <f>IFERROR(L25/K25,0)</f>
         <v/>
       </c>
-      <c r="E49" s="40">
+      <c r="E49" s="42">
         <f>IFERROR(M25/L25,0)</f>
         <v/>
       </c>
-      <c r="F49" s="40">
-        <f>IFERROR(Q25/N25,0)</f>
-        <v/>
-      </c>
-      <c r="G49" s="41">
+      <c r="F49" s="42">
+        <f>IFERROR(R25/N25,0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="43">
         <f>O25-N25</f>
         <v/>
       </c>
-      <c r="H49" s="40">
+      <c r="H49" s="42">
         <f>I25*$F$4</f>
         <v/>
       </c>
-      <c r="I49" s="42">
+      <c r="I49" s="44">
         <f>F25*((1+$F$4)^J25-1)*D49</f>
         <v/>
       </c>
-      <c r="J49" s="40">
+      <c r="J49" s="42">
         <f>I49*E49</f>
         <v/>
       </c>
-      <c r="K49" s="40">
-        <f>IF(I49&lt;=G49,F49,F49+R25/O25)</f>
-        <v/>
-      </c>
-      <c r="L49" s="40">
+      <c r="K49" s="42">
+        <f>IF(I49&lt;=G49,F49,F49+S25/O25)</f>
+        <v/>
+      </c>
+      <c r="L49" s="42">
         <f>J49-H49-I49*K49</f>
         <v/>
       </c>
-      <c r="M49" s="40">
+      <c r="M49" s="42">
         <f>IFERROR(H49/I49,0)</f>
         <v/>
       </c>
@@ -2846,55 +3234,57 @@
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="n"/>
       <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="37" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>MBway</t>
         </is>
       </c>
-      <c r="C50" s="38">
+      <c r="C50" s="40">
         <f>C26</f>
         <v/>
       </c>
-      <c r="D50" s="39">
+      <c r="D50" s="41">
         <f>IFERROR(L26/K26,0)</f>
         <v/>
       </c>
-      <c r="E50" s="40">
+      <c r="E50" s="42">
         <f>IFERROR(M26/L26,0)</f>
         <v/>
       </c>
-      <c r="F50" s="40">
-        <f>IFERROR(Q26/N26,0)</f>
-        <v/>
-      </c>
-      <c r="G50" s="41">
+      <c r="F50" s="42">
+        <f>IFERROR(R26/N26,0)</f>
+        <v/>
+      </c>
+      <c r="G50" s="43">
         <f>O26-N26</f>
         <v/>
       </c>
-      <c r="H50" s="40">
+      <c r="H50" s="42">
         <f>I26*$F$4</f>
         <v/>
       </c>
-      <c r="I50" s="42">
+      <c r="I50" s="44">
         <f>F26*((1+$F$4)^J26-1)*D50</f>
         <v/>
       </c>
-      <c r="J50" s="40">
+      <c r="J50" s="42">
         <f>I50*E50</f>
         <v/>
       </c>
-      <c r="K50" s="40">
-        <f>IF(I50&lt;=G50,F50,F50+R26/O26)</f>
-        <v/>
-      </c>
-      <c r="L50" s="40">
+      <c r="K50" s="42">
+        <f>IF(I50&lt;=G50,F50,F50+S26/O26)</f>
+        <v/>
+      </c>
+      <c r="L50" s="42">
         <f>J50-H50-I50*K50</f>
         <v/>
       </c>
-      <c r="M50" s="40">
+      <c r="M50" s="42">
         <f>IFERROR(H50/I50,0)</f>
         <v/>
       </c>
@@ -2903,51 +3293,53 @@
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="n"/>
       <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="37" t="inlineStr"/>
-      <c r="C51" s="38">
+      <c r="B51" s="39" t="inlineStr"/>
+      <c r="C51" s="40">
         <f>C27</f>
         <v/>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="41">
         <f>IFERROR(L27/K27,0)</f>
         <v/>
       </c>
-      <c r="E51" s="40">
+      <c r="E51" s="42">
         <f>IFERROR(M27/L27,0)</f>
         <v/>
       </c>
-      <c r="F51" s="40">
-        <f>IFERROR(Q27/N27,0)</f>
-        <v/>
-      </c>
-      <c r="G51" s="41">
+      <c r="F51" s="42">
+        <f>IFERROR(R27/N27,0)</f>
+        <v/>
+      </c>
+      <c r="G51" s="43">
         <f>O27-N27</f>
         <v/>
       </c>
-      <c r="H51" s="40">
+      <c r="H51" s="42">
         <f>I27*$F$4</f>
         <v/>
       </c>
-      <c r="I51" s="42">
+      <c r="I51" s="44">
         <f>F27*((1+$F$4)^J27-1)*D51</f>
         <v/>
       </c>
-      <c r="J51" s="40">
+      <c r="J51" s="42">
         <f>I51*E51</f>
         <v/>
       </c>
-      <c r="K51" s="40">
-        <f>IF(I51&lt;=G51,F51,F51+R27/O27)</f>
-        <v/>
-      </c>
-      <c r="L51" s="40">
+      <c r="K51" s="42">
+        <f>IF(I51&lt;=G51,F51,F51+S27/O27)</f>
+        <v/>
+      </c>
+      <c r="L51" s="42">
         <f>J51-H51-I51*K51</f>
         <v/>
       </c>
-      <c r="M51" s="40">
+      <c r="M51" s="42">
         <f>IFERROR(H51/I51,0)</f>
         <v/>
       </c>
@@ -2956,51 +3348,53 @@
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="n"/>
       <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="37" t="inlineStr"/>
-      <c r="C52" s="38">
+      <c r="B52" s="39" t="inlineStr"/>
+      <c r="C52" s="40">
         <f>C28</f>
         <v/>
       </c>
-      <c r="D52" s="39">
+      <c r="D52" s="41">
         <f>IFERROR(L28/K28,0)</f>
         <v/>
       </c>
-      <c r="E52" s="40">
+      <c r="E52" s="42">
         <f>IFERROR(M28/L28,0)</f>
         <v/>
       </c>
-      <c r="F52" s="40">
-        <f>IFERROR(Q28/N28,0)</f>
-        <v/>
-      </c>
-      <c r="G52" s="41">
+      <c r="F52" s="42">
+        <f>IFERROR(R28/N28,0)</f>
+        <v/>
+      </c>
+      <c r="G52" s="43">
         <f>O28-N28</f>
         <v/>
       </c>
-      <c r="H52" s="40">
+      <c r="H52" s="42">
         <f>I28*$F$4</f>
         <v/>
       </c>
-      <c r="I52" s="42">
+      <c r="I52" s="44">
         <f>F28*((1+$F$4)^J28-1)*D52</f>
         <v/>
       </c>
-      <c r="J52" s="40">
+      <c r="J52" s="42">
         <f>I52*E52</f>
         <v/>
       </c>
-      <c r="K52" s="40">
-        <f>IF(I52&lt;=G52,F52,F52+R28/O28)</f>
-        <v/>
-      </c>
-      <c r="L52" s="40">
+      <c r="K52" s="42">
+        <f>IF(I52&lt;=G52,F52,F52+S28/O28)</f>
+        <v/>
+      </c>
+      <c r="L52" s="42">
         <f>J52-H52-I52*K52</f>
         <v/>
       </c>
-      <c r="M52" s="40">
+      <c r="M52" s="42">
         <f>IFERROR(H52/I52,0)</f>
         <v/>
       </c>
@@ -3009,51 +3403,53 @@
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="n"/>
       <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="37" t="inlineStr"/>
-      <c r="C53" s="38">
+      <c r="B53" s="39" t="inlineStr"/>
+      <c r="C53" s="40">
         <f>C29</f>
         <v/>
       </c>
-      <c r="D53" s="39">
+      <c r="D53" s="41">
         <f>IFERROR(L29/K29,0)</f>
         <v/>
       </c>
-      <c r="E53" s="40">
+      <c r="E53" s="42">
         <f>IFERROR(M29/L29,0)</f>
         <v/>
       </c>
-      <c r="F53" s="40">
-        <f>IFERROR(Q29/N29,0)</f>
-        <v/>
-      </c>
-      <c r="G53" s="41">
+      <c r="F53" s="42">
+        <f>IFERROR(R29/N29,0)</f>
+        <v/>
+      </c>
+      <c r="G53" s="43">
         <f>O29-N29</f>
         <v/>
       </c>
-      <c r="H53" s="40">
+      <c r="H53" s="42">
         <f>I29*$F$4</f>
         <v/>
       </c>
-      <c r="I53" s="42">
+      <c r="I53" s="44">
         <f>F29*((1+$F$4)^J29-1)*D53</f>
         <v/>
       </c>
-      <c r="J53" s="40">
+      <c r="J53" s="42">
         <f>I53*E53</f>
         <v/>
       </c>
-      <c r="K53" s="40">
-        <f>IF(I53&lt;=G53,F53,F53+R29/O29)</f>
-        <v/>
-      </c>
-      <c r="L53" s="40">
+      <c r="K53" s="42">
+        <f>IF(I53&lt;=G53,F53,F53+S29/O29)</f>
+        <v/>
+      </c>
+      <c r="L53" s="42">
         <f>J53-H53-I53*K53</f>
         <v/>
       </c>
-      <c r="M53" s="40">
+      <c r="M53" s="42">
         <f>IFERROR(H53/I53,0)</f>
         <v/>
       </c>
@@ -3062,55 +3458,57 @@
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
       <c r="R53" s="5" t="n"/>
+      <c r="S53" s="5" t="n"/>
+      <c r="T53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>Pigier</t>
         </is>
       </c>
-      <c r="C54" s="38">
+      <c r="C54" s="40">
         <f>C30</f>
         <v/>
       </c>
-      <c r="D54" s="39">
+      <c r="D54" s="41">
         <f>IFERROR(L30/K30,0)</f>
         <v/>
       </c>
-      <c r="E54" s="40">
+      <c r="E54" s="42">
         <f>IFERROR(M30/L30,0)</f>
         <v/>
       </c>
-      <c r="F54" s="40">
-        <f>IFERROR(Q30/N30,0)</f>
-        <v/>
-      </c>
-      <c r="G54" s="41">
+      <c r="F54" s="42">
+        <f>IFERROR(R30/N30,0)</f>
+        <v/>
+      </c>
+      <c r="G54" s="43">
         <f>O30-N30</f>
         <v/>
       </c>
-      <c r="H54" s="40">
+      <c r="H54" s="42">
         <f>I30*$F$4</f>
         <v/>
       </c>
-      <c r="I54" s="42">
+      <c r="I54" s="44">
         <f>F30*((1+$F$4)^J30-1)*D54</f>
         <v/>
       </c>
-      <c r="J54" s="40">
+      <c r="J54" s="42">
         <f>I54*E54</f>
         <v/>
       </c>
-      <c r="K54" s="40">
-        <f>IF(I54&lt;=G54,F54,F54+R30/O30)</f>
-        <v/>
-      </c>
-      <c r="L54" s="40">
+      <c r="K54" s="42">
+        <f>IF(I54&lt;=G54,F54,F54+S30/O30)</f>
+        <v/>
+      </c>
+      <c r="L54" s="42">
         <f>J54-H54-I54*K54</f>
         <v/>
       </c>
-      <c r="M54" s="40">
+      <c r="M54" s="42">
         <f>IFERROR(H54/I54,0)</f>
         <v/>
       </c>
@@ -3119,51 +3517,53 @@
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
       <c r="R54" s="5" t="n"/>
+      <c r="S54" s="5" t="n"/>
+      <c r="T54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="37" t="inlineStr"/>
-      <c r="C55" s="38">
+      <c r="B55" s="39" t="inlineStr"/>
+      <c r="C55" s="40">
         <f>C31</f>
         <v/>
       </c>
-      <c r="D55" s="39">
+      <c r="D55" s="41">
         <f>IFERROR(L31/K31,0)</f>
         <v/>
       </c>
-      <c r="E55" s="40">
+      <c r="E55" s="42">
         <f>IFERROR(M31/L31,0)</f>
         <v/>
       </c>
-      <c r="F55" s="40">
-        <f>IFERROR(Q31/N31,0)</f>
-        <v/>
-      </c>
-      <c r="G55" s="41">
+      <c r="F55" s="42">
+        <f>IFERROR(R31/N31,0)</f>
+        <v/>
+      </c>
+      <c r="G55" s="43">
         <f>O31-N31</f>
         <v/>
       </c>
-      <c r="H55" s="40">
+      <c r="H55" s="42">
         <f>I31*$F$4</f>
         <v/>
       </c>
-      <c r="I55" s="42">
+      <c r="I55" s="44">
         <f>F31*((1+$F$4)^J31-1)*D55</f>
         <v/>
       </c>
-      <c r="J55" s="40">
+      <c r="J55" s="42">
         <f>I55*E55</f>
         <v/>
       </c>
-      <c r="K55" s="40">
-        <f>IF(I55&lt;=G55,F55,F55+R31/O31)</f>
-        <v/>
-      </c>
-      <c r="L55" s="40">
+      <c r="K55" s="42">
+        <f>IF(I55&lt;=G55,F55,F55+S31/O31)</f>
+        <v/>
+      </c>
+      <c r="L55" s="42">
         <f>J55-H55-I55*K55</f>
         <v/>
       </c>
-      <c r="M55" s="40">
+      <c r="M55" s="42">
         <f>IFERROR(H55/I55,0)</f>
         <v/>
       </c>
@@ -3172,55 +3572,57 @@
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="37" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>Tunon</t>
         </is>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="40">
         <f>C32</f>
         <v/>
       </c>
-      <c r="D56" s="39">
+      <c r="D56" s="41">
         <f>IFERROR(L32/K32,0)</f>
         <v/>
       </c>
-      <c r="E56" s="40">
+      <c r="E56" s="42">
         <f>IFERROR(M32/L32,0)</f>
         <v/>
       </c>
-      <c r="F56" s="40">
-        <f>IFERROR(Q32/N32,0)</f>
-        <v/>
-      </c>
-      <c r="G56" s="41">
+      <c r="F56" s="42">
+        <f>IFERROR(R32/N32,0)</f>
+        <v/>
+      </c>
+      <c r="G56" s="43">
         <f>O32-N32</f>
         <v/>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="42">
         <f>I32*$F$4</f>
         <v/>
       </c>
-      <c r="I56" s="42">
+      <c r="I56" s="44">
         <f>F32*((1+$F$4)^J32-1)*D56</f>
         <v/>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="42">
         <f>I56*E56</f>
         <v/>
       </c>
-      <c r="K56" s="40">
-        <f>IF(I56&lt;=G56,F56,F56+R32/O32)</f>
-        <v/>
-      </c>
-      <c r="L56" s="40">
+      <c r="K56" s="42">
+        <f>IF(I56&lt;=G56,F56,F56+S32/O32)</f>
+        <v/>
+      </c>
+      <c r="L56" s="42">
         <f>J56-H56-I56*K56</f>
         <v/>
       </c>
-      <c r="M56" s="40">
+      <c r="M56" s="42">
         <f>IFERROR(H56/I56,0)</f>
         <v/>
       </c>
@@ -3229,51 +3631,53 @@
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
       <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="37" t="inlineStr"/>
-      <c r="C57" s="38">
+      <c r="B57" s="39" t="inlineStr"/>
+      <c r="C57" s="40">
         <f>C33</f>
         <v/>
       </c>
-      <c r="D57" s="39">
+      <c r="D57" s="41">
         <f>IFERROR(L33/K33,0)</f>
         <v/>
       </c>
-      <c r="E57" s="40">
+      <c r="E57" s="42">
         <f>IFERROR(M33/L33,0)</f>
         <v/>
       </c>
-      <c r="F57" s="40">
-        <f>IFERROR(Q33/N33,0)</f>
-        <v/>
-      </c>
-      <c r="G57" s="41">
+      <c r="F57" s="42">
+        <f>IFERROR(R33/N33,0)</f>
+        <v/>
+      </c>
+      <c r="G57" s="43">
         <f>O33-N33</f>
         <v/>
       </c>
-      <c r="H57" s="40">
+      <c r="H57" s="42">
         <f>I33*$F$4</f>
         <v/>
       </c>
-      <c r="I57" s="42">
+      <c r="I57" s="44">
         <f>F33*((1+$F$4)^J33-1)*D57</f>
         <v/>
       </c>
-      <c r="J57" s="40">
+      <c r="J57" s="42">
         <f>I57*E57</f>
         <v/>
       </c>
-      <c r="K57" s="40">
-        <f>IF(I57&lt;=G57,F57,F57+R33/O33)</f>
-        <v/>
-      </c>
-      <c r="L57" s="40">
+      <c r="K57" s="42">
+        <f>IF(I57&lt;=G57,F57,F57+S33/O33)</f>
+        <v/>
+      </c>
+      <c r="L57" s="42">
         <f>J57-H57-I57*K57</f>
         <v/>
       </c>
-      <c r="M57" s="40">
+      <c r="M57" s="42">
         <f>IFERROR(H57/I57,0)</f>
         <v/>
       </c>
@@ -3282,56 +3686,58 @@
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
       <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>GROUPE</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
+      <c r="C58" s="33" t="inlineStr">
         <is>
           <t>14 campus</t>
         </is>
       </c>
-      <c r="D58" s="43">
+      <c r="D58" s="45">
         <f>IFERROR(L34/K34,0)</f>
         <v/>
       </c>
-      <c r="E58" s="34">
+      <c r="E58" s="35">
         <f>IFERROR(M34/L34,0)</f>
         <v/>
       </c>
-      <c r="F58" s="34">
-        <f>IFERROR(Q34/N34,0)</f>
-        <v/>
-      </c>
-      <c r="G58" s="33">
+      <c r="F58" s="35">
+        <f>IFERROR(R34/N34,0)</f>
+        <v/>
+      </c>
+      <c r="G58" s="34">
         <f>SUM(G44:G57)</f>
         <v/>
       </c>
-      <c r="H58" s="34">
+      <c r="H58" s="35">
         <f>SUM(H44:H57)</f>
         <v/>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="46">
         <f>SUM(I44:I57)</f>
         <v/>
       </c>
-      <c r="J58" s="34">
+      <c r="J58" s="35">
         <f>SUM(J44:J57)</f>
         <v/>
       </c>
-      <c r="K58" s="34">
+      <c r="K58" s="35">
         <f>IFERROR(SUMPRODUCT(I44:I57,K44:K57)/I58,0)</f>
         <v/>
       </c>
-      <c r="L58" s="34">
+      <c r="L58" s="35">
         <f>SUM(L44:L57)</f>
         <v/>
       </c>
-      <c r="M58" s="34">
+      <c r="M58" s="35">
         <f>IFERROR(H58/I58,0)</f>
         <v/>
       </c>
@@ -3340,6 +3746,8 @@
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
       <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -3360,12 +3768,14 @@
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="n"/>
       <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>Lecture des fonds :  bleu = restitué par la vue,  ocre = calculé par le masque.  Un coût marginal en rouge signale un campus où la classe doit ouvrir.</t>
+          <t>Lecture des fonds :  bleu = restitué par la vue,  ocre = calculé par le masque,  sable = paramètre du modèle.  Un coût marginal en rouge signale un campus où la classe doit ouvrir.</t>
         </is>
       </c>
       <c r="C60" s="5" t="n"/>
@@ -3384,6 +3794,8 @@
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="n"/>
       <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -3404,6 +3816,8 @@
       <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="n"/>
       <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -3424,6 +3838,8 @@
       <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="n"/>
       <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n"/>
+      <c r="T62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -3444,6 +3860,8 @@
       <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="n"/>
       <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -3464,6 +3882,8 @@
       <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="n"/>
       <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n"/>
+      <c r="T64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -3484,6 +3904,8 @@
       <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="n"/>
       <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -3504,6 +3926,8 @@
       <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="n"/>
       <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -3524,6 +3948,8 @@
       <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="n"/>
       <c r="R67" s="5" t="n"/>
+      <c r="S67" s="5" t="n"/>
+      <c r="T67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -3544,6 +3970,8 @@
       <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="n"/>
       <c r="R68" s="5" t="n"/>
+      <c r="S68" s="5" t="n"/>
+      <c r="T68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -3564,6 +3992,8 @@
       <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="n"/>
       <c r="R69" s="5" t="n"/>
+      <c r="S69" s="5" t="n"/>
+      <c r="T69" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M44:M57">
@@ -3593,18 +4023,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -3621,6 +4056,11 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="1" t="n"/>
@@ -3636,6 +4076,11 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -3647,6 +4092,11 @@
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -3658,10 +4108,15 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="n"/>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>La comptabilité ne connaît pas le programme.</t>
         </is>
@@ -3673,12 +4128,17 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="5" t="n"/>
-      <c r="B6" s="46" t="inlineStr">
-        <is>
-          <t>AW_002_000004_000001 est au grain CAMPUS × COMPTE. Un coût par élève et par programme ne se lit donc pas : il s'alloue. V_ALLOCATION le fait déjà, avec deux clés différentes — et c'est de là que vient toute la suite.</t>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>AW_002_000004_000001 est au grain CAMPUS × COMPTE. Un coût par élève et par programme ne se lit donc pas : il s'alloue. V_ALLOCATION le fait déjà, avec des clés différentes selon la nature de la charge — et c'est de là que vient tout le reste.</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -3688,6 +4148,11 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -3699,12 +4164,17 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>①  Deux poches, deux clés</t>
+          <t>①  Trois poches d'enseignement, trois comportements</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -3714,12 +4184,17 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Le même euro de charge variable ne se répartit pas de la même façon selon ce qu'il paie.</t>
+          <t>Le même euro de charge ne se répartit pas de la même façon, et surtout ne réagit pas de la même façon quand un élève de plus arrive.</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -3729,6 +4204,11 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -3740,6 +4220,11 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="n"/>
@@ -3755,95 +4240,164 @@
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
           <t>Clé d'allocation</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>Varie avec</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>Uniforme à l'intérieur d'un campus ?</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Comportement</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Bouge si un élève de plus arrive ?</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>Vacataires</t>
-        </is>
-      </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="D12" s="48" t="inlineStr">
-        <is>
-          <t>HEURES</t>
-        </is>
-      </c>
-      <c r="E12" s="48" t="inlineStr">
-        <is>
-          <t>le programme et la modalité</t>
-        </is>
-      </c>
-      <c r="F12" s="49" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>Consommables</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>604 + 6063</t>
+        </is>
+      </c>
+      <c r="D12" s="51">
+        <f>'Le moteur'!R34</f>
+        <v/>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>EFFECTIFS</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>le campus</t>
+        </is>
+      </c>
+      <c r="G12" s="53" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>OUI — c'est le seul euro qui suit vraiment l'élève</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="47" t="inlineStr">
-        <is>
-          <t>Consommables</t>
-        </is>
-      </c>
-      <c r="C13" s="48" t="inlineStr">
-        <is>
-          <t>604 + 6063</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>EFFECTIFS</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>le campus seulement</t>
-        </is>
-      </c>
-      <c r="F13" s="50" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>Vacataires</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D13" s="51">
+        <f>'Le moteur'!S34</f>
+        <v/>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>HEURES</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>le programme</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="inlineStr">
+        <is>
+          <t>SEMI-VARIABLE</t>
+        </is>
+      </c>
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>Seulement si la classe doit ouvrir</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+      <c r="D14" s="51">
+        <f>'Le moteur'!T34</f>
+        <v/>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>HEURES</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>le nombre de postes</t>
+        </is>
+      </c>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t>CAPACITÉ</t>
+        </is>
+      </c>
+      <c r="H14" s="58" t="inlineStr">
+        <is>
+          <t>NON — payé pareil pour 24 ou 32 élèves dans la salle</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -3859,6 +4413,11 @@
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -3870,6 +4429,11 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -3881,6 +4445,11 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="n"/>
@@ -3896,12 +4465,17 @@
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Ce que coûte un élève déjà inscrit, tous frais variables confondus. Chaque ligne est une réalité du réseau ; la moyenne, elle, n'est nulle part.</t>
+          <t>Ce que coûte un élève déjà inscrit, vacataire et consommables. Chaque ligne est une réalité du réseau ; la moyenne, elle, n'est nulle part. Le tarif horaire est déduit du réel : 621 ÷ heures.</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -3911,6 +4485,11 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -3922,6 +4501,11 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n"/>
@@ -3965,170 +4549,205 @@
           <t>Écart à la moyenne</t>
         </is>
       </c>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C22" s="51" t="n">
+      <c r="C22" s="59" t="n">
         <v>840</v>
       </c>
-      <c r="D22" s="52" t="n">
+      <c r="D22" s="60" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="F22" s="54">
+      <c r="E22" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="F22" s="62">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="G22" s="55" t="n">
-        <v>372.0952839268527</v>
-      </c>
-      <c r="H22" s="54">
+      <c r="G22" s="51" t="n">
+        <v>372.0952843881691</v>
+      </c>
+      <c r="H22" s="62">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="63">
         <f>IFERROR(H22/$H$26-1,0)</f>
         <v/>
       </c>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="47" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="59" t="n">
         <v>1688</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="60" t="n">
         <v>21.04265402843602</v>
       </c>
-      <c r="E23" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="F23" s="54">
+      <c r="E23" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="F23" s="62">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="G23" s="55" t="n">
-        <v>362.7752087347463</v>
-      </c>
-      <c r="H23" s="54">
+      <c r="G23" s="51" t="n">
+        <v>361.8303545853921</v>
+      </c>
+      <c r="H23" s="62">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="56">
+      <c r="I23" s="63">
         <f>IFERROR(H23/$H$26-1,0)</f>
         <v/>
       </c>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="47" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C24" s="51" t="n">
+      <c r="C24" s="59" t="n">
         <v>424</v>
       </c>
-      <c r="D24" s="52" t="n">
+      <c r="D24" s="60" t="n">
         <v>24.05660377358491</v>
       </c>
-      <c r="E24" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="F24" s="54">
+      <c r="E24" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="F24" s="62">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="G24" s="55" t="n">
-        <v>372.0952839268527</v>
-      </c>
-      <c r="H24" s="54">
+      <c r="G24" s="51" t="n">
+        <v>372.0952832735557</v>
+      </c>
+      <c r="H24" s="62">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="56">
+      <c r="I24" s="63">
         <f>IFERROR(H24/$H$26-1,0)</f>
         <v/>
       </c>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="47" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C25" s="51" t="n">
+      <c r="C25" s="59" t="n">
         <v>162</v>
       </c>
-      <c r="D25" s="52" t="n">
+      <c r="D25" s="60" t="n">
         <v>34.5679012345679</v>
       </c>
-      <c r="E25" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="F25" s="54">
+      <c r="E25" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="F25" s="62">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="G25" s="55" t="n">
-        <v>299.9004975124378</v>
-      </c>
-      <c r="H25" s="54">
+      <c r="G25" s="51" t="n">
+        <v>299.900755961781</v>
+      </c>
+      <c r="H25" s="62">
         <f>F25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="56">
+      <c r="I25" s="63">
         <f>IFERROR(H25/$H$26-1,0)</f>
         <v/>
       </c>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="57" t="inlineStr">
+      <c r="B26" s="64" t="inlineStr">
         <is>
           <t>MOYENNE PONDÉRÉE</t>
         </is>
       </c>
-      <c r="C26" s="58">
+      <c r="C26" s="65">
         <f>SUM(C22:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="59">
-        <f>IFERROR(SUMPRODUCT(C22:C25,D22:D25)/C26,0)</f>
-        <v/>
-      </c>
-      <c r="E26" s="60" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="F26" s="61">
+      <c r="D26" s="66">
+        <f>IFERROR('Le moteur'!Q34/C26,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="67">
+        <f>IFERROR('Le moteur'!S34/'Le moteur'!Q34,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="68">
         <f>D26*E26</f>
         <v/>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="68">
         <f>IFERROR(SUMPRODUCT(C22:C25,G22:G25)/C26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="68">
         <f>F26+G26</f>
         <v/>
       </c>
-      <c r="I26" s="62" t="inlineStr">
+      <c r="I26" s="69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -4140,13 +4759,17 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="63" t="inlineStr">
-        <is>
-          <t>Un facteur 1,40 entre les extrêmes. Le coût variable « moyen » du réseau ne décrit aucun élève réel — il ne sert qu'à cadrer, jamais à décider.</t>
-        </is>
+      <c r="B28" s="70">
+        <f>"Un facteur "&amp;TEXT(MAX(H22:H25)/MIN(H22:H25),"0.00")&amp;" entre les extrêmes. Le coût variable « moyen » du réseau — "&amp;TEXT(H26,"#,##0 €")&amp;" — ne décrit aucun élève réel : il cadre, il ne décide pas."</f>
+        <v/>
       </c>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -4155,6 +4778,11 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -4166,12 +4794,17 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>③  La poche uniforme : les consommables, campus par campus</t>
+          <t>③  Le coût d'enseignement campus par campus  ·  ce qui suit l'élève, ce qui suit la classe, ce qui ne bouge pas</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -4181,12 +4814,17 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Clé EFFECTIFS. À l'intérieur d'un campus, tous les élèves portent le même montant — mais d'un campus à l'autre l'écart est de 24 %.</t>
+          <t>Aucun montant n'est saisi ici : chaque euro pointe le tableau ① de l'onglet « Le moteur ». La colonne « quote-part vacataire / place » est exactement le terme que le masque ajoute quand une classe doit ouvrir.</t>
         </is>
       </c>
       <c r="C31" s="5" t="n"/>
@@ -4196,6 +4834,11 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -4207,8 +4850,13 @@
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="25" t="inlineStr">
         <is>
@@ -4222,427 +4870,752 @@
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
+          <t>Places libres</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
           <t>Consommables 604+6063</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>Consommables / élève</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
-        <is>
-          <t>Places libres</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Heures d'enseignement</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>Vacataires 621</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>Quote-part vacataire / place</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>Permanents 6411</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Permanents / élève</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="47" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Montpellier</t>
         </is>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="59">
         <f>'Le moteur'!N20</f>
         <v/>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="59">
+        <f>'Le moteur'!G44</f>
+        <v/>
+      </c>
+      <c r="E34" s="51">
+        <f>'Le moteur'!R20</f>
+        <v/>
+      </c>
+      <c r="F34" s="51">
+        <f>IFERROR(E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="71">
         <f>'Le moteur'!Q20</f>
         <v/>
       </c>
-      <c r="E34" s="55">
-        <f>IFERROR(D34/C34,0)</f>
-        <v/>
-      </c>
-      <c r="F34" s="51">
-        <f>'Le moteur'!G44</f>
-        <v/>
-      </c>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
+      <c r="H34" s="51">
+        <f>'Le moteur'!S20</f>
+        <v/>
+      </c>
+      <c r="I34" s="51">
+        <f>IFERROR(H34/'Le moteur'!O20,0)</f>
+        <v/>
+      </c>
+      <c r="J34" s="51">
+        <f>'Le moteur'!T20</f>
+        <v/>
+      </c>
+      <c r="K34" s="51">
+        <f>IFERROR(J34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="47" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Nantes</t>
         </is>
       </c>
-      <c r="C35" s="51">
+      <c r="C35" s="59">
         <f>'Le moteur'!N21</f>
         <v/>
       </c>
-      <c r="D35" s="55">
+      <c r="D35" s="59">
+        <f>'Le moteur'!G45</f>
+        <v/>
+      </c>
+      <c r="E35" s="51">
+        <f>'Le moteur'!R21</f>
+        <v/>
+      </c>
+      <c r="F35" s="51">
+        <f>IFERROR(E35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="71">
         <f>'Le moteur'!Q21</f>
         <v/>
       </c>
-      <c r="E35" s="55">
-        <f>IFERROR(D35/C35,0)</f>
-        <v/>
-      </c>
-      <c r="F35" s="51">
-        <f>'Le moteur'!G45</f>
-        <v/>
-      </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
+      <c r="H35" s="51">
+        <f>'Le moteur'!S21</f>
+        <v/>
+      </c>
+      <c r="I35" s="51">
+        <f>IFERROR(H35/'Le moteur'!O21,0)</f>
+        <v/>
+      </c>
+      <c r="J35" s="51">
+        <f>'Le moteur'!T21</f>
+        <v/>
+      </c>
+      <c r="K35" s="51">
+        <f>IFERROR(J35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Rennes</t>
         </is>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="59">
         <f>'Le moteur'!N22</f>
         <v/>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="59">
+        <f>'Le moteur'!G46</f>
+        <v/>
+      </c>
+      <c r="E36" s="51">
+        <f>'Le moteur'!R22</f>
+        <v/>
+      </c>
+      <c r="F36" s="51">
+        <f>IFERROR(E36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="71">
         <f>'Le moteur'!Q22</f>
         <v/>
       </c>
-      <c r="E36" s="55">
-        <f>IFERROR(D36/C36,0)</f>
-        <v/>
-      </c>
-      <c r="F36" s="51">
-        <f>'Le moteur'!G46</f>
-        <v/>
-      </c>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
+      <c r="H36" s="51">
+        <f>'Le moteur'!S22</f>
+        <v/>
+      </c>
+      <c r="I36" s="51">
+        <f>IFERROR(H36/'Le moteur'!O22,0)</f>
+        <v/>
+      </c>
+      <c r="J36" s="51">
+        <f>'Le moteur'!T22</f>
+        <v/>
+      </c>
+      <c r="K36" s="51">
+        <f>IFERROR(J36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="47" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>ISCOM Lille</t>
         </is>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="59">
         <f>'Le moteur'!N23</f>
         <v/>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="59">
+        <f>'Le moteur'!G47</f>
+        <v/>
+      </c>
+      <c r="E37" s="51">
+        <f>'Le moteur'!R23</f>
+        <v/>
+      </c>
+      <c r="F37" s="51">
+        <f>IFERROR(E37/C37,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="71">
         <f>'Le moteur'!Q23</f>
         <v/>
       </c>
-      <c r="E37" s="55">
-        <f>IFERROR(D37/C37,0)</f>
-        <v/>
-      </c>
-      <c r="F37" s="51">
-        <f>'Le moteur'!G47</f>
-        <v/>
-      </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
+      <c r="H37" s="51">
+        <f>'Le moteur'!S23</f>
+        <v/>
+      </c>
+      <c r="I37" s="51">
+        <f>IFERROR(H37/'Le moteur'!O23,0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="51">
+        <f>'Le moteur'!T23</f>
+        <v/>
+      </c>
+      <c r="K37" s="51">
+        <f>IFERROR(J37/C37,0)</f>
+        <v/>
+      </c>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="47" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>ISCOM Paris</t>
         </is>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="59">
         <f>'Le moteur'!N24</f>
         <v/>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="59">
+        <f>'Le moteur'!G48</f>
+        <v/>
+      </c>
+      <c r="E38" s="51">
+        <f>'Le moteur'!R24</f>
+        <v/>
+      </c>
+      <c r="F38" s="51">
+        <f>IFERROR(E38/C38,0)</f>
+        <v/>
+      </c>
+      <c r="G38" s="71">
         <f>'Le moteur'!Q24</f>
         <v/>
       </c>
-      <c r="E38" s="55">
-        <f>IFERROR(D38/C38,0)</f>
-        <v/>
-      </c>
-      <c r="F38" s="51">
-        <f>'Le moteur'!G48</f>
-        <v/>
-      </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
+      <c r="H38" s="51">
+        <f>'Le moteur'!S24</f>
+        <v/>
+      </c>
+      <c r="I38" s="51">
+        <f>IFERROR(H38/'Le moteur'!O24,0)</f>
+        <v/>
+      </c>
+      <c r="J38" s="51">
+        <f>'Le moteur'!T24</f>
+        <v/>
+      </c>
+      <c r="K38" s="51">
+        <f>IFERROR(J38/C38,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="47" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>ISCOM Toulouse</t>
         </is>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="59">
         <f>'Le moteur'!N25</f>
         <v/>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="59">
+        <f>'Le moteur'!G49</f>
+        <v/>
+      </c>
+      <c r="E39" s="51">
+        <f>'Le moteur'!R25</f>
+        <v/>
+      </c>
+      <c r="F39" s="51">
+        <f>IFERROR(E39/C39,0)</f>
+        <v/>
+      </c>
+      <c r="G39" s="71">
         <f>'Le moteur'!Q25</f>
         <v/>
       </c>
-      <c r="E39" s="55">
-        <f>IFERROR(D39/C39,0)</f>
-        <v/>
-      </c>
-      <c r="F39" s="51">
-        <f>'Le moteur'!G49</f>
-        <v/>
-      </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
+      <c r="H39" s="51">
+        <f>'Le moteur'!S25</f>
+        <v/>
+      </c>
+      <c r="I39" s="51">
+        <f>IFERROR(H39/'Le moteur'!O25,0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="51">
+        <f>'Le moteur'!T25</f>
+        <v/>
+      </c>
+      <c r="K39" s="51">
+        <f>IFERROR(J39/C39,0)</f>
+        <v/>
+      </c>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="47" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>MBway Bordeaux</t>
         </is>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="59">
         <f>'Le moteur'!N26</f>
         <v/>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="59">
+        <f>'Le moteur'!G50</f>
+        <v/>
+      </c>
+      <c r="E40" s="51">
+        <f>'Le moteur'!R26</f>
+        <v/>
+      </c>
+      <c r="F40" s="51">
+        <f>IFERROR(E40/C40,0)</f>
+        <v/>
+      </c>
+      <c r="G40" s="71">
         <f>'Le moteur'!Q26</f>
         <v/>
       </c>
-      <c r="E40" s="55">
-        <f>IFERROR(D40/C40,0)</f>
-        <v/>
-      </c>
-      <c r="F40" s="51">
-        <f>'Le moteur'!G50</f>
-        <v/>
-      </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
+      <c r="H40" s="51">
+        <f>'Le moteur'!S26</f>
+        <v/>
+      </c>
+      <c r="I40" s="51">
+        <f>IFERROR(H40/'Le moteur'!O26,0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="51">
+        <f>'Le moteur'!T26</f>
+        <v/>
+      </c>
+      <c r="K40" s="51">
+        <f>IFERROR(J40/C40,0)</f>
+        <v/>
+      </c>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="47" t="inlineStr">
+      <c r="B41" s="49" t="inlineStr">
         <is>
           <t>MBway Lyon</t>
         </is>
       </c>
-      <c r="C41" s="51">
+      <c r="C41" s="59">
         <f>'Le moteur'!N27</f>
         <v/>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="59">
+        <f>'Le moteur'!G51</f>
+        <v/>
+      </c>
+      <c r="E41" s="51">
+        <f>'Le moteur'!R27</f>
+        <v/>
+      </c>
+      <c r="F41" s="51">
+        <f>IFERROR(E41/C41,0)</f>
+        <v/>
+      </c>
+      <c r="G41" s="71">
         <f>'Le moteur'!Q27</f>
         <v/>
       </c>
-      <c r="E41" s="55">
-        <f>IFERROR(D41/C41,0)</f>
-        <v/>
-      </c>
-      <c r="F41" s="51">
-        <f>'Le moteur'!G51</f>
-        <v/>
-      </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
+      <c r="H41" s="51">
+        <f>'Le moteur'!S27</f>
+        <v/>
+      </c>
+      <c r="I41" s="51">
+        <f>IFERROR(H41/'Le moteur'!O27,0)</f>
+        <v/>
+      </c>
+      <c r="J41" s="51">
+        <f>'Le moteur'!T27</f>
+        <v/>
+      </c>
+      <c r="K41" s="51">
+        <f>IFERROR(J41/C41,0)</f>
+        <v/>
+      </c>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="47" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>MBway Nantes</t>
         </is>
       </c>
-      <c r="C42" s="51">
+      <c r="C42" s="59">
         <f>'Le moteur'!N28</f>
         <v/>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="59">
+        <f>'Le moteur'!G52</f>
+        <v/>
+      </c>
+      <c r="E42" s="51">
+        <f>'Le moteur'!R28</f>
+        <v/>
+      </c>
+      <c r="F42" s="51">
+        <f>IFERROR(E42/C42,0)</f>
+        <v/>
+      </c>
+      <c r="G42" s="71">
         <f>'Le moteur'!Q28</f>
         <v/>
       </c>
-      <c r="E42" s="55">
-        <f>IFERROR(D42/C42,0)</f>
-        <v/>
-      </c>
-      <c r="F42" s="51">
-        <f>'Le moteur'!G52</f>
-        <v/>
-      </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
+      <c r="H42" s="51">
+        <f>'Le moteur'!S28</f>
+        <v/>
+      </c>
+      <c r="I42" s="51">
+        <f>IFERROR(H42/'Le moteur'!O28,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="51">
+        <f>'Le moteur'!T28</f>
+        <v/>
+      </c>
+      <c r="K42" s="51">
+        <f>IFERROR(J42/C42,0)</f>
+        <v/>
+      </c>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="47" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>MBway Paris</t>
         </is>
       </c>
-      <c r="C43" s="51">
+      <c r="C43" s="59">
         <f>'Le moteur'!N29</f>
         <v/>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="59">
+        <f>'Le moteur'!G53</f>
+        <v/>
+      </c>
+      <c r="E43" s="51">
+        <f>'Le moteur'!R29</f>
+        <v/>
+      </c>
+      <c r="F43" s="51">
+        <f>IFERROR(E43/C43,0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="71">
         <f>'Le moteur'!Q29</f>
         <v/>
       </c>
-      <c r="E43" s="55">
-        <f>IFERROR(D43/C43,0)</f>
-        <v/>
-      </c>
-      <c r="F43" s="51">
-        <f>'Le moteur'!G53</f>
-        <v/>
-      </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
+      <c r="H43" s="51">
+        <f>'Le moteur'!S29</f>
+        <v/>
+      </c>
+      <c r="I43" s="51">
+        <f>IFERROR(H43/'Le moteur'!O29,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="51">
+        <f>'Le moteur'!T29</f>
+        <v/>
+      </c>
+      <c r="K43" s="51">
+        <f>IFERROR(J43/C43,0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="47" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>Pigier Bordeaux</t>
         </is>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="59">
         <f>'Le moteur'!N30</f>
         <v/>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="59">
+        <f>'Le moteur'!G54</f>
+        <v/>
+      </c>
+      <c r="E44" s="51">
+        <f>'Le moteur'!R30</f>
+        <v/>
+      </c>
+      <c r="F44" s="51">
+        <f>IFERROR(E44/C44,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="71">
         <f>'Le moteur'!Q30</f>
         <v/>
       </c>
-      <c r="E44" s="55">
-        <f>IFERROR(D44/C44,0)</f>
-        <v/>
-      </c>
-      <c r="F44" s="51">
-        <f>'Le moteur'!G54</f>
-        <v/>
-      </c>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
+      <c r="H44" s="51">
+        <f>'Le moteur'!S30</f>
+        <v/>
+      </c>
+      <c r="I44" s="51">
+        <f>IFERROR(H44/'Le moteur'!O30,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="51">
+        <f>'Le moteur'!T30</f>
+        <v/>
+      </c>
+      <c r="K44" s="51">
+        <f>IFERROR(J44/C44,0)</f>
+        <v/>
+      </c>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="47" t="inlineStr">
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>Pigier Lyon</t>
         </is>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="59">
         <f>'Le moteur'!N31</f>
         <v/>
       </c>
-      <c r="D45" s="55">
+      <c r="D45" s="59">
+        <f>'Le moteur'!G55</f>
+        <v/>
+      </c>
+      <c r="E45" s="51">
+        <f>'Le moteur'!R31</f>
+        <v/>
+      </c>
+      <c r="F45" s="51">
+        <f>IFERROR(E45/C45,0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="71">
         <f>'Le moteur'!Q31</f>
         <v/>
       </c>
-      <c r="E45" s="55">
-        <f>IFERROR(D45/C45,0)</f>
-        <v/>
-      </c>
-      <c r="F45" s="51">
-        <f>'Le moteur'!G55</f>
-        <v/>
-      </c>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
+      <c r="H45" s="51">
+        <f>'Le moteur'!S31</f>
+        <v/>
+      </c>
+      <c r="I45" s="51">
+        <f>IFERROR(H45/'Le moteur'!O31,0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="51">
+        <f>'Le moteur'!T31</f>
+        <v/>
+      </c>
+      <c r="K45" s="51">
+        <f>IFERROR(J45/C45,0)</f>
+        <v/>
+      </c>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="47" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>Tunon Lyon</t>
         </is>
       </c>
-      <c r="C46" s="51">
+      <c r="C46" s="59">
         <f>'Le moteur'!N32</f>
         <v/>
       </c>
-      <c r="D46" s="55">
+      <c r="D46" s="59">
+        <f>'Le moteur'!G56</f>
+        <v/>
+      </c>
+      <c r="E46" s="51">
+        <f>'Le moteur'!R32</f>
+        <v/>
+      </c>
+      <c r="F46" s="51">
+        <f>IFERROR(E46/C46,0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="71">
         <f>'Le moteur'!Q32</f>
         <v/>
       </c>
-      <c r="E46" s="55">
-        <f>IFERROR(D46/C46,0)</f>
-        <v/>
-      </c>
-      <c r="F46" s="51">
-        <f>'Le moteur'!G56</f>
-        <v/>
-      </c>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
+      <c r="H46" s="51">
+        <f>'Le moteur'!S32</f>
+        <v/>
+      </c>
+      <c r="I46" s="51">
+        <f>IFERROR(H46/'Le moteur'!O32,0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="51">
+        <f>'Le moteur'!T32</f>
+        <v/>
+      </c>
+      <c r="K46" s="51">
+        <f>IFERROR(J46/C46,0)</f>
+        <v/>
+      </c>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="47" t="inlineStr">
+      <c r="B47" s="49" t="inlineStr">
         <is>
           <t>Tunon Paris</t>
         </is>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="59">
         <f>'Le moteur'!N33</f>
         <v/>
       </c>
-      <c r="D47" s="55">
+      <c r="D47" s="59">
+        <f>'Le moteur'!G57</f>
+        <v/>
+      </c>
+      <c r="E47" s="51">
+        <f>'Le moteur'!R33</f>
+        <v/>
+      </c>
+      <c r="F47" s="51">
+        <f>IFERROR(E47/C47,0)</f>
+        <v/>
+      </c>
+      <c r="G47" s="71">
         <f>'Le moteur'!Q33</f>
         <v/>
       </c>
-      <c r="E47" s="55">
-        <f>IFERROR(D47/C47,0)</f>
-        <v/>
-      </c>
-      <c r="F47" s="51">
-        <f>'Le moteur'!G57</f>
-        <v/>
-      </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
+      <c r="H47" s="51">
+        <f>'Le moteur'!S33</f>
+        <v/>
+      </c>
+      <c r="I47" s="51">
+        <f>IFERROR(H47/'Le moteur'!O33,0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="51">
+        <f>'Le moteur'!T33</f>
+        <v/>
+      </c>
+      <c r="K47" s="51">
+        <f>IFERROR(J47/C47,0)</f>
+        <v/>
+      </c>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="57" t="inlineStr">
-        <is>
-          <t>GROUPE</t>
-        </is>
-      </c>
-      <c r="C48" s="58">
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <t>GROUPE · 14 campus</t>
+        </is>
+      </c>
+      <c r="C48" s="65">
         <f>SUM(C34:C47)</f>
         <v/>
       </c>
-      <c r="D48" s="61">
+      <c r="D48" s="65">
         <f>SUM(D34:D47)</f>
         <v/>
       </c>
-      <c r="E48" s="61">
-        <f>IFERROR(D48/C48,0)</f>
-        <v/>
-      </c>
-      <c r="F48" s="58">
-        <f>SUM(F34:F47)</f>
-        <v/>
-      </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
+      <c r="E48" s="68">
+        <f>SUM(E34:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="68">
+        <f>IFERROR(E48/C48,0)</f>
+        <v/>
+      </c>
+      <c r="G48" s="72">
+        <f>SUM(G34:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="68">
+        <f>SUM(H34:H47)</f>
+        <v/>
+      </c>
+      <c r="I48" s="68">
+        <f>IFERROR(H48/'Le moteur'!O34,0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="68">
+        <f>SUM(J34:J47)</f>
+        <v/>
+      </c>
+      <c r="K48" s="68">
+        <f>IFERROR(J48/C48,0)</f>
+        <v/>
+      </c>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -4654,10 +5627,18 @@
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="5" t="n"/>
+      <c r="B50" s="70">
+        <f>"Les permanents pèsent "&amp;TEXT(J48/(E48+H48+J48),"0 %")&amp;" du coût d'enseignement du réseau, et pas un euro d'entre eux ne bouge quand un élève de plus s'assoit."</f>
+        <v/>
+      </c>
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="5" t="n"/>
       <c r="E50" s="5" t="n"/>
@@ -4665,14 +5646,15 @@
       <c r="G50" s="5" t="n"/>
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+    </row>
+    <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="36" t="inlineStr">
-        <is>
-          <t>④  Mais ce n'est pas ce coût-là que le masque soustrait</t>
-        </is>
-      </c>
+      <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5" t="n"/>
       <c r="E51" s="5" t="n"/>
@@ -4680,12 +5662,17 @@
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
-    </row>
-    <row r="52" ht="14" customHeight="1">
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>Le geste ajoute des élèves dans des classes qui existent déjà. Leur vacataire est déjà payé : il ne coûte pas un euro de plus. Le coût MARGINAL n'est donc pas le coût moyen.</t>
+      <c r="B52" s="38" t="inlineStr">
+        <is>
+          <t>④  Mais ce n'est pas ce coût-là que le masque soustrait</t>
         </is>
       </c>
       <c r="C52" s="5" t="n"/>
@@ -4695,10 +5682,19 @@
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="n"/>
-    </row>
-    <row r="53">
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="5" t="n"/>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>Le geste ajoute des élèves dans des classes qui existent déjà. Leur vacataire est déjà payé, leur professeur permanent aussi : ils ne coûtent pas un euro de plus. Le coût MARGINAL n'est donc pas le coût moyen.</t>
+        </is>
+      </c>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
       <c r="E53" s="5" t="n"/>
@@ -4706,70 +5702,94 @@
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="64" t="inlineStr">
-        <is>
-          <t>TANT QU'IL RESTE UNE PLACE</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="65" t="inlineStr">
-        <is>
-          <t>les consommables seuls  —  300 ou 372 € selon le campus</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="66" t="inlineStr">
-        <is>
-          <t>QUAND LA CLASSE EST PLEINE</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="67" t="inlineStr">
-        <is>
-          <t>+ la quote-part du vacataire d'une classe neuve  —  et là, le programme compte</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="13" t="n"/>
-      <c r="I55" s="13" t="n"/>
+      <c r="B55" s="73" t="inlineStr">
+        <is>
+          <t>TANT QU'IL RESTE UNE PLACE</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="74">
+        <f>"les consommables seuls  —  de "&amp;TEXT(MIN(F34:F47),"#,##0 €")&amp;" à "&amp;TEXT(MAX(F34:F47),"#,##0 €")&amp;" selon le campus"</f>
+        <v/>
+      </c>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="n"/>
+      <c r="L55" s="21" t="n"/>
+      <c r="M55" s="21" t="n"/>
+      <c r="N55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="68" t="inlineStr">
-        <is>
-          <t>Le masque bascule seul : IF(inscrits gagnés &lt;= places libres ; conso ; conso + vacataires du campus / places du campus).</t>
-        </is>
-      </c>
-      <c r="F56" s="19" t="n"/>
-      <c r="G56" s="19" t="n"/>
-      <c r="H56" s="19" t="n"/>
-      <c r="I56" s="19" t="n"/>
+      <c r="B56" s="75" t="inlineStr">
+        <is>
+          <t>QUAND LA CLASSE EST PLEINE</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="76" t="inlineStr">
+        <is>
+          <t>+ la quote-part du vacataire d'une classe neuve  —  et là, le programme compte</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="13" t="n"/>
+      <c r="I56" s="13" t="n"/>
+      <c r="J56" s="13" t="n"/>
+      <c r="K56" s="13" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="13" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="77" t="inlineStr">
+        <is>
+          <t>Le masque bascule seul : IF(inscrits gagnés &lt;= places libres ; consommables ; consommables + vacataires du campus ÷ places du campus).</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
+      <c r="G57" s="19" t="n"/>
+      <c r="H57" s="19" t="n"/>
+      <c r="I57" s="19" t="n"/>
+      <c r="J57" s="19" t="n"/>
+      <c r="K57" s="19" t="n"/>
+      <c r="L57" s="19" t="n"/>
+      <c r="M57" s="19" t="n"/>
+      <c r="N57" s="19" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -4781,180 +5801,223 @@
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+    </row>
+    <row r="59">
       <c r="A59" s="5" t="n"/>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>Programme qui ouvre</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
+      <c r="C60" s="26" t="inlineStr">
         <is>
           <t>Heures / classe</t>
         </is>
       </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Tarif horaire</t>
         </is>
       </c>
-      <c r="E59" s="26" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>Coût du vacataire</t>
         </is>
       </c>
-      <c r="F59" s="26" t="inlineStr">
+      <c r="F60" s="26" t="inlineStr">
         <is>
           <t>Capacité de la classe</t>
         </is>
       </c>
-      <c r="G59" s="26" t="inlineStr">
+      <c r="G60" s="26" t="inlineStr">
         <is>
           <t>Coût d'ouverture / place</t>
         </is>
       </c>
-      <c r="H59" s="26" t="inlineStr">
+      <c r="H60" s="26" t="inlineStr">
         <is>
           <t>+ consommables ⇒ coût marginal</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="47" t="inlineStr">
-        <is>
-          <t>Bachelor · alternance</t>
-        </is>
-      </c>
-      <c r="C60" s="69" t="n">
-        <v>480</v>
-      </c>
-      <c r="D60" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="E60" s="55">
-        <f>C60*D60</f>
-        <v/>
-      </c>
-      <c r="F60" s="51" t="n">
-        <v>32</v>
-      </c>
-      <c r="G60" s="54">
-        <f>E60/F60</f>
-        <v/>
-      </c>
-      <c r="H60" s="70" t="inlineStr">
-        <is>
-          <t>de 657 à 729 € selon le campus</t>
-        </is>
-      </c>
       <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
-      <c r="B61" s="47" t="inlineStr">
-        <is>
-          <t>Mastère · alternance</t>
-        </is>
-      </c>
-      <c r="C61" s="69" t="n">
-        <v>420</v>
-      </c>
-      <c r="D61" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="E61" s="55">
+      <c r="B61" s="49" t="inlineStr">
+        <is>
+          <t>Bachelor · alternance</t>
+        </is>
+      </c>
+      <c r="C61" s="71">
+        <f>'Intégration &amp; contrôles'!C9</f>
+        <v/>
+      </c>
+      <c r="D61" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="E61" s="51">
         <f>C61*D61</f>
         <v/>
       </c>
-      <c r="F61" s="51" t="n">
-        <v>26</v>
-      </c>
-      <c r="G61" s="54">
+      <c r="F61" s="59">
+        <f>'Intégration &amp; contrôles'!D9</f>
+        <v/>
+      </c>
+      <c r="G61" s="62">
         <f>E61/F61</f>
         <v/>
       </c>
-      <c r="H61" s="70" t="inlineStr">
-        <is>
-          <t>de 684 à 756 € selon le campus</t>
-        </is>
+      <c r="H61" s="78">
+        <f>"de "&amp;TEXT(G61+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G61+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
+        <v/>
       </c>
       <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
-      <c r="B62" s="47" t="inlineStr">
-        <is>
-          <t>Bachelor · initial</t>
-        </is>
-      </c>
-      <c r="C62" s="69" t="n">
-        <v>600</v>
-      </c>
-      <c r="D62" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="E62" s="55">
+      <c r="B62" s="49" t="inlineStr">
+        <is>
+          <t>Mastère · alternance</t>
+        </is>
+      </c>
+      <c r="C62" s="71">
+        <f>'Intégration &amp; contrôles'!C13</f>
+        <v/>
+      </c>
+      <c r="D62" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="E62" s="51">
         <f>C62*D62</f>
         <v/>
       </c>
-      <c r="F62" s="51" t="n">
-        <v>32</v>
-      </c>
-      <c r="G62" s="54">
+      <c r="F62" s="59">
+        <f>'Intégration &amp; contrôles'!D13</f>
+        <v/>
+      </c>
+      <c r="G62" s="62">
         <f>E62/F62</f>
         <v/>
       </c>
-      <c r="H62" s="70" t="inlineStr">
-        <is>
-          <t>de 746 à 818 € selon le campus</t>
-        </is>
+      <c r="H62" s="78">
+        <f>"de "&amp;TEXT(G62+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G62+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
+        <v/>
       </c>
       <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
-      <c r="B63" s="47" t="inlineStr">
-        <is>
-          <t>BTS · alternance</t>
-        </is>
-      </c>
-      <c r="C63" s="69" t="n">
-        <v>700</v>
-      </c>
-      <c r="D63" s="53" t="n">
-        <v>23.80424443106562</v>
-      </c>
-      <c r="E63" s="55">
+      <c r="B63" s="49" t="inlineStr">
+        <is>
+          <t>Bachelor · initial</t>
+        </is>
+      </c>
+      <c r="C63" s="71">
+        <f>'Intégration &amp; contrôles'!C10</f>
+        <v/>
+      </c>
+      <c r="D63" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="E63" s="51">
         <f>C63*D63</f>
         <v/>
       </c>
-      <c r="F63" s="51" t="n">
-        <v>30</v>
-      </c>
-      <c r="G63" s="54">
+      <c r="F63" s="59">
+        <f>'Intégration &amp; contrôles'!D10</f>
+        <v/>
+      </c>
+      <c r="G63" s="62">
         <f>E63/F63</f>
         <v/>
       </c>
-      <c r="H63" s="70" t="inlineStr">
-        <is>
-          <t>de 855 à 927 € selon le campus</t>
-        </is>
+      <c r="H63" s="78">
+        <f>"de "&amp;TEXT(G63+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G63+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
+        <v/>
       </c>
       <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>BTS · alternance</t>
+        </is>
+      </c>
+      <c r="C64" s="71">
+        <f>'Intégration &amp; contrôles'!C11</f>
+        <v/>
+      </c>
+      <c r="D64" s="61">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="E64" s="51">
+        <f>C64*D64</f>
+        <v/>
+      </c>
+      <c r="F64" s="59">
+        <f>'Intégration &amp; contrôles'!D11</f>
+        <v/>
+      </c>
+      <c r="G64" s="62">
+        <f>E64/F64</f>
+        <v/>
+      </c>
+      <c r="H64" s="78">
+        <f>"de "&amp;TEXT(G64+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G64+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
+        <v/>
+      </c>
       <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -4966,40 +6029,55 @@
       <c r="G65" s="5" t="n"/>
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="n"/>
-    </row>
-    <row r="66" ht="18" customHeight="1">
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+    </row>
+    <row r="66">
       <c r="A66" s="5" t="n"/>
-      <c r="B66" s="71" t="inlineStr">
-        <is>
-          <t>Et le compte 6231 n'est jamais là-dedans.</t>
-        </is>
-      </c>
-      <c r="C66" s="72" t="n"/>
-      <c r="D66" s="72" t="n"/>
-      <c r="E66" s="72" t="n"/>
-      <c r="F66" s="72" t="n"/>
-      <c r="G66" s="72" t="n"/>
-      <c r="H66" s="72" t="n"/>
-      <c r="I66" s="72" t="n"/>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>Heures et capacités viennent de l'onglet « Intégration &amp; contrôles » ; le tarif horaire de la ligne MOYENNE PONDÉRÉE ci-dessus. Rien n'est saisi dans ce tableau.</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
-      <c r="B67" s="73" t="inlineStr">
-        <is>
-          <t>6231 est le budget d'acquisition lui-même. Il est déjà soustrait comme Δ budget dans le compte de résultat du geste : le remettre dans le coût variable le compterait deux fois.</t>
-        </is>
-      </c>
-      <c r="C67" s="74" t="n"/>
-      <c r="D67" s="74" t="n"/>
-      <c r="E67" s="74" t="n"/>
-      <c r="F67" s="74" t="n"/>
-      <c r="G67" s="74" t="n"/>
-      <c r="H67" s="74" t="n"/>
-      <c r="I67" s="74" t="n"/>
-    </row>
-    <row r="68">
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="5" t="n"/>
+      <c r="B68" s="79" t="inlineStr">
+        <is>
+          <t>⑤  Et les enseignants permanents, ils sont où ?</t>
+        </is>
+      </c>
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="5" t="n"/>
       <c r="E68" s="5" t="n"/>
@@ -5007,10 +6085,19 @@
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
-    </row>
-    <row r="69">
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
       <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="n"/>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Dans le modèle, et alloués à l'heure comme les vacataires — mais pas dans le coût variable. Voici les vingt comptes de charges du P&amp;L et, pour chacun, la seule question qui compte.</t>
+        </is>
+      </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="5" t="n"/>
       <c r="E69" s="5" t="n"/>
@@ -5018,10 +6105,19 @@
       <c r="G69" s="5" t="n"/>
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="n"/>
-    </row>
-    <row r="70">
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="16" customHeight="1">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="n"/>
+      <c r="B70" s="80" t="inlineStr">
+        <is>
+          <t>Un professeur permanent est un ENGAGEMENT DE CAPACITÉ, pas un coût à l'élève : il est payé pareil que la salle contienne 24 ou 32 étudiants. C'est pour cela qu'il pèse le plus lourd du coût d'enseignement et qu'il ne figure quand même pas dans le coût marginal. Le vacataire, lui, est la seule ressource enseignante que l'on achète à la classe — et le 621 est du personnel EXTÉRIEUR : une facture, donc sans charges sociales 645 en plus.</t>
+        </is>
+      </c>
       <c r="C70" s="5" t="n"/>
       <c r="D70" s="5" t="n"/>
       <c r="E70" s="5" t="n"/>
@@ -5029,6 +6125,11 @@
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -5040,10 +6141,19 @@
       <c r="G71" s="5" t="n"/>
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="n"/>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>Ces montants sont restitués par la COMPTABILITÉ (AW_002_000004_000001), et non repris du tableau ① : c'est ce qui permet de les réconcilier avec la vue — quatre contrôles, onglet « Intégration &amp; contrôles ».</t>
+        </is>
+      </c>
       <c r="C72" s="5" t="n"/>
       <c r="D72" s="5" t="n"/>
       <c r="E72" s="5" t="n"/>
@@ -5051,105 +6161,1028 @@
       <c r="G72" s="5" t="n"/>
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="n"/>
-    </row>
-    <row r="73">
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Compte et libellé</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
+        <is>
+          <t>Part des charges</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>Poche du modèle</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>Clé d'allocation</t>
+        </is>
+      </c>
+      <c r="H73" s="26" t="inlineStr">
+        <is>
+          <t>Comportement</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>Bouge si un élève de plus arrive ?</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
+      <c r="B74" s="49" t="inlineStr">
+        <is>
+          <t>604 · Achats d'études et supports pédagogiques</t>
+        </is>
+      </c>
+      <c r="C74" s="52" t="n"/>
+      <c r="D74" s="51" t="n">
+        <v>677808</v>
+      </c>
+      <c r="E74" s="81">
+        <f>IFERROR(D74/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F74" s="52" t="inlineStr">
+        <is>
+          <t>COST_ODIR</t>
+        </is>
+      </c>
+      <c r="G74" s="52" t="inlineStr">
+        <is>
+          <t>EFFECTIFS</t>
+        </is>
+      </c>
+      <c r="H74" s="53" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="I74" s="54" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
+      <c r="B75" s="49" t="inlineStr">
+        <is>
+          <t>6063 · Fournitures pédagogiques et administratives</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="n"/>
+      <c r="D75" s="51" t="n">
+        <v>451874</v>
+      </c>
+      <c r="E75" s="81">
+        <f>IFERROR(D75/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F75" s="52" t="inlineStr">
+        <is>
+          <t>COST_ODIR</t>
+        </is>
+      </c>
+      <c r="G75" s="52" t="inlineStr">
+        <is>
+          <t>EFFECTIFS</t>
+        </is>
+      </c>
+      <c r="H75" s="53" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="I75" s="54" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
+      <c r="B76" s="49" t="inlineStr">
+        <is>
+          <t>621 · Personnel extérieur — enseignants vacataires</t>
+        </is>
+      </c>
+      <c r="C76" s="52" t="n"/>
+      <c r="D76" s="51" t="n">
+        <v>1581554</v>
+      </c>
+      <c r="E76" s="81">
+        <f>IFERROR(D76/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F76" s="52" t="inlineStr">
+        <is>
+          <t>COST_VAC</t>
+        </is>
+      </c>
+      <c r="G76" s="52" t="inlineStr">
+        <is>
+          <t>HEURES</t>
+        </is>
+      </c>
+      <c r="H76" s="55" t="inlineStr">
+        <is>
+          <t>Semi-variable</t>
+        </is>
+      </c>
+      <c r="I76" s="56" t="inlineStr">
+        <is>
+          <t>Seulement si une classe doit ouvrir</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
+      <c r="B77" s="49" t="inlineStr">
+        <is>
+          <t>6411 · Salaires — enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C77" s="52" t="n"/>
+      <c r="D77" s="51" t="n">
+        <v>3841069.840000001</v>
+      </c>
+      <c r="E77" s="81">
+        <f>IFERROR(D77/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F77" s="52" t="inlineStr">
+        <is>
+          <t>COST_PERM</t>
+        </is>
+      </c>
+      <c r="G77" s="52" t="inlineStr">
+        <is>
+          <t>HEURES</t>
+        </is>
+      </c>
+      <c r="H77" s="57" t="inlineStr">
+        <is>
+          <t>Capacité</t>
+        </is>
+      </c>
+      <c r="I77" s="58" t="inlineStr">
+        <is>
+          <t>NON — le poste est engagé à l'année, pas à l'élève</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="5" t="n"/>
-      <c r="I78" s="5" t="n"/>
+      <c r="B78" s="49" t="inlineStr">
+        <is>
+          <t>6231 · Annonces et insertions — budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C78" s="52" t="n"/>
+      <c r="D78" s="51" t="n">
+        <v>434174</v>
+      </c>
+      <c r="E78" s="81">
+        <f>IFERROR(D78/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F78" s="52" t="inlineStr">
+        <is>
+          <t>COST_ODIR</t>
+        </is>
+      </c>
+      <c r="G78" s="52" t="inlineStr">
+        <is>
+          <t>ENTRANTS</t>
+        </is>
+      </c>
+      <c r="H78" s="82" t="inlineStr">
+        <is>
+          <t>Levier</t>
+        </is>
+      </c>
+      <c r="I78" s="83" t="inlineStr">
+        <is>
+          <t>C'EST LA SAISIE — déjà soustrait comme Δ budget</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
+      <c r="B79" s="49" t="inlineStr">
+        <is>
+          <t>6413 · Salaires — personnel administratif des campus</t>
+        </is>
+      </c>
+      <c r="C79" s="52" t="n"/>
+      <c r="D79" s="51" t="n">
+        <v>2033330.6</v>
+      </c>
+      <c r="E79" s="81">
+        <f>IFERROR(D79/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F79" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G79" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H79" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I79" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
+      <c r="B80" s="49" t="inlineStr">
+        <is>
+          <t>645 · Charges sociales sur les salaires</t>
+        </is>
+      </c>
+      <c r="C80" s="52" t="n"/>
+      <c r="D80" s="51" t="n">
+        <v>3162957.9</v>
+      </c>
+      <c r="E80" s="81">
+        <f>IFERROR(D80/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F80" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G80" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H80" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I80" s="85" t="inlineStr">
+        <is>
+          <t>NON — et 621 n'en porte pas : c'est une facture, pas une paie</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
+      <c r="B81" s="49" t="inlineStr">
+        <is>
+          <t>613 · Locations immobilières des campus</t>
+        </is>
+      </c>
+      <c r="C81" s="52" t="n"/>
+      <c r="D81" s="51" t="n">
+        <v>2372423.51</v>
+      </c>
+      <c r="E81" s="81">
+        <f>IFERROR(D81/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F81" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G81" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H81" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I81" s="85" t="inlineStr">
+        <is>
+          <t>NON — c'est le mur qui coûte, pas l'élève</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="49" t="inlineStr">
+        <is>
+          <t>615 · Entretien et réparations</t>
+        </is>
+      </c>
+      <c r="C82" s="52" t="n"/>
+      <c r="D82" s="51" t="n">
+        <v>338915.38</v>
+      </c>
+      <c r="E82" s="81">
+        <f>IFERROR(D82/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F82" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G82" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H82" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I82" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="49" t="inlineStr">
+        <is>
+          <t>616 · Primes d'assurance</t>
+        </is>
+      </c>
+      <c r="C83" s="52" t="n"/>
+      <c r="D83" s="51" t="n">
+        <v>225926.43</v>
+      </c>
+      <c r="E83" s="81">
+        <f>IFERROR(D83/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F83" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G83" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H83" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I83" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="49" t="inlineStr">
+        <is>
+          <t>625 · Déplacements, missions et réceptions</t>
+        </is>
+      </c>
+      <c r="C84" s="52" t="n"/>
+      <c r="D84" s="51" t="n">
+        <v>338890.3800000001</v>
+      </c>
+      <c r="E84" s="81">
+        <f>IFERROR(D84/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F84" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G84" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H84" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I84" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n"/>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="49" t="inlineStr">
+        <is>
+          <t>63511 · Contribution économique territoriale</t>
+        </is>
+      </c>
+      <c r="C85" s="52" t="n"/>
+      <c r="D85" s="51" t="n">
+        <v>225943.95</v>
+      </c>
+      <c r="E85" s="81">
+        <f>IFERROR(D85/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F85" s="52" t="inlineStr">
+        <is>
+          <t>COST_STRUCT</t>
+        </is>
+      </c>
+      <c r="G85" s="52" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="H85" s="84" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="I85" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n"/>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="49" t="inlineStr">
+        <is>
+          <t>6236 · Catalogues et imprimés — marketing de marque</t>
+        </is>
+      </c>
+      <c r="C86" s="52" t="n"/>
+      <c r="D86" s="51" t="n">
+        <v>676344</v>
+      </c>
+      <c r="E86" s="81">
+        <f>IFERROR(D86/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F86" s="52" t="inlineStr">
+        <is>
+          <t>COST_MARQUE</t>
+        </is>
+      </c>
+      <c r="G86" s="52" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="H86" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I86" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="49" t="inlineStr">
+        <is>
+          <t>6414 · Salaires du siège</t>
+        </is>
+      </c>
+      <c r="C87" s="52" t="n"/>
+      <c r="D87" s="51" t="n">
+        <v>1242649</v>
+      </c>
+      <c r="E87" s="81">
+        <f>IFERROR(D87/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F87" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G87" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H87" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I87" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="49" t="inlineStr">
+        <is>
+          <t>6226 · Honoraires</t>
+        </is>
+      </c>
+      <c r="C88" s="52" t="n"/>
+      <c r="D88" s="51" t="n">
+        <v>564841</v>
+      </c>
+      <c r="E88" s="81">
+        <f>IFERROR(D88/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F88" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G88" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H88" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I88" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="49" t="inlineStr">
+        <is>
+          <t>626 · Frais postaux et de télécommunications</t>
+        </is>
+      </c>
+      <c r="C89" s="52" t="n"/>
+      <c r="D89" s="51" t="n">
+        <v>451872</v>
+      </c>
+      <c r="E89" s="81">
+        <f>IFERROR(D89/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F89" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G89" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H89" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I89" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="49" t="inlineStr">
+        <is>
+          <t>6281 · Cotisations et concours divers</t>
+        </is>
+      </c>
+      <c r="C90" s="52" t="n"/>
+      <c r="D90" s="51" t="n">
+        <v>180749</v>
+      </c>
+      <c r="E90" s="81">
+        <f>IFERROR(D90/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F90" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G90" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H90" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I90" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="49" t="inlineStr">
+        <is>
+          <t>6331 · Versement mobilité</t>
+        </is>
+      </c>
+      <c r="C91" s="52" t="n"/>
+      <c r="D91" s="51" t="n">
+        <v>338904</v>
+      </c>
+      <c r="E91" s="81">
+        <f>IFERROR(D91/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F91" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G91" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H91" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I91" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="49" t="inlineStr">
+        <is>
+          <t>6333 · Participation à la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="C92" s="52" t="n"/>
+      <c r="D92" s="51" t="n">
+        <v>112968</v>
+      </c>
+      <c r="E92" s="81">
+        <f>IFERROR(D92/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F92" s="52" t="inlineStr">
+        <is>
+          <t>COST_HOLDING</t>
+        </is>
+      </c>
+      <c r="G92" s="52" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="H92" s="84" t="inlineStr">
+        <is>
+          <t>Siège</t>
+        </is>
+      </c>
+      <c r="I92" s="85" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="49" t="inlineStr">
+        <is>
+          <t>6811 · Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C93" s="52" t="n"/>
+      <c r="D93" s="51" t="n">
+        <v>1352683</v>
+      </c>
+      <c r="E93" s="81">
+        <f>IFERROR(D93/$D$94,0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="52" t="inlineStr">
+        <is>
+          <t>hors modèle</t>
+        </is>
+      </c>
+      <c r="G93" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="84" t="inlineStr">
+        <is>
+          <t>Hors EBITDA</t>
+        </is>
+      </c>
+      <c r="I93" s="85" t="inlineStr">
+        <is>
+          <t>NON — sous la ligne d'EBITDA</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="64" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES 2026  ·  dotations incluses</t>
+        </is>
+      </c>
+      <c r="C94" s="64" t="n"/>
+      <c r="D94" s="68">
+        <f>SUM(D74:D93)</f>
+        <v/>
+      </c>
+      <c r="E94" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="64" t="inlineStr"/>
+      <c r="G94" s="64" t="inlineStr"/>
+      <c r="H94" s="64" t="inlineStr"/>
+      <c r="I94" s="64" t="inlineStr"/>
+      <c r="J94" s="5" t="n"/>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="87" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires 2026  ·  706 + 7062 + 708</t>
+        </is>
+      </c>
+      <c r="C95" s="87" t="n"/>
+      <c r="D95" s="88" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="E95" s="89" t="inlineStr"/>
+      <c r="F95" s="87" t="inlineStr"/>
+      <c r="G95" s="87" t="inlineStr"/>
+      <c r="H95" s="87" t="inlineStr"/>
+      <c r="I95" s="87" t="inlineStr"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="n"/>
+      <c r="N95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="64" t="inlineStr">
+        <is>
+          <t>EBITDA 2026  =  CA − charges hors dotations</t>
+        </is>
+      </c>
+      <c r="C96" s="64" t="n"/>
+      <c r="D96" s="90">
+        <f>D95-D94+D93</f>
+        <v/>
+      </c>
+      <c r="E96" s="86" t="inlineStr"/>
+      <c r="F96" s="64" t="inlineStr"/>
+      <c r="G96" s="64" t="inlineStr"/>
+      <c r="H96" s="64" t="inlineStr"/>
+      <c r="I96" s="64" t="inlineStr"/>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="91">
+        <f>"Sur "&amp;TEXT(D94,"#,##0 €")&amp;" de charges, "&amp;TEXT(D74+D75,"#,##0 €")&amp;" seulement bougent quand un élève de plus s'assoit — soit "&amp;TEXT((D74+D75)/D94,"0.0 %")&amp;". Tout le reste est de la capacité déjà engagée : c'est précisément ce qui rend le geste d'acquisition aussi rentable tant qu'il reste des places."</f>
+        <v/>
+      </c>
+      <c r="C98" s="92" t="n"/>
+      <c r="D98" s="92" t="n"/>
+      <c r="E98" s="92" t="n"/>
+      <c r="F98" s="92" t="n"/>
+      <c r="G98" s="92" t="n"/>
+      <c r="H98" s="92" t="n"/>
+      <c r="I98" s="92" t="n"/>
+      <c r="J98" s="92" t="n"/>
+      <c r="K98" s="92" t="n"/>
+      <c r="L98" s="92" t="n"/>
+      <c r="M98" s="92" t="n"/>
+      <c r="N98" s="92" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="n"/>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="n"/>
+      <c r="M99" s="5" t="n"/>
+      <c r="N99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="5" t="n"/>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="5" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H22:H25">
@@ -5164,8 +7197,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E47">
+  <conditionalFormatting sqref="F34:F47">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00DCEBC0"/>
+        <color rgb="00F7F7F5"/>
+        <color rgb="00F6C9CC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34:I47">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00DCEBC0"/>
+        <color rgb="00F7F7F5"/>
+        <color rgb="00F6C9CC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K47">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5178,4 +7235,1945 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>EDUSERVICES · le moteur d'acquisition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>INTÉGRATION TAGETIK  &amp;  CONTRÔLES</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="3" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>ⓐ  Les paramètres du modèle  ·  les seules hypothèses du classeur</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Elles ne sortent d'aucune vue : elles décrivent la maquette pédagogique. Fond sable = hypothèse. Changer une cellule ici change tout l'onglet « Le coût variable ».</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Programme</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Heures / classe</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Capacité de la classe</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Origine</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="93" t="inlineStr">
+        <is>
+          <t>Bachelor · alternance</t>
+        </is>
+      </c>
+      <c r="C9" s="94" t="n">
+        <v>480</v>
+      </c>
+      <c r="D9" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" s="96" t="inlineStr">
+        <is>
+          <t>maquette pédagogique</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="93" t="inlineStr">
+        <is>
+          <t>Bachelor · initial</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="n">
+        <v>600</v>
+      </c>
+      <c r="D10" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="96" t="inlineStr">
+        <is>
+          <t>maquette pédagogique</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="93" t="inlineStr">
+        <is>
+          <t>BTS · alternance</t>
+        </is>
+      </c>
+      <c r="C11" s="94" t="n">
+        <v>700</v>
+      </c>
+      <c r="D11" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="96" t="inlineStr">
+        <is>
+          <t>maquette pédagogique</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="97" t="inlineStr">
+        <is>
+          <t>BTS · initial</t>
+        </is>
+      </c>
+      <c r="C12" s="98" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="99" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="100" t="inlineStr">
+        <is>
+          <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="93" t="inlineStr">
+        <is>
+          <t>Mastère · alternance</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="n">
+        <v>420</v>
+      </c>
+      <c r="D13" s="95" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="96" t="inlineStr">
+        <is>
+          <t>maquette pédagogique</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="97" t="inlineStr">
+        <is>
+          <t>Mastère · initial</t>
+        </is>
+      </c>
+      <c r="C14" s="98" t="n">
+        <v>520</v>
+      </c>
+      <c r="D14" s="99" t="n">
+        <v>26</v>
+      </c>
+      <c r="E14" s="100" t="inlineStr">
+        <is>
+          <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Le tarif horaire, lui, n'est PAS un paramètre : il se déduit du réel, compte 621 ÷ heures d'enseignement. Il vit dans l'onglet « Le coût variable ».</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ⓑ  Le mapping  ·  colonne du classeur ↔ colonne de V_MOTEUR_CAL</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Le tableau ① de l'onglet « Le moteur » est la vue, colonne pour colonne. Deux colonnes sont à ajouter à la vue — elles sont signalées en rouge, et tagetik/V_MOTEUR_CAL.sql les porte déjà.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Colonne du classeur</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Colonne de la vue</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>B  ·  Marque</t>
+        </is>
+      </c>
+      <c r="C22" s="101" t="inlineStr">
+        <is>
+          <t>MARQUE</t>
+        </is>
+      </c>
+      <c r="D22" s="101" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="E22" s="101" t="inlineStr">
+        <is>
+          <t>regroupement d'affichage</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>C  ·  Campus</t>
+        </is>
+      </c>
+      <c r="C23" s="101" t="inlineStr">
+        <is>
+          <t>CAMPUS</t>
+        </is>
+      </c>
+      <c r="D23" s="101" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="E23" s="101" t="inlineStr">
+        <is>
+          <t>libellé azienda</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>D  ·  Leads payants 2024</t>
+        </is>
+      </c>
+      <c r="C24" s="101" t="inlineStr">
+        <is>
+          <t>LEAD_PAY_2024</t>
+        </is>
+      </c>
+      <c r="D24" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E24" s="101" t="inlineStr"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="87" t="inlineStr">
+        <is>
+          <t>E  ·  Leads payants 2025</t>
+        </is>
+      </c>
+      <c r="C25" s="101" t="inlineStr">
+        <is>
+          <t>LEAD_PAY_2025</t>
+        </is>
+      </c>
+      <c r="D25" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E25" s="101" t="inlineStr"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="87" t="inlineStr">
+        <is>
+          <t>F  ·  Leads payants 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="101" t="inlineStr">
+        <is>
+          <t>LEAD_PAY_2026</t>
+        </is>
+      </c>
+      <c r="D26" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E26" s="101" t="inlineStr">
+        <is>
+          <t>base du geste</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="87" t="inlineStr">
+        <is>
+          <t>G  ·  Budget acq. 2024</t>
+        </is>
+      </c>
+      <c r="C27" s="101" t="inlineStr">
+        <is>
+          <t>SPEND_ACQ_2024</t>
+        </is>
+      </c>
+      <c r="D27" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E27" s="101" t="inlineStr"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="87" t="inlineStr">
+        <is>
+          <t>H  ·  Budget acq. 2025</t>
+        </is>
+      </c>
+      <c r="C28" s="101" t="inlineStr">
+        <is>
+          <t>SPEND_ACQ_2025</t>
+        </is>
+      </c>
+      <c r="D28" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E28" s="101" t="inlineStr"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>I  ·  Budget acq. 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="101" t="inlineStr">
+        <is>
+          <t>SPEND_ACQ_2026</t>
+        </is>
+      </c>
+      <c r="D29" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E29" s="101">
+        <f> compte 6231</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="87" t="inlineStr">
+        <is>
+          <t>J  ·  Élasticité</t>
+        </is>
+      </c>
+      <c r="C30" s="101" t="inlineStr">
+        <is>
+          <t>ELASTICITE</t>
+        </is>
+      </c>
+      <c r="D30" s="102" t="inlineStr">
+        <is>
+          <t>NON additive</t>
+        </is>
+      </c>
+      <c r="E30" s="101" t="inlineStr">
+        <is>
+          <t>régression log-log, reste au campus</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="87" t="inlineStr">
+        <is>
+          <t>K  ·  Leads totaux 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="101" t="inlineStr">
+        <is>
+          <t>LEAD_TOT_N</t>
+        </is>
+      </c>
+      <c r="D31" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E31" s="101" t="inlineStr">
+        <is>
+          <t>dénominateur de la conversion</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="87" t="inlineStr">
+        <is>
+          <t>L  ·  Inscrits 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="101" t="inlineStr">
+        <is>
+          <t>INSCRITS_N</t>
+        </is>
+      </c>
+      <c r="D32" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E32" s="101" t="inlineStr">
+        <is>
+          <t>numérateur de la conversion</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="87" t="inlineStr">
+        <is>
+          <t>M  ·  CA nouveaux 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="101" t="inlineStr">
+        <is>
+          <t>CA_NEW_N</t>
+        </is>
+      </c>
+      <c r="D33" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E33" s="101" t="inlineStr"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="87" t="inlineStr">
+        <is>
+          <t>N  ·  Effectifs 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="101" t="inlineStr">
+        <is>
+          <t>EFFECTIFS_N</t>
+        </is>
+      </c>
+      <c r="D34" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E34" s="101" t="inlineStr"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="87" t="inlineStr">
+        <is>
+          <t>O  ·  Places 2026</t>
+        </is>
+      </c>
+      <c r="C35" s="101" t="inlineStr">
+        <is>
+          <t>PLACES_N</t>
+        </is>
+      </c>
+      <c r="D35" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E35" s="101" t="inlineStr">
+        <is>
+          <t>classes × capacité</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="87" t="inlineStr">
+        <is>
+          <t>P  ·  Classes 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="101" t="inlineStr">
+        <is>
+          <t>CLASSES_N</t>
+        </is>
+      </c>
+      <c r="D36" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E36" s="101" t="inlineStr"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="103" t="inlineStr">
+        <is>
+          <t>Q  ·  Heures d'enseignement 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="104" t="inlineStr">
+        <is>
+          <t>HEURES_N</t>
+        </is>
+      </c>
+      <c r="D37" s="104" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E37" s="104" t="inlineStr">
+        <is>
+          <t>À AJOUTER À LA VUE</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="87" t="inlineStr">
+        <is>
+          <t>R  ·  Consommables 604+6063</t>
+        </is>
+      </c>
+      <c r="C38" s="101" t="inlineStr">
+        <is>
+          <t>COUT_CONSO_N</t>
+        </is>
+      </c>
+      <c r="D38" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E38" s="101" t="inlineStr"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="87" t="inlineStr">
+        <is>
+          <t>S  ·  Vacataires 621</t>
+        </is>
+      </c>
+      <c r="C39" s="101" t="inlineStr">
+        <is>
+          <t>COUT_VACAT_N</t>
+        </is>
+      </c>
+      <c r="D39" s="101" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E39" s="101" t="inlineStr"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="103" t="inlineStr">
+        <is>
+          <t>T  ·  Enseignants permanents 6411</t>
+        </is>
+      </c>
+      <c r="C40" s="104" t="inlineStr">
+        <is>
+          <t>COUT_PERM_N</t>
+        </is>
+      </c>
+      <c r="D40" s="104" t="inlineStr">
+        <is>
+          <t>mesure</t>
+        </is>
+      </c>
+      <c r="E40" s="104" t="inlineStr">
+        <is>
+          <t>À AJOUTER À LA VUE</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="38" t="inlineStr">
+        <is>
+          <t>ⓒ  Les formules du masque  ·  la ligne 44, campus Ipac Montpellier</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Toutes les autres lignes sont la même formule, décalée. Aucune n'utilise de constante : chacune pointe le tableau ① ou la saisie F4.</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Mesure</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Col.</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Formule du classeur</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>Ce qu'elle dit</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="82" t="inlineStr">
+        <is>
+          <t>Δ budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C47" s="82" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D47" s="105" t="inlineStr">
+        <is>
+          <t>SAISIE</t>
+        </is>
+      </c>
+      <c r="E47" s="82" t="n"/>
+      <c r="F47" s="82" t="inlineStr">
+        <is>
+          <t>la seule cellule modifiable du classeur</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="106" t="inlineStr">
+        <is>
+          <t>Conversion lead → inscrit</t>
+        </is>
+      </c>
+      <c r="C48" s="107" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D48" s="108" t="inlineStr">
+        <is>
+          <t>=IFERROR(L20/K20,0)</t>
+        </is>
+      </c>
+      <c r="E48" s="107" t="n"/>
+      <c r="F48" s="107" t="inlineStr">
+        <is>
+          <t>INSCRITS_N ÷ LEAD_TOT_N — jamais pré-calculée, sinon la ligne groupe se trompe</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="106" t="inlineStr">
+        <is>
+          <t>CA par inscrit</t>
+        </is>
+      </c>
+      <c r="C49" s="107" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D49" s="108" t="inlineStr">
+        <is>
+          <t>=IFERROR(M20/L20,0)</t>
+        </is>
+      </c>
+      <c r="E49" s="107" t="n"/>
+      <c r="F49" s="107" t="inlineStr">
+        <is>
+          <t>CA_NEW_N ÷ INSCRITS_N</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="106" t="inlineStr">
+        <is>
+          <t>Consommables / élève</t>
+        </is>
+      </c>
+      <c r="C50" s="107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D50" s="108" t="inlineStr">
+        <is>
+          <t>=IFERROR(R20/N20,0)</t>
+        </is>
+      </c>
+      <c r="E50" s="107" t="n"/>
+      <c r="F50" s="107" t="inlineStr">
+        <is>
+          <t>COUT_CONSO_N ÷ EFFECTIFS_N</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="106" t="inlineStr">
+        <is>
+          <t>Places libres</t>
+        </is>
+      </c>
+      <c r="C51" s="107" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D51" s="108" t="inlineStr">
+        <is>
+          <t>=O20-N20</t>
+        </is>
+      </c>
+      <c r="E51" s="107" t="n"/>
+      <c r="F51" s="107" t="inlineStr">
+        <is>
+          <t>PLACES_N − EFFECTIFS_N : la borne physique du geste</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="106" t="inlineStr">
+        <is>
+          <t>Δ budget</t>
+        </is>
+      </c>
+      <c r="C52" s="107" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D52" s="108" t="inlineStr">
+        <is>
+          <t>=I20*$F$4</t>
+        </is>
+      </c>
+      <c r="E52" s="107" t="n"/>
+      <c r="F52" s="107" t="inlineStr">
+        <is>
+          <t>le geste, appliqué au budget 2026</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="106" t="inlineStr">
+        <is>
+          <t>Inscrits gagnés</t>
+        </is>
+      </c>
+      <c r="C53" s="107" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D53" s="108" t="inlineStr">
+        <is>
+          <t>=F20*((1+$F$4)^J20-1)*D44</t>
+        </is>
+      </c>
+      <c r="E53" s="107" t="n"/>
+      <c r="F53" s="107" t="inlineStr">
+        <is>
+          <t>leads payants × l'effet d'élasticité, converti au taux du campus</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="106" t="inlineStr">
+        <is>
+          <t>CA gagné</t>
+        </is>
+      </c>
+      <c r="C54" s="107" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="D54" s="108" t="inlineStr">
+        <is>
+          <t>=I44*E44</t>
+        </is>
+      </c>
+      <c r="E54" s="107" t="n"/>
+      <c r="F54" s="107" t="inlineStr">
+        <is>
+          <t>inscrits gagnés × CA par inscrit</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="106" t="inlineStr">
+        <is>
+          <t>Coût marginal / élève</t>
+        </is>
+      </c>
+      <c r="C55" s="107" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D55" s="108" t="inlineStr">
+        <is>
+          <t>=IF(I44&lt;=G44,F44,F44+S20/O20)</t>
+        </is>
+      </c>
+      <c r="E55" s="107" t="n"/>
+      <c r="F55" s="107" t="inlineStr">
+        <is>
+          <t>consommables seuls, + quote-part vacataire si la classe doit ouvrir</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="106" t="inlineStr">
+        <is>
+          <t>EBITDA gagné</t>
+        </is>
+      </c>
+      <c r="C56" s="107" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D56" s="108" t="inlineStr">
+        <is>
+          <t>=J44-H44-I44*K44</t>
+        </is>
+      </c>
+      <c r="E56" s="107" t="n"/>
+      <c r="F56" s="107" t="inlineStr">
+        <is>
+          <t>CA gagné − Δ budget − coût de service</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="106" t="inlineStr">
+        <is>
+          <t>CAC marginal</t>
+        </is>
+      </c>
+      <c r="C57" s="107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D57" s="108" t="inlineStr">
+        <is>
+          <t>=IFERROR(H44/I44,0)</t>
+        </is>
+      </c>
+      <c r="E57" s="107" t="n"/>
+      <c r="F57" s="107" t="inlineStr">
+        <is>
+          <t>Δ budget ÷ inscrits gagnés</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>ⓓ  Les contrôles  ·  ils doivent tous valoir zéro</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>Chacun confronte deux sources indépendantes. Le dernier n'est pas un écart mais une marge : il dit combien de sièges restent avant que le coût marginal ne bascule.</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>Contrôle</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n"/>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Source A</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui est comparé</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>Budget d'acquisition : dépense CRM 2026 = compte 6231</t>
+        </is>
+      </c>
+      <c r="C64" s="52" t="n"/>
+      <c r="D64" s="51">
+        <f>'Le moteur'!I34</f>
+        <v/>
+      </c>
+      <c r="E64" s="51">
+        <f>'Le coût variable'!D78</f>
+        <v/>
+      </c>
+      <c r="F64" s="51">
+        <f>D64-E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="50">
+        <f>IF(ABS(F64)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H64" s="78" t="inlineStr">
+        <is>
+          <t>socle CRM contre comptabilité</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="49" t="inlineStr">
+        <is>
+          <t>Consommables : comptes 604 + 6063 = COUT_CONSO_N</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="n"/>
+      <c r="D65" s="51">
+        <f>'Le coût variable'!D74+'Le coût variable'!D75</f>
+        <v/>
+      </c>
+      <c r="E65" s="51">
+        <f>'Le moteur'!R34</f>
+        <v/>
+      </c>
+      <c r="F65" s="51">
+        <f>D65-E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="50">
+        <f>IF(ABS(F65)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H65" s="78" t="inlineStr">
+        <is>
+          <t>comptes contre agrégat de la vue</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="49" t="inlineStr">
+        <is>
+          <t>Vacataires : compte 621 = COUT_VACAT_N</t>
+        </is>
+      </c>
+      <c r="C66" s="52" t="n"/>
+      <c r="D66" s="51">
+        <f>'Le coût variable'!D76</f>
+        <v/>
+      </c>
+      <c r="E66" s="51">
+        <f>'Le moteur'!S34</f>
+        <v/>
+      </c>
+      <c r="F66" s="51">
+        <f>D66-E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="50">
+        <f>IF(ABS(F66)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H66" s="78" t="inlineStr">
+        <is>
+          <t>comptes contre agrégat de la vue</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="49" t="inlineStr">
+        <is>
+          <t>Permanents : compte 6411 = COUT_PERM_N</t>
+        </is>
+      </c>
+      <c r="C67" s="52" t="n"/>
+      <c r="D67" s="51">
+        <f>'Le coût variable'!D77</f>
+        <v/>
+      </c>
+      <c r="E67" s="51">
+        <f>'Le moteur'!T34</f>
+        <v/>
+      </c>
+      <c r="F67" s="51">
+        <f>D67-E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="50">
+        <f>IF(ABS(F67)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H67" s="78" t="inlineStr">
+        <is>
+          <t>comptes contre agrégat de la vue</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="49" t="inlineStr">
+        <is>
+          <t>Effectifs : grain programme = grain campus</t>
+        </is>
+      </c>
+      <c r="C68" s="52" t="n"/>
+      <c r="D68" s="59">
+        <f>'Le coût variable'!C26</f>
+        <v/>
+      </c>
+      <c r="E68" s="59">
+        <f>'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="F68" s="59">
+        <f>D68-E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="50">
+        <f>IF(ABS(F68)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H68" s="78" t="inlineStr">
+        <is>
+          <t>cycle × modalité contre campus</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n"/>
+      <c r="J68" s="5" t="n"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="49" t="inlineStr">
+        <is>
+          <t>Allocation : consommables alloués aux programmes = total réseau</t>
+        </is>
+      </c>
+      <c r="C69" s="52" t="n"/>
+      <c r="D69" s="51">
+        <f>SUMPRODUCT('Le coût variable'!C22:C25,'Le coût variable'!G22:G25)</f>
+        <v/>
+      </c>
+      <c r="E69" s="51">
+        <f>'Le moteur'!R34</f>
+        <v/>
+      </c>
+      <c r="F69" s="51">
+        <f>D69-E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="50">
+        <f>IF(ABS(F69)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H69" s="78" t="inlineStr">
+        <is>
+          <t>la clé EFFECTIFS ne perd rien</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="49" t="inlineStr">
+        <is>
+          <t>EBITDA gagné : CA gagné − Δ budget − coût de service</t>
+        </is>
+      </c>
+      <c r="C70" s="52" t="n"/>
+      <c r="D70" s="51">
+        <f>'Le moteur'!J58-'Le moteur'!H58-'Le moteur'!I58*'Le moteur'!K58</f>
+        <v/>
+      </c>
+      <c r="E70" s="51">
+        <f>'Le moteur'!L58</f>
+        <v/>
+      </c>
+      <c r="F70" s="51">
+        <f>D70-E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="50">
+        <f>IF(ABS(F70)&lt;1,"OK","À VÉRIFIER")</f>
+        <v/>
+      </c>
+      <c r="H70" s="78" t="inlineStr">
+        <is>
+          <t>additivité de la ligne groupe</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="49" t="inlineStr">
+        <is>
+          <t>Régime du coût marginal : inscrits gagnés ≤ places libres</t>
+        </is>
+      </c>
+      <c r="C71" s="52" t="n"/>
+      <c r="D71" s="59">
+        <f>'Le moteur'!I58</f>
+        <v/>
+      </c>
+      <c r="E71" s="59">
+        <f>'Le moteur'!G58</f>
+        <v/>
+      </c>
+      <c r="F71" s="59">
+        <f>E71-D71</f>
+        <v/>
+      </c>
+      <c r="G71" s="50">
+        <f>IF(F71&gt;0,"OK · marge","BASCULE")</f>
+        <v/>
+      </c>
+      <c r="H71" s="78" t="inlineStr">
+        <is>
+          <t>si dépassé, une classe ouvre</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="109" t="inlineStr">
+        <is>
+          <t>Ce qu'il reste à faire côté Tagetik</t>
+        </is>
+      </c>
+      <c r="C74" s="110" t="n"/>
+      <c r="D74" s="110" t="n"/>
+      <c r="E74" s="110" t="n"/>
+      <c r="F74" s="110" t="n"/>
+      <c r="G74" s="110" t="n"/>
+      <c r="H74" s="110" t="n"/>
+      <c r="I74" s="110" t="n"/>
+      <c r="J74" s="110" t="n"/>
+      <c r="K74" s="110" t="n"/>
+      <c r="L74" s="110" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="111" t="inlineStr">
+        <is>
+          <t>① ajouter HEURES_N et COUT_PERM_N à V_MOTEUR_CAL (le .sql du dépôt les porte).  ② brancher le tableau ① sur la vue, une ligne par campus, hiérarchie MARQUE ▸ CAMPUS.  ③ le tableau ② est un masque de saisie : seule F4 est ouverte.  ④ l'onglet « Le coût variable » ne lit que le tableau ① et les paramètres ci-dessus.</t>
+        </is>
+      </c>
+      <c r="C75" s="112" t="n"/>
+      <c r="D75" s="112" t="n"/>
+      <c r="E75" s="112" t="n"/>
+      <c r="F75" s="112" t="n"/>
+      <c r="G75" s="112" t="n"/>
+      <c r="H75" s="112" t="n"/>
+      <c r="I75" s="112" t="n"/>
+      <c r="J75" s="112" t="n"/>
+      <c r="K75" s="112" t="n"/>
+      <c r="L75" s="112" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G64:G71">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>ISNUMBER(SEARCH("OK",$G64))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>NOT(ISNUMBER(SEARCH("OK",$G64)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Le moteur" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Le coût variable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Intégration &amp; contrôles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Projection 2027" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%;&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00&quot; €&quot;"/>
@@ -28,8 +29,10 @@
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
     <numFmt numFmtId="171" formatCode="0.0&quot; h&quot;"/>
     <numFmt numFmtId="172" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="173" formatCode="+0.00%;-0.00%;&quot;—&quot;"/>
+    <numFmt numFmtId="174" formatCode="+0.00&quot; pt&quot;;-0.00&quot; pt&quot;"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -242,6 +245,12 @@
       <color rgb="00007AC3"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005F8A17"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -291,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -377,11 +386,30 @@
         <color rgb="00007AC3"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E6E2D6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C3B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C3B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C3B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C3B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -580,9 +608,15 @@
     <xf numFmtId="168" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -607,9 +641,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -621,9 +652,6 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -697,6 +725,83 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="33" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="36" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4908,7 +5013,11 @@
           <t>Permanents / élève</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n"/>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>Croissance possible avant saturation</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="n"/>
       <c r="N33" s="5" t="n"/>
     </row>
@@ -4955,7 +5064,10 @@
         <f>IFERROR(J34/C34,0)</f>
         <v/>
       </c>
-      <c r="L34" s="5" t="n"/>
+      <c r="L34" s="72">
+        <f>IFERROR(D34/C34,0)</f>
+        <v/>
+      </c>
       <c r="M34" s="5" t="n"/>
       <c r="N34" s="5" t="n"/>
     </row>
@@ -5002,7 +5114,10 @@
         <f>IFERROR(J35/C35,0)</f>
         <v/>
       </c>
-      <c r="L35" s="5" t="n"/>
+      <c r="L35" s="72">
+        <f>IFERROR(D35/C35,0)</f>
+        <v/>
+      </c>
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
     </row>
@@ -5049,7 +5164,10 @@
         <f>IFERROR(J36/C36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="5" t="n"/>
+      <c r="L36" s="72">
+        <f>IFERROR(D36/C36,0)</f>
+        <v/>
+      </c>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
     </row>
@@ -5096,7 +5214,10 @@
         <f>IFERROR(J37/C37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="5" t="n"/>
+      <c r="L37" s="72">
+        <f>IFERROR(D37/C37,0)</f>
+        <v/>
+      </c>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
     </row>
@@ -5143,7 +5264,10 @@
         <f>IFERROR(J38/C38,0)</f>
         <v/>
       </c>
-      <c r="L38" s="5" t="n"/>
+      <c r="L38" s="72">
+        <f>IFERROR(D38/C38,0)</f>
+        <v/>
+      </c>
       <c r="M38" s="5" t="n"/>
       <c r="N38" s="5" t="n"/>
     </row>
@@ -5190,7 +5314,10 @@
         <f>IFERROR(J39/C39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="5" t="n"/>
+      <c r="L39" s="72">
+        <f>IFERROR(D39/C39,0)</f>
+        <v/>
+      </c>
       <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
     </row>
@@ -5237,7 +5364,10 @@
         <f>IFERROR(J40/C40,0)</f>
         <v/>
       </c>
-      <c r="L40" s="5" t="n"/>
+      <c r="L40" s="72">
+        <f>IFERROR(D40/C40,0)</f>
+        <v/>
+      </c>
       <c r="M40" s="5" t="n"/>
       <c r="N40" s="5" t="n"/>
     </row>
@@ -5284,7 +5414,10 @@
         <f>IFERROR(J41/C41,0)</f>
         <v/>
       </c>
-      <c r="L41" s="5" t="n"/>
+      <c r="L41" s="72">
+        <f>IFERROR(D41/C41,0)</f>
+        <v/>
+      </c>
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
     </row>
@@ -5331,7 +5464,10 @@
         <f>IFERROR(J42/C42,0)</f>
         <v/>
       </c>
-      <c r="L42" s="5" t="n"/>
+      <c r="L42" s="72">
+        <f>IFERROR(D42/C42,0)</f>
+        <v/>
+      </c>
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
     </row>
@@ -5378,7 +5514,10 @@
         <f>IFERROR(J43/C43,0)</f>
         <v/>
       </c>
-      <c r="L43" s="5" t="n"/>
+      <c r="L43" s="72">
+        <f>IFERROR(D43/C43,0)</f>
+        <v/>
+      </c>
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
     </row>
@@ -5425,7 +5564,10 @@
         <f>IFERROR(J44/C44,0)</f>
         <v/>
       </c>
-      <c r="L44" s="5" t="n"/>
+      <c r="L44" s="72">
+        <f>IFERROR(D44/C44,0)</f>
+        <v/>
+      </c>
       <c r="M44" s="5" t="n"/>
       <c r="N44" s="5" t="n"/>
     </row>
@@ -5472,7 +5614,10 @@
         <f>IFERROR(J45/C45,0)</f>
         <v/>
       </c>
-      <c r="L45" s="5" t="n"/>
+      <c r="L45" s="72">
+        <f>IFERROR(D45/C45,0)</f>
+        <v/>
+      </c>
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
     </row>
@@ -5519,7 +5664,10 @@
         <f>IFERROR(J46/C46,0)</f>
         <v/>
       </c>
-      <c r="L46" s="5" t="n"/>
+      <c r="L46" s="72">
+        <f>IFERROR(D46/C46,0)</f>
+        <v/>
+      </c>
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
     </row>
@@ -5566,7 +5714,10 @@
         <f>IFERROR(J47/C47,0)</f>
         <v/>
       </c>
-      <c r="L47" s="5" t="n"/>
+      <c r="L47" s="72">
+        <f>IFERROR(D47/C47,0)</f>
+        <v/>
+      </c>
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
     </row>
@@ -5593,7 +5744,7 @@
         <f>IFERROR(E48/C48,0)</f>
         <v/>
       </c>
-      <c r="G48" s="72">
+      <c r="G48" s="73">
         <f>SUM(G34:G47)</f>
         <v/>
       </c>
@@ -5613,13 +5764,20 @@
         <f>IFERROR(J48/C48,0)</f>
         <v/>
       </c>
-      <c r="L48" s="5" t="n"/>
+      <c r="L48" s="74">
+        <f>MIN(L34:L47)</f>
+        <v/>
+      </c>
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>La dernière colonne ne se somme pas : au groupe, la croissance possible est celle du PREMIER campus qui sature, pas la moyenne du réseau.</t>
+        </is>
+      </c>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="5" t="n"/>
       <c r="E49" s="5" t="n"/>
@@ -5726,13 +5884,13 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="73" t="inlineStr">
+      <c r="B55" s="75" t="inlineStr">
         <is>
           <t>TANT QU'IL RESTE UNE PLACE</t>
         </is>
       </c>
       <c r="C55" s="21" t="n"/>
-      <c r="D55" s="74">
+      <c r="D55" s="76">
         <f>"les consommables seuls  —  de "&amp;TEXT(MIN(F34:F47),"#,##0 €")&amp;" à "&amp;TEXT(MAX(F34:F47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -5749,13 +5907,13 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="75" t="inlineStr">
+      <c r="B56" s="77" t="inlineStr">
         <is>
           <t>QUAND LA CLASSE EST PLEINE</t>
         </is>
       </c>
       <c r="C56" s="13" t="n"/>
-      <c r="D56" s="76" t="inlineStr">
+      <c r="D56" s="78" t="inlineStr">
         <is>
           <t>+ la quote-part du vacataire d'une classe neuve  —  et là, le programme compte</t>
         </is>
@@ -5775,7 +5933,7 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="19" t="n"/>
       <c r="C57" s="19" t="n"/>
-      <c r="D57" s="77" t="inlineStr">
+      <c r="D57" s="79" t="inlineStr">
         <is>
           <t>Le masque bascule seul : IF(inscrits gagnés &lt;= places libres ; consommables ; consommables + vacataires du campus ÷ places du campus).</t>
         </is>
@@ -5894,7 +6052,7 @@
         <f>E61/F61</f>
         <v/>
       </c>
-      <c r="H61" s="78">
+      <c r="H61" s="80">
         <f>"de "&amp;TEXT(G61+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G61+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -5932,7 +6090,7 @@
         <f>E62/F62</f>
         <v/>
       </c>
-      <c r="H62" s="78">
+      <c r="H62" s="80">
         <f>"de "&amp;TEXT(G62+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G62+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -5970,7 +6128,7 @@
         <f>E63/F63</f>
         <v/>
       </c>
-      <c r="H63" s="78">
+      <c r="H63" s="80">
         <f>"de "&amp;TEXT(G63+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G63+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6008,7 +6166,7 @@
         <f>E64/F64</f>
         <v/>
       </c>
-      <c r="H64" s="78">
+      <c r="H64" s="80">
         <f>"de "&amp;TEXT(G64+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G64+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6073,7 +6231,7 @@
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="79" t="inlineStr">
+      <c r="B68" s="81" t="inlineStr">
         <is>
           <t>⑤  Et les enseignants permanents, ils sont où ?</t>
         </is>
@@ -6113,7 +6271,7 @@
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="80" t="inlineStr">
+      <c r="B70" s="82" t="inlineStr">
         <is>
           <t>Un professeur permanent est un ENGAGEMENT DE CAPACITÉ, pas un coût à l'élève : il est payé pareil que la salle contienne 24 ou 32 étudiants. C'est pour cela qu'il pèse le plus lourd du coût d'enseignement et qu'il ne figure quand même pas dans le coût marginal. Le vacataire, lui, est la seule ressource enseignante que l'on achète à la classe — et le 621 est du personnel EXTÉRIEUR : une facture, donc sans charges sociales 645 en plus.</t>
         </is>
@@ -6222,7 +6380,7 @@
       <c r="D74" s="51" t="n">
         <v>677808</v>
       </c>
-      <c r="E74" s="81">
+      <c r="E74" s="72">
         <f>IFERROR(D74/$D$94,0)</f>
         <v/>
       </c>
@@ -6263,7 +6421,7 @@
       <c r="D75" s="51" t="n">
         <v>451874</v>
       </c>
-      <c r="E75" s="81">
+      <c r="E75" s="72">
         <f>IFERROR(D75/$D$94,0)</f>
         <v/>
       </c>
@@ -6304,7 +6462,7 @@
       <c r="D76" s="51" t="n">
         <v>1581554</v>
       </c>
-      <c r="E76" s="81">
+      <c r="E76" s="72">
         <f>IFERROR(D76/$D$94,0)</f>
         <v/>
       </c>
@@ -6345,7 +6503,7 @@
       <c r="D77" s="51" t="n">
         <v>3841069.840000001</v>
       </c>
-      <c r="E77" s="81">
+      <c r="E77" s="72">
         <f>IFERROR(D77/$D$94,0)</f>
         <v/>
       </c>
@@ -6386,7 +6544,7 @@
       <c r="D78" s="51" t="n">
         <v>434174</v>
       </c>
-      <c r="E78" s="81">
+      <c r="E78" s="72">
         <f>IFERROR(D78/$D$94,0)</f>
         <v/>
       </c>
@@ -6400,12 +6558,12 @@
           <t>ENTRANTS</t>
         </is>
       </c>
-      <c r="H78" s="82" t="inlineStr">
+      <c r="H78" s="83" t="inlineStr">
         <is>
           <t>Levier</t>
         </is>
       </c>
-      <c r="I78" s="83" t="inlineStr">
+      <c r="I78" s="84" t="inlineStr">
         <is>
           <t>C'EST LA SAISIE — déjà soustrait comme Δ budget</t>
         </is>
@@ -6427,7 +6585,7 @@
       <c r="D79" s="51" t="n">
         <v>2033330.6</v>
       </c>
-      <c r="E79" s="81">
+      <c r="E79" s="72">
         <f>IFERROR(D79/$D$94,0)</f>
         <v/>
       </c>
@@ -6441,12 +6599,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H79" s="84" t="inlineStr">
+      <c r="H79" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I79" s="85" t="inlineStr">
+      <c r="I79" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6468,7 +6626,7 @@
       <c r="D80" s="51" t="n">
         <v>3162957.9</v>
       </c>
-      <c r="E80" s="81">
+      <c r="E80" s="72">
         <f>IFERROR(D80/$D$94,0)</f>
         <v/>
       </c>
@@ -6482,12 +6640,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H80" s="84" t="inlineStr">
+      <c r="H80" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I80" s="85" t="inlineStr">
+      <c r="I80" s="86" t="inlineStr">
         <is>
           <t>NON — et 621 n'en porte pas : c'est une facture, pas une paie</t>
         </is>
@@ -6509,7 +6667,7 @@
       <c r="D81" s="51" t="n">
         <v>2372423.51</v>
       </c>
-      <c r="E81" s="81">
+      <c r="E81" s="72">
         <f>IFERROR(D81/$D$94,0)</f>
         <v/>
       </c>
@@ -6523,12 +6681,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H81" s="84" t="inlineStr">
+      <c r="H81" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I81" s="85" t="inlineStr">
+      <c r="I81" s="86" t="inlineStr">
         <is>
           <t>NON — c'est le mur qui coûte, pas l'élève</t>
         </is>
@@ -6550,7 +6708,7 @@
       <c r="D82" s="51" t="n">
         <v>338915.38</v>
       </c>
-      <c r="E82" s="81">
+      <c r="E82" s="72">
         <f>IFERROR(D82/$D$94,0)</f>
         <v/>
       </c>
@@ -6564,12 +6722,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H82" s="84" t="inlineStr">
+      <c r="H82" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I82" s="85" t="inlineStr">
+      <c r="I82" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6591,7 +6749,7 @@
       <c r="D83" s="51" t="n">
         <v>225926.43</v>
       </c>
-      <c r="E83" s="81">
+      <c r="E83" s="72">
         <f>IFERROR(D83/$D$94,0)</f>
         <v/>
       </c>
@@ -6605,12 +6763,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H83" s="84" t="inlineStr">
+      <c r="H83" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I83" s="85" t="inlineStr">
+      <c r="I83" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6632,7 +6790,7 @@
       <c r="D84" s="51" t="n">
         <v>338890.3800000001</v>
       </c>
-      <c r="E84" s="81">
+      <c r="E84" s="72">
         <f>IFERROR(D84/$D$94,0)</f>
         <v/>
       </c>
@@ -6646,12 +6804,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H84" s="84" t="inlineStr">
+      <c r="H84" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I84" s="85" t="inlineStr">
+      <c r="I84" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6673,7 +6831,7 @@
       <c r="D85" s="51" t="n">
         <v>225943.95</v>
       </c>
-      <c r="E85" s="81">
+      <c r="E85" s="72">
         <f>IFERROR(D85/$D$94,0)</f>
         <v/>
       </c>
@@ -6687,12 +6845,12 @@
           <t>K3</t>
         </is>
       </c>
-      <c r="H85" s="84" t="inlineStr">
+      <c r="H85" s="85" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="I85" s="85" t="inlineStr">
+      <c r="I85" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6714,7 +6872,7 @@
       <c r="D86" s="51" t="n">
         <v>676344</v>
       </c>
-      <c r="E86" s="81">
+      <c r="E86" s="72">
         <f>IFERROR(D86/$D$94,0)</f>
         <v/>
       </c>
@@ -6728,12 +6886,12 @@
           <t>K4</t>
         </is>
       </c>
-      <c r="H86" s="84" t="inlineStr">
+      <c r="H86" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I86" s="85" t="inlineStr">
+      <c r="I86" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6755,7 +6913,7 @@
       <c r="D87" s="51" t="n">
         <v>1242649</v>
       </c>
-      <c r="E87" s="81">
+      <c r="E87" s="72">
         <f>IFERROR(D87/$D$94,0)</f>
         <v/>
       </c>
@@ -6769,12 +6927,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H87" s="84" t="inlineStr">
+      <c r="H87" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I87" s="85" t="inlineStr">
+      <c r="I87" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6796,7 +6954,7 @@
       <c r="D88" s="51" t="n">
         <v>564841</v>
       </c>
-      <c r="E88" s="81">
+      <c r="E88" s="72">
         <f>IFERROR(D88/$D$94,0)</f>
         <v/>
       </c>
@@ -6810,12 +6968,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H88" s="84" t="inlineStr">
+      <c r="H88" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I88" s="85" t="inlineStr">
+      <c r="I88" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6837,7 +6995,7 @@
       <c r="D89" s="51" t="n">
         <v>451872</v>
       </c>
-      <c r="E89" s="81">
+      <c r="E89" s="72">
         <f>IFERROR(D89/$D$94,0)</f>
         <v/>
       </c>
@@ -6851,12 +7009,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H89" s="84" t="inlineStr">
+      <c r="H89" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I89" s="85" t="inlineStr">
+      <c r="I89" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6878,7 +7036,7 @@
       <c r="D90" s="51" t="n">
         <v>180749</v>
       </c>
-      <c r="E90" s="81">
+      <c r="E90" s="72">
         <f>IFERROR(D90/$D$94,0)</f>
         <v/>
       </c>
@@ -6892,12 +7050,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H90" s="84" t="inlineStr">
+      <c r="H90" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I90" s="85" t="inlineStr">
+      <c r="I90" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6919,7 +7077,7 @@
       <c r="D91" s="51" t="n">
         <v>338904</v>
       </c>
-      <c r="E91" s="81">
+      <c r="E91" s="72">
         <f>IFERROR(D91/$D$94,0)</f>
         <v/>
       </c>
@@ -6933,12 +7091,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H91" s="84" t="inlineStr">
+      <c r="H91" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I91" s="85" t="inlineStr">
+      <c r="I91" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -6960,7 +7118,7 @@
       <c r="D92" s="51" t="n">
         <v>112968</v>
       </c>
-      <c r="E92" s="81">
+      <c r="E92" s="72">
         <f>IFERROR(D92/$D$94,0)</f>
         <v/>
       </c>
@@ -6974,12 +7132,12 @@
           <t>K1</t>
         </is>
       </c>
-      <c r="H92" s="84" t="inlineStr">
+      <c r="H92" s="85" t="inlineStr">
         <is>
           <t>Siège</t>
         </is>
       </c>
-      <c r="I92" s="85" t="inlineStr">
+      <c r="I92" s="86" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -7001,7 +7159,7 @@
       <c r="D93" s="51" t="n">
         <v>1352683</v>
       </c>
-      <c r="E93" s="81">
+      <c r="E93" s="72">
         <f>IFERROR(D93/$D$94,0)</f>
         <v/>
       </c>
@@ -7015,12 +7173,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H93" s="84" t="inlineStr">
+      <c r="H93" s="85" t="inlineStr">
         <is>
           <t>Hors EBITDA</t>
         </is>
       </c>
-      <c r="I93" s="85" t="inlineStr">
+      <c r="I93" s="86" t="inlineStr">
         <is>
           <t>NON — sous la ligne d'EBITDA</t>
         </is>
@@ -7043,7 +7201,7 @@
         <f>SUM(D74:D93)</f>
         <v/>
       </c>
-      <c r="E94" s="86" t="n">
+      <c r="E94" s="74" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="64" t="inlineStr"/>
@@ -7090,7 +7248,7 @@
         <f>D95-D94+D93</f>
         <v/>
       </c>
-      <c r="E96" s="86" t="inlineStr"/>
+      <c r="E96" s="74" t="inlineStr"/>
       <c r="F96" s="64" t="inlineStr"/>
       <c r="G96" s="64" t="inlineStr"/>
       <c r="H96" s="64" t="inlineStr"/>
@@ -8329,12 +8487,12 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="82" t="inlineStr">
+      <c r="B47" s="83" t="inlineStr">
         <is>
           <t>Δ budget d'acquisition</t>
         </is>
       </c>
-      <c r="C47" s="82" t="inlineStr">
+      <c r="C47" s="83" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
@@ -8344,8 +8502,8 @@
           <t>SAISIE</t>
         </is>
       </c>
-      <c r="E47" s="82" t="n"/>
-      <c r="F47" s="82" t="inlineStr">
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="inlineStr">
         <is>
           <t>la seule cellule modifiable du classeur</t>
         </is>
@@ -8797,7 +8955,7 @@
         <f>IF(ABS(F64)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H64" s="78" t="inlineStr">
+      <c r="H64" s="80" t="inlineStr">
         <is>
           <t>socle CRM contre comptabilité</t>
         </is>
@@ -8831,7 +8989,7 @@
         <f>IF(ABS(F65)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H65" s="78" t="inlineStr">
+      <c r="H65" s="80" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -8865,7 +9023,7 @@
         <f>IF(ABS(F66)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H66" s="78" t="inlineStr">
+      <c r="H66" s="80" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -8899,7 +9057,7 @@
         <f>IF(ABS(F67)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H67" s="78" t="inlineStr">
+      <c r="H67" s="80" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -8933,7 +9091,7 @@
         <f>IF(ABS(F68)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H68" s="78" t="inlineStr">
+      <c r="H68" s="80" t="inlineStr">
         <is>
           <t>cycle × modalité contre campus</t>
         </is>
@@ -8967,7 +9125,7 @@
         <f>IF(ABS(F69)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H69" s="78" t="inlineStr">
+      <c r="H69" s="80" t="inlineStr">
         <is>
           <t>la clé EFFECTIFS ne perd rien</t>
         </is>
@@ -9001,7 +9159,7 @@
         <f>IF(ABS(F70)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H70" s="78" t="inlineStr">
+      <c r="H70" s="80" t="inlineStr">
         <is>
           <t>additivité de la ligne groupe</t>
         </is>
@@ -9035,7 +9193,7 @@
         <f>IF(F71&gt;0,"OK · marge","BASCULE")</f>
         <v/>
       </c>
-      <c r="H71" s="78" t="inlineStr">
+      <c r="H71" s="80" t="inlineStr">
         <is>
           <t>si dépassé, une classe ouvre</t>
         </is>
@@ -9176,4 +9334,1965 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>EDUSERVICES · le moteur d'acquisition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>PROJETER LES COÛTS 2027  —  un inducteur par comportement</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="3" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>La base 2027 n'existe pas. Il n'y a rien à restituer.</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>Les deux seules lignes 2027 de la comptabilité sont techniques. Le 2027 se construit — et le moteur, lui, ne le construit pas : c'est un modèle MARGINAL, qui applique des coûts unitaires 2026 à un volume marginal. Ici on fait l'autre travail : une règle de projection par comportement, et le comportement est la colonne du tableau ⑤.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>ⓐ  Les neuf saisies  ·  chacune est une décision, et chacune a un propriétaire</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Six d'entre elles sont les leviers de l'onglet Cadrage, reprises telles quelles. La septième n'est pas saisie ici : elle est LIÉE au geste du premier onglet.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Saisie</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Valeur retenue</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>D'où elle vient</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="113" t="inlineStr">
+        <is>
+          <t>Croissance des effectifs 2027</t>
+        </is>
+      </c>
+      <c r="C12" s="114" t="n"/>
+      <c r="D12" s="114" t="n"/>
+      <c r="E12" s="115" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F12" s="114" t="n"/>
+      <c r="G12" s="116" t="inlineStr">
+        <is>
+          <t>constatée 2026 : +6,2 %</t>
+        </is>
+      </c>
+      <c r="H12" s="114" t="n"/>
+      <c r="I12" s="114" t="n"/>
+      <c r="J12" s="114" t="n"/>
+      <c r="K12" s="114" t="n"/>
+      <c r="L12" s="114" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="113" t="inlineStr">
+        <is>
+          <t>Hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="C13" s="114" t="n"/>
+      <c r="D13" s="114" t="n"/>
+      <c r="E13" s="115" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F13" s="114" t="n"/>
+      <c r="G13" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H13" s="114" t="n"/>
+      <c r="I13" s="114" t="n"/>
+      <c r="J13" s="114" t="n"/>
+      <c r="K13" s="114" t="n"/>
+      <c r="L13" s="114" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="113" t="inlineStr">
+        <is>
+          <t>Inflation des charges externes</t>
+        </is>
+      </c>
+      <c r="C14" s="114" t="n"/>
+      <c r="D14" s="114" t="n"/>
+      <c r="E14" s="115" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F14" s="114" t="n"/>
+      <c r="G14" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H14" s="114" t="n"/>
+      <c r="I14" s="114" t="n"/>
+      <c r="J14" s="114" t="n"/>
+      <c r="K14" s="114" t="n"/>
+      <c r="L14" s="114" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="113" t="inlineStr">
+        <is>
+          <t>Effort de productivité achats &amp; structure</t>
+        </is>
+      </c>
+      <c r="C15" s="114" t="n"/>
+      <c r="D15" s="114" t="n"/>
+      <c r="E15" s="115" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F15" s="114" t="n"/>
+      <c r="G15" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H15" s="114" t="n"/>
+      <c r="I15" s="114" t="n"/>
+      <c r="J15" s="114" t="n"/>
+      <c r="K15" s="114" t="n"/>
+      <c r="L15" s="114" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="113" t="inlineStr">
+        <is>
+          <t>Politique salariale sur la masse permanente</t>
+        </is>
+      </c>
+      <c r="C16" s="114" t="n"/>
+      <c r="D16" s="114" t="n"/>
+      <c r="E16" s="115" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F16" s="114" t="n"/>
+      <c r="G16" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H16" s="114" t="n"/>
+      <c r="I16" s="114" t="n"/>
+      <c r="J16" s="114" t="n"/>
+      <c r="K16" s="114" t="n"/>
+      <c r="L16" s="114" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="113" t="inlineStr">
+        <is>
+          <t>Variation des effectifs permanents</t>
+        </is>
+      </c>
+      <c r="C17" s="114" t="n"/>
+      <c r="D17" s="114" t="n"/>
+      <c r="E17" s="115" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F17" s="114" t="n"/>
+      <c r="G17" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H17" s="114" t="n"/>
+      <c r="I17" s="114" t="n"/>
+      <c r="J17" s="114" t="n"/>
+      <c r="K17" s="114" t="n"/>
+      <c r="L17" s="114" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="113" t="inlineStr">
+        <is>
+          <t>Δ budget d'acquisition  (6231)</t>
+        </is>
+      </c>
+      <c r="C18" s="114" t="n"/>
+      <c r="D18" s="114" t="n"/>
+      <c r="E18" s="117">
+        <f>'Le moteur'!F4</f>
+        <v/>
+      </c>
+      <c r="F18" s="114" t="n"/>
+      <c r="G18" s="116" t="inlineStr">
+        <is>
+          <t>LIÉ au geste, onglet « Le moteur »</t>
+        </is>
+      </c>
+      <c r="H18" s="114" t="n"/>
+      <c r="I18" s="114" t="n"/>
+      <c r="J18" s="114" t="n"/>
+      <c r="K18" s="114" t="n"/>
+      <c r="L18" s="114" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="113" t="inlineStr">
+        <is>
+          <t>Δ budget de marque  (6236)</t>
+        </is>
+      </c>
+      <c r="C19" s="114" t="n"/>
+      <c r="D19" s="114" t="n"/>
+      <c r="E19" s="115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F19" s="114" t="n"/>
+      <c r="G19" s="116" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H19" s="114" t="n"/>
+      <c r="I19" s="114" t="n"/>
+      <c r="J19" s="114" t="n"/>
+      <c r="K19" s="114" t="n"/>
+      <c r="L19" s="114" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="113" t="inlineStr">
+        <is>
+          <t>Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C20" s="114" t="n"/>
+      <c r="D20" s="114" t="n"/>
+      <c r="E20" s="115" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F20" s="114" t="n"/>
+      <c r="G20" s="116" t="inlineStr">
+        <is>
+          <t>plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="H20" s="114" t="n"/>
+      <c r="I20" s="114" t="n"/>
+      <c r="J20" s="114" t="n"/>
+      <c r="K20" s="114" t="n"/>
+      <c r="L20" s="114" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>ⓑ  Le volume 2027  ·  et la seule question qui fasse bouger le 621</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>Un vacataire de plus ne se paie pas parce qu'il y a des élèves de plus : il se paie parce qu'une CLASSE ouvre. Tant qu'aucune n'ouvre, le 621 ne prend que son prix.</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Grandeur</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>Effectifs 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="118" t="n"/>
+      <c r="D26" s="118" t="n"/>
+      <c r="E26" s="59">
+        <f>'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="F26" s="118" t="n"/>
+      <c r="G26" s="119" t="inlineStr"/>
+      <c r="H26" s="118" t="n"/>
+      <c r="I26" s="118" t="n"/>
+      <c r="J26" s="118" t="n"/>
+      <c r="K26" s="118" t="n"/>
+      <c r="L26" s="118" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>Effectifs 2027</t>
+        </is>
+      </c>
+      <c r="C27" s="118" t="n"/>
+      <c r="D27" s="118" t="n"/>
+      <c r="E27" s="120">
+        <f>E26*(1+$E$12)</f>
+        <v/>
+      </c>
+      <c r="F27" s="118" t="n"/>
+      <c r="G27" s="119" t="inlineStr">
+        <is>
+          <t>la croissance saisie</t>
+        </is>
+      </c>
+      <c r="H27" s="118" t="n"/>
+      <c r="I27" s="118" t="n"/>
+      <c r="J27" s="118" t="n"/>
+      <c r="K27" s="118" t="n"/>
+      <c r="L27" s="118" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>Places du réseau</t>
+        </is>
+      </c>
+      <c r="C28" s="118" t="n"/>
+      <c r="D28" s="118" t="n"/>
+      <c r="E28" s="59">
+        <f>'Le moteur'!O34</f>
+        <v/>
+      </c>
+      <c r="F28" s="118" t="n"/>
+      <c r="G28" s="119" t="inlineStr">
+        <is>
+          <t>135 classes, inchangées depuis 2024</t>
+        </is>
+      </c>
+      <c r="H28" s="118" t="n"/>
+      <c r="I28" s="118" t="n"/>
+      <c r="J28" s="118" t="n"/>
+      <c r="K28" s="118" t="n"/>
+      <c r="L28" s="118" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>Classes 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="118" t="n"/>
+      <c r="D29" s="118" t="n"/>
+      <c r="E29" s="59">
+        <f>'Le moteur'!P34</f>
+        <v/>
+      </c>
+      <c r="F29" s="118" t="n"/>
+      <c r="G29" s="119" t="inlineStr"/>
+      <c r="H29" s="118" t="n"/>
+      <c r="I29" s="118" t="n"/>
+      <c r="J29" s="118" t="n"/>
+      <c r="K29" s="118" t="n"/>
+      <c r="L29" s="118" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>Capacité moyenne d'une classe</t>
+        </is>
+      </c>
+      <c r="C30" s="118" t="n"/>
+      <c r="D30" s="118" t="n"/>
+      <c r="E30" s="121">
+        <f>IFERROR(E28/E29,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="118" t="n"/>
+      <c r="G30" s="119" t="inlineStr"/>
+      <c r="H30" s="118" t="n"/>
+      <c r="I30" s="118" t="n"/>
+      <c r="J30" s="118" t="n"/>
+      <c r="K30" s="118" t="n"/>
+      <c r="L30" s="118" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>Croissance possible avant saturation</t>
+        </is>
+      </c>
+      <c r="C31" s="118" t="n"/>
+      <c r="D31" s="118" t="n"/>
+      <c r="E31" s="122">
+        <f>'Le coût variable'!L48</f>
+        <v/>
+      </c>
+      <c r="F31" s="118" t="n"/>
+      <c r="G31" s="119" t="inlineStr">
+        <is>
+          <t>le premier campus qui sature : MBway Paris</t>
+        </is>
+      </c>
+      <c r="H31" s="118" t="n"/>
+      <c r="I31" s="118" t="n"/>
+      <c r="J31" s="118" t="n"/>
+      <c r="K31" s="118" t="n"/>
+      <c r="L31" s="118" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>Classes à ouvrir en 2027</t>
+        </is>
+      </c>
+      <c r="C32" s="118" t="n"/>
+      <c r="D32" s="118" t="n"/>
+      <c r="E32" s="120">
+        <f>MAX(0,ROUNDUP((E27-E28)/E30,0))</f>
+        <v/>
+      </c>
+      <c r="F32" s="118" t="n"/>
+      <c r="G32" s="119" t="inlineStr">
+        <is>
+          <t>aucune : la marche ne tombe pas en 2027</t>
+        </is>
+      </c>
+      <c r="H32" s="118" t="n"/>
+      <c r="I32" s="118" t="n"/>
+      <c r="J32" s="118" t="n"/>
+      <c r="K32" s="118" t="n"/>
+      <c r="L32" s="118" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="52" t="inlineStr">
+        <is>
+          <t>Classes 2027</t>
+        </is>
+      </c>
+      <c r="C33" s="118" t="n"/>
+      <c r="D33" s="118" t="n"/>
+      <c r="E33" s="59">
+        <f>E29+E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="118" t="n"/>
+      <c r="G33" s="119" t="inlineStr"/>
+      <c r="H33" s="118" t="n"/>
+      <c r="I33" s="118" t="n"/>
+      <c r="J33" s="118" t="n"/>
+      <c r="K33" s="118" t="n"/>
+      <c r="L33" s="118" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>Inducteur du compte 621</t>
+        </is>
+      </c>
+      <c r="C34" s="118" t="n"/>
+      <c r="D34" s="118" t="n"/>
+      <c r="E34" s="123">
+        <f>IFERROR(E33/E29,0)</f>
+        <v/>
+      </c>
+      <c r="F34" s="118" t="n"/>
+      <c r="G34" s="119" t="inlineStr">
+        <is>
+          <t>le ratio de CLASSES, pas d'effectifs</t>
+        </is>
+      </c>
+      <c r="H34" s="118" t="n"/>
+      <c r="I34" s="118" t="n"/>
+      <c r="J34" s="118" t="n"/>
+      <c r="K34" s="118" t="n"/>
+      <c r="L34" s="118" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>À +6,2 % l'an, MBway Paris tient jusqu'en 2029. C'est vérifiable ligne à ligne dans l'onglet « Le coût variable », dernière colonne — ce n'est pas une affirmation.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>ⓒ  La projection, compte par compte</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Montant 2026 lié au tableau ⑤. Chaque compte reçoit un effet volume et un effet prix — jamais les deux au hasard : c'est son comportement qui les désigne.</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Compte et libellé</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Inducteur de volume</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>Effet volume</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>Effet prix</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2027</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>Variation</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui décide</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="106" t="inlineStr">
+        <is>
+          <t>604 · Achats d'études et supports pédagogiques</t>
+        </is>
+      </c>
+      <c r="C42" s="107" t="n"/>
+      <c r="D42" s="124">
+        <f>'Le coût variable'!D74</f>
+        <v/>
+      </c>
+      <c r="E42" s="125" t="inlineStr">
+        <is>
+          <t>effectifs</t>
+        </is>
+      </c>
+      <c r="F42" s="126">
+        <f>1+$E$12</f>
+        <v/>
+      </c>
+      <c r="G42" s="126">
+        <f>1+$E$14</f>
+        <v/>
+      </c>
+      <c r="H42" s="127">
+        <f>D42*F42*G42</f>
+        <v/>
+      </c>
+      <c r="I42" s="128">
+        <f>IFERROR(H42/D42-1,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="129" t="inlineStr">
+        <is>
+          <t>le remplissage</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="106" t="inlineStr">
+        <is>
+          <t>6063 · Fournitures pédagogiques et administratives</t>
+        </is>
+      </c>
+      <c r="C43" s="107" t="n"/>
+      <c r="D43" s="124">
+        <f>'Le coût variable'!D75</f>
+        <v/>
+      </c>
+      <c r="E43" s="125" t="inlineStr">
+        <is>
+          <t>effectifs</t>
+        </is>
+      </c>
+      <c r="F43" s="126">
+        <f>1+$E$12</f>
+        <v/>
+      </c>
+      <c r="G43" s="126">
+        <f>1+$E$14</f>
+        <v/>
+      </c>
+      <c r="H43" s="127">
+        <f>D43*F43*G43</f>
+        <v/>
+      </c>
+      <c r="I43" s="128">
+        <f>IFERROR(H43/D43-1,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="129" t="inlineStr">
+        <is>
+          <t>le remplissage</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="106" t="inlineStr">
+        <is>
+          <t>621 · Personnel extérieur — enseignants vacataires</t>
+        </is>
+      </c>
+      <c r="C44" s="107" t="n"/>
+      <c r="D44" s="124">
+        <f>'Le coût variable'!D76</f>
+        <v/>
+      </c>
+      <c r="E44" s="125" t="inlineStr">
+        <is>
+          <t>CLASSES, pas effectifs</t>
+        </is>
+      </c>
+      <c r="F44" s="126">
+        <f>$E$34</f>
+        <v/>
+      </c>
+      <c r="G44" s="126">
+        <f>1+$E$14</f>
+        <v/>
+      </c>
+      <c r="H44" s="127">
+        <f>D44*F44*G44</f>
+        <v/>
+      </c>
+      <c r="I44" s="128">
+        <f>IFERROR(H44/D44-1,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="130" t="inlineStr">
+        <is>
+          <t>l'ouverture d'une classe</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="106" t="inlineStr">
+        <is>
+          <t>6411 · Salaires — enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C45" s="107" t="n"/>
+      <c r="D45" s="124">
+        <f>'Le coût variable'!D77</f>
+        <v/>
+      </c>
+      <c r="E45" s="125" t="inlineStr">
+        <is>
+          <t>postes permanents</t>
+        </is>
+      </c>
+      <c r="F45" s="126">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="G45" s="126">
+        <f>1+$E$16</f>
+        <v/>
+      </c>
+      <c r="H45" s="127">
+        <f>D45*F45*G45</f>
+        <v/>
+      </c>
+      <c r="I45" s="128">
+        <f>IFERROR(H45/D45-1,0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="131" t="inlineStr">
+        <is>
+          <t>le recrutement</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="106" t="inlineStr">
+        <is>
+          <t>6231 · Annonces et insertions — budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C46" s="107" t="n"/>
+      <c r="D46" s="124">
+        <f>'Le coût variable'!D78</f>
+        <v/>
+      </c>
+      <c r="E46" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="126">
+        <f>1+$E$18</f>
+        <v/>
+      </c>
+      <c r="H46" s="127">
+        <f>D46*F46*G46</f>
+        <v/>
+      </c>
+      <c r="I46" s="128">
+        <f>IFERROR(H46/D46-1,0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="132" t="inlineStr">
+        <is>
+          <t>LE GESTE — onglet « Le moteur »</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="106" t="inlineStr">
+        <is>
+          <t>6413 · Salaires — personnel administratif des campus</t>
+        </is>
+      </c>
+      <c r="C47" s="107" t="n"/>
+      <c r="D47" s="124">
+        <f>'Le coût variable'!D79</f>
+        <v/>
+      </c>
+      <c r="E47" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="126">
+        <f>1+$E$16</f>
+        <v/>
+      </c>
+      <c r="H47" s="127">
+        <f>D47*F47*G47</f>
+        <v/>
+      </c>
+      <c r="I47" s="128">
+        <f>IFERROR(H47/D47-1,0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="125" t="inlineStr">
+        <is>
+          <t>la politique salariale</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="106" t="inlineStr">
+        <is>
+          <t>645 · Charges sociales sur les salaires</t>
+        </is>
+      </c>
+      <c r="C48" s="107" t="n"/>
+      <c r="D48" s="124">
+        <f>'Le coût variable'!D80</f>
+        <v/>
+      </c>
+      <c r="E48" s="125" t="inlineStr">
+        <is>
+          <t>la masse salariale</t>
+        </is>
+      </c>
+      <c r="F48" s="126">
+        <f>(H45+H47+H55)/(D45+D47+D55)</f>
+        <v/>
+      </c>
+      <c r="G48" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="127">
+        <f>D48*F48*G48</f>
+        <v/>
+      </c>
+      <c r="I48" s="128">
+        <f>IFERROR(H48/D48-1,0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="125" t="inlineStr">
+        <is>
+          <t>assis sur la masse</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="106" t="inlineStr">
+        <is>
+          <t>613 · Locations immobilières des campus</t>
+        </is>
+      </c>
+      <c r="C49" s="107" t="n"/>
+      <c r="D49" s="124">
+        <f>'Le coût variable'!D81</f>
+        <v/>
+      </c>
+      <c r="E49" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H49" s="127">
+        <f>D49*F49*G49</f>
+        <v/>
+      </c>
+      <c r="I49" s="128">
+        <f>IFERROR(H49/D49-1,0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="106" t="inlineStr">
+        <is>
+          <t>615 · Entretien et réparations</t>
+        </is>
+      </c>
+      <c r="C50" s="107" t="n"/>
+      <c r="D50" s="124">
+        <f>'Le coût variable'!D82</f>
+        <v/>
+      </c>
+      <c r="E50" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H50" s="127">
+        <f>D50*F50*G50</f>
+        <v/>
+      </c>
+      <c r="I50" s="128">
+        <f>IFERROR(H50/D50-1,0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="106" t="inlineStr">
+        <is>
+          <t>616 · Primes d'assurance</t>
+        </is>
+      </c>
+      <c r="C51" s="107" t="n"/>
+      <c r="D51" s="124">
+        <f>'Le coût variable'!D83</f>
+        <v/>
+      </c>
+      <c r="E51" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H51" s="127">
+        <f>D51*F51*G51</f>
+        <v/>
+      </c>
+      <c r="I51" s="128">
+        <f>IFERROR(H51/D51-1,0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="106" t="inlineStr">
+        <is>
+          <t>625 · Déplacements, missions et réceptions</t>
+        </is>
+      </c>
+      <c r="C52" s="107" t="n"/>
+      <c r="D52" s="124">
+        <f>'Le coût variable'!D84</f>
+        <v/>
+      </c>
+      <c r="E52" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H52" s="127">
+        <f>D52*F52*G52</f>
+        <v/>
+      </c>
+      <c r="I52" s="128">
+        <f>IFERROR(H52/D52-1,0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="106" t="inlineStr">
+        <is>
+          <t>63511 · Contribution économique territoriale</t>
+        </is>
+      </c>
+      <c r="C53" s="107" t="n"/>
+      <c r="D53" s="124">
+        <f>'Le coût variable'!D85</f>
+        <v/>
+      </c>
+      <c r="E53" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H53" s="127">
+        <f>D53*F53*G53</f>
+        <v/>
+      </c>
+      <c r="I53" s="128">
+        <f>IFERROR(H53/D53-1,0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="125" t="inlineStr">
+        <is>
+          <t>la fiscalité locale</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="106" t="inlineStr">
+        <is>
+          <t>6236 · Catalogues et imprimés — marketing de marque</t>
+        </is>
+      </c>
+      <c r="C54" s="107" t="n"/>
+      <c r="D54" s="124">
+        <f>'Le coût variable'!D86</f>
+        <v/>
+      </c>
+      <c r="E54" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="126">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H54" s="127">
+        <f>D54*F54*G54</f>
+        <v/>
+      </c>
+      <c r="I54" s="128">
+        <f>IFERROR(H54/D54-1,0)</f>
+        <v/>
+      </c>
+      <c r="J54" s="125" t="inlineStr">
+        <is>
+          <t>le budget de marque</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="106" t="inlineStr">
+        <is>
+          <t>6414 · Salaires du siège</t>
+        </is>
+      </c>
+      <c r="C55" s="107" t="n"/>
+      <c r="D55" s="124">
+        <f>'Le coût variable'!D87</f>
+        <v/>
+      </c>
+      <c r="E55" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="126">
+        <f>1+$E$16</f>
+        <v/>
+      </c>
+      <c r="H55" s="127">
+        <f>D55*F55*G55</f>
+        <v/>
+      </c>
+      <c r="I55" s="128">
+        <f>IFERROR(H55/D55-1,0)</f>
+        <v/>
+      </c>
+      <c r="J55" s="125" t="inlineStr">
+        <is>
+          <t>la politique salariale</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="106" t="inlineStr">
+        <is>
+          <t>6226 · Honoraires</t>
+        </is>
+      </c>
+      <c r="C56" s="107" t="n"/>
+      <c r="D56" s="124">
+        <f>'Le coût variable'!D88</f>
+        <v/>
+      </c>
+      <c r="E56" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H56" s="127">
+        <f>D56*F56*G56</f>
+        <v/>
+      </c>
+      <c r="I56" s="128">
+        <f>IFERROR(H56/D56-1,0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="106" t="inlineStr">
+        <is>
+          <t>626 · Frais postaux et de télécommunications</t>
+        </is>
+      </c>
+      <c r="C57" s="107" t="n"/>
+      <c r="D57" s="124">
+        <f>'Le coût variable'!D89</f>
+        <v/>
+      </c>
+      <c r="E57" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H57" s="127">
+        <f>D57*F57*G57</f>
+        <v/>
+      </c>
+      <c r="I57" s="128">
+        <f>IFERROR(H57/D57-1,0)</f>
+        <v/>
+      </c>
+      <c r="J57" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="106" t="inlineStr">
+        <is>
+          <t>6281 · Cotisations et concours divers</t>
+        </is>
+      </c>
+      <c r="C58" s="107" t="n"/>
+      <c r="D58" s="124">
+        <f>'Le coût variable'!D90</f>
+        <v/>
+      </c>
+      <c r="E58" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="126">
+        <f>1+$E$14-$E$15</f>
+        <v/>
+      </c>
+      <c r="H58" s="127">
+        <f>D58*F58*G58</f>
+        <v/>
+      </c>
+      <c r="I58" s="128">
+        <f>IFERROR(H58/D58-1,0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="125" t="inlineStr">
+        <is>
+          <t>l'indexation, moins l'effort</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="106" t="inlineStr">
+        <is>
+          <t>6331 · Versement mobilité</t>
+        </is>
+      </c>
+      <c r="C59" s="107" t="n"/>
+      <c r="D59" s="124">
+        <f>'Le coût variable'!D91</f>
+        <v/>
+      </c>
+      <c r="E59" s="125" t="inlineStr">
+        <is>
+          <t>la masse salariale</t>
+        </is>
+      </c>
+      <c r="F59" s="126">
+        <f>(H45+H47+H55)/(D45+D47+D55)</f>
+        <v/>
+      </c>
+      <c r="G59" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="127">
+        <f>D59*F59*G59</f>
+        <v/>
+      </c>
+      <c r="I59" s="128">
+        <f>IFERROR(H59/D59-1,0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="125" t="inlineStr">
+        <is>
+          <t>assis sur la masse</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="106" t="inlineStr">
+        <is>
+          <t>6333 · Participation à la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="C60" s="107" t="n"/>
+      <c r="D60" s="124">
+        <f>'Le coût variable'!D92</f>
+        <v/>
+      </c>
+      <c r="E60" s="125" t="inlineStr">
+        <is>
+          <t>la masse salariale</t>
+        </is>
+      </c>
+      <c r="F60" s="126">
+        <f>(H45+H47+H55)/(D45+D47+D55)</f>
+        <v/>
+      </c>
+      <c r="G60" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="127">
+        <f>D60*F60*G60</f>
+        <v/>
+      </c>
+      <c r="I60" s="128">
+        <f>IFERROR(H60/D60-1,0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="125" t="inlineStr">
+        <is>
+          <t>assis sur la masse</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="106" t="inlineStr">
+        <is>
+          <t>6811 · Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C61" s="107" t="n"/>
+      <c r="D61" s="124">
+        <f>'Le coût variable'!D93</f>
+        <v/>
+      </c>
+      <c r="E61" s="125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="126">
+        <f>1+$E$20</f>
+        <v/>
+      </c>
+      <c r="H61" s="127">
+        <f>D61*F61*G61</f>
+        <v/>
+      </c>
+      <c r="I61" s="128">
+        <f>IFERROR(H61/D61-1,0)</f>
+        <v/>
+      </c>
+      <c r="J61" s="125" t="inlineStr">
+        <is>
+          <t>le plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="64" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES  ·  dotations incluses</t>
+        </is>
+      </c>
+      <c r="C62" s="64" t="n"/>
+      <c r="D62" s="68">
+        <f>SUM(D42:D61)</f>
+        <v/>
+      </c>
+      <c r="E62" s="64" t="inlineStr"/>
+      <c r="F62" s="133" t="inlineStr"/>
+      <c r="G62" s="133" t="inlineStr"/>
+      <c r="H62" s="68">
+        <f>SUM(H42:H61)</f>
+        <v/>
+      </c>
+      <c r="I62" s="69">
+        <f>IFERROR(H62/D62-1,0)</f>
+        <v/>
+      </c>
+      <c r="J62" s="64" t="inlineStr"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="87" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="C63" s="87" t="n"/>
+      <c r="D63" s="88">
+        <f>'Le coût variable'!D95</f>
+        <v/>
+      </c>
+      <c r="E63" s="87" t="inlineStr">
+        <is>
+          <t>volume × prix</t>
+        </is>
+      </c>
+      <c r="F63" s="134">
+        <f>1+$E$12</f>
+        <v/>
+      </c>
+      <c r="G63" s="134">
+        <f>1+$E$13</f>
+        <v/>
+      </c>
+      <c r="H63" s="88">
+        <f>D63*F63*G63</f>
+        <v/>
+      </c>
+      <c r="I63" s="135">
+        <f>IFERROR(H63/D63-1,0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="87" t="inlineStr">
+        <is>
+          <t>le socle CRM et le tarif</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>EBITDA  ·  hors dotations</t>
+        </is>
+      </c>
+      <c r="C64" s="64" t="n"/>
+      <c r="D64" s="136">
+        <f>D63-D62+D61</f>
+        <v/>
+      </c>
+      <c r="E64" s="64" t="inlineStr"/>
+      <c r="F64" s="133" t="inlineStr"/>
+      <c r="G64" s="133" t="inlineStr"/>
+      <c r="H64" s="136">
+        <f>H63-H62+H61</f>
+        <v/>
+      </c>
+      <c r="I64" s="69">
+        <f>IFERROR(H64/D64-1,0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="64" t="inlineStr"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="49" t="inlineStr">
+        <is>
+          <t>Marge d'EBITDA</t>
+        </is>
+      </c>
+      <c r="C65" s="49" t="n"/>
+      <c r="D65" s="137">
+        <f>IFERROR(D64/D63,0)</f>
+        <v/>
+      </c>
+      <c r="E65" s="49" t="inlineStr"/>
+      <c r="F65" s="123" t="inlineStr"/>
+      <c r="G65" s="123" t="inlineStr"/>
+      <c r="H65" s="137">
+        <f>IFERROR(H64/H63,0)</f>
+        <v/>
+      </c>
+      <c r="I65" s="138">
+        <f>H65-D65</f>
+        <v/>
+      </c>
+      <c r="J65" s="49" t="inlineStr"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="139">
+        <f>"2027 : "&amp;TEXT(H64,"#,##0 €")&amp;" d'EBITDA, marge "&amp;TEXT(H65,"0.0 %")&amp;"  —  contre "&amp;TEXT(D65,"0.0 %")&amp;" en 2026. Le gain ne vient pas d'une économie : il vient de "&amp;TEXT(E27-E26,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes."</f>
+        <v/>
+      </c>
+      <c r="C67" s="110" t="n"/>
+      <c r="D67" s="110" t="n"/>
+      <c r="E67" s="110" t="n"/>
+      <c r="F67" s="110" t="n"/>
+      <c r="G67" s="110" t="n"/>
+      <c r="H67" s="110" t="n"/>
+      <c r="I67" s="110" t="n"/>
+      <c r="J67" s="110" t="n"/>
+      <c r="K67" s="110" t="n"/>
+      <c r="L67" s="110" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="111" t="inlineStr">
+        <is>
+          <t>Le jour où une classe doit ouvrir, la ligne 621 change d'inducteur toute seule — et c'est là que la marge s'arrête de monter. Le classeur dit quand : onglet « Le coût variable », dernière colonne.</t>
+        </is>
+      </c>
+      <c r="C68" s="112" t="n"/>
+      <c r="D68" s="112" t="n"/>
+      <c r="E68" s="112" t="n"/>
+      <c r="F68" s="112" t="n"/>
+      <c r="G68" s="112" t="n"/>
+      <c r="H68" s="112" t="n"/>
+      <c r="I68" s="112" t="n"/>
+      <c r="J68" s="112" t="n"/>
+      <c r="K68" s="112" t="n"/>
+      <c r="L68" s="112" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
+      <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="5" t="n"/>
+      <c r="J70" s="5" t="n"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I42:I61">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00DCEBC0"/>
+        <color rgb="00F7F7F5"/>
+        <color rgb="00F6C9CC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%;&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00&quot; €&quot;"/>
@@ -30,9 +30,10 @@
     <numFmt numFmtId="171" formatCode="0.0&quot; h&quot;"/>
     <numFmt numFmtId="172" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="173" formatCode="+0.00%;-0.00%;&quot;—&quot;"/>
-    <numFmt numFmtId="174" formatCode="+0.00&quot; pt&quot;;-0.00&quot; pt&quot;"/>
+    <numFmt numFmtId="174" formatCode="+0.00%"/>
+    <numFmt numFmtId="175" formatCode="+0.00&quot; pt&quot;;-0.00&quot; pt&quot;"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -247,9 +248,32 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="006B7075"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="005F8A17"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B26B00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C41822"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B7075"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -409,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -725,81 +749,132 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="33" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="36" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="36" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="38" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="41" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="36" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="175" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="22" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9342,19 +9417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.4" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -9381,7 +9456,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>PROJETER LES COÛTS 2027  —  un inducteur par comportement</t>
+          <t>PROJETER 2027  —  le CA en quatre lignes, les coûts en sept familles</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -9427,7 +9502,7 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="47" t="inlineStr">
         <is>
-          <t>La base 2027 n'existe pas. Il n'y a rien à restituer.</t>
+          <t>La croissance se défait en deux, et la seconde moitié, c'est le moteur.</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -9445,7 +9520,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>Les deux seules lignes 2027 de la comptabilité sont techniques. Le 2027 se construit — et le moteur, lui, ne le construit pas : c'est un modèle MARGINAL, qui applique des coûts unitaires 2026 à un volume marginal. Ici on fait l'autre travail : une règle de projection par comportement, et le comportement est la colonne du tableau ⑤.</t>
+          <t>On sait séparer ce que porte le socle de ce qu'ajoute le budget d'acquisition : +181 élèves en 2026, dont 31,8 dus au +10 % d'acquisition et 149,2 au socle. Le socle se saisit ; le geste, lui, n'est pas saisi — il est LIÉ aux cellules du premier onglet. C'est ce qui fait que ce budget et le moteur disent le même chiffre.</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -9477,7 +9552,7 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>ⓐ  Les neuf saisies  ·  chacune est une décision, et chacune a un propriétaire</t>
+          <t>ⓐ  Les huit saisies  ·  et la neuvième, qui n'en est pas une</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -9495,7 +9570,7 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Six d'entre elles sont les leviers de l'onglet Cadrage, reprises telles quelles. La septième n'est pas saisie ici : elle est LIÉE au geste du premier onglet.</t>
+          <t>Chacune est une décision, et chacune a un propriétaire. Le Δ budget d'acquisition ne se saisit pas ici : il vient du geste de l'onglet « Le moteur ».</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -9549,262 +9624,262 @@
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="113" t="inlineStr">
         <is>
-          <t>Croissance des effectifs 2027</t>
-        </is>
-      </c>
-      <c r="C12" s="114" t="n"/>
-      <c r="D12" s="114" t="n"/>
-      <c r="E12" s="115" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F12" s="114" t="n"/>
-      <c r="G12" s="116" t="inlineStr">
-        <is>
-          <t>constatée 2026 : +6,2 %</t>
-        </is>
-      </c>
-      <c r="H12" s="114" t="n"/>
-      <c r="I12" s="114" t="n"/>
-      <c r="J12" s="114" t="n"/>
-      <c r="K12" s="114" t="n"/>
-      <c r="L12" s="114" t="n"/>
+          <t>CE QUI FAIT LE CHIFFRE D'AFFAIRES</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="113" t="inlineStr">
-        <is>
-          <t>Hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="C13" s="114" t="n"/>
-      <c r="D13" s="114" t="n"/>
-      <c r="E13" s="115" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F13" s="114" t="n"/>
-      <c r="G13" s="116" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H13" s="114" t="n"/>
-      <c r="I13" s="114" t="n"/>
-      <c r="J13" s="114" t="n"/>
-      <c r="K13" s="114" t="n"/>
-      <c r="L13" s="114" t="n"/>
+      <c r="B13" s="114" t="inlineStr">
+        <is>
+          <t>Croissance du socle, hors geste d'acquisition</t>
+        </is>
+      </c>
+      <c r="C13" s="115" t="n"/>
+      <c r="D13" s="115" t="n"/>
+      <c r="E13" s="116" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="F13" s="115" t="n"/>
+      <c r="G13" s="117" t="inlineStr">
+        <is>
+          <t>constatée 2026, geste défalqué</t>
+        </is>
+      </c>
+      <c r="H13" s="115" t="n"/>
+      <c r="I13" s="115" t="n"/>
+      <c r="J13" s="115" t="n"/>
+      <c r="K13" s="115" t="n"/>
+      <c r="L13" s="115" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="113" t="inlineStr">
-        <is>
-          <t>Inflation des charges externes</t>
-        </is>
-      </c>
-      <c r="C14" s="114" t="n"/>
-      <c r="D14" s="114" t="n"/>
-      <c r="E14" s="115" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F14" s="114" t="n"/>
-      <c r="G14" s="116" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H14" s="114" t="n"/>
-      <c r="I14" s="114" t="n"/>
-      <c r="J14" s="114" t="n"/>
-      <c r="K14" s="114" t="n"/>
-      <c r="L14" s="114" t="n"/>
+      <c r="B14" s="114" t="inlineStr">
+        <is>
+          <t>Hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="C14" s="115" t="n"/>
+      <c r="D14" s="115" t="n"/>
+      <c r="E14" s="116" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F14" s="115" t="n"/>
+      <c r="G14" s="117" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H14" s="115" t="n"/>
+      <c r="I14" s="115" t="n"/>
+      <c r="J14" s="115" t="n"/>
+      <c r="K14" s="115" t="n"/>
+      <c r="L14" s="115" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="113" t="inlineStr">
-        <is>
-          <t>Effort de productivité achats &amp; structure</t>
-        </is>
-      </c>
-      <c r="C15" s="114" t="n"/>
-      <c r="D15" s="114" t="n"/>
-      <c r="E15" s="115" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="F15" s="114" t="n"/>
-      <c r="G15" s="116" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H15" s="114" t="n"/>
-      <c r="I15" s="114" t="n"/>
-      <c r="J15" s="114" t="n"/>
-      <c r="K15" s="114" t="n"/>
-      <c r="L15" s="114" t="n"/>
-    </row>
-    <row r="16">
+      <c r="B15" s="114" t="inlineStr">
+        <is>
+          <t>Δ budget d'acquisition  (6231)</t>
+        </is>
+      </c>
+      <c r="C15" s="115" t="n"/>
+      <c r="D15" s="115" t="n"/>
+      <c r="E15" s="118">
+        <f>'Le moteur'!F4</f>
+        <v/>
+      </c>
+      <c r="F15" s="115" t="n"/>
+      <c r="G15" s="119" t="inlineStr">
+        <is>
+          <t>LIÉ au geste, onglet « Le moteur »</t>
+        </is>
+      </c>
+      <c r="H15" s="115" t="n"/>
+      <c r="I15" s="115" t="n"/>
+      <c r="J15" s="115" t="n"/>
+      <c r="K15" s="115" t="n"/>
+      <c r="L15" s="115" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="113" t="inlineStr">
         <is>
-          <t>Politique salariale sur la masse permanente</t>
-        </is>
-      </c>
-      <c r="C16" s="114" t="n"/>
-      <c r="D16" s="114" t="n"/>
-      <c r="E16" s="115" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F16" s="114" t="n"/>
-      <c r="G16" s="116" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H16" s="114" t="n"/>
-      <c r="I16" s="114" t="n"/>
-      <c r="J16" s="114" t="n"/>
-      <c r="K16" s="114" t="n"/>
-      <c r="L16" s="114" t="n"/>
+          <t>CE QUI FAIT LES COÛTS</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="113" t="inlineStr">
-        <is>
-          <t>Variation des effectifs permanents</t>
-        </is>
-      </c>
-      <c r="C17" s="114" t="n"/>
-      <c r="D17" s="114" t="n"/>
-      <c r="E17" s="115" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F17" s="114" t="n"/>
-      <c r="G17" s="116" t="inlineStr">
+      <c r="B17" s="114" t="inlineStr">
+        <is>
+          <t>Inflation des charges externes</t>
+        </is>
+      </c>
+      <c r="C17" s="115" t="n"/>
+      <c r="D17" s="115" t="n"/>
+      <c r="E17" s="116" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F17" s="115" t="n"/>
+      <c r="G17" s="117" t="inlineStr">
         <is>
           <t>levier Cadrage · coûts</t>
         </is>
       </c>
-      <c r="H17" s="114" t="n"/>
-      <c r="I17" s="114" t="n"/>
-      <c r="J17" s="114" t="n"/>
-      <c r="K17" s="114" t="n"/>
-      <c r="L17" s="114" t="n"/>
+      <c r="H17" s="115" t="n"/>
+      <c r="I17" s="115" t="n"/>
+      <c r="J17" s="115" t="n"/>
+      <c r="K17" s="115" t="n"/>
+      <c r="L17" s="115" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="113" t="inlineStr">
-        <is>
-          <t>Δ budget d'acquisition  (6231)</t>
-        </is>
-      </c>
-      <c r="C18" s="114" t="n"/>
-      <c r="D18" s="114" t="n"/>
-      <c r="E18" s="117">
-        <f>'Le moteur'!F4</f>
-        <v/>
-      </c>
-      <c r="F18" s="114" t="n"/>
-      <c r="G18" s="116" t="inlineStr">
-        <is>
-          <t>LIÉ au geste, onglet « Le moteur »</t>
-        </is>
-      </c>
-      <c r="H18" s="114" t="n"/>
-      <c r="I18" s="114" t="n"/>
-      <c r="J18" s="114" t="n"/>
-      <c r="K18" s="114" t="n"/>
-      <c r="L18" s="114" t="n"/>
+      <c r="B18" s="114" t="inlineStr">
+        <is>
+          <t>Effort de productivité achats &amp; structure</t>
+        </is>
+      </c>
+      <c r="C18" s="115" t="n"/>
+      <c r="D18" s="115" t="n"/>
+      <c r="E18" s="116" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F18" s="115" t="n"/>
+      <c r="G18" s="117" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H18" s="115" t="n"/>
+      <c r="I18" s="115" t="n"/>
+      <c r="J18" s="115" t="n"/>
+      <c r="K18" s="115" t="n"/>
+      <c r="L18" s="115" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="113" t="inlineStr">
-        <is>
-          <t>Δ budget de marque  (6236)</t>
-        </is>
-      </c>
-      <c r="C19" s="114" t="n"/>
-      <c r="D19" s="114" t="n"/>
-      <c r="E19" s="115" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F19" s="114" t="n"/>
-      <c r="G19" s="116" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H19" s="114" t="n"/>
-      <c r="I19" s="114" t="n"/>
-      <c r="J19" s="114" t="n"/>
-      <c r="K19" s="114" t="n"/>
-      <c r="L19" s="114" t="n"/>
+      <c r="B19" s="114" t="inlineStr">
+        <is>
+          <t>Politique salariale sur la masse permanente</t>
+        </is>
+      </c>
+      <c r="C19" s="115" t="n"/>
+      <c r="D19" s="115" t="n"/>
+      <c r="E19" s="116" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F19" s="115" t="n"/>
+      <c r="G19" s="117" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H19" s="115" t="n"/>
+      <c r="I19" s="115" t="n"/>
+      <c r="J19" s="115" t="n"/>
+      <c r="K19" s="115" t="n"/>
+      <c r="L19" s="115" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="113" t="inlineStr">
-        <is>
-          <t>Dotations aux amortissements</t>
-        </is>
-      </c>
-      <c r="C20" s="114" t="n"/>
-      <c r="D20" s="114" t="n"/>
-      <c r="E20" s="115" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F20" s="114" t="n"/>
-      <c r="G20" s="116" t="inlineStr">
-        <is>
-          <t>plan d'amortissement</t>
-        </is>
-      </c>
-      <c r="H20" s="114" t="n"/>
-      <c r="I20" s="114" t="n"/>
-      <c r="J20" s="114" t="n"/>
-      <c r="K20" s="114" t="n"/>
-      <c r="L20" s="114" t="n"/>
+      <c r="B20" s="114" t="inlineStr">
+        <is>
+          <t>Variation des effectifs permanents</t>
+        </is>
+      </c>
+      <c r="C20" s="115" t="n"/>
+      <c r="D20" s="115" t="n"/>
+      <c r="E20" s="116" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F20" s="115" t="n"/>
+      <c r="G20" s="117" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H20" s="115" t="n"/>
+      <c r="I20" s="115" t="n"/>
+      <c r="J20" s="115" t="n"/>
+      <c r="K20" s="115" t="n"/>
+      <c r="L20" s="115" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
+      <c r="B21" s="114" t="inlineStr">
+        <is>
+          <t>Δ budget de marque  (6236)</t>
+        </is>
+      </c>
+      <c r="C21" s="115" t="n"/>
+      <c r="D21" s="115" t="n"/>
+      <c r="E21" s="116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="115" t="n"/>
+      <c r="G21" s="117" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H21" s="115" t="n"/>
+      <c r="I21" s="115" t="n"/>
+      <c r="J21" s="115" t="n"/>
+      <c r="K21" s="115" t="n"/>
+      <c r="L21" s="115" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>ⓑ  Le volume 2027  ·  et la seule question qui fasse bouger le 621</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="14" customHeight="1">
+      <c r="B22" s="114" t="inlineStr">
+        <is>
+          <t>Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C22" s="115" t="n"/>
+      <c r="D22" s="115" t="n"/>
+      <c r="E22" s="116" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="115" t="n"/>
+      <c r="G22" s="117" t="inlineStr">
+        <is>
+          <t>plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="H22" s="115" t="n"/>
+      <c r="I22" s="115" t="n"/>
+      <c r="J22" s="115" t="n"/>
+      <c r="K22" s="115" t="n"/>
+      <c r="L22" s="115" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>Un vacataire de plus ne se paie pas parce qu'il y a des élèves de plus : il se paie parce qu'une CLASSE ouvre. Tant qu'aucune n'ouvre, le 621 ne prend que son prix.</t>
-        </is>
-      </c>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
@@ -9816,9 +9891,13 @@
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>ⓑ  Le volume 2027  ·  ce que porte le socle, ce qu'ajoute le geste</t>
+        </is>
+      </c>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
@@ -9830,26 +9909,18 @@
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
     </row>
-    <row r="25" ht="24" customHeight="1">
+    <row r="25" ht="14" customHeight="1">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>Grandeur</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F25" s="26" t="n"/>
-      <c r="G25" s="26" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>La ligne « ce que le geste ajoute » n'est pas calculée ici : c'est la cellule I58 de l'onglet « Le moteur ». Bouger F4 là-bas bouge ce budget-ci.</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
@@ -9858,294 +9929,326 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="52" t="inlineStr">
-        <is>
-          <t>Effectifs 2026</t>
-        </is>
-      </c>
-      <c r="C26" s="118" t="n"/>
-      <c r="D26" s="118" t="n"/>
-      <c r="E26" s="59">
-        <f>'Le moteur'!N34</f>
-        <v/>
-      </c>
-      <c r="F26" s="118" t="n"/>
-      <c r="G26" s="119" t="inlineStr"/>
-      <c r="H26" s="118" t="n"/>
-      <c r="I26" s="118" t="n"/>
-      <c r="J26" s="118" t="n"/>
-      <c r="K26" s="118" t="n"/>
-      <c r="L26" s="118" t="n"/>
-    </row>
-    <row r="27">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>Effectifs 2027</t>
-        </is>
-      </c>
-      <c r="C27" s="118" t="n"/>
-      <c r="D27" s="118" t="n"/>
-      <c r="E27" s="120">
-        <f>E26*(1+$E$12)</f>
-        <v/>
-      </c>
-      <c r="F27" s="118" t="n"/>
-      <c r="G27" s="119" t="inlineStr">
-        <is>
-          <t>la croissance saisie</t>
-        </is>
-      </c>
-      <c r="H27" s="118" t="n"/>
-      <c r="I27" s="118" t="n"/>
-      <c r="J27" s="118" t="n"/>
-      <c r="K27" s="118" t="n"/>
-      <c r="L27" s="118" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Grandeur</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="52" t="inlineStr">
-        <is>
-          <t>Places du réseau</t>
-        </is>
-      </c>
-      <c r="C28" s="118" t="n"/>
-      <c r="D28" s="118" t="n"/>
+      <c r="B28" s="120" t="inlineStr">
+        <is>
+          <t>Effectifs 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="121" t="n"/>
+      <c r="D28" s="121" t="n"/>
       <c r="E28" s="59">
-        <f>'Le moteur'!O34</f>
-        <v/>
-      </c>
-      <c r="F28" s="118" t="n"/>
-      <c r="G28" s="119" t="inlineStr">
-        <is>
-          <t>135 classes, inchangées depuis 2024</t>
-        </is>
-      </c>
-      <c r="H28" s="118" t="n"/>
-      <c r="I28" s="118" t="n"/>
-      <c r="J28" s="118" t="n"/>
-      <c r="K28" s="118" t="n"/>
-      <c r="L28" s="118" t="n"/>
+        <f>'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="F28" s="121" t="n"/>
+      <c r="G28" s="122" t="inlineStr">
+        <is>
+          <t>restitué</t>
+        </is>
+      </c>
+      <c r="H28" s="121" t="n"/>
+      <c r="I28" s="121" t="n"/>
+      <c r="J28" s="121" t="n"/>
+      <c r="K28" s="121" t="n"/>
+      <c r="L28" s="121" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="52" t="inlineStr">
-        <is>
-          <t>Classes 2026</t>
-        </is>
-      </c>
-      <c r="C29" s="118" t="n"/>
-      <c r="D29" s="118" t="n"/>
-      <c r="E29" s="59">
-        <f>'Le moteur'!P34</f>
-        <v/>
-      </c>
-      <c r="F29" s="118" t="n"/>
-      <c r="G29" s="119" t="inlineStr"/>
-      <c r="H29" s="118" t="n"/>
-      <c r="I29" s="118" t="n"/>
-      <c r="J29" s="118" t="n"/>
-      <c r="K29" s="118" t="n"/>
-      <c r="L29" s="118" t="n"/>
+      <c r="B29" s="120" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="n"/>
+      <c r="D29" s="121" t="n"/>
+      <c r="E29" s="123">
+        <f>E28*$E$13</f>
+        <v/>
+      </c>
+      <c r="F29" s="121" t="n"/>
+      <c r="G29" s="122" t="inlineStr">
+        <is>
+          <t>rétention, passage, notoriété</t>
+        </is>
+      </c>
+      <c r="H29" s="121" t="n"/>
+      <c r="I29" s="121" t="n"/>
+      <c r="J29" s="121" t="n"/>
+      <c r="K29" s="121" t="n"/>
+      <c r="L29" s="121" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="52" t="inlineStr">
-        <is>
-          <t>Capacité moyenne d'une classe</t>
-        </is>
-      </c>
-      <c r="C30" s="118" t="n"/>
-      <c r="D30" s="118" t="n"/>
-      <c r="E30" s="121">
-        <f>IFERROR(E28/E29,0)</f>
-        <v/>
-      </c>
-      <c r="F30" s="118" t="n"/>
-      <c r="G30" s="119" t="inlineStr"/>
-      <c r="H30" s="118" t="n"/>
-      <c r="I30" s="118" t="n"/>
-      <c r="J30" s="118" t="n"/>
-      <c r="K30" s="118" t="n"/>
-      <c r="L30" s="118" t="n"/>
+      <c r="B30" s="120" t="inlineStr">
+        <is>
+          <t>+ ce que le geste ajoute</t>
+        </is>
+      </c>
+      <c r="C30" s="121" t="n"/>
+      <c r="D30" s="121" t="n"/>
+      <c r="E30" s="123">
+        <f>'Le moteur'!I58</f>
+        <v/>
+      </c>
+      <c r="F30" s="121" t="n"/>
+      <c r="G30" s="122" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — les inscrits gagnés par le Δ budget</t>
+        </is>
+      </c>
+      <c r="H30" s="121" t="n"/>
+      <c r="I30" s="121" t="n"/>
+      <c r="J30" s="121" t="n"/>
+      <c r="K30" s="121" t="n"/>
+      <c r="L30" s="121" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>Croissance possible avant saturation</t>
-        </is>
-      </c>
-      <c r="C31" s="118" t="n"/>
-      <c r="D31" s="118" t="n"/>
-      <c r="E31" s="122">
-        <f>'Le coût variable'!L48</f>
-        <v/>
-      </c>
-      <c r="F31" s="118" t="n"/>
-      <c r="G31" s="119" t="inlineStr">
-        <is>
-          <t>le premier campus qui sature : MBway Paris</t>
-        </is>
-      </c>
-      <c r="H31" s="118" t="n"/>
-      <c r="I31" s="118" t="n"/>
-      <c r="J31" s="118" t="n"/>
-      <c r="K31" s="118" t="n"/>
-      <c r="L31" s="118" t="n"/>
+      <c r="B31" s="49">
+        <f> Effectifs 2027</f>
+        <v/>
+      </c>
+      <c r="C31" s="121" t="n"/>
+      <c r="D31" s="121" t="n"/>
+      <c r="E31" s="124">
+        <f>E28+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="121" t="n"/>
+      <c r="G31" s="122" t="inlineStr"/>
+      <c r="H31" s="121" t="n"/>
+      <c r="I31" s="121" t="n"/>
+      <c r="J31" s="121" t="n"/>
+      <c r="K31" s="121" t="n"/>
+      <c r="L31" s="121" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="49" t="inlineStr">
-        <is>
-          <t>Classes à ouvrir en 2027</t>
-        </is>
-      </c>
-      <c r="C32" s="118" t="n"/>
-      <c r="D32" s="118" t="n"/>
-      <c r="E32" s="120">
-        <f>MAX(0,ROUNDUP((E27-E28)/E30,0))</f>
-        <v/>
-      </c>
-      <c r="F32" s="118" t="n"/>
-      <c r="G32" s="119" t="inlineStr">
-        <is>
-          <t>aucune : la marche ne tombe pas en 2027</t>
-        </is>
-      </c>
-      <c r="H32" s="118" t="n"/>
-      <c r="I32" s="118" t="n"/>
-      <c r="J32" s="118" t="n"/>
-      <c r="K32" s="118" t="n"/>
-      <c r="L32" s="118" t="n"/>
+      <c r="B32" s="120" t="inlineStr">
+        <is>
+          <t>Croissance totale</t>
+        </is>
+      </c>
+      <c r="C32" s="121" t="n"/>
+      <c r="D32" s="121" t="n"/>
+      <c r="E32" s="125">
+        <f>IFERROR(E31/E28-1,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="121" t="n"/>
+      <c r="G32" s="122" t="inlineStr">
+        <is>
+          <t>elle n'est pas saisie : elle se déduit</t>
+        </is>
+      </c>
+      <c r="H32" s="121" t="n"/>
+      <c r="I32" s="121" t="n"/>
+      <c r="J32" s="121" t="n"/>
+      <c r="K32" s="121" t="n"/>
+      <c r="L32" s="121" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
-      <c r="B33" s="52" t="inlineStr">
-        <is>
-          <t>Classes 2027</t>
-        </is>
-      </c>
-      <c r="C33" s="118" t="n"/>
-      <c r="D33" s="118" t="n"/>
+      <c r="B33" s="120" t="inlineStr">
+        <is>
+          <t>Places du réseau</t>
+        </is>
+      </c>
+      <c r="C33" s="121" t="n"/>
+      <c r="D33" s="121" t="n"/>
       <c r="E33" s="59">
-        <f>E29+E32</f>
-        <v/>
-      </c>
-      <c r="F33" s="118" t="n"/>
-      <c r="G33" s="119" t="inlineStr"/>
-      <c r="H33" s="118" t="n"/>
-      <c r="I33" s="118" t="n"/>
-      <c r="J33" s="118" t="n"/>
-      <c r="K33" s="118" t="n"/>
-      <c r="L33" s="118" t="n"/>
+        <f>'Le moteur'!O34</f>
+        <v/>
+      </c>
+      <c r="F33" s="121" t="n"/>
+      <c r="G33" s="122" t="inlineStr">
+        <is>
+          <t>135 classes, inchangées depuis 2024</t>
+        </is>
+      </c>
+      <c r="H33" s="121" t="n"/>
+      <c r="I33" s="121" t="n"/>
+      <c r="J33" s="121" t="n"/>
+      <c r="K33" s="121" t="n"/>
+      <c r="L33" s="121" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="49" t="inlineStr">
-        <is>
-          <t>Inducteur du compte 621</t>
-        </is>
-      </c>
-      <c r="C34" s="118" t="n"/>
-      <c r="D34" s="118" t="n"/>
-      <c r="E34" s="123">
-        <f>IFERROR(E33/E29,0)</f>
-        <v/>
-      </c>
-      <c r="F34" s="118" t="n"/>
-      <c r="G34" s="119" t="inlineStr">
-        <is>
-          <t>le ratio de CLASSES, pas d'effectifs</t>
-        </is>
-      </c>
-      <c r="H34" s="118" t="n"/>
-      <c r="I34" s="118" t="n"/>
-      <c r="J34" s="118" t="n"/>
-      <c r="K34" s="118" t="n"/>
-      <c r="L34" s="118" t="n"/>
+      <c r="B34" s="120" t="inlineStr">
+        <is>
+          <t>Classes 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="121" t="n"/>
+      <c r="D34" s="121" t="n"/>
+      <c r="E34" s="59">
+        <f>'Le moteur'!P34</f>
+        <v/>
+      </c>
+      <c r="F34" s="121" t="n"/>
+      <c r="G34" s="122" t="inlineStr"/>
+      <c r="H34" s="121" t="n"/>
+      <c r="I34" s="121" t="n"/>
+      <c r="J34" s="121" t="n"/>
+      <c r="K34" s="121" t="n"/>
+      <c r="L34" s="121" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>À +6,2 % l'an, MBway Paris tient jusqu'en 2029. C'est vérifiable ligne à ligne dans l'onglet « Le coût variable », dernière colonne — ce n'est pas une affirmation.</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
+      <c r="B35" s="120" t="inlineStr">
+        <is>
+          <t>Capacité moyenne d'une classe</t>
+        </is>
+      </c>
+      <c r="C35" s="121" t="n"/>
+      <c r="D35" s="121" t="n"/>
+      <c r="E35" s="123">
+        <f>IFERROR(E33/E34,0)</f>
+        <v/>
+      </c>
+      <c r="F35" s="121" t="n"/>
+      <c r="G35" s="122" t="inlineStr"/>
+      <c r="H35" s="121" t="n"/>
+      <c r="I35" s="121" t="n"/>
+      <c r="J35" s="121" t="n"/>
+      <c r="K35" s="121" t="n"/>
+      <c r="L35" s="121" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
+      <c r="B36" s="120" t="inlineStr">
+        <is>
+          <t>Croissance possible avant saturation</t>
+        </is>
+      </c>
+      <c r="C36" s="121" t="n"/>
+      <c r="D36" s="121" t="n"/>
+      <c r="E36" s="72">
+        <f>'Le coût variable'!L48</f>
+        <v/>
+      </c>
+      <c r="F36" s="121" t="n"/>
+      <c r="G36" s="122" t="inlineStr">
+        <is>
+          <t>le premier campus qui sature : MBway Paris</t>
+        </is>
+      </c>
+      <c r="H36" s="121" t="n"/>
+      <c r="I36" s="121" t="n"/>
+      <c r="J36" s="121" t="n"/>
+      <c r="K36" s="121" t="n"/>
+      <c r="L36" s="121" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>Classes à ouvrir en 2027</t>
+        </is>
+      </c>
+      <c r="C37" s="121" t="n"/>
+      <c r="D37" s="121" t="n"/>
+      <c r="E37" s="126">
+        <f>MAX(0,ROUNDUP((E31-E33)/E35,0))</f>
+        <v/>
+      </c>
+      <c r="F37" s="121" t="n"/>
+      <c r="G37" s="122" t="inlineStr">
+        <is>
+          <t>aucune — et c'est toute la démonstration</t>
+        </is>
+      </c>
+      <c r="H37" s="121" t="n"/>
+      <c r="I37" s="121" t="n"/>
+      <c r="J37" s="121" t="n"/>
+      <c r="K37" s="121" t="n"/>
+      <c r="L37" s="121" t="n"/>
+    </row>
+    <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="38" t="inlineStr">
-        <is>
-          <t>ⓒ  La projection, compte par compte</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="14" customHeight="1">
+      <c r="B38" s="120" t="inlineStr">
+        <is>
+          <t>Classes 2027</t>
+        </is>
+      </c>
+      <c r="C38" s="121" t="n"/>
+      <c r="D38" s="121" t="n"/>
+      <c r="E38" s="59">
+        <f>E34+E37</f>
+        <v/>
+      </c>
+      <c r="F38" s="121" t="n"/>
+      <c r="G38" s="122" t="inlineStr"/>
+      <c r="H38" s="121" t="n"/>
+      <c r="I38" s="121" t="n"/>
+      <c r="J38" s="121" t="n"/>
+      <c r="K38" s="121" t="n"/>
+      <c r="L38" s="121" t="n"/>
+    </row>
+    <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>Montant 2026 lié au tableau ⑤. Chaque compte reçoit un effet volume et un effet prix — jamais les deux au hasard : c'est son comportement qui les désigne.</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
+      <c r="B39" s="120" t="inlineStr">
+        <is>
+          <t>Inducteur du compte 621</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="n"/>
+      <c r="D39" s="121" t="n"/>
+      <c r="E39" s="127">
+        <f>IFERROR(E38/E34,0)</f>
+        <v/>
+      </c>
+      <c r="F39" s="121" t="n"/>
+      <c r="G39" s="122" t="inlineStr">
+        <is>
+          <t>le ratio de CLASSES, jamais celui des effectifs</t>
+        </is>
+      </c>
+      <c r="H39" s="121" t="n"/>
+      <c r="I39" s="121" t="n"/>
+      <c r="J39" s="121" t="n"/>
+      <c r="K39" s="121" t="n"/>
+      <c r="L39" s="121" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -10161,731 +10264,370 @@
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Compte et libellé</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2026</t>
-        </is>
-      </c>
-      <c r="E41" s="26" t="inlineStr">
-        <is>
-          <t>Inducteur de volume</t>
-        </is>
-      </c>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>Effet volume</t>
-        </is>
-      </c>
-      <c r="G41" s="26" t="inlineStr">
-        <is>
-          <t>Effet prix</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2027</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="inlineStr">
-        <is>
-          <t>Variation</t>
-        </is>
-      </c>
-      <c r="J41" s="26" t="inlineStr">
-        <is>
-          <t>Ce qui décide</t>
-        </is>
-      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>À +6 % l'an, MBway Paris tient jusqu'en 2029. Vérifiable ligne à ligne : onglet « Le coût variable », dernière colonne du tableau campus.</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="106" t="inlineStr">
-        <is>
-          <t>604 · Achats d'études et supports pédagogiques</t>
-        </is>
-      </c>
-      <c r="C42" s="107" t="n"/>
-      <c r="D42" s="124">
-        <f>'Le coût variable'!D74</f>
-        <v/>
-      </c>
-      <c r="E42" s="125" t="inlineStr">
-        <is>
-          <t>effectifs</t>
-        </is>
-      </c>
-      <c r="F42" s="126">
-        <f>1+$E$12</f>
-        <v/>
-      </c>
-      <c r="G42" s="126">
-        <f>1+$E$14</f>
-        <v/>
-      </c>
-      <c r="H42" s="127">
-        <f>D42*F42*G42</f>
-        <v/>
-      </c>
-      <c r="I42" s="128">
-        <f>IFERROR(H42/D42-1,0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="129" t="inlineStr">
-        <is>
-          <t>le remplissage</t>
-        </is>
-      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="20" customHeight="1">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="106" t="inlineStr">
-        <is>
-          <t>6063 · Fournitures pédagogiques et administratives</t>
-        </is>
-      </c>
-      <c r="C43" s="107" t="n"/>
-      <c r="D43" s="124">
-        <f>'Le coût variable'!D75</f>
-        <v/>
-      </c>
-      <c r="E43" s="125" t="inlineStr">
-        <is>
-          <t>effectifs</t>
-        </is>
-      </c>
-      <c r="F43" s="126">
-        <f>1+$E$12</f>
-        <v/>
-      </c>
-      <c r="G43" s="126">
-        <f>1+$E$14</f>
-        <v/>
-      </c>
-      <c r="H43" s="127">
-        <f>D43*F43*G43</f>
-        <v/>
-      </c>
-      <c r="I43" s="128">
-        <f>IFERROR(H43/D43-1,0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="129" t="inlineStr">
-        <is>
-          <t>le remplissage</t>
-        </is>
-      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>ⓒ  Le chiffre d'affaires 2027  ·  quatre lignes, et une seule est une décision</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="106" t="inlineStr">
-        <is>
-          <t>621 · Personnel extérieur — enseignants vacataires</t>
-        </is>
-      </c>
-      <c r="C44" s="107" t="n"/>
-      <c r="D44" s="124">
-        <f>'Le coût variable'!D76</f>
-        <v/>
-      </c>
-      <c r="E44" s="125" t="inlineStr">
-        <is>
-          <t>CLASSES, pas effectifs</t>
-        </is>
-      </c>
-      <c r="F44" s="126">
-        <f>$E$34</f>
-        <v/>
-      </c>
-      <c r="G44" s="126">
-        <f>1+$E$14</f>
-        <v/>
-      </c>
-      <c r="H44" s="127">
-        <f>D44*F44*G44</f>
-        <v/>
-      </c>
-      <c r="I44" s="128">
-        <f>IFERROR(H44/D44-1,0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="130" t="inlineStr">
-        <is>
-          <t>l'ouverture d'une classe</t>
-        </is>
-      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Le socle est déjà inscrit, le geste est celui du moteur, le prix est un arbitrage. Rien d'autre n'entre dans le CA.</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
       <c r="K44" s="5" t="n"/>
       <c r="L44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="106" t="inlineStr">
-        <is>
-          <t>6411 · Salaires — enseignants permanents</t>
-        </is>
-      </c>
-      <c r="C45" s="107" t="n"/>
-      <c r="D45" s="124">
-        <f>'Le coût variable'!D77</f>
-        <v/>
-      </c>
-      <c r="E45" s="125" t="inlineStr">
-        <is>
-          <t>postes permanents</t>
-        </is>
-      </c>
-      <c r="F45" s="126">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="G45" s="126">
-        <f>1+$E$16</f>
-        <v/>
-      </c>
-      <c r="H45" s="127">
-        <f>D45*F45*G45</f>
-        <v/>
-      </c>
-      <c r="I45" s="128">
-        <f>IFERROR(H45/D45-1,0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="131" t="inlineStr">
-        <is>
-          <t>le recrutement</t>
-        </is>
-      </c>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
       <c r="K45" s="5" t="n"/>
       <c r="L45" s="5" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="106" t="inlineStr">
-        <is>
-          <t>6231 · Annonces et insertions — budget d'acquisition</t>
-        </is>
-      </c>
-      <c r="C46" s="107" t="n"/>
-      <c r="D46" s="124">
-        <f>'Le coût variable'!D78</f>
-        <v/>
-      </c>
-      <c r="E46" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="126">
-        <f>1+$E$18</f>
-        <v/>
-      </c>
-      <c r="H46" s="127">
-        <f>D46*F46*G46</f>
-        <v/>
-      </c>
-      <c r="I46" s="128">
-        <f>IFERROR(H46/D46-1,0)</f>
-        <v/>
-      </c>
-      <c r="J46" s="132" t="inlineStr">
-        <is>
-          <t>LE GESTE — onglet « Le moteur »</t>
-        </is>
-      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Ligne</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="106" t="inlineStr">
-        <is>
-          <t>6413 · Salaires — personnel administratif des campus</t>
-        </is>
-      </c>
-      <c r="C47" s="107" t="n"/>
-      <c r="D47" s="124">
-        <f>'Le coût variable'!D79</f>
-        <v/>
-      </c>
-      <c r="E47" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="126">
-        <f>1+$E$16</f>
-        <v/>
-      </c>
-      <c r="H47" s="127">
-        <f>D47*F47*G47</f>
-        <v/>
-      </c>
-      <c r="I47" s="128">
-        <f>IFERROR(H47/D47-1,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="125" t="inlineStr">
-        <is>
-          <t>la politique salariale</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
+      <c r="B47" s="120" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="121" t="n"/>
+      <c r="D47" s="121" t="n"/>
+      <c r="E47" s="51">
+        <f>'Le coût variable'!D95</f>
+        <v/>
+      </c>
+      <c r="F47" s="121" t="n"/>
+      <c r="G47" s="122" t="inlineStr">
+        <is>
+          <t>restitué · 706 + 7062 + 708</t>
+        </is>
+      </c>
+      <c r="H47" s="121" t="n"/>
+      <c r="I47" s="121" t="n"/>
+      <c r="J47" s="121" t="n"/>
+      <c r="K47" s="121" t="n"/>
+      <c r="L47" s="121" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="106" t="inlineStr">
-        <is>
-          <t>645 · Charges sociales sur les salaires</t>
-        </is>
-      </c>
-      <c r="C48" s="107" t="n"/>
-      <c r="D48" s="124">
-        <f>'Le coût variable'!D80</f>
-        <v/>
-      </c>
-      <c r="E48" s="125" t="inlineStr">
-        <is>
-          <t>la masse salariale</t>
-        </is>
-      </c>
-      <c r="F48" s="126">
-        <f>(H45+H47+H55)/(D45+D47+D55)</f>
-        <v/>
-      </c>
-      <c r="G48" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="127">
-        <f>D48*F48*G48</f>
-        <v/>
-      </c>
-      <c r="I48" s="128">
-        <f>IFERROR(H48/D48-1,0)</f>
-        <v/>
-      </c>
-      <c r="J48" s="125" t="inlineStr">
-        <is>
-          <t>assis sur la masse</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
+      <c r="B48" s="120" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C48" s="121" t="n"/>
+      <c r="D48" s="121" t="n"/>
+      <c r="E48" s="51">
+        <f>E47*$E$13</f>
+        <v/>
+      </c>
+      <c r="F48" s="121" t="n"/>
+      <c r="G48" s="122" t="inlineStr">
+        <is>
+          <t>la rentrée déjà engagée</t>
+        </is>
+      </c>
+      <c r="H48" s="121" t="n"/>
+      <c r="I48" s="121" t="n"/>
+      <c r="J48" s="121" t="n"/>
+      <c r="K48" s="121" t="n"/>
+      <c r="L48" s="121" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="106" t="inlineStr">
-        <is>
-          <t>613 · Locations immobilières des campus</t>
-        </is>
-      </c>
-      <c r="C49" s="107" t="n"/>
-      <c r="D49" s="124">
-        <f>'Le coût variable'!D81</f>
-        <v/>
-      </c>
-      <c r="E49" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H49" s="127">
-        <f>D49*F49*G49</f>
-        <v/>
-      </c>
-      <c r="I49" s="128">
-        <f>IFERROR(H49/D49-1,0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
+      <c r="B49" s="120" t="inlineStr">
+        <is>
+          <t>+ ce que le geste ajoute</t>
+        </is>
+      </c>
+      <c r="C49" s="121" t="n"/>
+      <c r="D49" s="121" t="n"/>
+      <c r="E49" s="51">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="F49" s="121" t="n"/>
+      <c r="G49" s="122" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — le CA gagné par le Δ budget</t>
+        </is>
+      </c>
+      <c r="H49" s="121" t="n"/>
+      <c r="I49" s="121" t="n"/>
+      <c r="J49" s="121" t="n"/>
+      <c r="K49" s="121" t="n"/>
+      <c r="L49" s="121" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="106" t="inlineStr">
-        <is>
-          <t>615 · Entretien et réparations</t>
-        </is>
-      </c>
-      <c r="C50" s="107" t="n"/>
-      <c r="D50" s="124">
-        <f>'Le coût variable'!D82</f>
-        <v/>
-      </c>
-      <c r="E50" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H50" s="127">
-        <f>D50*F50*G50</f>
-        <v/>
-      </c>
-      <c r="I50" s="128">
-        <f>IFERROR(H50/D50-1,0)</f>
-        <v/>
-      </c>
-      <c r="J50" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="n"/>
-      <c r="L50" s="5" t="n"/>
+      <c r="B50" s="120" t="inlineStr">
+        <is>
+          <t>+ effet prix</t>
+        </is>
+      </c>
+      <c r="C50" s="121" t="n"/>
+      <c r="D50" s="121" t="n"/>
+      <c r="E50" s="51">
+        <f>(E47+E48+E49)*$E$14</f>
+        <v/>
+      </c>
+      <c r="F50" s="121" t="n"/>
+      <c r="G50" s="122" t="inlineStr">
+        <is>
+          <t>la hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="H50" s="121" t="n"/>
+      <c r="I50" s="121" t="n"/>
+      <c r="J50" s="121" t="n"/>
+      <c r="K50" s="121" t="n"/>
+      <c r="L50" s="121" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="106" t="inlineStr">
-        <is>
-          <t>616 · Primes d'assurance</t>
-        </is>
-      </c>
-      <c r="C51" s="107" t="n"/>
-      <c r="D51" s="124">
-        <f>'Le coût variable'!D83</f>
-        <v/>
-      </c>
-      <c r="E51" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H51" s="127">
-        <f>D51*F51*G51</f>
-        <v/>
-      </c>
-      <c r="I51" s="128">
-        <f>IFERROR(H51/D51-1,0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
+      <c r="B51" s="49">
+        <f> Chiffre d'affaires 2027</f>
+        <v/>
+      </c>
+      <c r="C51" s="121" t="n"/>
+      <c r="D51" s="121" t="n"/>
+      <c r="E51" s="128">
+        <f>SUM(E47:E50)</f>
+        <v/>
+      </c>
+      <c r="F51" s="121" t="n"/>
+      <c r="G51" s="122" t="inlineStr"/>
+      <c r="H51" s="121" t="n"/>
+      <c r="I51" s="121" t="n"/>
+      <c r="J51" s="121" t="n"/>
+      <c r="K51" s="121" t="n"/>
+      <c r="L51" s="121" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="106" t="inlineStr">
-        <is>
-          <t>625 · Déplacements, missions et réceptions</t>
-        </is>
-      </c>
-      <c r="C52" s="107" t="n"/>
-      <c r="D52" s="124">
-        <f>'Le coût variable'!D84</f>
-        <v/>
-      </c>
-      <c r="E52" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H52" s="127">
-        <f>D52*F52*G52</f>
-        <v/>
-      </c>
-      <c r="I52" s="128">
-        <f>IFERROR(H52/D52-1,0)</f>
-        <v/>
-      </c>
-      <c r="J52" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
       <c r="K52" s="5" t="n"/>
       <c r="L52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="106" t="inlineStr">
-        <is>
-          <t>63511 · Contribution économique territoriale</t>
-        </is>
-      </c>
-      <c r="C53" s="107" t="n"/>
-      <c r="D53" s="124">
-        <f>'Le coût variable'!D85</f>
-        <v/>
-      </c>
-      <c r="E53" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H53" s="127">
-        <f>D53*F53*G53</f>
-        <v/>
-      </c>
-      <c r="I53" s="128">
-        <f>IFERROR(H53/D53-1,0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="125" t="inlineStr">
-        <is>
-          <t>la fiscalité locale</t>
-        </is>
-      </c>
+      <c r="B53" s="129">
+        <f>"Sur "&amp;TEXT(E51-E47,"#,##0 €")&amp;" de croissance, "&amp;TEXT(E48/(E51-E47),"0 %")&amp;" viennent du socle déjà inscrit, "&amp;TEXT(E49/(E51-E47),"0 %")&amp;" du geste d'acquisition et "&amp;TEXT(E50/(E51-E47),"0 %")&amp;" du prix. Le chiffre d'affaires ne se décrète pas."</f>
+        <v/>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
       <c r="K53" s="5" t="n"/>
       <c r="L53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="106" t="inlineStr">
-        <is>
-          <t>6236 · Catalogues et imprimés — marketing de marque</t>
-        </is>
-      </c>
-      <c r="C54" s="107" t="n"/>
-      <c r="D54" s="124">
-        <f>'Le coût variable'!D86</f>
-        <v/>
-      </c>
-      <c r="E54" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="126">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H54" s="127">
-        <f>D54*F54*G54</f>
-        <v/>
-      </c>
-      <c r="I54" s="128">
-        <f>IFERROR(H54/D54-1,0)</f>
-        <v/>
-      </c>
-      <c r="J54" s="125" t="inlineStr">
-        <is>
-          <t>le budget de marque</t>
-        </is>
-      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
       <c r="K54" s="5" t="n"/>
       <c r="L54" s="5" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="106" t="inlineStr">
-        <is>
-          <t>6414 · Salaires du siège</t>
-        </is>
-      </c>
-      <c r="C55" s="107" t="n"/>
-      <c r="D55" s="124">
-        <f>'Le coût variable'!D87</f>
-        <v/>
-      </c>
-      <c r="E55" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="126">
-        <f>1+$E$16</f>
-        <v/>
-      </c>
-      <c r="H55" s="127">
-        <f>D55*F55*G55</f>
-        <v/>
-      </c>
-      <c r="I55" s="128">
-        <f>IFERROR(H55/D55-1,0)</f>
-        <v/>
-      </c>
-      <c r="J55" s="125" t="inlineStr">
-        <is>
-          <t>la politique salariale</t>
-        </is>
-      </c>
+      <c r="B55" s="38" t="inlineStr">
+        <is>
+          <t>ⓓ  Les coûts 2027  ·  sept familles, sept règles</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="5" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="106" t="inlineStr">
-        <is>
-          <t>6226 · Honoraires</t>
-        </is>
-      </c>
-      <c r="C56" s="107" t="n"/>
-      <c r="D56" s="124">
-        <f>'Le coût variable'!D88</f>
-        <v/>
-      </c>
-      <c r="E56" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H56" s="127">
-        <f>D56*F56*G56</f>
-        <v/>
-      </c>
-      <c r="I56" s="128">
-        <f>IFERROR(H56/D56-1,0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Un budget qui indexe tout au même taux ne dit rien. Celui-ci donne à chaque euro l'inducteur de son comportement — et c'est ce qui fait apparaître où est le levier, et surtout où il n'est pas.</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="106" t="inlineStr">
-        <is>
-          <t>626 · Frais postaux et de télécommunications</t>
-        </is>
-      </c>
-      <c r="C57" s="107" t="n"/>
-      <c r="D57" s="124">
-        <f>'Le coût variable'!D89</f>
-        <v/>
-      </c>
-      <c r="E57" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H57" s="127">
-        <f>D57*F57*G57</f>
-        <v/>
-      </c>
-      <c r="I57" s="128">
-        <f>IFERROR(H57/D57-1,0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
-        </is>
-      </c>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="n"/>
-      <c r="B58" s="106" t="inlineStr">
-        <is>
-          <t>6281 · Cotisations et concours divers</t>
-        </is>
-      </c>
-      <c r="C58" s="107" t="n"/>
-      <c r="D58" s="124">
-        <f>'Le coût variable'!D90</f>
-        <v/>
-      </c>
-      <c r="E58" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="126">
-        <f>1+$E$14-$E$15</f>
-        <v/>
-      </c>
-      <c r="H58" s="127">
-        <f>D58*F58*G58</f>
-        <v/>
-      </c>
-      <c r="I58" s="128">
-        <f>IFERROR(H58/D58-1,0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="125" t="inlineStr">
-        <is>
-          <t>l'indexation, moins l'effort</t>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Famille · compte</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui la fait bouger</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>Effet volume</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Effet prix</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2027</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>Variation</t>
+        </is>
+      </c>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui décide</t>
         </is>
       </c>
       <c r="K58" s="5" t="n"/>
@@ -10893,39 +10635,34 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
-      <c r="B59" s="106" t="inlineStr">
-        <is>
-          <t>6331 · Versement mobilité</t>
-        </is>
-      </c>
-      <c r="C59" s="107" t="n"/>
-      <c r="D59" s="124">
-        <f>'Le coût variable'!D91</f>
-        <v/>
-      </c>
-      <c r="E59" s="125" t="inlineStr">
-        <is>
-          <t>la masse salariale</t>
-        </is>
-      </c>
-      <c r="F59" s="126">
-        <f>(H45+H47+H55)/(D45+D47+D55)</f>
-        <v/>
-      </c>
-      <c r="G59" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="127">
-        <f>D59*F59*G59</f>
-        <v/>
-      </c>
-      <c r="I59" s="128">
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>①  Suit l'ÉLÈVE</t>
+        </is>
+      </c>
+      <c r="C59" s="64" t="n"/>
+      <c r="D59" s="68">
+        <f>SUM(D60:D61)</f>
+        <v/>
+      </c>
+      <c r="E59" s="130" t="inlineStr">
+        <is>
+          <t>effectifs × inflation</t>
+        </is>
+      </c>
+      <c r="F59" s="131" t="inlineStr"/>
+      <c r="G59" s="131" t="inlineStr"/>
+      <c r="H59" s="68">
+        <f>SUM(H60:H61)</f>
+        <v/>
+      </c>
+      <c r="I59" s="132">
         <f>IFERROR(H59/D59-1,0)</f>
         <v/>
       </c>
-      <c r="J59" s="125" t="inlineStr">
-        <is>
-          <t>assis sur la masse</t>
+      <c r="J59" s="133" t="inlineStr">
+        <is>
+          <t>604 + 6063</t>
         </is>
       </c>
       <c r="K59" s="5" t="n"/>
@@ -10933,81 +10670,67 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
-      <c r="B60" s="106" t="inlineStr">
-        <is>
-          <t>6333 · Participation à la formation professionnelle</t>
+      <c r="B60" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      604 · Achats d'études et supports pédagogiques</t>
         </is>
       </c>
       <c r="C60" s="107" t="n"/>
-      <c r="D60" s="124">
-        <f>'Le coût variable'!D92</f>
-        <v/>
-      </c>
-      <c r="E60" s="125" t="inlineStr">
-        <is>
-          <t>la masse salariale</t>
-        </is>
-      </c>
-      <c r="F60" s="126">
-        <f>(H45+H47+H55)/(D45+D47+D55)</f>
-        <v/>
-      </c>
-      <c r="G60" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="127">
+      <c r="D60" s="135">
+        <f>'Le coût variable'!D74</f>
+        <v/>
+      </c>
+      <c r="E60" s="107" t="inlineStr"/>
+      <c r="F60" s="136">
+        <f>$E$31/$E$28</f>
+        <v/>
+      </c>
+      <c r="G60" s="136">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H60" s="135">
         <f>D60*F60*G60</f>
         <v/>
       </c>
-      <c r="I60" s="128">
+      <c r="I60" s="137">
         <f>IFERROR(H60/D60-1,0)</f>
         <v/>
       </c>
-      <c r="J60" s="125" t="inlineStr">
-        <is>
-          <t>assis sur la masse</t>
-        </is>
-      </c>
+      <c r="J60" s="107" t="inlineStr"/>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
-      <c r="B61" s="106" t="inlineStr">
-        <is>
-          <t>6811 · Dotations aux amortissements</t>
+      <c r="B61" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6063 · Fournitures pédagogiques et administratives</t>
         </is>
       </c>
       <c r="C61" s="107" t="n"/>
-      <c r="D61" s="124">
-        <f>'Le coût variable'!D93</f>
-        <v/>
-      </c>
-      <c r="E61" s="125" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="126">
-        <f>1+$E$20</f>
-        <v/>
-      </c>
-      <c r="H61" s="127">
+      <c r="D61" s="135">
+        <f>'Le coût variable'!D75</f>
+        <v/>
+      </c>
+      <c r="E61" s="107" t="inlineStr"/>
+      <c r="F61" s="136">
+        <f>$E$31/$E$28</f>
+        <v/>
+      </c>
+      <c r="G61" s="136">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H61" s="135">
         <f>D61*F61*G61</f>
         <v/>
       </c>
-      <c r="I61" s="128">
+      <c r="I61" s="137">
         <f>IFERROR(H61/D61-1,0)</f>
         <v/>
       </c>
-      <c r="J61" s="125" t="inlineStr">
-        <is>
-          <t>le plan d'amortissement</t>
-        </is>
-      </c>
+      <c r="J61" s="107" t="inlineStr"/>
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="5" t="n"/>
     </row>
@@ -11015,67 +10738,67 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="64" t="inlineStr">
         <is>
-          <t>TOTAL DES CHARGES  ·  dotations incluses</t>
+          <t>②  Suit la CLASSE</t>
         </is>
       </c>
       <c r="C62" s="64" t="n"/>
       <c r="D62" s="68">
-        <f>SUM(D42:D61)</f>
-        <v/>
-      </c>
-      <c r="E62" s="64" t="inlineStr"/>
-      <c r="F62" s="133" t="inlineStr"/>
-      <c r="G62" s="133" t="inlineStr"/>
+        <f>SUM(D63:D63)</f>
+        <v/>
+      </c>
+      <c r="E62" s="138" t="inlineStr">
+        <is>
+          <t>classes × inflation</t>
+        </is>
+      </c>
+      <c r="F62" s="131" t="inlineStr"/>
+      <c r="G62" s="131" t="inlineStr"/>
       <c r="H62" s="68">
-        <f>SUM(H42:H61)</f>
-        <v/>
-      </c>
-      <c r="I62" s="69">
+        <f>SUM(H63:H63)</f>
+        <v/>
+      </c>
+      <c r="I62" s="139">
         <f>IFERROR(H62/D62-1,0)</f>
         <v/>
       </c>
-      <c r="J62" s="64" t="inlineStr"/>
+      <c r="J62" s="133" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
-      <c r="B63" s="87" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires</t>
-        </is>
-      </c>
-      <c r="C63" s="87" t="n"/>
-      <c r="D63" s="88">
-        <f>'Le coût variable'!D95</f>
-        <v/>
-      </c>
-      <c r="E63" s="87" t="inlineStr">
-        <is>
-          <t>volume × prix</t>
-        </is>
-      </c>
-      <c r="F63" s="134">
-        <f>1+$E$12</f>
-        <v/>
-      </c>
-      <c r="G63" s="134">
-        <f>1+$E$13</f>
-        <v/>
-      </c>
-      <c r="H63" s="88">
+      <c r="B63" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      621 · Personnel extérieur — enseignants vacataires</t>
+        </is>
+      </c>
+      <c r="C63" s="107" t="n"/>
+      <c r="D63" s="135">
+        <f>'Le coût variable'!D76</f>
+        <v/>
+      </c>
+      <c r="E63" s="107" t="inlineStr"/>
+      <c r="F63" s="136">
+        <f>$E$39</f>
+        <v/>
+      </c>
+      <c r="G63" s="136">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H63" s="135">
         <f>D63*F63*G63</f>
         <v/>
       </c>
-      <c r="I63" s="135">
+      <c r="I63" s="137">
         <f>IFERROR(H63/D63-1,0)</f>
         <v/>
       </c>
-      <c r="J63" s="87" t="inlineStr">
-        <is>
-          <t>le socle CRM et le tarif</t>
-        </is>
-      </c>
+      <c r="J63" s="107" t="inlineStr"/>
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
     </row>
@@ -11083,205 +10806,1201 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="64" t="inlineStr">
         <is>
-          <t>EBITDA  ·  hors dotations</t>
+          <t>③  Suit les POSTES</t>
         </is>
       </c>
       <c r="C64" s="64" t="n"/>
-      <c r="D64" s="136">
-        <f>D63-D62+D61</f>
-        <v/>
-      </c>
-      <c r="E64" s="64" t="inlineStr"/>
-      <c r="F64" s="133" t="inlineStr"/>
-      <c r="G64" s="133" t="inlineStr"/>
-      <c r="H64" s="136">
-        <f>H63-H62+H61</f>
-        <v/>
-      </c>
-      <c r="I64" s="69">
+      <c r="D64" s="68">
+        <f>SUM(D65:D67)</f>
+        <v/>
+      </c>
+      <c r="E64" s="140" t="inlineStr">
+        <is>
+          <t>politique salariale, + les postes créés</t>
+        </is>
+      </c>
+      <c r="F64" s="131" t="inlineStr"/>
+      <c r="G64" s="131" t="inlineStr"/>
+      <c r="H64" s="68">
+        <f>SUM(H65:H67)</f>
+        <v/>
+      </c>
+      <c r="I64" s="141">
         <f>IFERROR(H64/D64-1,0)</f>
         <v/>
       </c>
-      <c r="J64" s="64" t="inlineStr"/>
+      <c r="J64" s="133" t="inlineStr">
+        <is>
+          <t>6411 + 6413 + 6414</t>
+        </is>
+      </c>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
-      <c r="B65" s="49" t="inlineStr">
-        <is>
-          <t>Marge d'EBITDA</t>
-        </is>
-      </c>
-      <c r="C65" s="49" t="n"/>
-      <c r="D65" s="137">
-        <f>IFERROR(D64/D63,0)</f>
-        <v/>
-      </c>
-      <c r="E65" s="49" t="inlineStr"/>
-      <c r="F65" s="123" t="inlineStr"/>
-      <c r="G65" s="123" t="inlineStr"/>
-      <c r="H65" s="137">
-        <f>IFERROR(H64/H63,0)</f>
-        <v/>
-      </c>
-      <c r="I65" s="138">
-        <f>H65-D65</f>
-        <v/>
-      </c>
-      <c r="J65" s="49" t="inlineStr"/>
+      <c r="B65" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6411 · Salaires — enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C65" s="107" t="n"/>
+      <c r="D65" s="135">
+        <f>'Le coût variable'!D77</f>
+        <v/>
+      </c>
+      <c r="E65" s="107" t="inlineStr"/>
+      <c r="F65" s="136">
+        <f>1+$E$20</f>
+        <v/>
+      </c>
+      <c r="G65" s="136">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H65" s="135">
+        <f>D65*F65*G65</f>
+        <v/>
+      </c>
+      <c r="I65" s="137">
+        <f>IFERROR(H65/D65-1,0)</f>
+        <v/>
+      </c>
+      <c r="J65" s="107" t="inlineStr"/>
       <c r="K65" s="5" t="n"/>
       <c r="L65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
+      <c r="B66" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6413 · Salaires — personnel administratif des campus</t>
+        </is>
+      </c>
+      <c r="C66" s="107" t="n"/>
+      <c r="D66" s="135">
+        <f>'Le coût variable'!D79</f>
+        <v/>
+      </c>
+      <c r="E66" s="107" t="inlineStr"/>
+      <c r="F66" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="136">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H66" s="135">
+        <f>D66*F66*G66</f>
+        <v/>
+      </c>
+      <c r="I66" s="137">
+        <f>IFERROR(H66/D66-1,0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="107" t="inlineStr"/>
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="n"/>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67">
       <c r="A67" s="5" t="n"/>
-      <c r="B67" s="139">
-        <f>"2027 : "&amp;TEXT(H64,"#,##0 €")&amp;" d'EBITDA, marge "&amp;TEXT(H65,"0.0 %")&amp;"  —  contre "&amp;TEXT(D65,"0.0 %")&amp;" en 2026. Le gain ne vient pas d'une économie : il vient de "&amp;TEXT(E27-E26,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes."</f>
-        <v/>
-      </c>
-      <c r="C67" s="110" t="n"/>
-      <c r="D67" s="110" t="n"/>
-      <c r="E67" s="110" t="n"/>
-      <c r="F67" s="110" t="n"/>
-      <c r="G67" s="110" t="n"/>
-      <c r="H67" s="110" t="n"/>
-      <c r="I67" s="110" t="n"/>
-      <c r="J67" s="110" t="n"/>
-      <c r="K67" s="110" t="n"/>
-      <c r="L67" s="110" t="n"/>
+      <c r="B67" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6414 · Salaires du siège</t>
+        </is>
+      </c>
+      <c r="C67" s="107" t="n"/>
+      <c r="D67" s="135">
+        <f>'Le coût variable'!D87</f>
+        <v/>
+      </c>
+      <c r="E67" s="107" t="inlineStr"/>
+      <c r="F67" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="136">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H67" s="135">
+        <f>D67*F67*G67</f>
+        <v/>
+      </c>
+      <c r="I67" s="137">
+        <f>IFERROR(H67/D67-1,0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="107" t="inlineStr"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="111" t="inlineStr">
-        <is>
-          <t>Le jour où une classe doit ouvrir, la ligne 621 change d'inducteur toute seule — et c'est là que la marge s'arrête de monter. Le classeur dit quand : onglet « Le coût variable », dernière colonne.</t>
-        </is>
-      </c>
-      <c r="C68" s="112" t="n"/>
-      <c r="D68" s="112" t="n"/>
-      <c r="E68" s="112" t="n"/>
-      <c r="F68" s="112" t="n"/>
-      <c r="G68" s="112" t="n"/>
-      <c r="H68" s="112" t="n"/>
-      <c r="I68" s="112" t="n"/>
-      <c r="J68" s="112" t="n"/>
-      <c r="K68" s="112" t="n"/>
-      <c r="L68" s="112" t="n"/>
+      <c r="B68" s="64" t="inlineStr">
+        <is>
+          <t>④  Assis sur la MASSE</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="n"/>
+      <c r="D68" s="68">
+        <f>SUM(D69:D71)</f>
+        <v/>
+      </c>
+      <c r="E68" s="140" t="inlineStr">
+        <is>
+          <t>au prorata de la masse salariale</t>
+        </is>
+      </c>
+      <c r="F68" s="131" t="inlineStr"/>
+      <c r="G68" s="131" t="inlineStr"/>
+      <c r="H68" s="68">
+        <f>SUM(H69:H71)</f>
+        <v/>
+      </c>
+      <c r="I68" s="141">
+        <f>IFERROR(H68/D68-1,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="133" t="inlineStr">
+        <is>
+          <t>645 + 6331 + 6333</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
+      <c r="B69" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      645 · Charges sociales sur les salaires</t>
+        </is>
+      </c>
+      <c r="C69" s="107" t="n"/>
+      <c r="D69" s="135">
+        <f>'Le coût variable'!D80</f>
+        <v/>
+      </c>
+      <c r="E69" s="107" t="inlineStr"/>
+      <c r="F69" s="136">
+        <f>(H65+H66+H67)/(D65+D66+D67)</f>
+        <v/>
+      </c>
+      <c r="G69" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="135">
+        <f>D69*F69*G69</f>
+        <v/>
+      </c>
+      <c r="I69" s="137">
+        <f>IFERROR(H69/D69-1,0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="107" t="inlineStr"/>
       <c r="K69" s="5" t="n"/>
       <c r="L69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
+      <c r="B70" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6331 · Versement mobilité</t>
+        </is>
+      </c>
+      <c r="C70" s="107" t="n"/>
+      <c r="D70" s="135">
+        <f>'Le coût variable'!D91</f>
+        <v/>
+      </c>
+      <c r="E70" s="107" t="inlineStr"/>
+      <c r="F70" s="136">
+        <f>(H65+H66+H67)/(D65+D66+D67)</f>
+        <v/>
+      </c>
+      <c r="G70" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="135">
+        <f>D70*F70*G70</f>
+        <v/>
+      </c>
+      <c r="I70" s="137">
+        <f>IFERROR(H70/D70-1,0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="107" t="inlineStr"/>
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
+      <c r="B71" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6333 · Participation à la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="C71" s="107" t="n"/>
+      <c r="D71" s="135">
+        <f>'Le coût variable'!D92</f>
+        <v/>
+      </c>
+      <c r="E71" s="107" t="inlineStr"/>
+      <c r="F71" s="136">
+        <f>(H65+H66+H67)/(D65+D66+D67)</f>
+        <v/>
+      </c>
+      <c r="G71" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="135">
+        <f>D71*F71*G71</f>
+        <v/>
+      </c>
+      <c r="I71" s="137">
+        <f>IFERROR(H71/D71-1,0)</f>
+        <v/>
+      </c>
+      <c r="J71" s="107" t="inlineStr"/>
       <c r="K71" s="5" t="n"/>
       <c r="L71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
+      <c r="B72" s="64" t="inlineStr">
+        <is>
+          <t>⑤  INDEXÉ</t>
+        </is>
+      </c>
+      <c r="C72" s="64" t="n"/>
+      <c r="D72" s="68">
+        <f>SUM(D73:D80)</f>
+        <v/>
+      </c>
+      <c r="E72" s="142" t="inlineStr">
+        <is>
+          <t>inflation moins l'effort de productivité</t>
+        </is>
+      </c>
+      <c r="F72" s="131" t="inlineStr"/>
+      <c r="G72" s="131" t="inlineStr"/>
+      <c r="H72" s="68">
+        <f>SUM(H73:H80)</f>
+        <v/>
+      </c>
+      <c r="I72" s="143">
+        <f>IFERROR(H72/D72-1,0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="133" t="inlineStr">
+        <is>
+          <t>613 · 615 · 616 · 625 · 63511 · 6226 · 626 · 6281</t>
+        </is>
+      </c>
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
+      <c r="B73" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      613 · Locations immobilières des campus</t>
+        </is>
+      </c>
+      <c r="C73" s="107" t="n"/>
+      <c r="D73" s="135">
+        <f>'Le coût variable'!D81</f>
+        <v/>
+      </c>
+      <c r="E73" s="107" t="inlineStr"/>
+      <c r="F73" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H73" s="135">
+        <f>D73*F73*G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="137">
+        <f>IFERROR(H73/D73-1,0)</f>
+        <v/>
+      </c>
+      <c r="J73" s="107" t="inlineStr"/>
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
+      <c r="B74" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      615 · Entretien et réparations</t>
+        </is>
+      </c>
+      <c r="C74" s="107" t="n"/>
+      <c r="D74" s="135">
+        <f>'Le coût variable'!D82</f>
+        <v/>
+      </c>
+      <c r="E74" s="107" t="inlineStr"/>
+      <c r="F74" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H74" s="135">
+        <f>D74*F74*G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="137">
+        <f>IFERROR(H74/D74-1,0)</f>
+        <v/>
+      </c>
+      <c r="J74" s="107" t="inlineStr"/>
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
+      <c r="B75" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      616 · Primes d'assurance</t>
+        </is>
+      </c>
+      <c r="C75" s="107" t="n"/>
+      <c r="D75" s="135">
+        <f>'Le coût variable'!D83</f>
+        <v/>
+      </c>
+      <c r="E75" s="107" t="inlineStr"/>
+      <c r="F75" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H75" s="135">
+        <f>D75*F75*G75</f>
+        <v/>
+      </c>
+      <c r="I75" s="137">
+        <f>IFERROR(H75/D75-1,0)</f>
+        <v/>
+      </c>
+      <c r="J75" s="107" t="inlineStr"/>
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      625 · Déplacements, missions et réceptions</t>
+        </is>
+      </c>
+      <c r="C76" s="107" t="n"/>
+      <c r="D76" s="135">
+        <f>'Le coût variable'!D84</f>
+        <v/>
+      </c>
+      <c r="E76" s="107" t="inlineStr"/>
+      <c r="F76" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H76" s="135">
+        <f>D76*F76*G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="137">
+        <f>IFERROR(H76/D76-1,0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="107" t="inlineStr"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      63511 · Contribution économique territoriale</t>
+        </is>
+      </c>
+      <c r="C77" s="107" t="n"/>
+      <c r="D77" s="135">
+        <f>'Le coût variable'!D85</f>
+        <v/>
+      </c>
+      <c r="E77" s="107" t="inlineStr"/>
+      <c r="F77" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H77" s="135">
+        <f>D77*F77*G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="137">
+        <f>IFERROR(H77/D77-1,0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="107" t="inlineStr"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6226 · Honoraires</t>
+        </is>
+      </c>
+      <c r="C78" s="107" t="n"/>
+      <c r="D78" s="135">
+        <f>'Le coût variable'!D88</f>
+        <v/>
+      </c>
+      <c r="E78" s="107" t="inlineStr"/>
+      <c r="F78" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H78" s="135">
+        <f>D78*F78*G78</f>
+        <v/>
+      </c>
+      <c r="I78" s="137">
+        <f>IFERROR(H78/D78-1,0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="107" t="inlineStr"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      626 · Frais postaux et de télécommunications</t>
+        </is>
+      </c>
+      <c r="C79" s="107" t="n"/>
+      <c r="D79" s="135">
+        <f>'Le coût variable'!D89</f>
+        <v/>
+      </c>
+      <c r="E79" s="107" t="inlineStr"/>
+      <c r="F79" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H79" s="135">
+        <f>D79*F79*G79</f>
+        <v/>
+      </c>
+      <c r="I79" s="137">
+        <f>IFERROR(H79/D79-1,0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="107" t="inlineStr"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6281 · Cotisations et concours divers</t>
+        </is>
+      </c>
+      <c r="C80" s="107" t="n"/>
+      <c r="D80" s="135">
+        <f>'Le coût variable'!D90</f>
+        <v/>
+      </c>
+      <c r="E80" s="107" t="inlineStr"/>
+      <c r="F80" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="136">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H80" s="135">
+        <f>D80*F80*G80</f>
+        <v/>
+      </c>
+      <c r="I80" s="137">
+        <f>IFERROR(H80/D80-1,0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="107" t="inlineStr"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="64" t="inlineStr">
+        <is>
+          <t>⑥  DÉCIDÉ</t>
+        </is>
+      </c>
+      <c r="C81" s="64" t="n"/>
+      <c r="D81" s="68">
+        <f>SUM(D82:D83)</f>
+        <v/>
+      </c>
+      <c r="E81" s="144" t="inlineStr">
+        <is>
+          <t>le geste, et le budget de marque</t>
+        </is>
+      </c>
+      <c r="F81" s="131" t="inlineStr"/>
+      <c r="G81" s="131" t="inlineStr"/>
+      <c r="H81" s="68">
+        <f>SUM(H82:H83)</f>
+        <v/>
+      </c>
+      <c r="I81" s="145">
+        <f>IFERROR(H81/D81-1,0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="133" t="inlineStr">
+        <is>
+          <t>6231 + 6236</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6231 · Annonces et insertions — budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C82" s="107" t="n"/>
+      <c r="D82" s="135">
+        <f>'Le coût variable'!D78</f>
+        <v/>
+      </c>
+      <c r="E82" s="107" t="inlineStr"/>
+      <c r="F82" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="136">
+        <f>1+$E$15</f>
+        <v/>
+      </c>
+      <c r="H82" s="135">
+        <f>D82*F82*G82</f>
+        <v/>
+      </c>
+      <c r="I82" s="137">
+        <f>IFERROR(H82/D82-1,0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="107" t="inlineStr"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6236 · Catalogues et imprimés — marketing de marque</t>
+        </is>
+      </c>
+      <c r="C83" s="107" t="n"/>
+      <c r="D83" s="135">
+        <f>'Le coût variable'!D86</f>
+        <v/>
+      </c>
+      <c r="E83" s="107" t="inlineStr"/>
+      <c r="F83" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="136">
+        <f>1+$E$21</f>
+        <v/>
+      </c>
+      <c r="H83" s="135">
+        <f>D83*F83*G83</f>
+        <v/>
+      </c>
+      <c r="I83" s="137">
+        <f>IFERROR(H83/D83-1,0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="107" t="inlineStr"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="64" t="inlineStr">
+        <is>
+          <t>⑦  HORS EBITDA</t>
+        </is>
+      </c>
+      <c r="C84" s="64" t="n"/>
+      <c r="D84" s="68">
+        <f>SUM(D85:D85)</f>
+        <v/>
+      </c>
+      <c r="E84" s="142" t="inlineStr">
+        <is>
+          <t>le plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="F84" s="131" t="inlineStr"/>
+      <c r="G84" s="131" t="inlineStr"/>
+      <c r="H84" s="68">
+        <f>SUM(H85:H85)</f>
+        <v/>
+      </c>
+      <c r="I84" s="143">
+        <f>IFERROR(H84/D84-1,0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="133" t="inlineStr">
+        <is>
+          <t>6811</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6811 · Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C85" s="107" t="n"/>
+      <c r="D85" s="135">
+        <f>'Le coût variable'!D93</f>
+        <v/>
+      </c>
+      <c r="E85" s="107" t="inlineStr"/>
+      <c r="F85" s="136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="136">
+        <f>1+$E$22</f>
+        <v/>
+      </c>
+      <c r="H85" s="135">
+        <f>D85*F85*G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="137">
+        <f>IFERROR(H85/D85-1,0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="107" t="inlineStr"/>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="64" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES  ·  dotations incluses</t>
+        </is>
+      </c>
+      <c r="C86" s="64" t="n"/>
+      <c r="D86" s="68">
+        <f>D59+D62+D64+D68+D72+D81+D84</f>
+        <v/>
+      </c>
+      <c r="E86" s="64" t="inlineStr"/>
+      <c r="F86" s="131" t="inlineStr"/>
+      <c r="G86" s="131" t="inlineStr"/>
+      <c r="H86" s="68">
+        <f>H59+H62+H64+H68+H72+H81+H84</f>
+        <v/>
+      </c>
+      <c r="I86" s="69">
+        <f>IFERROR(H86/D86-1,0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="64" t="inlineStr"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="87" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="C87" s="87" t="n"/>
+      <c r="D87" s="88">
+        <f>'Le coût variable'!D95</f>
+        <v/>
+      </c>
+      <c r="E87" s="87" t="inlineStr"/>
+      <c r="F87" s="146" t="inlineStr"/>
+      <c r="G87" s="146" t="inlineStr"/>
+      <c r="H87" s="88">
+        <f>E51</f>
+        <v/>
+      </c>
+      <c r="I87" s="147">
+        <f>IFERROR(H87/D87-1,0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="87" t="inlineStr">
+        <is>
+          <t>bloc ⓒ ci-dessus</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="64" t="inlineStr">
+        <is>
+          <t>EBITDA  ·  hors dotations</t>
+        </is>
+      </c>
+      <c r="C88" s="64" t="n"/>
+      <c r="D88" s="148">
+        <f>D87-D86+D85</f>
+        <v/>
+      </c>
+      <c r="E88" s="64" t="inlineStr"/>
+      <c r="F88" s="131" t="inlineStr"/>
+      <c r="G88" s="131" t="inlineStr"/>
+      <c r="H88" s="148">
+        <f>H87-H86+H85</f>
+        <v/>
+      </c>
+      <c r="I88" s="69">
+        <f>IFERROR(H88/D88-1,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="64" t="inlineStr"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="49" t="inlineStr">
+        <is>
+          <t>Marge d'EBITDA</t>
+        </is>
+      </c>
+      <c r="C89" s="49" t="n"/>
+      <c r="D89" s="149">
+        <f>IFERROR(D88/D87,0)</f>
+        <v/>
+      </c>
+      <c r="E89" s="49" t="inlineStr"/>
+      <c r="F89" s="150" t="inlineStr"/>
+      <c r="G89" s="150" t="inlineStr"/>
+      <c r="H89" s="149">
+        <f>IFERROR(H88/H87,0)</f>
+        <v/>
+      </c>
+      <c r="I89" s="151">
+        <f>H89-D89</f>
+        <v/>
+      </c>
+      <c r="J89" s="49" t="inlineStr"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>ⓔ  Est-ce qu'on retombe sur le moteur ?</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>Le CA gagné est le même nombre — c'est le même lien. Le coût de service, lui, est calculé de deux façons différentes : le moteur pondère campus par campus, le budget applique un taux au réseau. L'écart qui en résulte est affiché, pas gommé.</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>Ce que le geste rapporte</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="n"/>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Le moteur</t>
+        </is>
+      </c>
+      <c r="E94" s="26" t="n"/>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>Le budget 2027</t>
+        </is>
+      </c>
+      <c r="G94" s="26" t="n"/>
+      <c r="H94" s="26" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="I94" s="26" t="n"/>
+      <c r="J94" s="26" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="52" t="inlineStr">
+        <is>
+          <t>CA gagné par le geste</t>
+        </is>
+      </c>
+      <c r="C95" s="121" t="n"/>
+      <c r="D95" s="51">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="E95" s="121" t="n"/>
+      <c r="F95" s="51">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="G95" s="121" t="n"/>
+      <c r="H95" s="152">
+        <f>F95-D95</f>
+        <v/>
+      </c>
+      <c r="I95" s="121" t="n"/>
+      <c r="J95" s="122" t="inlineStr">
+        <is>
+          <t>le même lien — zéro par construction</t>
+        </is>
+      </c>
+      <c r="K95" s="121" t="n"/>
+      <c r="L95" s="121" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="52" t="inlineStr">
+        <is>
+          <t>Coût de servir ces élèves</t>
+        </is>
+      </c>
+      <c r="C96" s="121" t="n"/>
+      <c r="D96" s="51">
+        <f>'Le moteur'!I58*'Le moteur'!K58</f>
+        <v/>
+      </c>
+      <c r="E96" s="121" t="n"/>
+      <c r="F96" s="51">
+        <f>D59*'Le moteur'!I58/'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="G96" s="121" t="n"/>
+      <c r="H96" s="152">
+        <f>F96-D96</f>
+        <v/>
+      </c>
+      <c r="I96" s="121" t="n"/>
+      <c r="J96" s="122" t="inlineStr">
+        <is>
+          <t>consommables du réseau au prorata des inscrits gagnés</t>
+        </is>
+      </c>
+      <c r="K96" s="121" t="n"/>
+      <c r="L96" s="121" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="49" t="inlineStr">
+        <is>
+          <t>EBITDA gagné</t>
+        </is>
+      </c>
+      <c r="C97" s="121" t="n"/>
+      <c r="D97" s="153">
+        <f>'Le moteur'!L58</f>
+        <v/>
+      </c>
+      <c r="E97" s="121" t="n"/>
+      <c r="F97" s="153">
+        <f>F95-(H82-D82)-F96</f>
+        <v/>
+      </c>
+      <c r="G97" s="121" t="n"/>
+      <c r="H97" s="154">
+        <f>F97-D97</f>
+        <v/>
+      </c>
+      <c r="I97" s="121" t="n"/>
+      <c r="J97" s="122" t="inlineStr">
+        <is>
+          <t>CA gagné − Δ budget 6231 − coût de service</t>
+        </is>
+      </c>
+      <c r="K97" s="121" t="n"/>
+      <c r="L97" s="121" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="155">
+        <f>"Le budget 2027 retombe sur l'EBITDA gagné du moteur à "&amp;TEXT(ABS(H97),"#,##0 €")&amp;" près, soit "&amp;TEXT(ABS(H97/D97),"0.00 %")&amp;" — et l'écart a une cause nommée, pas une tolérance."</f>
+        <v/>
+      </c>
+      <c r="C99" s="110" t="n"/>
+      <c r="D99" s="110" t="n"/>
+      <c r="E99" s="110" t="n"/>
+      <c r="F99" s="110" t="n"/>
+      <c r="G99" s="110" t="n"/>
+      <c r="H99" s="110" t="n"/>
+      <c r="I99" s="110" t="n"/>
+      <c r="J99" s="110" t="n"/>
+      <c r="K99" s="110" t="n"/>
+      <c r="L99" s="110" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="156">
+        <f>"2027 : "&amp;TEXT(H88,"#,##0 €")&amp;" d'EBITDA, marge "&amp;TEXT(H89,"0.0 %")&amp;" contre "&amp;TEXT(D89,"0.0 %")&amp;" en 2026. Le gain ne vient d'aucune économie : il vient de "&amp;TEXT(E31-E28,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes — dont "&amp;TEXT(E30,"#,##0")&amp;" que le geste a payés."</f>
+        <v/>
+      </c>
+      <c r="C100" s="112" t="n"/>
+      <c r="D100" s="112" t="n"/>
+      <c r="E100" s="112" t="n"/>
+      <c r="F100" s="112" t="n"/>
+      <c r="G100" s="112" t="n"/>
+      <c r="H100" s="112" t="n"/>
+      <c r="I100" s="112" t="n"/>
+      <c r="J100" s="112" t="n"/>
+      <c r="K100" s="112" t="n"/>
+      <c r="L100" s="112" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="5" t="n"/>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
+      <c r="J103" s="5" t="n"/>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
+      <c r="J104" s="5" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5" t="n"/>
+      <c r="I106" s="5" t="n"/>
+      <c r="J106" s="5" t="n"/>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n"/>
+      <c r="J107" s="5" t="n"/>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n"/>
+      <c r="J108" s="5" t="n"/>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
+      <c r="J109" s="5" t="n"/>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I42:I61">
+  <conditionalFormatting sqref="I60 I61 I63 I65 I66 I67 I69 I70 I71 I73 I74 I75 I76 I77 I78 I79 I80 I82 I83 I85">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Le moteur" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Le coût variable" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Intégration &amp; contrôles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Projection 2027" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget 2027" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Le coût variable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Intégration &amp; contrôles" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%;&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00&quot; €&quot;"/>
@@ -31,9 +31,8 @@
     <numFmt numFmtId="172" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="173" formatCode="+0.00%;-0.00%;&quot;—&quot;"/>
     <numFmt numFmtId="174" formatCode="+0.00%"/>
-    <numFmt numFmtId="175" formatCode="+0.00&quot; pt&quot;;-0.00&quot; pt&quot;"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -203,28 +202,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00007AC3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B7075"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="006B7075"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="005F8A17"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00262626"/>
       <sz val="9"/>
@@ -260,8 +237,31 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="005F8A17"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005F8A17"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B7075"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00B26B00"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00B26B00"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -271,9 +271,33 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00C41822"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B7075"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="006B7075"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00007AC3"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005F8A17"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="10">
@@ -324,7 +348,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -396,14 +420,6 @@
       <top style="thin">
         <color rgb="00007AC3"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00007AC3"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00007AC3"/>
-      </top>
     </border>
     <border>
       <bottom style="thin">
@@ -433,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -563,18 +579,202 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="29" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="34" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="35" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="38" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="43" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -593,9 +793,6 @@
     <xf numFmtId="0" fontId="27" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="171" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -605,12 +802,6 @@
     <xf numFmtId="165" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -620,21 +811,12 @@
     <xf numFmtId="166" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -662,219 +844,58 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="33" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="36" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="38" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="39" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="40" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="41" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="36" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="32" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4203,6 +4224,2619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>EDUSERVICES · le moteur d'acquisition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>BUDGET 2027  —  le CA en quatre lignes, les coûts en six familles</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="3" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>La croissance se défait en deux, et la seconde moitié, c'est le moteur.</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>On sait séparer ce que porte le socle de ce qu'ajoute le budget d'acquisition : +181 élèves en 2026, dont 31,8 dus au +10 % d'acquisition et 149,2 au socle. Le socle se saisit ; le geste, lui, n'est pas saisi — il est LIÉ aux cellules du premier onglet. C'est ce qui fait que ce budget et le moteur disent le même chiffre.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>ⓐ  Les huit saisies  ·  et la neuvième, qui n'en est pas une</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Chacune est une décision, et chacune a un propriétaire. Le Δ budget d'acquisition ne se saisit pas ici : il vient du geste de l'onglet « Le moteur ».</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Saisie</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Valeur retenue</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>D'où elle vient</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>CE QUI FAIT LE CHIFFRE D'AFFAIRES</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>Croissance du socle, hors geste d'acquisition</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="n"/>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="52" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="F13" s="51" t="n"/>
+      <c r="G13" s="53" t="inlineStr">
+        <is>
+          <t>constatée 2026, geste défalqué</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="n"/>
+      <c r="I13" s="51" t="n"/>
+      <c r="J13" s="51" t="n"/>
+      <c r="K13" s="51" t="n"/>
+      <c r="L13" s="51" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>Hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="52" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="n"/>
+      <c r="J14" s="51" t="n"/>
+      <c r="K14" s="51" t="n"/>
+      <c r="L14" s="51" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>Δ budget d'acquisition  (6231)</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="n"/>
+      <c r="D15" s="51" t="n"/>
+      <c r="E15" s="54">
+        <f>'Le moteur'!F4</f>
+        <v/>
+      </c>
+      <c r="F15" s="51" t="n"/>
+      <c r="G15" s="55" t="inlineStr">
+        <is>
+          <t>LIÉ au geste, onglet « Le moteur »</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="n"/>
+      <c r="I15" s="51" t="n"/>
+      <c r="J15" s="51" t="n"/>
+      <c r="K15" s="51" t="n"/>
+      <c r="L15" s="51" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>CE QUI FAIT LES COÛTS</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="50" t="inlineStr">
+        <is>
+          <t>Inflation des charges externes</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="n"/>
+      <c r="D17" s="51" t="n"/>
+      <c r="E17" s="52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F17" s="51" t="n"/>
+      <c r="G17" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="n"/>
+      <c r="I17" s="51" t="n"/>
+      <c r="J17" s="51" t="n"/>
+      <c r="K17" s="51" t="n"/>
+      <c r="L17" s="51" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="50" t="inlineStr">
+        <is>
+          <t>Effort de productivité achats &amp; structure</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="n"/>
+      <c r="D18" s="51" t="n"/>
+      <c r="E18" s="52" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F18" s="51" t="n"/>
+      <c r="G18" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H18" s="51" t="n"/>
+      <c r="I18" s="51" t="n"/>
+      <c r="J18" s="51" t="n"/>
+      <c r="K18" s="51" t="n"/>
+      <c r="L18" s="51" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>Politique salariale sur la masse permanente</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="n"/>
+      <c r="D19" s="51" t="n"/>
+      <c r="E19" s="52" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F19" s="51" t="n"/>
+      <c r="G19" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H19" s="51" t="n"/>
+      <c r="I19" s="51" t="n"/>
+      <c r="J19" s="51" t="n"/>
+      <c r="K19" s="51" t="n"/>
+      <c r="L19" s="51" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="50" t="inlineStr">
+        <is>
+          <t>Variation des effectifs permanents</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H20" s="51" t="n"/>
+      <c r="I20" s="51" t="n"/>
+      <c r="J20" s="51" t="n"/>
+      <c r="K20" s="51" t="n"/>
+      <c r="L20" s="51" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="50" t="inlineStr">
+        <is>
+          <t>Δ budget de marque  (6236)</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="53" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H21" s="51" t="n"/>
+      <c r="I21" s="51" t="n"/>
+      <c r="J21" s="51" t="n"/>
+      <c r="K21" s="51" t="n"/>
+      <c r="L21" s="51" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="50" t="inlineStr">
+        <is>
+          <t>Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="n"/>
+      <c r="D22" s="51" t="n"/>
+      <c r="E22" s="52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="51" t="n"/>
+      <c r="G22" s="53" t="inlineStr">
+        <is>
+          <t>plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="H22" s="51" t="n"/>
+      <c r="I22" s="51" t="n"/>
+      <c r="J22" s="51" t="n"/>
+      <c r="K22" s="51" t="n"/>
+      <c r="L22" s="51" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>ⓑ  Le volume 2027  ·  ce que porte le socle, ce qu'ajoute le geste</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>La ligne « ce que le geste ajoute » n'est pas calculée ici : c'est la cellule I58 de l'onglet « Le moteur ». Bouger F4 là-bas bouge ce budget-ci.</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Grandeur</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="n"/>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>Effectifs 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="n"/>
+      <c r="D28" s="57" t="n"/>
+      <c r="E28" s="58">
+        <f>'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="F28" s="57" t="n"/>
+      <c r="G28" s="59" t="inlineStr">
+        <is>
+          <t>restitué</t>
+        </is>
+      </c>
+      <c r="H28" s="57" t="n"/>
+      <c r="I28" s="57" t="n"/>
+      <c r="J28" s="57" t="n"/>
+      <c r="K28" s="57" t="n"/>
+      <c r="L28" s="57" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="60">
+        <f>E28*$E$13</f>
+        <v/>
+      </c>
+      <c r="F29" s="57" t="n"/>
+      <c r="G29" s="59" t="inlineStr">
+        <is>
+          <t>rétention, passage, notoriété</t>
+        </is>
+      </c>
+      <c r="H29" s="57" t="n"/>
+      <c r="I29" s="57" t="n"/>
+      <c r="J29" s="57" t="n"/>
+      <c r="K29" s="57" t="n"/>
+      <c r="L29" s="57" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>+ ce que le geste ajoute</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="n"/>
+      <c r="D30" s="57" t="n"/>
+      <c r="E30" s="60">
+        <f>'Le moteur'!I58</f>
+        <v/>
+      </c>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — les inscrits gagnés par le Δ budget</t>
+        </is>
+      </c>
+      <c r="H30" s="57" t="n"/>
+      <c r="I30" s="57" t="n"/>
+      <c r="J30" s="57" t="n"/>
+      <c r="K30" s="57" t="n"/>
+      <c r="L30" s="57" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="61">
+        <f> Effectifs 2027</f>
+        <v/>
+      </c>
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="62">
+        <f>E28+E29+E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="59" t="inlineStr"/>
+      <c r="H31" s="57" t="n"/>
+      <c r="I31" s="57" t="n"/>
+      <c r="J31" s="57" t="n"/>
+      <c r="K31" s="57" t="n"/>
+      <c r="L31" s="57" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>Croissance totale</t>
+        </is>
+      </c>
+      <c r="C32" s="57" t="n"/>
+      <c r="D32" s="57" t="n"/>
+      <c r="E32" s="63">
+        <f>IFERROR(E31/E28-1,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="57" t="n"/>
+      <c r="G32" s="59" t="inlineStr">
+        <is>
+          <t>elle n'est pas saisie : elle se déduit</t>
+        </is>
+      </c>
+      <c r="H32" s="57" t="n"/>
+      <c r="I32" s="57" t="n"/>
+      <c r="J32" s="57" t="n"/>
+      <c r="K32" s="57" t="n"/>
+      <c r="L32" s="57" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>Places du réseau</t>
+        </is>
+      </c>
+      <c r="C33" s="57" t="n"/>
+      <c r="D33" s="57" t="n"/>
+      <c r="E33" s="58">
+        <f>'Le moteur'!O34</f>
+        <v/>
+      </c>
+      <c r="F33" s="57" t="n"/>
+      <c r="G33" s="59" t="inlineStr">
+        <is>
+          <t>135 classes, inchangées depuis 2024</t>
+        </is>
+      </c>
+      <c r="H33" s="57" t="n"/>
+      <c r="I33" s="57" t="n"/>
+      <c r="J33" s="57" t="n"/>
+      <c r="K33" s="57" t="n"/>
+      <c r="L33" s="57" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="56" t="inlineStr">
+        <is>
+          <t>Classes 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="57" t="n"/>
+      <c r="D34" s="57" t="n"/>
+      <c r="E34" s="58">
+        <f>'Le moteur'!P34</f>
+        <v/>
+      </c>
+      <c r="F34" s="57" t="n"/>
+      <c r="G34" s="59" t="inlineStr"/>
+      <c r="H34" s="57" t="n"/>
+      <c r="I34" s="57" t="n"/>
+      <c r="J34" s="57" t="n"/>
+      <c r="K34" s="57" t="n"/>
+      <c r="L34" s="57" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="56" t="inlineStr">
+        <is>
+          <t>Capacité moyenne d'une classe</t>
+        </is>
+      </c>
+      <c r="C35" s="57" t="n"/>
+      <c r="D35" s="57" t="n"/>
+      <c r="E35" s="60">
+        <f>IFERROR(E33/E34,0)</f>
+        <v/>
+      </c>
+      <c r="F35" s="57" t="n"/>
+      <c r="G35" s="59" t="inlineStr"/>
+      <c r="H35" s="57" t="n"/>
+      <c r="I35" s="57" t="n"/>
+      <c r="J35" s="57" t="n"/>
+      <c r="K35" s="57" t="n"/>
+      <c r="L35" s="57" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="56" t="inlineStr">
+        <is>
+          <t>Croissance possible avant saturation</t>
+        </is>
+      </c>
+      <c r="C36" s="57" t="n"/>
+      <c r="D36" s="57" t="n"/>
+      <c r="E36" s="64">
+        <f>'Le coût variable'!L48</f>
+        <v/>
+      </c>
+      <c r="F36" s="57" t="n"/>
+      <c r="G36" s="59" t="inlineStr">
+        <is>
+          <t>le premier campus qui sature : MBway Paris</t>
+        </is>
+      </c>
+      <c r="H36" s="57" t="n"/>
+      <c r="I36" s="57" t="n"/>
+      <c r="J36" s="57" t="n"/>
+      <c r="K36" s="57" t="n"/>
+      <c r="L36" s="57" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>Classes à ouvrir en 2027</t>
+        </is>
+      </c>
+      <c r="C37" s="57" t="n"/>
+      <c r="D37" s="57" t="n"/>
+      <c r="E37" s="65">
+        <f>MAX(0,ROUNDUP((E31-E33)/E35,0))</f>
+        <v/>
+      </c>
+      <c r="F37" s="57" t="n"/>
+      <c r="G37" s="59" t="inlineStr">
+        <is>
+          <t>aucune — et c'est toute la démonstration</t>
+        </is>
+      </c>
+      <c r="H37" s="57" t="n"/>
+      <c r="I37" s="57" t="n"/>
+      <c r="J37" s="57" t="n"/>
+      <c r="K37" s="57" t="n"/>
+      <c r="L37" s="57" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="56" t="inlineStr">
+        <is>
+          <t>Classes 2027</t>
+        </is>
+      </c>
+      <c r="C38" s="57" t="n"/>
+      <c r="D38" s="57" t="n"/>
+      <c r="E38" s="58">
+        <f>E34+E37</f>
+        <v/>
+      </c>
+      <c r="F38" s="57" t="n"/>
+      <c r="G38" s="59" t="inlineStr"/>
+      <c r="H38" s="57" t="n"/>
+      <c r="I38" s="57" t="n"/>
+      <c r="J38" s="57" t="n"/>
+      <c r="K38" s="57" t="n"/>
+      <c r="L38" s="57" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>Inducteur du compte 621</t>
+        </is>
+      </c>
+      <c r="C39" s="57" t="n"/>
+      <c r="D39" s="57" t="n"/>
+      <c r="E39" s="66">
+        <f>IFERROR(E38/E34,0)</f>
+        <v/>
+      </c>
+      <c r="F39" s="57" t="n"/>
+      <c r="G39" s="59" t="inlineStr">
+        <is>
+          <t>le ratio de CLASSES, jamais celui des effectifs</t>
+        </is>
+      </c>
+      <c r="H39" s="57" t="n"/>
+      <c r="I39" s="57" t="n"/>
+      <c r="J39" s="57" t="n"/>
+      <c r="K39" s="57" t="n"/>
+      <c r="L39" s="57" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>À +6 % l'an, MBway Paris tient jusqu'en 2029. Vérifiable ligne à ligne : onglet « Le coût variable », dernière colonne du tableau campus.</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>ⓒ  Le chiffre d'affaires 2027  ·  quatre lignes, et une seule est une décision</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Le socle est déjà inscrit, le geste est celui du moteur, le prix est un arbitrage. Rien d'autre n'entre dans le CA.</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Ligne</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="56" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="57" t="n"/>
+      <c r="D47" s="57" t="n"/>
+      <c r="E47" s="67" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="F47" s="57" t="n"/>
+      <c r="G47" s="59" t="inlineStr">
+        <is>
+          <t>restitué · 706 + 7062 + 708</t>
+        </is>
+      </c>
+      <c r="H47" s="57" t="n"/>
+      <c r="I47" s="57" t="n"/>
+      <c r="J47" s="57" t="n"/>
+      <c r="K47" s="57" t="n"/>
+      <c r="L47" s="57" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="56" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C48" s="57" t="n"/>
+      <c r="D48" s="57" t="n"/>
+      <c r="E48" s="67">
+        <f>E47*$E$13</f>
+        <v/>
+      </c>
+      <c r="F48" s="57" t="n"/>
+      <c r="G48" s="59" t="inlineStr">
+        <is>
+          <t>la rentrée déjà engagée</t>
+        </is>
+      </c>
+      <c r="H48" s="57" t="n"/>
+      <c r="I48" s="57" t="n"/>
+      <c r="J48" s="57" t="n"/>
+      <c r="K48" s="57" t="n"/>
+      <c r="L48" s="57" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="56" t="inlineStr">
+        <is>
+          <t>+ ce que le geste ajoute</t>
+        </is>
+      </c>
+      <c r="C49" s="57" t="n"/>
+      <c r="D49" s="57" t="n"/>
+      <c r="E49" s="67">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="F49" s="57" t="n"/>
+      <c r="G49" s="59" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — le CA gagné par le Δ budget</t>
+        </is>
+      </c>
+      <c r="H49" s="57" t="n"/>
+      <c r="I49" s="57" t="n"/>
+      <c r="J49" s="57" t="n"/>
+      <c r="K49" s="57" t="n"/>
+      <c r="L49" s="57" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="56" t="inlineStr">
+        <is>
+          <t>+ effet prix</t>
+        </is>
+      </c>
+      <c r="C50" s="57" t="n"/>
+      <c r="D50" s="57" t="n"/>
+      <c r="E50" s="67">
+        <f>(E47+E48+E49)*$E$14</f>
+        <v/>
+      </c>
+      <c r="F50" s="57" t="n"/>
+      <c r="G50" s="59" t="inlineStr">
+        <is>
+          <t>la hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="H50" s="57" t="n"/>
+      <c r="I50" s="57" t="n"/>
+      <c r="J50" s="57" t="n"/>
+      <c r="K50" s="57" t="n"/>
+      <c r="L50" s="57" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="61">
+        <f> Chiffre d'affaires 2027</f>
+        <v/>
+      </c>
+      <c r="C51" s="57" t="n"/>
+      <c r="D51" s="57" t="n"/>
+      <c r="E51" s="68">
+        <f>SUM(E47:E50)</f>
+        <v/>
+      </c>
+      <c r="F51" s="57" t="n"/>
+      <c r="G51" s="59" t="inlineStr"/>
+      <c r="H51" s="57" t="n"/>
+      <c r="I51" s="57" t="n"/>
+      <c r="J51" s="57" t="n"/>
+      <c r="K51" s="57" t="n"/>
+      <c r="L51" s="57" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="69">
+        <f>"Sur "&amp;TEXT(E51-E47,"#,##0 €")&amp;" de croissance, "&amp;TEXT(E48/(E51-E47),"0 %")&amp;" viennent du socle déjà inscrit, "&amp;TEXT(E49/(E51-E47),"0 %")&amp;" du geste d'acquisition et "&amp;TEXT(E50/(E51-E47),"0 %")&amp;" du prix. Le chiffre d'affaires ne se décrète pas."</f>
+        <v/>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="38" t="inlineStr">
+        <is>
+          <t>ⓓ  Les coûts de CAMPUS  ·  six familles, six règles</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Un budget qui indexe tout au même taux ne dit rien. Celui-ci donne à chaque euro l'inducteur de son comportement — et c'est ce qui fait apparaître où est le levier, et surtout où il n'est pas.</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Famille · compte</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui la fait bouger</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>Effet volume</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>Effet prix</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2027</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>Variation</t>
+        </is>
+      </c>
+      <c r="J58" s="26" t="inlineStr">
+        <is>
+          <t>Bouge si un élève de plus arrive ?</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="70" t="inlineStr">
+        <is>
+          <t>①  Suit l'ÉLÈVE</t>
+        </is>
+      </c>
+      <c r="C59" s="70" t="n"/>
+      <c r="D59" s="71">
+        <f>SUM(D60:D61)</f>
+        <v/>
+      </c>
+      <c r="E59" s="72" t="inlineStr">
+        <is>
+          <t>effectifs × inflation</t>
+        </is>
+      </c>
+      <c r="F59" s="73" t="inlineStr"/>
+      <c r="G59" s="73" t="inlineStr"/>
+      <c r="H59" s="71">
+        <f>SUM(H60:H61)</f>
+        <v/>
+      </c>
+      <c r="I59" s="74">
+        <f>IFERROR(H59/D59-1,0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="75" t="inlineStr">
+        <is>
+          <t>OUI — le seul euro qui suive vraiment l'élève</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      604 · Achats d'études et supports pédagogiques</t>
+        </is>
+      </c>
+      <c r="C60" s="77" t="n"/>
+      <c r="D60" s="78" t="n">
+        <v>677808</v>
+      </c>
+      <c r="E60" s="79" t="inlineStr"/>
+      <c r="F60" s="80">
+        <f>$E$31/$E$28</f>
+        <v/>
+      </c>
+      <c r="G60" s="80">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H60" s="78">
+        <f>D60*F60*G60</f>
+        <v/>
+      </c>
+      <c r="I60" s="81">
+        <f>IFERROR(H60/D60-1,0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="77" t="inlineStr"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6063 · Fournitures pédagogiques et administratives</t>
+        </is>
+      </c>
+      <c r="C61" s="77" t="n"/>
+      <c r="D61" s="78" t="n">
+        <v>451874</v>
+      </c>
+      <c r="E61" s="79" t="inlineStr"/>
+      <c r="F61" s="80">
+        <f>$E$31/$E$28</f>
+        <v/>
+      </c>
+      <c r="G61" s="80">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H61" s="78">
+        <f>D61*F61*G61</f>
+        <v/>
+      </c>
+      <c r="I61" s="81">
+        <f>IFERROR(H61/D61-1,0)</f>
+        <v/>
+      </c>
+      <c r="J61" s="77" t="inlineStr"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="70" t="inlineStr">
+        <is>
+          <t>②  Suit la CLASSE</t>
+        </is>
+      </c>
+      <c r="C62" s="70" t="n"/>
+      <c r="D62" s="71">
+        <f>SUM(D63:D63)</f>
+        <v/>
+      </c>
+      <c r="E62" s="82" t="inlineStr">
+        <is>
+          <t>classes × inflation</t>
+        </is>
+      </c>
+      <c r="F62" s="73" t="inlineStr"/>
+      <c r="G62" s="73" t="inlineStr"/>
+      <c r="H62" s="71">
+        <f>SUM(H63:H63)</f>
+        <v/>
+      </c>
+      <c r="I62" s="83">
+        <f>IFERROR(H62/D62-1,0)</f>
+        <v/>
+      </c>
+      <c r="J62" s="84" t="inlineStr">
+        <is>
+          <t>seulement si une classe doit ouvrir</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      621 · Personnel extérieur — enseignants vacataires</t>
+        </is>
+      </c>
+      <c r="C63" s="77" t="n"/>
+      <c r="D63" s="78" t="n">
+        <v>1581554</v>
+      </c>
+      <c r="E63" s="79" t="inlineStr"/>
+      <c r="F63" s="80">
+        <f>$E$39</f>
+        <v/>
+      </c>
+      <c r="G63" s="80">
+        <f>1+$E$17</f>
+        <v/>
+      </c>
+      <c r="H63" s="78">
+        <f>D63*F63*G63</f>
+        <v/>
+      </c>
+      <c r="I63" s="81">
+        <f>IFERROR(H63/D63-1,0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="77" t="inlineStr"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="70" t="inlineStr">
+        <is>
+          <t>③  Suit les POSTES</t>
+        </is>
+      </c>
+      <c r="C64" s="70" t="n"/>
+      <c r="D64" s="71">
+        <f>SUM(D65:D66)</f>
+        <v/>
+      </c>
+      <c r="E64" s="85" t="inlineStr">
+        <is>
+          <t>politique salariale, + les postes créés</t>
+        </is>
+      </c>
+      <c r="F64" s="73" t="inlineStr"/>
+      <c r="G64" s="73" t="inlineStr"/>
+      <c r="H64" s="71">
+        <f>SUM(H65:H66)</f>
+        <v/>
+      </c>
+      <c r="I64" s="86">
+        <f>IFERROR(H64/D64-1,0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="87" t="inlineStr">
+        <is>
+          <t>NON — le poste est engagé à l'année</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6411 · Salaires — enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C65" s="77" t="n"/>
+      <c r="D65" s="78" t="n">
+        <v>3841069.84</v>
+      </c>
+      <c r="E65" s="79" t="inlineStr"/>
+      <c r="F65" s="80">
+        <f>1+$E$20</f>
+        <v/>
+      </c>
+      <c r="G65" s="80">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H65" s="78">
+        <f>D65*F65*G65</f>
+        <v/>
+      </c>
+      <c r="I65" s="81">
+        <f>IFERROR(H65/D65-1,0)</f>
+        <v/>
+      </c>
+      <c r="J65" s="77" t="inlineStr"/>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6413 · Salaires — personnel administratif des campus</t>
+        </is>
+      </c>
+      <c r="C66" s="77" t="n"/>
+      <c r="D66" s="78" t="n">
+        <v>2033330.6</v>
+      </c>
+      <c r="E66" s="79" t="inlineStr"/>
+      <c r="F66" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="80">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H66" s="78">
+        <f>D66*F66*G66</f>
+        <v/>
+      </c>
+      <c r="I66" s="81">
+        <f>IFERROR(H66/D66-1,0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="77" t="inlineStr"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="70" t="inlineStr">
+        <is>
+          <t>④  Assis sur la MASSE</t>
+        </is>
+      </c>
+      <c r="C67" s="70" t="n"/>
+      <c r="D67" s="71">
+        <f>SUM(D68:D68)</f>
+        <v/>
+      </c>
+      <c r="E67" s="85" t="inlineStr">
+        <is>
+          <t>au prorata de la masse salariale des campus</t>
+        </is>
+      </c>
+      <c r="F67" s="73" t="inlineStr"/>
+      <c r="G67" s="73" t="inlineStr"/>
+      <c r="H67" s="71">
+        <f>SUM(H68:H68)</f>
+        <v/>
+      </c>
+      <c r="I67" s="86">
+        <f>IFERROR(H67/D67-1,0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="87" t="inlineStr">
+        <is>
+          <t>NON — elle suit la masse, pas l'élève</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      645 · Charges sociales sur les salaires</t>
+        </is>
+      </c>
+      <c r="C68" s="77" t="n"/>
+      <c r="D68" s="78" t="n">
+        <v>3162957.9</v>
+      </c>
+      <c r="E68" s="79" t="inlineStr"/>
+      <c r="F68" s="80">
+        <f>(H65+H66)/(D65+D66)</f>
+        <v/>
+      </c>
+      <c r="G68" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="78">
+        <f>D68*F68*G68</f>
+        <v/>
+      </c>
+      <c r="I68" s="81">
+        <f>IFERROR(H68/D68-1,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="77" t="inlineStr"/>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="70" t="inlineStr">
+        <is>
+          <t>⑤  INDEXÉ</t>
+        </is>
+      </c>
+      <c r="C69" s="70" t="n"/>
+      <c r="D69" s="71">
+        <f>SUM(D70:D74)</f>
+        <v/>
+      </c>
+      <c r="E69" s="88" t="inlineStr">
+        <is>
+          <t>inflation moins l'effort de productivité</t>
+        </is>
+      </c>
+      <c r="F69" s="73" t="inlineStr"/>
+      <c r="G69" s="73" t="inlineStr"/>
+      <c r="H69" s="71">
+        <f>SUM(H70:H74)</f>
+        <v/>
+      </c>
+      <c r="I69" s="89">
+        <f>IFERROR(H69/D69-1,0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="90" t="inlineStr">
+        <is>
+          <t>NON — c'est le mur qui coûte, pas l'élève</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      613 · Locations immobilières des campus</t>
+        </is>
+      </c>
+      <c r="C70" s="77" t="n"/>
+      <c r="D70" s="78" t="n">
+        <v>2372423.51</v>
+      </c>
+      <c r="E70" s="79" t="inlineStr"/>
+      <c r="F70" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="80">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H70" s="78">
+        <f>D70*F70*G70</f>
+        <v/>
+      </c>
+      <c r="I70" s="81">
+        <f>IFERROR(H70/D70-1,0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="77" t="inlineStr"/>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      615 · Entretien et réparations</t>
+        </is>
+      </c>
+      <c r="C71" s="77" t="n"/>
+      <c r="D71" s="78" t="n">
+        <v>338915.38</v>
+      </c>
+      <c r="E71" s="79" t="inlineStr"/>
+      <c r="F71" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="80">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H71" s="78">
+        <f>D71*F71*G71</f>
+        <v/>
+      </c>
+      <c r="I71" s="81">
+        <f>IFERROR(H71/D71-1,0)</f>
+        <v/>
+      </c>
+      <c r="J71" s="77" t="inlineStr"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      616 · Primes d'assurance</t>
+        </is>
+      </c>
+      <c r="C72" s="77" t="n"/>
+      <c r="D72" s="78" t="n">
+        <v>225926.43</v>
+      </c>
+      <c r="E72" s="79" t="inlineStr"/>
+      <c r="F72" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="80">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H72" s="78">
+        <f>D72*F72*G72</f>
+        <v/>
+      </c>
+      <c r="I72" s="81">
+        <f>IFERROR(H72/D72-1,0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="77" t="inlineStr"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      625 · Déplacements, missions et réceptions</t>
+        </is>
+      </c>
+      <c r="C73" s="77" t="n"/>
+      <c r="D73" s="78" t="n">
+        <v>338890.38</v>
+      </c>
+      <c r="E73" s="79" t="inlineStr"/>
+      <c r="F73" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="80">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H73" s="78">
+        <f>D73*F73*G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="81">
+        <f>IFERROR(H73/D73-1,0)</f>
+        <v/>
+      </c>
+      <c r="J73" s="77" t="inlineStr"/>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      63511 · Contribution économique territoriale</t>
+        </is>
+      </c>
+      <c r="C74" s="77" t="n"/>
+      <c r="D74" s="78" t="n">
+        <v>225943.95</v>
+      </c>
+      <c r="E74" s="79" t="inlineStr"/>
+      <c r="F74" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="80">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H74" s="78">
+        <f>D74*F74*G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="81">
+        <f>IFERROR(H74/D74-1,0)</f>
+        <v/>
+      </c>
+      <c r="J74" s="77" t="inlineStr"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="70" t="inlineStr">
+        <is>
+          <t>⑥  DÉCIDÉ</t>
+        </is>
+      </c>
+      <c r="C75" s="70" t="n"/>
+      <c r="D75" s="71">
+        <f>SUM(D76:D76)</f>
+        <v/>
+      </c>
+      <c r="E75" s="91" t="inlineStr">
+        <is>
+          <t>le geste lui-même</t>
+        </is>
+      </c>
+      <c r="F75" s="73" t="inlineStr"/>
+      <c r="G75" s="73" t="inlineStr"/>
+      <c r="H75" s="71">
+        <f>SUM(H76:H76)</f>
+        <v/>
+      </c>
+      <c r="I75" s="92">
+        <f>IFERROR(H75/D75-1,0)</f>
+        <v/>
+      </c>
+      <c r="J75" s="93" t="inlineStr">
+        <is>
+          <t>c'est la saisie elle-même</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6231 · Annonces et insertions — budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C76" s="77" t="n"/>
+      <c r="D76" s="78" t="n">
+        <v>434174</v>
+      </c>
+      <c r="E76" s="79" t="inlineStr"/>
+      <c r="F76" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="80">
+        <f>1+$E$15</f>
+        <v/>
+      </c>
+      <c r="H76" s="78">
+        <f>D76*F76*G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="81">
+        <f>IFERROR(H76/D76-1,0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="77" t="inlineStr"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="70" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES DE CAMPUS</t>
+        </is>
+      </c>
+      <c r="C77" s="70" t="n"/>
+      <c r="D77" s="71">
+        <f>D59+D62+D64+D67+D69+D75</f>
+        <v/>
+      </c>
+      <c r="E77" s="70" t="inlineStr"/>
+      <c r="F77" s="73" t="inlineStr"/>
+      <c r="G77" s="73" t="inlineStr"/>
+      <c r="H77" s="71">
+        <f>H59+H62+H64+H67+H69+H75</f>
+        <v/>
+      </c>
+      <c r="I77" s="94">
+        <f>IFERROR(H77/D77-1,0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="70" t="inlineStr"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="95" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="C78" s="95" t="n"/>
+      <c r="D78" s="96" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="E78" s="95" t="inlineStr"/>
+      <c r="F78" s="97" t="inlineStr"/>
+      <c r="G78" s="97" t="inlineStr"/>
+      <c r="H78" s="96">
+        <f>E51</f>
+        <v/>
+      </c>
+      <c r="I78" s="98">
+        <f>IFERROR(H78/D78-1,0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="95" t="inlineStr">
+        <is>
+          <t>bloc ⓒ ci-dessus</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>EBITDA PROPRE  ·  avant quote-part du siège</t>
+        </is>
+      </c>
+      <c r="C79" s="70" t="n"/>
+      <c r="D79" s="99">
+        <f>D78-D77</f>
+        <v/>
+      </c>
+      <c r="E79" s="70" t="inlineStr"/>
+      <c r="F79" s="73" t="inlineStr"/>
+      <c r="G79" s="73" t="inlineStr"/>
+      <c r="H79" s="99">
+        <f>H78-H77</f>
+        <v/>
+      </c>
+      <c r="I79" s="94">
+        <f>IFERROR(H79/D79-1,0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="70" t="inlineStr">
+        <is>
+          <t>ce que les campus produisent</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="100" t="inlineStr">
+        <is>
+          <t>LE SIÈGE  ·  il ne suit aucun inducteur d'activité — il se décide, puis se cascade</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6236 · Catalogues et imprimés — marketing de marque</t>
+        </is>
+      </c>
+      <c r="C82" s="102" t="n"/>
+      <c r="D82" s="67" t="n">
+        <v>676344</v>
+      </c>
+      <c r="E82" s="59" t="inlineStr">
+        <is>
+          <t>décidé — cascade K4</t>
+        </is>
+      </c>
+      <c r="F82" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="66">
+        <f>1+$E$21</f>
+        <v/>
+      </c>
+      <c r="H82" s="67">
+        <f>D82*F82*G82</f>
+        <v/>
+      </c>
+      <c r="I82" s="103">
+        <f>IFERROR(H82/D82-1,0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="102" t="inlineStr"/>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6414 · Salaires du siège</t>
+        </is>
+      </c>
+      <c r="C83" s="102" t="n"/>
+      <c r="D83" s="67" t="n">
+        <v>1242649</v>
+      </c>
+      <c r="E83" s="59" t="inlineStr">
+        <is>
+          <t>politique salariale</t>
+        </is>
+      </c>
+      <c r="F83" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="66">
+        <f>1+$E$19</f>
+        <v/>
+      </c>
+      <c r="H83" s="67">
+        <f>D83*F83*G83</f>
+        <v/>
+      </c>
+      <c r="I83" s="103">
+        <f>IFERROR(H83/D83-1,0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="102" t="inlineStr"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6226 · Honoraires</t>
+        </is>
+      </c>
+      <c r="C84" s="102" t="n"/>
+      <c r="D84" s="67" t="n">
+        <v>564841</v>
+      </c>
+      <c r="E84" s="59" t="inlineStr"/>
+      <c r="F84" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="66">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H84" s="67">
+        <f>D84*F84*G84</f>
+        <v/>
+      </c>
+      <c r="I84" s="103">
+        <f>IFERROR(H84/D84-1,0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="102" t="inlineStr"/>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      626 · Frais postaux et de télécommunications</t>
+        </is>
+      </c>
+      <c r="C85" s="102" t="n"/>
+      <c r="D85" s="67" t="n">
+        <v>451872</v>
+      </c>
+      <c r="E85" s="59" t="inlineStr"/>
+      <c r="F85" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="66">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H85" s="67">
+        <f>D85*F85*G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="103">
+        <f>IFERROR(H85/D85-1,0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="102" t="inlineStr"/>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6281 · Cotisations et concours divers</t>
+        </is>
+      </c>
+      <c r="C86" s="102" t="n"/>
+      <c r="D86" s="67" t="n">
+        <v>180749</v>
+      </c>
+      <c r="E86" s="59" t="inlineStr"/>
+      <c r="F86" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="66">
+        <f>1+$E$17-$E$18</f>
+        <v/>
+      </c>
+      <c r="H86" s="67">
+        <f>D86*F86*G86</f>
+        <v/>
+      </c>
+      <c r="I86" s="103">
+        <f>IFERROR(H86/D86-1,0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="102" t="inlineStr"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6331 · Versement mobilité</t>
+        </is>
+      </c>
+      <c r="C87" s="102" t="n"/>
+      <c r="D87" s="67" t="n">
+        <v>338904</v>
+      </c>
+      <c r="E87" s="59" t="inlineStr">
+        <is>
+          <t>assis sur la masse</t>
+        </is>
+      </c>
+      <c r="F87" s="66">
+        <f>(H65+H66+H83)/(D65+D66+D83)</f>
+        <v/>
+      </c>
+      <c r="G87" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="67">
+        <f>D87*F87*G87</f>
+        <v/>
+      </c>
+      <c r="I87" s="103">
+        <f>IFERROR(H87/D87-1,0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="102" t="inlineStr"/>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6333 · Participation à la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="C88" s="102" t="n"/>
+      <c r="D88" s="67" t="n">
+        <v>112968</v>
+      </c>
+      <c r="E88" s="59" t="inlineStr">
+        <is>
+          <t>assis sur la masse</t>
+        </is>
+      </c>
+      <c r="F88" s="66">
+        <f>(H65+H66+H83)/(D65+D66+D83)</f>
+        <v/>
+      </c>
+      <c r="G88" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="67">
+        <f>D88*F88*G88</f>
+        <v/>
+      </c>
+      <c r="I88" s="103">
+        <f>IFERROR(H88/D88-1,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="102" t="inlineStr"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="70" t="inlineStr">
+        <is>
+          <t>QUOTE-PART DU SIÈGE  ·  6236 + 6414 + 6226 + 626 + 6281 + 6331 + 6333</t>
+        </is>
+      </c>
+      <c r="C89" s="70" t="n"/>
+      <c r="D89" s="71">
+        <f>D82+D83+D84+D85+D86+D87+D88</f>
+        <v/>
+      </c>
+      <c r="E89" s="70" t="inlineStr"/>
+      <c r="F89" s="73" t="inlineStr"/>
+      <c r="G89" s="73" t="inlineStr"/>
+      <c r="H89" s="71">
+        <f>H82+H83+H84+H85+H86+H87+H88</f>
+        <v/>
+      </c>
+      <c r="I89" s="94">
+        <f>IFERROR(H89/D89-1,0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="70" t="inlineStr">
+        <is>
+          <t>cascades K1 et K4</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="70" t="inlineStr">
+        <is>
+          <t>EBITDA NET  ·  celui du groupe</t>
+        </is>
+      </c>
+      <c r="C91" s="70" t="n"/>
+      <c r="D91" s="104">
+        <f>D79-D89</f>
+        <v/>
+      </c>
+      <c r="E91" s="70" t="inlineStr"/>
+      <c r="F91" s="73" t="inlineStr"/>
+      <c r="G91" s="73" t="inlineStr"/>
+      <c r="H91" s="104">
+        <f>H79-H89</f>
+        <v/>
+      </c>
+      <c r="I91" s="94">
+        <f>IFERROR(H91/D91-1,0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="70" t="inlineStr">
+        <is>
+          <t>dotations exclues</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="61" t="inlineStr">
+        <is>
+          <t>Marge — propre  ·  nette</t>
+        </is>
+      </c>
+      <c r="C92" s="61" t="n"/>
+      <c r="D92" s="105">
+        <f>IFERROR(D79/D78,0)</f>
+        <v/>
+      </c>
+      <c r="E92" s="61" t="inlineStr"/>
+      <c r="F92" s="106" t="inlineStr"/>
+      <c r="G92" s="106" t="inlineStr"/>
+      <c r="H92" s="105">
+        <f>IFERROR(H79/H78,0)</f>
+        <v/>
+      </c>
+      <c r="I92" s="107" t="n"/>
+      <c r="J92" s="61">
+        <f>"nette : "&amp;TEXT(D91/D78,"0.0 %")&amp;"  →  "&amp;TEXT(H91/H78,"0.0 %")</f>
+        <v/>
+      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6811 · Dotations aux amortissements  ·  sous la ligne d'EBITDA</t>
+        </is>
+      </c>
+      <c r="C94" s="102" t="n"/>
+      <c r="D94" s="67" t="n">
+        <v>1352683</v>
+      </c>
+      <c r="E94" s="59" t="inlineStr">
+        <is>
+          <t>hors modèle</t>
+        </is>
+      </c>
+      <c r="F94" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="66">
+        <f>1+$E$22</f>
+        <v/>
+      </c>
+      <c r="H94" s="67">
+        <f>D94*F94*G94</f>
+        <v/>
+      </c>
+      <c r="I94" s="103">
+        <f>IFERROR(H94/D94-1,0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="102" t="inlineStr"/>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="23" t="inlineStr">
+        <is>
+          <t>ⓔ  Est-ce qu'on retombe sur le moteur ?</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="24" t="inlineStr">
+        <is>
+          <t>Le CA gagné est le même nombre — c'est le même lien. Le coût de service, lui, est calculé de deux façons : le moteur pondère campus par campus, le budget applique un taux au réseau. L'écart qui en résulte est affiché, pas gommé.</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="5" t="n"/>
+      <c r="J99" s="5" t="n"/>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="n"/>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Ce que le geste rapporte</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="n"/>
+      <c r="D100" s="26" t="inlineStr">
+        <is>
+          <t>Le moteur</t>
+        </is>
+      </c>
+      <c r="E100" s="26" t="n"/>
+      <c r="F100" s="26" t="inlineStr">
+        <is>
+          <t>Le budget 2027</t>
+        </is>
+      </c>
+      <c r="G100" s="26" t="n"/>
+      <c r="H100" s="26" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="I100" s="26" t="n"/>
+      <c r="J100" s="26" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="102" t="inlineStr">
+        <is>
+          <t>CA gagné par le geste</t>
+        </is>
+      </c>
+      <c r="C101" s="57" t="n"/>
+      <c r="D101" s="67">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="E101" s="57" t="n"/>
+      <c r="F101" s="67">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="G101" s="57" t="n"/>
+      <c r="H101" s="108">
+        <f>F101-D101</f>
+        <v/>
+      </c>
+      <c r="I101" s="57" t="n"/>
+      <c r="J101" s="59" t="inlineStr">
+        <is>
+          <t>le même lien — zéro par construction</t>
+        </is>
+      </c>
+      <c r="K101" s="57" t="n"/>
+      <c r="L101" s="57" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+      <c r="B102" s="102" t="inlineStr">
+        <is>
+          <t>Coût de servir ces élèves</t>
+        </is>
+      </c>
+      <c r="C102" s="57" t="n"/>
+      <c r="D102" s="67">
+        <f>'Le moteur'!I58*'Le moteur'!K58</f>
+        <v/>
+      </c>
+      <c r="E102" s="57" t="n"/>
+      <c r="F102" s="67">
+        <f>D59*'Le moteur'!I58/'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="G102" s="57" t="n"/>
+      <c r="H102" s="108">
+        <f>F102-D102</f>
+        <v/>
+      </c>
+      <c r="I102" s="57" t="n"/>
+      <c r="J102" s="59" t="inlineStr">
+        <is>
+          <t>consommables du réseau au prorata des inscrits gagnés</t>
+        </is>
+      </c>
+      <c r="K102" s="57" t="n"/>
+      <c r="L102" s="57" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="61" t="inlineStr">
+        <is>
+          <t>EBITDA gagné</t>
+        </is>
+      </c>
+      <c r="C103" s="57" t="n"/>
+      <c r="D103" s="109">
+        <f>'Le moteur'!L58</f>
+        <v/>
+      </c>
+      <c r="E103" s="57" t="n"/>
+      <c r="F103" s="109">
+        <f>F101-(H76-D76)-F102</f>
+        <v/>
+      </c>
+      <c r="G103" s="57" t="n"/>
+      <c r="H103" s="110">
+        <f>F103-D103</f>
+        <v/>
+      </c>
+      <c r="I103" s="57" t="n"/>
+      <c r="J103" s="59" t="inlineStr">
+        <is>
+          <t>CA gagné − Δ budget 6231 − coût de service</t>
+        </is>
+      </c>
+      <c r="K103" s="57" t="n"/>
+      <c r="L103" s="57" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
+      <c r="J104" s="5" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="111">
+        <f>"Le budget 2027 retombe sur l'EBITDA gagné du moteur à "&amp;TEXT(ABS(H103),"#,##0 €")&amp;" près, soit "&amp;TEXT(ABS(H103/D103),"0.00 %")&amp;" — et l'écart a une cause nommée, pas une tolérance."</f>
+        <v/>
+      </c>
+      <c r="C105" s="112" t="n"/>
+      <c r="D105" s="112" t="n"/>
+      <c r="E105" s="112" t="n"/>
+      <c r="F105" s="112" t="n"/>
+      <c r="G105" s="112" t="n"/>
+      <c r="H105" s="112" t="n"/>
+      <c r="I105" s="112" t="n"/>
+      <c r="J105" s="112" t="n"/>
+      <c r="K105" s="112" t="n"/>
+      <c r="L105" s="112" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="113">
+        <f>"2027 : marge propre "&amp;TEXT(D79/D78,"0.0 %")&amp;" → "&amp;TEXT(H79/H78,"0.0 %")&amp;",  marge nette "&amp;TEXT(D91/D78,"0.0 %")&amp;" → "&amp;TEXT(H91/H78,"0.0 %")&amp;".  La nette gagne plus que la propre : ce n'est pas une performance de campus, c'est le siège qui se dilue — il croît de "&amp;TEXT(H89/D89-1,"0.0 %")&amp;" quand le CA croît de "&amp;TEXT(H78/D78-1,"0.0 %")&amp;"."</f>
+        <v/>
+      </c>
+      <c r="C106" s="13" t="n"/>
+      <c r="D106" s="13" t="n"/>
+      <c r="E106" s="13" t="n"/>
+      <c r="F106" s="13" t="n"/>
+      <c r="G106" s="13" t="n"/>
+      <c r="H106" s="13" t="n"/>
+      <c r="I106" s="13" t="n"/>
+      <c r="J106" s="13" t="n"/>
+      <c r="K106" s="13" t="n"/>
+      <c r="L106" s="13" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="114">
+        <f>"Le gain ne vient d'aucune économie : il vient de "&amp;TEXT(E31-E28,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes — dont "&amp;TEXT(E30,"#,##0")&amp;" que le geste a payés."</f>
+        <v/>
+      </c>
+      <c r="C107" s="115" t="n"/>
+      <c r="D107" s="115" t="n"/>
+      <c r="E107" s="115" t="n"/>
+      <c r="F107" s="115" t="n"/>
+      <c r="G107" s="115" t="n"/>
+      <c r="H107" s="115" t="n"/>
+      <c r="I107" s="115" t="n"/>
+      <c r="J107" s="115" t="n"/>
+      <c r="K107" s="115" t="n"/>
+      <c r="L107" s="115" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n"/>
+      <c r="J108" s="5" t="n"/>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I60 I61 I63 I65 I66 I68 I70 I71 I72 I73 I74 I76">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00DCEBC0"/>
+        <color rgb="00F7F7F5"/>
+        <color rgb="00F6C9CC"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4452,36 +7086,36 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>Consommables</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="116" t="inlineStr">
         <is>
           <t>604 + 6063</t>
         </is>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="67">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr">
+      <c r="E12" s="102" t="inlineStr">
         <is>
           <t>EFFECTIFS</t>
         </is>
       </c>
-      <c r="F12" s="52" t="inlineStr">
+      <c r="F12" s="102" t="inlineStr">
         <is>
           <t>le campus</t>
         </is>
       </c>
-      <c r="G12" s="53" t="inlineStr">
+      <c r="G12" s="117" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="H12" s="54" t="inlineStr">
+      <c r="H12" s="118" t="inlineStr">
         <is>
           <t>OUI — c'est le seul euro qui suit vraiment l'élève</t>
         </is>
@@ -4495,36 +7129,36 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>Vacataires</t>
         </is>
       </c>
-      <c r="C13" s="50" t="inlineStr">
+      <c r="C13" s="116" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="67">
         <f>'Le moteur'!S34</f>
         <v/>
       </c>
-      <c r="E13" s="52" t="inlineStr">
+      <c r="E13" s="102" t="inlineStr">
         <is>
           <t>HEURES</t>
         </is>
       </c>
-      <c r="F13" s="52" t="inlineStr">
+      <c r="F13" s="102" t="inlineStr">
         <is>
           <t>le programme</t>
         </is>
       </c>
-      <c r="G13" s="55" t="inlineStr">
+      <c r="G13" s="119" t="inlineStr">
         <is>
           <t>SEMI-VARIABLE</t>
         </is>
       </c>
-      <c r="H13" s="56" t="inlineStr">
+      <c r="H13" s="120" t="inlineStr">
         <is>
           <t>Seulement si la classe doit ouvrir</t>
         </is>
@@ -4538,36 +7172,36 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>Enseignants permanents</t>
         </is>
       </c>
-      <c r="C14" s="50" t="inlineStr">
+      <c r="C14" s="116" t="inlineStr">
         <is>
           <t>6411</t>
         </is>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="67">
         <f>'Le moteur'!T34</f>
         <v/>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E14" s="102" t="inlineStr">
         <is>
           <t>HEURES</t>
         </is>
       </c>
-      <c r="F14" s="52" t="inlineStr">
+      <c r="F14" s="102" t="inlineStr">
         <is>
           <t>le nombre de postes</t>
         </is>
       </c>
-      <c r="G14" s="57" t="inlineStr">
+      <c r="G14" s="121" t="inlineStr">
         <is>
           <t>CAPACITÉ</t>
         </is>
       </c>
-      <c r="H14" s="58" t="inlineStr">
+      <c r="H14" s="122" t="inlineStr">
         <is>
           <t>NON — payé pareil pour 24 ou 32 élèves dans la salle</t>
         </is>
@@ -4737,33 +7371,33 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C22" s="59" t="n">
+      <c r="C22" s="58" t="n">
         <v>840</v>
       </c>
-      <c r="D22" s="60" t="n">
+      <c r="D22" s="123" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F22" s="62">
+      <c r="F22" s="125">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="G22" s="51" t="n">
+      <c r="G22" s="67" t="n">
         <v>372.0952843881691</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="125">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="63">
+      <c r="I22" s="103">
         <f>IFERROR(H22/$H$26-1,0)</f>
         <v/>
       </c>
@@ -4775,33 +7409,33 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C23" s="59" t="n">
+      <c r="C23" s="58" t="n">
         <v>1688</v>
       </c>
-      <c r="D23" s="60" t="n">
+      <c r="D23" s="123" t="n">
         <v>21.04265402843602</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="125">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="G23" s="51" t="n">
+      <c r="G23" s="67" t="n">
         <v>361.8303545853921</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="125">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="103">
         <f>IFERROR(H23/$H$26-1,0)</f>
         <v/>
       </c>
@@ -4813,33 +7447,33 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C24" s="59" t="n">
+      <c r="C24" s="58" t="n">
         <v>424</v>
       </c>
-      <c r="D24" s="60" t="n">
+      <c r="D24" s="123" t="n">
         <v>24.05660377358491</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="125">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="G24" s="51" t="n">
+      <c r="G24" s="67" t="n">
         <v>372.0952832735557</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="125">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="63">
+      <c r="I24" s="103">
         <f>IFERROR(H24/$H$26-1,0)</f>
         <v/>
       </c>
@@ -4851,33 +7485,33 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C25" s="59" t="n">
+      <c r="C25" s="58" t="n">
         <v>162</v>
       </c>
-      <c r="D25" s="60" t="n">
+      <c r="D25" s="123" t="n">
         <v>34.5679012345679</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="125">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="G25" s="51" t="n">
+      <c r="G25" s="67" t="n">
         <v>299.900755961781</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="125">
         <f>F25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="63">
+      <c r="I25" s="103">
         <f>IFERROR(H25/$H$26-1,0)</f>
         <v/>
       </c>
@@ -4889,36 +7523,36 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="64" t="inlineStr">
+      <c r="B26" s="70" t="inlineStr">
         <is>
           <t>MOYENNE PONDÉRÉE</t>
         </is>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="126">
         <f>SUM(C22:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="127">
         <f>IFERROR('Le moteur'!Q34/C26,0)</f>
         <v/>
       </c>
-      <c r="E26" s="67">
+      <c r="E26" s="128">
         <f>IFERROR('Le moteur'!S34/'Le moteur'!Q34,0)</f>
         <v/>
       </c>
-      <c r="F26" s="68">
+      <c r="F26" s="71">
         <f>D26*E26</f>
         <v/>
       </c>
-      <c r="G26" s="68">
+      <c r="G26" s="71">
         <f>IFERROR(SUMPRODUCT(C22:C25,G22:G25)/C26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="68">
+      <c r="H26" s="71">
         <f>F26+G26</f>
         <v/>
       </c>
-      <c r="I26" s="69" t="inlineStr">
+      <c r="I26" s="94" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4947,7 +7581,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="70">
+      <c r="B28" s="129">
         <f>"Un facteur "&amp;TEXT(MAX(H22:H25)/MIN(H22:H25),"0.00")&amp;" entre les extrêmes. Le coût variable « moyen » du réseau — "&amp;TEXT(H26,"#,##0 €")&amp;" — ne décrit aucun élève réel : il cadre, il ne décide pas."</f>
         <v/>
       </c>
@@ -5098,48 +7732,48 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="49" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Montpellier</t>
         </is>
       </c>
-      <c r="C34" s="59">
+      <c r="C34" s="58">
         <f>'Le moteur'!N20</f>
         <v/>
       </c>
-      <c r="D34" s="59">
+      <c r="D34" s="58">
         <f>'Le moteur'!G44</f>
         <v/>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="67">
         <f>'Le moteur'!R20</f>
         <v/>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="67">
         <f>IFERROR(E34/C34,0)</f>
         <v/>
       </c>
-      <c r="G34" s="71">
+      <c r="G34" s="130">
         <f>'Le moteur'!Q20</f>
         <v/>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="67">
         <f>'Le moteur'!S20</f>
         <v/>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="67">
         <f>IFERROR(H34/'Le moteur'!O20,0)</f>
         <v/>
       </c>
-      <c r="J34" s="51">
+      <c r="J34" s="67">
         <f>'Le moteur'!T20</f>
         <v/>
       </c>
-      <c r="K34" s="51">
+      <c r="K34" s="67">
         <f>IFERROR(J34/C34,0)</f>
         <v/>
       </c>
-      <c r="L34" s="72">
+      <c r="L34" s="64">
         <f>IFERROR(D34/C34,0)</f>
         <v/>
       </c>
@@ -5148,48 +7782,48 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Nantes</t>
         </is>
       </c>
-      <c r="C35" s="59">
+      <c r="C35" s="58">
         <f>'Le moteur'!N21</f>
         <v/>
       </c>
-      <c r="D35" s="59">
+      <c r="D35" s="58">
         <f>'Le moteur'!G45</f>
         <v/>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="67">
         <f>'Le moteur'!R21</f>
         <v/>
       </c>
-      <c r="F35" s="51">
+      <c r="F35" s="67">
         <f>IFERROR(E35/C35,0)</f>
         <v/>
       </c>
-      <c r="G35" s="71">
+      <c r="G35" s="130">
         <f>'Le moteur'!Q21</f>
         <v/>
       </c>
-      <c r="H35" s="51">
+      <c r="H35" s="67">
         <f>'Le moteur'!S21</f>
         <v/>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="67">
         <f>IFERROR(H35/'Le moteur'!O21,0)</f>
         <v/>
       </c>
-      <c r="J35" s="51">
+      <c r="J35" s="67">
         <f>'Le moteur'!T21</f>
         <v/>
       </c>
-      <c r="K35" s="51">
+      <c r="K35" s="67">
         <f>IFERROR(J35/C35,0)</f>
         <v/>
       </c>
-      <c r="L35" s="72">
+      <c r="L35" s="64">
         <f>IFERROR(D35/C35,0)</f>
         <v/>
       </c>
@@ -5198,48 +7832,48 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="49" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Rennes</t>
         </is>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="58">
         <f>'Le moteur'!N22</f>
         <v/>
       </c>
-      <c r="D36" s="59">
+      <c r="D36" s="58">
         <f>'Le moteur'!G46</f>
         <v/>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="67">
         <f>'Le moteur'!R22</f>
         <v/>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="67">
         <f>IFERROR(E36/C36,0)</f>
         <v/>
       </c>
-      <c r="G36" s="71">
+      <c r="G36" s="130">
         <f>'Le moteur'!Q22</f>
         <v/>
       </c>
-      <c r="H36" s="51">
+      <c r="H36" s="67">
         <f>'Le moteur'!S22</f>
         <v/>
       </c>
-      <c r="I36" s="51">
+      <c r="I36" s="67">
         <f>IFERROR(H36/'Le moteur'!O22,0)</f>
         <v/>
       </c>
-      <c r="J36" s="51">
+      <c r="J36" s="67">
         <f>'Le moteur'!T22</f>
         <v/>
       </c>
-      <c r="K36" s="51">
+      <c r="K36" s="67">
         <f>IFERROR(J36/C36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="72">
+      <c r="L36" s="64">
         <f>IFERROR(D36/C36,0)</f>
         <v/>
       </c>
@@ -5248,48 +7882,48 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>ISCOM Lille</t>
         </is>
       </c>
-      <c r="C37" s="59">
+      <c r="C37" s="58">
         <f>'Le moteur'!N23</f>
         <v/>
       </c>
-      <c r="D37" s="59">
+      <c r="D37" s="58">
         <f>'Le moteur'!G47</f>
         <v/>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="67">
         <f>'Le moteur'!R23</f>
         <v/>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="67">
         <f>IFERROR(E37/C37,0)</f>
         <v/>
       </c>
-      <c r="G37" s="71">
+      <c r="G37" s="130">
         <f>'Le moteur'!Q23</f>
         <v/>
       </c>
-      <c r="H37" s="51">
+      <c r="H37" s="67">
         <f>'Le moteur'!S23</f>
         <v/>
       </c>
-      <c r="I37" s="51">
+      <c r="I37" s="67">
         <f>IFERROR(H37/'Le moteur'!O23,0)</f>
         <v/>
       </c>
-      <c r="J37" s="51">
+      <c r="J37" s="67">
         <f>'Le moteur'!T23</f>
         <v/>
       </c>
-      <c r="K37" s="51">
+      <c r="K37" s="67">
         <f>IFERROR(J37/C37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="72">
+      <c r="L37" s="64">
         <f>IFERROR(D37/C37,0)</f>
         <v/>
       </c>
@@ -5298,48 +7932,48 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>ISCOM Paris</t>
         </is>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="58">
         <f>'Le moteur'!N24</f>
         <v/>
       </c>
-      <c r="D38" s="59">
+      <c r="D38" s="58">
         <f>'Le moteur'!G48</f>
         <v/>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="67">
         <f>'Le moteur'!R24</f>
         <v/>
       </c>
-      <c r="F38" s="51">
+      <c r="F38" s="67">
         <f>IFERROR(E38/C38,0)</f>
         <v/>
       </c>
-      <c r="G38" s="71">
+      <c r="G38" s="130">
         <f>'Le moteur'!Q24</f>
         <v/>
       </c>
-      <c r="H38" s="51">
+      <c r="H38" s="67">
         <f>'Le moteur'!S24</f>
         <v/>
       </c>
-      <c r="I38" s="51">
+      <c r="I38" s="67">
         <f>IFERROR(H38/'Le moteur'!O24,0)</f>
         <v/>
       </c>
-      <c r="J38" s="51">
+      <c r="J38" s="67">
         <f>'Le moteur'!T24</f>
         <v/>
       </c>
-      <c r="K38" s="51">
+      <c r="K38" s="67">
         <f>IFERROR(J38/C38,0)</f>
         <v/>
       </c>
-      <c r="L38" s="72">
+      <c r="L38" s="64">
         <f>IFERROR(D38/C38,0)</f>
         <v/>
       </c>
@@ -5348,48 +7982,48 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="49" t="inlineStr">
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>ISCOM Toulouse</t>
         </is>
       </c>
-      <c r="C39" s="59">
+      <c r="C39" s="58">
         <f>'Le moteur'!N25</f>
         <v/>
       </c>
-      <c r="D39" s="59">
+      <c r="D39" s="58">
         <f>'Le moteur'!G49</f>
         <v/>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="67">
         <f>'Le moteur'!R25</f>
         <v/>
       </c>
-      <c r="F39" s="51">
+      <c r="F39" s="67">
         <f>IFERROR(E39/C39,0)</f>
         <v/>
       </c>
-      <c r="G39" s="71">
+      <c r="G39" s="130">
         <f>'Le moteur'!Q25</f>
         <v/>
       </c>
-      <c r="H39" s="51">
+      <c r="H39" s="67">
         <f>'Le moteur'!S25</f>
         <v/>
       </c>
-      <c r="I39" s="51">
+      <c r="I39" s="67">
         <f>IFERROR(H39/'Le moteur'!O25,0)</f>
         <v/>
       </c>
-      <c r="J39" s="51">
+      <c r="J39" s="67">
         <f>'Le moteur'!T25</f>
         <v/>
       </c>
-      <c r="K39" s="51">
+      <c r="K39" s="67">
         <f>IFERROR(J39/C39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="72">
+      <c r="L39" s="64">
         <f>IFERROR(D39/C39,0)</f>
         <v/>
       </c>
@@ -5398,48 +8032,48 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="49" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>MBway Bordeaux</t>
         </is>
       </c>
-      <c r="C40" s="59">
+      <c r="C40" s="58">
         <f>'Le moteur'!N26</f>
         <v/>
       </c>
-      <c r="D40" s="59">
+      <c r="D40" s="58">
         <f>'Le moteur'!G50</f>
         <v/>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="67">
         <f>'Le moteur'!R26</f>
         <v/>
       </c>
-      <c r="F40" s="51">
+      <c r="F40" s="67">
         <f>IFERROR(E40/C40,0)</f>
         <v/>
       </c>
-      <c r="G40" s="71">
+      <c r="G40" s="130">
         <f>'Le moteur'!Q26</f>
         <v/>
       </c>
-      <c r="H40" s="51">
+      <c r="H40" s="67">
         <f>'Le moteur'!S26</f>
         <v/>
       </c>
-      <c r="I40" s="51">
+      <c r="I40" s="67">
         <f>IFERROR(H40/'Le moteur'!O26,0)</f>
         <v/>
       </c>
-      <c r="J40" s="51">
+      <c r="J40" s="67">
         <f>'Le moteur'!T26</f>
         <v/>
       </c>
-      <c r="K40" s="51">
+      <c r="K40" s="67">
         <f>IFERROR(J40/C40,0)</f>
         <v/>
       </c>
-      <c r="L40" s="72">
+      <c r="L40" s="64">
         <f>IFERROR(D40/C40,0)</f>
         <v/>
       </c>
@@ -5448,48 +8082,48 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="49" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>MBway Lyon</t>
         </is>
       </c>
-      <c r="C41" s="59">
+      <c r="C41" s="58">
         <f>'Le moteur'!N27</f>
         <v/>
       </c>
-      <c r="D41" s="59">
+      <c r="D41" s="58">
         <f>'Le moteur'!G51</f>
         <v/>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="67">
         <f>'Le moteur'!R27</f>
         <v/>
       </c>
-      <c r="F41" s="51">
+      <c r="F41" s="67">
         <f>IFERROR(E41/C41,0)</f>
         <v/>
       </c>
-      <c r="G41" s="71">
+      <c r="G41" s="130">
         <f>'Le moteur'!Q27</f>
         <v/>
       </c>
-      <c r="H41" s="51">
+      <c r="H41" s="67">
         <f>'Le moteur'!S27</f>
         <v/>
       </c>
-      <c r="I41" s="51">
+      <c r="I41" s="67">
         <f>IFERROR(H41/'Le moteur'!O27,0)</f>
         <v/>
       </c>
-      <c r="J41" s="51">
+      <c r="J41" s="67">
         <f>'Le moteur'!T27</f>
         <v/>
       </c>
-      <c r="K41" s="51">
+      <c r="K41" s="67">
         <f>IFERROR(J41/C41,0)</f>
         <v/>
       </c>
-      <c r="L41" s="72">
+      <c r="L41" s="64">
         <f>IFERROR(D41/C41,0)</f>
         <v/>
       </c>
@@ -5498,48 +8132,48 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="49" t="inlineStr">
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>MBway Nantes</t>
         </is>
       </c>
-      <c r="C42" s="59">
+      <c r="C42" s="58">
         <f>'Le moteur'!N28</f>
         <v/>
       </c>
-      <c r="D42" s="59">
+      <c r="D42" s="58">
         <f>'Le moteur'!G52</f>
         <v/>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="67">
         <f>'Le moteur'!R28</f>
         <v/>
       </c>
-      <c r="F42" s="51">
+      <c r="F42" s="67">
         <f>IFERROR(E42/C42,0)</f>
         <v/>
       </c>
-      <c r="G42" s="71">
+      <c r="G42" s="130">
         <f>'Le moteur'!Q28</f>
         <v/>
       </c>
-      <c r="H42" s="51">
+      <c r="H42" s="67">
         <f>'Le moteur'!S28</f>
         <v/>
       </c>
-      <c r="I42" s="51">
+      <c r="I42" s="67">
         <f>IFERROR(H42/'Le moteur'!O28,0)</f>
         <v/>
       </c>
-      <c r="J42" s="51">
+      <c r="J42" s="67">
         <f>'Le moteur'!T28</f>
         <v/>
       </c>
-      <c r="K42" s="51">
+      <c r="K42" s="67">
         <f>IFERROR(J42/C42,0)</f>
         <v/>
       </c>
-      <c r="L42" s="72">
+      <c r="L42" s="64">
         <f>IFERROR(D42/C42,0)</f>
         <v/>
       </c>
@@ -5548,48 +8182,48 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="49" t="inlineStr">
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>MBway Paris</t>
         </is>
       </c>
-      <c r="C43" s="59">
+      <c r="C43" s="58">
         <f>'Le moteur'!N29</f>
         <v/>
       </c>
-      <c r="D43" s="59">
+      <c r="D43" s="58">
         <f>'Le moteur'!G53</f>
         <v/>
       </c>
-      <c r="E43" s="51">
+      <c r="E43" s="67">
         <f>'Le moteur'!R29</f>
         <v/>
       </c>
-      <c r="F43" s="51">
+      <c r="F43" s="67">
         <f>IFERROR(E43/C43,0)</f>
         <v/>
       </c>
-      <c r="G43" s="71">
+      <c r="G43" s="130">
         <f>'Le moteur'!Q29</f>
         <v/>
       </c>
-      <c r="H43" s="51">
+      <c r="H43" s="67">
         <f>'Le moteur'!S29</f>
         <v/>
       </c>
-      <c r="I43" s="51">
+      <c r="I43" s="67">
         <f>IFERROR(H43/'Le moteur'!O29,0)</f>
         <v/>
       </c>
-      <c r="J43" s="51">
+      <c r="J43" s="67">
         <f>'Le moteur'!T29</f>
         <v/>
       </c>
-      <c r="K43" s="51">
+      <c r="K43" s="67">
         <f>IFERROR(J43/C43,0)</f>
         <v/>
       </c>
-      <c r="L43" s="72">
+      <c r="L43" s="64">
         <f>IFERROR(D43/C43,0)</f>
         <v/>
       </c>
@@ -5598,48 +8232,48 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="49" t="inlineStr">
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>Pigier Bordeaux</t>
         </is>
       </c>
-      <c r="C44" s="59">
+      <c r="C44" s="58">
         <f>'Le moteur'!N30</f>
         <v/>
       </c>
-      <c r="D44" s="59">
+      <c r="D44" s="58">
         <f>'Le moteur'!G54</f>
         <v/>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="67">
         <f>'Le moteur'!R30</f>
         <v/>
       </c>
-      <c r="F44" s="51">
+      <c r="F44" s="67">
         <f>IFERROR(E44/C44,0)</f>
         <v/>
       </c>
-      <c r="G44" s="71">
+      <c r="G44" s="130">
         <f>'Le moteur'!Q30</f>
         <v/>
       </c>
-      <c r="H44" s="51">
+      <c r="H44" s="67">
         <f>'Le moteur'!S30</f>
         <v/>
       </c>
-      <c r="I44" s="51">
+      <c r="I44" s="67">
         <f>IFERROR(H44/'Le moteur'!O30,0)</f>
         <v/>
       </c>
-      <c r="J44" s="51">
+      <c r="J44" s="67">
         <f>'Le moteur'!T30</f>
         <v/>
       </c>
-      <c r="K44" s="51">
+      <c r="K44" s="67">
         <f>IFERROR(J44/C44,0)</f>
         <v/>
       </c>
-      <c r="L44" s="72">
+      <c r="L44" s="64">
         <f>IFERROR(D44/C44,0)</f>
         <v/>
       </c>
@@ -5648,48 +8282,48 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="49" t="inlineStr">
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>Pigier Lyon</t>
         </is>
       </c>
-      <c r="C45" s="59">
+      <c r="C45" s="58">
         <f>'Le moteur'!N31</f>
         <v/>
       </c>
-      <c r="D45" s="59">
+      <c r="D45" s="58">
         <f>'Le moteur'!G55</f>
         <v/>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="67">
         <f>'Le moteur'!R31</f>
         <v/>
       </c>
-      <c r="F45" s="51">
+      <c r="F45" s="67">
         <f>IFERROR(E45/C45,0)</f>
         <v/>
       </c>
-      <c r="G45" s="71">
+      <c r="G45" s="130">
         <f>'Le moteur'!Q31</f>
         <v/>
       </c>
-      <c r="H45" s="51">
+      <c r="H45" s="67">
         <f>'Le moteur'!S31</f>
         <v/>
       </c>
-      <c r="I45" s="51">
+      <c r="I45" s="67">
         <f>IFERROR(H45/'Le moteur'!O31,0)</f>
         <v/>
       </c>
-      <c r="J45" s="51">
+      <c r="J45" s="67">
         <f>'Le moteur'!T31</f>
         <v/>
       </c>
-      <c r="K45" s="51">
+      <c r="K45" s="67">
         <f>IFERROR(J45/C45,0)</f>
         <v/>
       </c>
-      <c r="L45" s="72">
+      <c r="L45" s="64">
         <f>IFERROR(D45/C45,0)</f>
         <v/>
       </c>
@@ -5698,48 +8332,48 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="49" t="inlineStr">
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>Tunon Lyon</t>
         </is>
       </c>
-      <c r="C46" s="59">
+      <c r="C46" s="58">
         <f>'Le moteur'!N32</f>
         <v/>
       </c>
-      <c r="D46" s="59">
+      <c r="D46" s="58">
         <f>'Le moteur'!G56</f>
         <v/>
       </c>
-      <c r="E46" s="51">
+      <c r="E46" s="67">
         <f>'Le moteur'!R32</f>
         <v/>
       </c>
-      <c r="F46" s="51">
+      <c r="F46" s="67">
         <f>IFERROR(E46/C46,0)</f>
         <v/>
       </c>
-      <c r="G46" s="71">
+      <c r="G46" s="130">
         <f>'Le moteur'!Q32</f>
         <v/>
       </c>
-      <c r="H46" s="51">
+      <c r="H46" s="67">
         <f>'Le moteur'!S32</f>
         <v/>
       </c>
-      <c r="I46" s="51">
+      <c r="I46" s="67">
         <f>IFERROR(H46/'Le moteur'!O32,0)</f>
         <v/>
       </c>
-      <c r="J46" s="51">
+      <c r="J46" s="67">
         <f>'Le moteur'!T32</f>
         <v/>
       </c>
-      <c r="K46" s="51">
+      <c r="K46" s="67">
         <f>IFERROR(J46/C46,0)</f>
         <v/>
       </c>
-      <c r="L46" s="72">
+      <c r="L46" s="64">
         <f>IFERROR(D46/C46,0)</f>
         <v/>
       </c>
@@ -5748,48 +8382,48 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="49" t="inlineStr">
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>Tunon Paris</t>
         </is>
       </c>
-      <c r="C47" s="59">
+      <c r="C47" s="58">
         <f>'Le moteur'!N33</f>
         <v/>
       </c>
-      <c r="D47" s="59">
+      <c r="D47" s="58">
         <f>'Le moteur'!G57</f>
         <v/>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="67">
         <f>'Le moteur'!R33</f>
         <v/>
       </c>
-      <c r="F47" s="51">
+      <c r="F47" s="67">
         <f>IFERROR(E47/C47,0)</f>
         <v/>
       </c>
-      <c r="G47" s="71">
+      <c r="G47" s="130">
         <f>'Le moteur'!Q33</f>
         <v/>
       </c>
-      <c r="H47" s="51">
+      <c r="H47" s="67">
         <f>'Le moteur'!S33</f>
         <v/>
       </c>
-      <c r="I47" s="51">
+      <c r="I47" s="67">
         <f>IFERROR(H47/'Le moteur'!O33,0)</f>
         <v/>
       </c>
-      <c r="J47" s="51">
+      <c r="J47" s="67">
         <f>'Le moteur'!T33</f>
         <v/>
       </c>
-      <c r="K47" s="51">
+      <c r="K47" s="67">
         <f>IFERROR(J47/C47,0)</f>
         <v/>
       </c>
-      <c r="L47" s="72">
+      <c r="L47" s="64">
         <f>IFERROR(D47/C47,0)</f>
         <v/>
       </c>
@@ -5798,48 +8432,48 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="64" t="inlineStr">
+      <c r="B48" s="70" t="inlineStr">
         <is>
           <t>GROUPE · 14 campus</t>
         </is>
       </c>
-      <c r="C48" s="65">
+      <c r="C48" s="126">
         <f>SUM(C34:C47)</f>
         <v/>
       </c>
-      <c r="D48" s="65">
+      <c r="D48" s="126">
         <f>SUM(D34:D47)</f>
         <v/>
       </c>
-      <c r="E48" s="68">
+      <c r="E48" s="71">
         <f>SUM(E34:E47)</f>
         <v/>
       </c>
-      <c r="F48" s="68">
+      <c r="F48" s="71">
         <f>IFERROR(E48/C48,0)</f>
         <v/>
       </c>
-      <c r="G48" s="73">
+      <c r="G48" s="131">
         <f>SUM(G34:G47)</f>
         <v/>
       </c>
-      <c r="H48" s="68">
+      <c r="H48" s="71">
         <f>SUM(H34:H47)</f>
         <v/>
       </c>
-      <c r="I48" s="68">
+      <c r="I48" s="71">
         <f>IFERROR(H48/'Le moteur'!O34,0)</f>
         <v/>
       </c>
-      <c r="J48" s="68">
+      <c r="J48" s="71">
         <f>SUM(J34:J47)</f>
         <v/>
       </c>
-      <c r="K48" s="68">
+      <c r="K48" s="71">
         <f>IFERROR(J48/C48,0)</f>
         <v/>
       </c>
-      <c r="L48" s="74">
+      <c r="L48" s="132">
         <f>MIN(L34:L47)</f>
         <v/>
       </c>
@@ -5868,7 +8502,7 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="70">
+      <c r="B50" s="129">
         <f>"Les permanents pèsent "&amp;TEXT(J48/(E48+H48+J48),"0 %")&amp;" du coût d'enseignement du réseau, et pas un euro d'entre eux ne bouge quand un élève de plus s'assoit."</f>
         <v/>
       </c>
@@ -5959,13 +8593,13 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="75" t="inlineStr">
+      <c r="B55" s="133" t="inlineStr">
         <is>
           <t>TANT QU'IL RESTE UNE PLACE</t>
         </is>
       </c>
       <c r="C55" s="21" t="n"/>
-      <c r="D55" s="76">
+      <c r="D55" s="134">
         <f>"les consommables seuls  —  de "&amp;TEXT(MIN(F34:F47),"#,##0 €")&amp;" à "&amp;TEXT(MAX(F34:F47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -5982,13 +8616,13 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="77" t="inlineStr">
+      <c r="B56" s="135" t="inlineStr">
         <is>
           <t>QUAND LA CLASSE EST PLEINE</t>
         </is>
       </c>
       <c r="C56" s="13" t="n"/>
-      <c r="D56" s="78" t="inlineStr">
+      <c r="D56" s="136" t="inlineStr">
         <is>
           <t>+ la quote-part du vacataire d'une classe neuve  —  et là, le programme compte</t>
         </is>
@@ -6008,7 +8642,7 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="19" t="n"/>
       <c r="C57" s="19" t="n"/>
-      <c r="D57" s="79" t="inlineStr">
+      <c r="D57" s="137" t="inlineStr">
         <is>
           <t>Le masque bascule seul : IF(inscrits gagnés &lt;= places libres ; consommables ; consommables + vacataires du campus ÷ places du campus).</t>
         </is>
@@ -6102,32 +8736,32 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
-      <c r="B61" s="49" t="inlineStr">
+      <c r="B61" s="61" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C61" s="71">
+      <c r="C61" s="130">
         <f>'Intégration &amp; contrôles'!C9</f>
         <v/>
       </c>
-      <c r="D61" s="61">
+      <c r="D61" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E61" s="51">
+      <c r="E61" s="67">
         <f>C61*D61</f>
         <v/>
       </c>
-      <c r="F61" s="59">
+      <c r="F61" s="58">
         <f>'Intégration &amp; contrôles'!D9</f>
         <v/>
       </c>
-      <c r="G61" s="62">
+      <c r="G61" s="125">
         <f>E61/F61</f>
         <v/>
       </c>
-      <c r="H61" s="80">
+      <c r="H61" s="138">
         <f>"de "&amp;TEXT(G61+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G61+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6140,32 +8774,32 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
-      <c r="B62" s="49" t="inlineStr">
+      <c r="B62" s="61" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C62" s="71">
+      <c r="C62" s="130">
         <f>'Intégration &amp; contrôles'!C13</f>
         <v/>
       </c>
-      <c r="D62" s="61">
+      <c r="D62" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E62" s="51">
+      <c r="E62" s="67">
         <f>C62*D62</f>
         <v/>
       </c>
-      <c r="F62" s="59">
+      <c r="F62" s="58">
         <f>'Intégration &amp; contrôles'!D13</f>
         <v/>
       </c>
-      <c r="G62" s="62">
+      <c r="G62" s="125">
         <f>E62/F62</f>
         <v/>
       </c>
-      <c r="H62" s="80">
+      <c r="H62" s="138">
         <f>"de "&amp;TEXT(G62+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G62+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6178,32 +8812,32 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
-      <c r="B63" s="49" t="inlineStr">
+      <c r="B63" s="61" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C63" s="71">
+      <c r="C63" s="130">
         <f>'Intégration &amp; contrôles'!C10</f>
         <v/>
       </c>
-      <c r="D63" s="61">
+      <c r="D63" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E63" s="51">
+      <c r="E63" s="67">
         <f>C63*D63</f>
         <v/>
       </c>
-      <c r="F63" s="59">
+      <c r="F63" s="58">
         <f>'Intégration &amp; contrôles'!D10</f>
         <v/>
       </c>
-      <c r="G63" s="62">
+      <c r="G63" s="125">
         <f>E63/F63</f>
         <v/>
       </c>
-      <c r="H63" s="80">
+      <c r="H63" s="138">
         <f>"de "&amp;TEXT(G63+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G63+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6216,32 +8850,32 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="49" t="inlineStr">
+      <c r="B64" s="61" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C64" s="71">
+      <c r="C64" s="130">
         <f>'Intégration &amp; contrôles'!C11</f>
         <v/>
       </c>
-      <c r="D64" s="61">
+      <c r="D64" s="124">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E64" s="51">
+      <c r="E64" s="67">
         <f>C64*D64</f>
         <v/>
       </c>
-      <c r="F64" s="59">
+      <c r="F64" s="58">
         <f>'Intégration &amp; contrôles'!D11</f>
         <v/>
       </c>
-      <c r="G64" s="62">
+      <c r="G64" s="125">
         <f>E64/F64</f>
         <v/>
       </c>
-      <c r="H64" s="80">
+      <c r="H64" s="138">
         <f>"de "&amp;TEXT(G64+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G64+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -6306,7 +8940,7 @@
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="81" t="inlineStr">
+      <c r="B68" s="139" t="inlineStr">
         <is>
           <t>⑤  Et les enseignants permanents, ils sont où ?</t>
         </is>
@@ -6328,7 +8962,7 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>Dans le modèle, et alloués à l'heure comme les vacataires — mais pas dans le coût variable. Voici les vingt comptes de charges du P&amp;L et, pour chacun, la seule question qui compte.</t>
+          <t>Dans le modèle, et alloués à l'heure comme les vacataires — mais jamais dans le coût marginal.</t>
         </is>
       </c>
       <c r="C69" s="5" t="n"/>
@@ -6344,100 +8978,75 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="n"/>
     </row>
-    <row r="70" ht="16" customHeight="1">
+    <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="82" t="inlineStr">
-        <is>
-          <t>Un professeur permanent est un ENGAGEMENT DE CAPACITÉ, pas un coût à l'élève : il est payé pareil que la salle contienne 24 ou 32 étudiants. C'est pour cela qu'il pèse le plus lourd du coût d'enseignement et qu'il ne figure quand même pas dans le coût marginal. Le vacataire, lui, est la seule ressource enseignante que l'on achète à la classe — et le 621 est du personnel EXTÉRIEUR : une facture, donc sans charges sociales 645 en plus.</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="n"/>
+      <c r="B70" s="134" t="inlineStr">
+        <is>
+          <t>Un professeur permanent est un ENGAGEMENT DE CAPACITÉ, pas un coût à l'élève : il est payé pareil que la salle contienne 24 ou 32 étudiants. Il varie avec le nombre de POSTES — donc par palier, et le palier suivant n'est pas une classe, c'est un campus.</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="21" t="n"/>
+      <c r="E70" s="21" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="21" t="n"/>
+      <c r="M70" s="21" t="n"/>
+      <c r="N70" s="21" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="n"/>
+      <c r="B71" s="136" t="inlineStr">
+        <is>
+          <t>Le vacataire est la seule ressource enseignante qui s'achète à la classe. Et le 621 est du personnel EXTÉRIEUR : une facture, donc sans charges sociales 645 en plus, contrairement au 6411.</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="13" t="n"/>
+      <c r="H71" s="13" t="n"/>
+      <c r="I71" s="13" t="n"/>
+      <c r="J71" s="13" t="n"/>
+      <c r="K71" s="13" t="n"/>
+      <c r="L71" s="13" t="n"/>
+      <c r="M71" s="13" t="n"/>
+      <c r="N71" s="13" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>Ces montants sont restitués par la COMPTABILITÉ (AW_002_000004_000001), et non repris du tableau ① : c'est ce qui permet de les réconcilier avec la vue — quatre contrôles, onglet « Intégration &amp; contrôles ».</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="n"/>
-    </row>
-    <row r="73" ht="30" customHeight="1">
+      <c r="B72" s="140">
+        <f>"Sur "&amp;TEXT('Budget 2027'!D77+'Budget 2027'!D89+'Budget 2027'!D94,"#,##0 €")&amp;" de charges, "&amp;TEXT('Budget 2027'!D59,"#,##0 €")&amp;" seulement bougent quand un élève de plus s'assoit — soit "&amp;TEXT('Budget 2027'!D59/('Budget 2027'!D77+'Budget 2027'!D89+'Budget 2027'!D94),"0.0 %")&amp;". Tout le reste est de la capacité déjà engagée : c'est ce qui rend le geste aussi rentable tant qu'il reste des places."</f>
+        <v/>
+      </c>
+      <c r="C72" s="19" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="19" t="n"/>
+      <c r="G72" s="19" t="n"/>
+      <c r="H72" s="19" t="n"/>
+      <c r="I72" s="19" t="n"/>
+      <c r="J72" s="19" t="n"/>
+      <c r="K72" s="19" t="n"/>
+      <c r="L72" s="19" t="n"/>
+      <c r="M72" s="19" t="n"/>
+      <c r="N72" s="19" t="n"/>
+    </row>
+    <row r="73">
       <c r="A73" s="5" t="n"/>
-      <c r="B73" s="25" t="inlineStr">
-        <is>
-          <t>Compte et libellé</t>
-        </is>
-      </c>
-      <c r="C73" s="26" t="n"/>
-      <c r="D73" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2026</t>
-        </is>
-      </c>
-      <c r="E73" s="26" t="inlineStr">
-        <is>
-          <t>Part des charges</t>
-        </is>
-      </c>
-      <c r="F73" s="26" t="inlineStr">
-        <is>
-          <t>Poche du modèle</t>
-        </is>
-      </c>
-      <c r="G73" s="26" t="inlineStr">
-        <is>
-          <t>Clé d'allocation</t>
-        </is>
-      </c>
-      <c r="H73" s="26" t="inlineStr">
-        <is>
-          <t>Comportement</t>
-        </is>
-      </c>
-      <c r="I73" s="26" t="inlineStr">
-        <is>
-          <t>Bouge si un élève de plus arrive ?</t>
-        </is>
-      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="5" t="n"/>
@@ -6446,39 +9055,18 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="49" t="inlineStr">
-        <is>
-          <t>604 · Achats d'études et supports pédagogiques</t>
-        </is>
-      </c>
-      <c r="C74" s="52" t="n"/>
-      <c r="D74" s="51" t="n">
-        <v>677808</v>
-      </c>
-      <c r="E74" s="72">
-        <f>IFERROR(D74/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F74" s="52" t="inlineStr">
-        <is>
-          <t>COST_ODIR</t>
-        </is>
-      </c>
-      <c r="G74" s="52" t="inlineStr">
-        <is>
-          <t>EFFECTIFS</t>
-        </is>
-      </c>
-      <c r="H74" s="53" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="I74" s="54" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>Le détail des vingt comptes — chacun avec son comportement et son inducteur — est dans l'onglet « Budget 2027 ». Il n'est pas dupliqué ici.</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="n"/>
@@ -6487,39 +9075,14 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="49" t="inlineStr">
-        <is>
-          <t>6063 · Fournitures pédagogiques et administratives</t>
-        </is>
-      </c>
-      <c r="C75" s="52" t="n"/>
-      <c r="D75" s="51" t="n">
-        <v>451874</v>
-      </c>
-      <c r="E75" s="72">
-        <f>IFERROR(D75/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F75" s="52" t="inlineStr">
-        <is>
-          <t>COST_ODIR</t>
-        </is>
-      </c>
-      <c r="G75" s="52" t="inlineStr">
-        <is>
-          <t>EFFECTIFS</t>
-        </is>
-      </c>
-      <c r="H75" s="53" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="I75" s="54" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
@@ -6528,39 +9091,14 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
-      <c r="B76" s="49" t="inlineStr">
-        <is>
-          <t>621 · Personnel extérieur — enseignants vacataires</t>
-        </is>
-      </c>
-      <c r="C76" s="52" t="n"/>
-      <c r="D76" s="51" t="n">
-        <v>1581554</v>
-      </c>
-      <c r="E76" s="72">
-        <f>IFERROR(D76/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F76" s="52" t="inlineStr">
-        <is>
-          <t>COST_VAC</t>
-        </is>
-      </c>
-      <c r="G76" s="52" t="inlineStr">
-        <is>
-          <t>HEURES</t>
-        </is>
-      </c>
-      <c r="H76" s="55" t="inlineStr">
-        <is>
-          <t>Semi-variable</t>
-        </is>
-      </c>
-      <c r="I76" s="56" t="inlineStr">
-        <is>
-          <t>Seulement si une classe doit ouvrir</t>
-        </is>
-      </c>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n"/>
@@ -6569,39 +9107,14 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
-      <c r="B77" s="49" t="inlineStr">
-        <is>
-          <t>6411 · Salaires — enseignants permanents</t>
-        </is>
-      </c>
-      <c r="C77" s="52" t="n"/>
-      <c r="D77" s="51" t="n">
-        <v>3841069.840000001</v>
-      </c>
-      <c r="E77" s="72">
-        <f>IFERROR(D77/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F77" s="52" t="inlineStr">
-        <is>
-          <t>COST_PERM</t>
-        </is>
-      </c>
-      <c r="G77" s="52" t="inlineStr">
-        <is>
-          <t>HEURES</t>
-        </is>
-      </c>
-      <c r="H77" s="57" t="inlineStr">
-        <is>
-          <t>Capacité</t>
-        </is>
-      </c>
-      <c r="I77" s="58" t="inlineStr">
-        <is>
-          <t>NON — le poste est engagé à l'année, pas à l'élève</t>
-        </is>
-      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="5" t="n"/>
@@ -6610,39 +9123,14 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
-      <c r="B78" s="49" t="inlineStr">
-        <is>
-          <t>6231 · Annonces et insertions — budget d'acquisition</t>
-        </is>
-      </c>
-      <c r="C78" s="52" t="n"/>
-      <c r="D78" s="51" t="n">
-        <v>434174</v>
-      </c>
-      <c r="E78" s="72">
-        <f>IFERROR(D78/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F78" s="52" t="inlineStr">
-        <is>
-          <t>COST_ODIR</t>
-        </is>
-      </c>
-      <c r="G78" s="52" t="inlineStr">
-        <is>
-          <t>ENTRANTS</t>
-        </is>
-      </c>
-      <c r="H78" s="83" t="inlineStr">
-        <is>
-          <t>Levier</t>
-        </is>
-      </c>
-      <c r="I78" s="84" t="inlineStr">
-        <is>
-          <t>C'EST LA SAISIE — déjà soustrait comme Δ budget</t>
-        </is>
-      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
@@ -6651,39 +9139,14 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
-      <c r="B79" s="49" t="inlineStr">
-        <is>
-          <t>6413 · Salaires — personnel administratif des campus</t>
-        </is>
-      </c>
-      <c r="C79" s="52" t="n"/>
-      <c r="D79" s="51" t="n">
-        <v>2033330.6</v>
-      </c>
-      <c r="E79" s="72">
-        <f>IFERROR(D79/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F79" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G79" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H79" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I79" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="n"/>
@@ -6692,39 +9155,14 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
-      <c r="B80" s="49" t="inlineStr">
-        <is>
-          <t>645 · Charges sociales sur les salaires</t>
-        </is>
-      </c>
-      <c r="C80" s="52" t="n"/>
-      <c r="D80" s="51" t="n">
-        <v>3162957.9</v>
-      </c>
-      <c r="E80" s="72">
-        <f>IFERROR(D80/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F80" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G80" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H80" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I80" s="86" t="inlineStr">
-        <is>
-          <t>NON — et 621 n'en porte pas : c'est une facture, pas une paie</t>
-        </is>
-      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n"/>
@@ -6733,39 +9171,14 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
-      <c r="B81" s="49" t="inlineStr">
-        <is>
-          <t>613 · Locations immobilières des campus</t>
-        </is>
-      </c>
-      <c r="C81" s="52" t="n"/>
-      <c r="D81" s="51" t="n">
-        <v>2372423.51</v>
-      </c>
-      <c r="E81" s="72">
-        <f>IFERROR(D81/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F81" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G81" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H81" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I81" s="86" t="inlineStr">
-        <is>
-          <t>NON — c'est le mur qui coûte, pas l'élève</t>
-        </is>
-      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
+      <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="n"/>
@@ -6774,39 +9187,14 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
-      <c r="B82" s="49" t="inlineStr">
-        <is>
-          <t>615 · Entretien et réparations</t>
-        </is>
-      </c>
-      <c r="C82" s="52" t="n"/>
-      <c r="D82" s="51" t="n">
-        <v>338915.38</v>
-      </c>
-      <c r="E82" s="72">
-        <f>IFERROR(D82/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F82" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G82" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H82" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I82" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="5" t="n"/>
       <c r="J82" s="5" t="n"/>
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="n"/>
@@ -6815,39 +9203,14 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
-      <c r="B83" s="49" t="inlineStr">
-        <is>
-          <t>616 · Primes d'assurance</t>
-        </is>
-      </c>
-      <c r="C83" s="52" t="n"/>
-      <c r="D83" s="51" t="n">
-        <v>225926.43</v>
-      </c>
-      <c r="E83" s="72">
-        <f>IFERROR(D83/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F83" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G83" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H83" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I83" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="5" t="n"/>
@@ -6856,39 +9219,14 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
-      <c r="B84" s="49" t="inlineStr">
-        <is>
-          <t>625 · Déplacements, missions et réceptions</t>
-        </is>
-      </c>
-      <c r="C84" s="52" t="n"/>
-      <c r="D84" s="51" t="n">
-        <v>338890.3800000001</v>
-      </c>
-      <c r="E84" s="72">
-        <f>IFERROR(D84/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F84" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G84" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H84" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I84" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="n"/>
@@ -6897,39 +9235,14 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
-      <c r="B85" s="49" t="inlineStr">
-        <is>
-          <t>63511 · Contribution économique territoriale</t>
-        </is>
-      </c>
-      <c r="C85" s="52" t="n"/>
-      <c r="D85" s="51" t="n">
-        <v>225943.95</v>
-      </c>
-      <c r="E85" s="72">
-        <f>IFERROR(D85/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F85" s="52" t="inlineStr">
-        <is>
-          <t>COST_STRUCT</t>
-        </is>
-      </c>
-      <c r="G85" s="52" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="H85" s="85" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-      <c r="I85" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="5" t="n"/>
@@ -6938,39 +9251,14 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
-      <c r="B86" s="49" t="inlineStr">
-        <is>
-          <t>6236 · Catalogues et imprimés — marketing de marque</t>
-        </is>
-      </c>
-      <c r="C86" s="52" t="n"/>
-      <c r="D86" s="51" t="n">
-        <v>676344</v>
-      </c>
-      <c r="E86" s="72">
-        <f>IFERROR(D86/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F86" s="52" t="inlineStr">
-        <is>
-          <t>COST_MARQUE</t>
-        </is>
-      </c>
-      <c r="G86" s="52" t="inlineStr">
-        <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="H86" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I86" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="n"/>
@@ -6979,39 +9267,14 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
-      <c r="B87" s="49" t="inlineStr">
-        <is>
-          <t>6414 · Salaires du siège</t>
-        </is>
-      </c>
-      <c r="C87" s="52" t="n"/>
-      <c r="D87" s="51" t="n">
-        <v>1242649</v>
-      </c>
-      <c r="E87" s="72">
-        <f>IFERROR(D87/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F87" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G87" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H87" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I87" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="n"/>
@@ -7020,39 +9283,14 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
-      <c r="B88" s="49" t="inlineStr">
-        <is>
-          <t>6226 · Honoraires</t>
-        </is>
-      </c>
-      <c r="C88" s="52" t="n"/>
-      <c r="D88" s="51" t="n">
-        <v>564841</v>
-      </c>
-      <c r="E88" s="72">
-        <f>IFERROR(D88/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F88" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G88" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H88" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I88" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="n"/>
@@ -7061,39 +9299,14 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
-      <c r="B89" s="49" t="inlineStr">
-        <is>
-          <t>626 · Frais postaux et de télécommunications</t>
-        </is>
-      </c>
-      <c r="C89" s="52" t="n"/>
-      <c r="D89" s="51" t="n">
-        <v>451872</v>
-      </c>
-      <c r="E89" s="72">
-        <f>IFERROR(D89/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F89" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G89" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H89" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I89" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="n"/>
@@ -7102,39 +9315,14 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
-      <c r="B90" s="49" t="inlineStr">
-        <is>
-          <t>6281 · Cotisations et concours divers</t>
-        </is>
-      </c>
-      <c r="C90" s="52" t="n"/>
-      <c r="D90" s="51" t="n">
-        <v>180749</v>
-      </c>
-      <c r="E90" s="72">
-        <f>IFERROR(D90/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F90" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G90" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H90" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I90" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="5" t="n"/>
@@ -7143,39 +9331,14 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
-      <c r="B91" s="49" t="inlineStr">
-        <is>
-          <t>6331 · Versement mobilité</t>
-        </is>
-      </c>
-      <c r="C91" s="52" t="n"/>
-      <c r="D91" s="51" t="n">
-        <v>338904</v>
-      </c>
-      <c r="E91" s="72">
-        <f>IFERROR(D91/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F91" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G91" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H91" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I91" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="5" t="n"/>
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="5" t="n"/>
@@ -7184,39 +9347,14 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
-      <c r="B92" s="49" t="inlineStr">
-        <is>
-          <t>6333 · Participation à la formation professionnelle</t>
-        </is>
-      </c>
-      <c r="C92" s="52" t="n"/>
-      <c r="D92" s="51" t="n">
-        <v>112968</v>
-      </c>
-      <c r="E92" s="72">
-        <f>IFERROR(D92/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F92" s="52" t="inlineStr">
-        <is>
-          <t>COST_HOLDING</t>
-        </is>
-      </c>
-      <c r="G92" s="52" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="H92" s="85" t="inlineStr">
-        <is>
-          <t>Siège</t>
-        </is>
-      </c>
-      <c r="I92" s="86" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
@@ -7225,39 +9363,14 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
-      <c r="B93" s="49" t="inlineStr">
-        <is>
-          <t>6811 · Dotations aux amortissements</t>
-        </is>
-      </c>
-      <c r="C93" s="52" t="n"/>
-      <c r="D93" s="51" t="n">
-        <v>1352683</v>
-      </c>
-      <c r="E93" s="72">
-        <f>IFERROR(D93/$D$94,0)</f>
-        <v/>
-      </c>
-      <c r="F93" s="52" t="inlineStr">
-        <is>
-          <t>hors modèle</t>
-        </is>
-      </c>
-      <c r="G93" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="85" t="inlineStr">
-        <is>
-          <t>Hors EBITDA</t>
-        </is>
-      </c>
-      <c r="I93" s="86" t="inlineStr">
-        <is>
-          <t>NON — sous la ligne d'EBITDA</t>
-        </is>
-      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="5" t="n"/>
       <c r="L93" s="5" t="n"/>
@@ -7266,23 +9379,14 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
-      <c r="B94" s="64" t="inlineStr">
-        <is>
-          <t>TOTAL DES CHARGES 2026  ·  dotations incluses</t>
-        </is>
-      </c>
-      <c r="C94" s="64" t="n"/>
-      <c r="D94" s="68">
-        <f>SUM(D74:D93)</f>
-        <v/>
-      </c>
-      <c r="E94" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="64" t="inlineStr"/>
-      <c r="G94" s="64" t="inlineStr"/>
-      <c r="H94" s="64" t="inlineStr"/>
-      <c r="I94" s="64" t="inlineStr"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="5" t="n"/>
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="5" t="n"/>
       <c r="L94" s="5" t="n"/>
@@ -7291,20 +9395,14 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
-      <c r="B95" s="87" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires 2026  ·  706 + 7062 + 708</t>
-        </is>
-      </c>
-      <c r="C95" s="87" t="n"/>
-      <c r="D95" s="88" t="n">
-        <v>23098985</v>
-      </c>
-      <c r="E95" s="89" t="inlineStr"/>
-      <c r="F95" s="87" t="inlineStr"/>
-      <c r="G95" s="87" t="inlineStr"/>
-      <c r="H95" s="87" t="inlineStr"/>
-      <c r="I95" s="87" t="inlineStr"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
@@ -7313,21 +9411,14 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
-      <c r="B96" s="64" t="inlineStr">
-        <is>
-          <t>EBITDA 2026  =  CA − charges hors dotations</t>
-        </is>
-      </c>
-      <c r="C96" s="64" t="n"/>
-      <c r="D96" s="90">
-        <f>D95-D94+D93</f>
-        <v/>
-      </c>
-      <c r="E96" s="74" t="inlineStr"/>
-      <c r="F96" s="64" t="inlineStr"/>
-      <c r="G96" s="64" t="inlineStr"/>
-      <c r="H96" s="64" t="inlineStr"/>
-      <c r="I96" s="64" t="inlineStr"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="5" t="n"/>
@@ -7350,24 +9441,21 @@
       <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
     </row>
-    <row r="98" ht="18" customHeight="1">
+    <row r="98">
       <c r="A98" s="5" t="n"/>
-      <c r="B98" s="91">
-        <f>"Sur "&amp;TEXT(D94,"#,##0 €")&amp;" de charges, "&amp;TEXT(D74+D75,"#,##0 €")&amp;" seulement bougent quand un élève de plus s'assoit — soit "&amp;TEXT((D74+D75)/D94,"0.0 %")&amp;". Tout le reste est de la capacité déjà engagée : c'est précisément ce qui rend le geste d'acquisition aussi rentable tant qu'il reste des places."</f>
-        <v/>
-      </c>
-      <c r="C98" s="92" t="n"/>
-      <c r="D98" s="92" t="n"/>
-      <c r="E98" s="92" t="n"/>
-      <c r="F98" s="92" t="n"/>
-      <c r="G98" s="92" t="n"/>
-      <c r="H98" s="92" t="n"/>
-      <c r="I98" s="92" t="n"/>
-      <c r="J98" s="92" t="n"/>
-      <c r="K98" s="92" t="n"/>
-      <c r="L98" s="92" t="n"/>
-      <c r="M98" s="92" t="n"/>
-      <c r="N98" s="92" t="n"/>
+      <c r="B98" s="5" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -7470,7 +9558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7639,18 +9727,18 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="141" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C9" s="94" t="n">
+      <c r="C9" s="142" t="n">
         <v>480</v>
       </c>
-      <c r="D9" s="95" t="n">
+      <c r="D9" s="143" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="96" t="inlineStr">
+      <c r="E9" s="144" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -7665,18 +9753,18 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="93" t="inlineStr">
+      <c r="B10" s="141" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C10" s="94" t="n">
+      <c r="C10" s="142" t="n">
         <v>600</v>
       </c>
-      <c r="D10" s="95" t="n">
+      <c r="D10" s="143" t="n">
         <v>32</v>
       </c>
-      <c r="E10" s="96" t="inlineStr">
+      <c r="E10" s="144" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -7691,18 +9779,18 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="141" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C11" s="94" t="n">
+      <c r="C11" s="142" t="n">
         <v>700</v>
       </c>
-      <c r="D11" s="95" t="n">
+      <c r="D11" s="143" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="96" t="inlineStr">
+      <c r="E11" s="144" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -7717,18 +9805,18 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="97" t="inlineStr">
+      <c r="B12" s="145" t="inlineStr">
         <is>
           <t>BTS · initial</t>
         </is>
       </c>
-      <c r="C12" s="98" t="n">
+      <c r="C12" s="146" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="99" t="n">
+      <c r="D12" s="147" t="n">
         <v>30</v>
       </c>
-      <c r="E12" s="100" t="inlineStr">
+      <c r="E12" s="148" t="inlineStr">
         <is>
           <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
         </is>
@@ -7743,18 +9831,18 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="141" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C13" s="94" t="n">
+      <c r="C13" s="142" t="n">
         <v>420</v>
       </c>
-      <c r="D13" s="95" t="n">
+      <c r="D13" s="143" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="96" t="inlineStr">
+      <c r="E13" s="144" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -7769,18 +9857,18 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="97" t="inlineStr">
+      <c r="B14" s="145" t="inlineStr">
         <is>
           <t>Mastère · initial</t>
         </is>
       </c>
-      <c r="C14" s="98" t="n">
+      <c r="C14" s="146" t="n">
         <v>520</v>
       </c>
-      <c r="D14" s="99" t="n">
+      <c r="D14" s="147" t="n">
         <v>26</v>
       </c>
-      <c r="E14" s="100" t="inlineStr">
+      <c r="E14" s="148" t="inlineStr">
         <is>
           <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
         </is>
@@ -7921,22 +10009,22 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="87" t="inlineStr">
+      <c r="B22" s="95" t="inlineStr">
         <is>
           <t>B  ·  Marque</t>
         </is>
       </c>
-      <c r="C22" s="101" t="inlineStr">
+      <c r="C22" s="149" t="inlineStr">
         <is>
           <t>MARQUE</t>
         </is>
       </c>
-      <c r="D22" s="101" t="inlineStr">
+      <c r="D22" s="149" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="E22" s="101" t="inlineStr">
+      <c r="E22" s="149" t="inlineStr">
         <is>
           <t>regroupement d'affichage</t>
         </is>
@@ -7951,22 +10039,22 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="87" t="inlineStr">
+      <c r="B23" s="95" t="inlineStr">
         <is>
           <t>C  ·  Campus</t>
         </is>
       </c>
-      <c r="C23" s="101" t="inlineStr">
+      <c r="C23" s="149" t="inlineStr">
         <is>
           <t>CAMPUS</t>
         </is>
       </c>
-      <c r="D23" s="101" t="inlineStr">
+      <c r="D23" s="149" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="E23" s="101" t="inlineStr">
+      <c r="E23" s="149" t="inlineStr">
         <is>
           <t>libellé azienda</t>
         </is>
@@ -7981,22 +10069,22 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="87" t="inlineStr">
+      <c r="B24" s="95" t="inlineStr">
         <is>
           <t>D  ·  Leads payants 2024</t>
         </is>
       </c>
-      <c r="C24" s="101" t="inlineStr">
+      <c r="C24" s="149" t="inlineStr">
         <is>
           <t>LEAD_PAY_2024</t>
         </is>
       </c>
-      <c r="D24" s="101" t="inlineStr">
+      <c r="D24" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E24" s="101" t="inlineStr"/>
+      <c r="E24" s="149" t="inlineStr"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
@@ -8007,22 +10095,22 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="87" t="inlineStr">
+      <c r="B25" s="95" t="inlineStr">
         <is>
           <t>E  ·  Leads payants 2025</t>
         </is>
       </c>
-      <c r="C25" s="101" t="inlineStr">
+      <c r="C25" s="149" t="inlineStr">
         <is>
           <t>LEAD_PAY_2025</t>
         </is>
       </c>
-      <c r="D25" s="101" t="inlineStr">
+      <c r="D25" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E25" s="101" t="inlineStr"/>
+      <c r="E25" s="149" t="inlineStr"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -8033,22 +10121,22 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="87" t="inlineStr">
+      <c r="B26" s="95" t="inlineStr">
         <is>
           <t>F  ·  Leads payants 2026</t>
         </is>
       </c>
-      <c r="C26" s="101" t="inlineStr">
+      <c r="C26" s="149" t="inlineStr">
         <is>
           <t>LEAD_PAY_2026</t>
         </is>
       </c>
-      <c r="D26" s="101" t="inlineStr">
+      <c r="D26" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E26" s="101" t="inlineStr">
+      <c r="E26" s="149" t="inlineStr">
         <is>
           <t>base du geste</t>
         </is>
@@ -8063,22 +10151,22 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="87" t="inlineStr">
+      <c r="B27" s="95" t="inlineStr">
         <is>
           <t>G  ·  Budget acq. 2024</t>
         </is>
       </c>
-      <c r="C27" s="101" t="inlineStr">
+      <c r="C27" s="149" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2024</t>
         </is>
       </c>
-      <c r="D27" s="101" t="inlineStr">
+      <c r="D27" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E27" s="101" t="inlineStr"/>
+      <c r="E27" s="149" t="inlineStr"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
@@ -8089,22 +10177,22 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="87" t="inlineStr">
+      <c r="B28" s="95" t="inlineStr">
         <is>
           <t>H  ·  Budget acq. 2025</t>
         </is>
       </c>
-      <c r="C28" s="101" t="inlineStr">
+      <c r="C28" s="149" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2025</t>
         </is>
       </c>
-      <c r="D28" s="101" t="inlineStr">
+      <c r="D28" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E28" s="101" t="inlineStr"/>
+      <c r="E28" s="149" t="inlineStr"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
@@ -8115,22 +10203,22 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="87" t="inlineStr">
+      <c r="B29" s="95" t="inlineStr">
         <is>
           <t>I  ·  Budget acq. 2026</t>
         </is>
       </c>
-      <c r="C29" s="101" t="inlineStr">
+      <c r="C29" s="149" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2026</t>
         </is>
       </c>
-      <c r="D29" s="101" t="inlineStr">
+      <c r="D29" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E29" s="101">
+      <c r="E29" s="149">
         <f> compte 6231</f>
         <v/>
       </c>
@@ -8144,22 +10232,22 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="87" t="inlineStr">
+      <c r="B30" s="95" t="inlineStr">
         <is>
           <t>J  ·  Élasticité</t>
         </is>
       </c>
-      <c r="C30" s="101" t="inlineStr">
+      <c r="C30" s="149" t="inlineStr">
         <is>
           <t>ELASTICITE</t>
         </is>
       </c>
-      <c r="D30" s="102" t="inlineStr">
+      <c r="D30" s="150" t="inlineStr">
         <is>
           <t>NON additive</t>
         </is>
       </c>
-      <c r="E30" s="101" t="inlineStr">
+      <c r="E30" s="149" t="inlineStr">
         <is>
           <t>régression log-log, reste au campus</t>
         </is>
@@ -8174,22 +10262,22 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="87" t="inlineStr">
+      <c r="B31" s="95" t="inlineStr">
         <is>
           <t>K  ·  Leads totaux 2026</t>
         </is>
       </c>
-      <c r="C31" s="101" t="inlineStr">
+      <c r="C31" s="149" t="inlineStr">
         <is>
           <t>LEAD_TOT_N</t>
         </is>
       </c>
-      <c r="D31" s="101" t="inlineStr">
+      <c r="D31" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E31" s="101" t="inlineStr">
+      <c r="E31" s="149" t="inlineStr">
         <is>
           <t>dénominateur de la conversion</t>
         </is>
@@ -8204,22 +10292,22 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="87" t="inlineStr">
+      <c r="B32" s="95" t="inlineStr">
         <is>
           <t>L  ·  Inscrits 2026</t>
         </is>
       </c>
-      <c r="C32" s="101" t="inlineStr">
+      <c r="C32" s="149" t="inlineStr">
         <is>
           <t>INSCRITS_N</t>
         </is>
       </c>
-      <c r="D32" s="101" t="inlineStr">
+      <c r="D32" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E32" s="101" t="inlineStr">
+      <c r="E32" s="149" t="inlineStr">
         <is>
           <t>numérateur de la conversion</t>
         </is>
@@ -8234,22 +10322,22 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
-      <c r="B33" s="87" t="inlineStr">
+      <c r="B33" s="95" t="inlineStr">
         <is>
           <t>M  ·  CA nouveaux 2026</t>
         </is>
       </c>
-      <c r="C33" s="101" t="inlineStr">
+      <c r="C33" s="149" t="inlineStr">
         <is>
           <t>CA_NEW_N</t>
         </is>
       </c>
-      <c r="D33" s="101" t="inlineStr">
+      <c r="D33" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E33" s="101" t="inlineStr"/>
+      <c r="E33" s="149" t="inlineStr"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
@@ -8260,22 +10348,22 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="87" t="inlineStr">
+      <c r="B34" s="95" t="inlineStr">
         <is>
           <t>N  ·  Effectifs 2026</t>
         </is>
       </c>
-      <c r="C34" s="101" t="inlineStr">
+      <c r="C34" s="149" t="inlineStr">
         <is>
           <t>EFFECTIFS_N</t>
         </is>
       </c>
-      <c r="D34" s="101" t="inlineStr">
+      <c r="D34" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E34" s="101" t="inlineStr"/>
+      <c r="E34" s="149" t="inlineStr"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
@@ -8286,22 +10374,22 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="87" t="inlineStr">
+      <c r="B35" s="95" t="inlineStr">
         <is>
           <t>O  ·  Places 2026</t>
         </is>
       </c>
-      <c r="C35" s="101" t="inlineStr">
+      <c r="C35" s="149" t="inlineStr">
         <is>
           <t>PLACES_N</t>
         </is>
       </c>
-      <c r="D35" s="101" t="inlineStr">
+      <c r="D35" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E35" s="101" t="inlineStr">
+      <c r="E35" s="149" t="inlineStr">
         <is>
           <t>classes × capacité</t>
         </is>
@@ -8316,22 +10404,22 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="87" t="inlineStr">
+      <c r="B36" s="95" t="inlineStr">
         <is>
           <t>P  ·  Classes 2026</t>
         </is>
       </c>
-      <c r="C36" s="101" t="inlineStr">
+      <c r="C36" s="149" t="inlineStr">
         <is>
           <t>CLASSES_N</t>
         </is>
       </c>
-      <c r="D36" s="101" t="inlineStr">
+      <c r="D36" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E36" s="101" t="inlineStr"/>
+      <c r="E36" s="149" t="inlineStr"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
@@ -8342,22 +10430,22 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="103" t="inlineStr">
+      <c r="B37" s="151" t="inlineStr">
         <is>
           <t>Q  ·  Heures d'enseignement 2026</t>
         </is>
       </c>
-      <c r="C37" s="104" t="inlineStr">
+      <c r="C37" s="152" t="inlineStr">
         <is>
           <t>HEURES_N</t>
         </is>
       </c>
-      <c r="D37" s="104" t="inlineStr">
+      <c r="D37" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E37" s="104" t="inlineStr">
+      <c r="E37" s="152" t="inlineStr">
         <is>
           <t>À AJOUTER À LA VUE</t>
         </is>
@@ -8372,22 +10460,22 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="87" t="inlineStr">
+      <c r="B38" s="95" t="inlineStr">
         <is>
           <t>R  ·  Consommables 604+6063</t>
         </is>
       </c>
-      <c r="C38" s="101" t="inlineStr">
+      <c r="C38" s="149" t="inlineStr">
         <is>
           <t>COUT_CONSO_N</t>
         </is>
       </c>
-      <c r="D38" s="101" t="inlineStr">
+      <c r="D38" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E38" s="101" t="inlineStr"/>
+      <c r="E38" s="149" t="inlineStr"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
@@ -8398,22 +10486,22 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="87" t="inlineStr">
+      <c r="B39" s="95" t="inlineStr">
         <is>
           <t>S  ·  Vacataires 621</t>
         </is>
       </c>
-      <c r="C39" s="101" t="inlineStr">
+      <c r="C39" s="149" t="inlineStr">
         <is>
           <t>COUT_VACAT_N</t>
         </is>
       </c>
-      <c r="D39" s="101" t="inlineStr">
+      <c r="D39" s="149" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E39" s="101" t="inlineStr"/>
+      <c r="E39" s="149" t="inlineStr"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
@@ -8424,22 +10512,22 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="103" t="inlineStr">
+      <c r="B40" s="151" t="inlineStr">
         <is>
           <t>T  ·  Enseignants permanents 6411</t>
         </is>
       </c>
-      <c r="C40" s="104" t="inlineStr">
+      <c r="C40" s="152" t="inlineStr">
         <is>
           <t>COUT_PERM_N</t>
         </is>
       </c>
-      <c r="D40" s="104" t="inlineStr">
+      <c r="D40" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E40" s="104" t="inlineStr">
+      <c r="E40" s="152" t="inlineStr">
         <is>
           <t>À AJOUTER À LA VUE</t>
         </is>
@@ -8562,23 +10650,23 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="153" t="inlineStr">
         <is>
           <t>Δ budget d'acquisition</t>
         </is>
       </c>
-      <c r="C47" s="83" t="inlineStr">
+      <c r="C47" s="153" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="D47" s="105" t="inlineStr">
+      <c r="D47" s="154" t="inlineStr">
         <is>
           <t>SAISIE</t>
         </is>
       </c>
-      <c r="E47" s="83" t="n"/>
-      <c r="F47" s="83" t="inlineStr">
+      <c r="E47" s="153" t="n"/>
+      <c r="F47" s="153" t="inlineStr">
         <is>
           <t>la seule cellule modifiable du classeur</t>
         </is>
@@ -8592,23 +10680,23 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="106" t="inlineStr">
+      <c r="B48" s="155" t="inlineStr">
         <is>
           <t>Conversion lead → inscrit</t>
         </is>
       </c>
-      <c r="C48" s="107" t="inlineStr">
+      <c r="C48" s="77" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D48" s="108" t="inlineStr">
+      <c r="D48" s="156" t="inlineStr">
         <is>
           <t>=IFERROR(L20/K20,0)</t>
         </is>
       </c>
-      <c r="E48" s="107" t="n"/>
-      <c r="F48" s="107" t="inlineStr">
+      <c r="E48" s="77" t="n"/>
+      <c r="F48" s="77" t="inlineStr">
         <is>
           <t>INSCRITS_N ÷ LEAD_TOT_N — jamais pré-calculée, sinon la ligne groupe se trompe</t>
         </is>
@@ -8622,23 +10710,23 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="106" t="inlineStr">
+      <c r="B49" s="155" t="inlineStr">
         <is>
           <t>CA par inscrit</t>
         </is>
       </c>
-      <c r="C49" s="107" t="inlineStr">
+      <c r="C49" s="77" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D49" s="108" t="inlineStr">
+      <c r="D49" s="156" t="inlineStr">
         <is>
           <t>=IFERROR(M20/L20,0)</t>
         </is>
       </c>
-      <c r="E49" s="107" t="n"/>
-      <c r="F49" s="107" t="inlineStr">
+      <c r="E49" s="77" t="n"/>
+      <c r="F49" s="77" t="inlineStr">
         <is>
           <t>CA_NEW_N ÷ INSCRITS_N</t>
         </is>
@@ -8652,23 +10740,23 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="106" t="inlineStr">
+      <c r="B50" s="155" t="inlineStr">
         <is>
           <t>Consommables / élève</t>
         </is>
       </c>
-      <c r="C50" s="107" t="inlineStr">
+      <c r="C50" s="77" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D50" s="108" t="inlineStr">
+      <c r="D50" s="156" t="inlineStr">
         <is>
           <t>=IFERROR(R20/N20,0)</t>
         </is>
       </c>
-      <c r="E50" s="107" t="n"/>
-      <c r="F50" s="107" t="inlineStr">
+      <c r="E50" s="77" t="n"/>
+      <c r="F50" s="77" t="inlineStr">
         <is>
           <t>COUT_CONSO_N ÷ EFFECTIFS_N</t>
         </is>
@@ -8682,23 +10770,23 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="106" t="inlineStr">
+      <c r="B51" s="155" t="inlineStr">
         <is>
           <t>Places libres</t>
         </is>
       </c>
-      <c r="C51" s="107" t="inlineStr">
+      <c r="C51" s="77" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D51" s="108" t="inlineStr">
+      <c r="D51" s="156" t="inlineStr">
         <is>
           <t>=O20-N20</t>
         </is>
       </c>
-      <c r="E51" s="107" t="n"/>
-      <c r="F51" s="107" t="inlineStr">
+      <c r="E51" s="77" t="n"/>
+      <c r="F51" s="77" t="inlineStr">
         <is>
           <t>PLACES_N − EFFECTIFS_N : la borne physique du geste</t>
         </is>
@@ -8712,23 +10800,23 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="106" t="inlineStr">
+      <c r="B52" s="155" t="inlineStr">
         <is>
           <t>Δ budget</t>
         </is>
       </c>
-      <c r="C52" s="107" t="inlineStr">
+      <c r="C52" s="77" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D52" s="108" t="inlineStr">
+      <c r="D52" s="156" t="inlineStr">
         <is>
           <t>=I20*$F$4</t>
         </is>
       </c>
-      <c r="E52" s="107" t="n"/>
-      <c r="F52" s="107" t="inlineStr">
+      <c r="E52" s="77" t="n"/>
+      <c r="F52" s="77" t="inlineStr">
         <is>
           <t>le geste, appliqué au budget 2026</t>
         </is>
@@ -8742,23 +10830,23 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="106" t="inlineStr">
+      <c r="B53" s="155" t="inlineStr">
         <is>
           <t>Inscrits gagnés</t>
         </is>
       </c>
-      <c r="C53" s="107" t="inlineStr">
+      <c r="C53" s="77" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D53" s="108" t="inlineStr">
+      <c r="D53" s="156" t="inlineStr">
         <is>
           <t>=F20*((1+$F$4)^J20-1)*D44</t>
         </is>
       </c>
-      <c r="E53" s="107" t="n"/>
-      <c r="F53" s="107" t="inlineStr">
+      <c r="E53" s="77" t="n"/>
+      <c r="F53" s="77" t="inlineStr">
         <is>
           <t>leads payants × l'effet d'élasticité, converti au taux du campus</t>
         </is>
@@ -8772,23 +10860,23 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="106" t="inlineStr">
+      <c r="B54" s="155" t="inlineStr">
         <is>
           <t>CA gagné</t>
         </is>
       </c>
-      <c r="C54" s="107" t="inlineStr">
+      <c r="C54" s="77" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D54" s="108" t="inlineStr">
+      <c r="D54" s="156" t="inlineStr">
         <is>
           <t>=I44*E44</t>
         </is>
       </c>
-      <c r="E54" s="107" t="n"/>
-      <c r="F54" s="107" t="inlineStr">
+      <c r="E54" s="77" t="n"/>
+      <c r="F54" s="77" t="inlineStr">
         <is>
           <t>inscrits gagnés × CA par inscrit</t>
         </is>
@@ -8802,23 +10890,23 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="106" t="inlineStr">
+      <c r="B55" s="155" t="inlineStr">
         <is>
           <t>Coût marginal / élève</t>
         </is>
       </c>
-      <c r="C55" s="107" t="inlineStr">
+      <c r="C55" s="77" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D55" s="108" t="inlineStr">
+      <c r="D55" s="156" t="inlineStr">
         <is>
           <t>=IF(I44&lt;=G44,F44,F44+S20/O20)</t>
         </is>
       </c>
-      <c r="E55" s="107" t="n"/>
-      <c r="F55" s="107" t="inlineStr">
+      <c r="E55" s="77" t="n"/>
+      <c r="F55" s="77" t="inlineStr">
         <is>
           <t>consommables seuls, + quote-part vacataire si la classe doit ouvrir</t>
         </is>
@@ -8832,23 +10920,23 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="106" t="inlineStr">
+      <c r="B56" s="155" t="inlineStr">
         <is>
           <t>EBITDA gagné</t>
         </is>
       </c>
-      <c r="C56" s="107" t="inlineStr">
+      <c r="C56" s="77" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D56" s="108" t="inlineStr">
+      <c r="D56" s="156" t="inlineStr">
         <is>
           <t>=J44-H44-I44*K44</t>
         </is>
       </c>
-      <c r="E56" s="107" t="n"/>
-      <c r="F56" s="107" t="inlineStr">
+      <c r="E56" s="77" t="n"/>
+      <c r="F56" s="77" t="inlineStr">
         <is>
           <t>CA gagné − Δ budget − coût de service</t>
         </is>
@@ -8862,23 +10950,23 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="106" t="inlineStr">
+      <c r="B57" s="155" t="inlineStr">
         <is>
           <t>CAC marginal</t>
         </is>
       </c>
-      <c r="C57" s="107" t="inlineStr">
+      <c r="C57" s="77" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D57" s="108" t="inlineStr">
+      <c r="D57" s="156" t="inlineStr">
         <is>
           <t>=IFERROR(H44/I44,0)</t>
         </is>
       </c>
-      <c r="E57" s="107" t="n"/>
-      <c r="F57" s="107" t="inlineStr">
+      <c r="E57" s="77" t="n"/>
+      <c r="F57" s="77" t="inlineStr">
         <is>
           <t>Δ budget ÷ inscrits gagnés</t>
         </is>
@@ -9008,29 +11096,29 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="49" t="inlineStr">
+      <c r="B64" s="61" t="inlineStr">
         <is>
           <t>Budget d'acquisition : dépense CRM 2026 = compte 6231</t>
         </is>
       </c>
-      <c r="C64" s="52" t="n"/>
-      <c r="D64" s="51">
+      <c r="C64" s="102" t="n"/>
+      <c r="D64" s="67">
         <f>'Le moteur'!I34</f>
         <v/>
       </c>
-      <c r="E64" s="51">
-        <f>'Le coût variable'!D78</f>
-        <v/>
-      </c>
-      <c r="F64" s="51">
+      <c r="E64" s="67">
+        <f>'Budget 2027'!D76</f>
+        <v/>
+      </c>
+      <c r="F64" s="67">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="50">
+      <c r="G64" s="116">
         <f>IF(ABS(F64)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H64" s="80" t="inlineStr">
+      <c r="H64" s="138" t="inlineStr">
         <is>
           <t>socle CRM contre comptabilité</t>
         </is>
@@ -9042,29 +11130,29 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
-      <c r="B65" s="49" t="inlineStr">
+      <c r="B65" s="61" t="inlineStr">
         <is>
           <t>Consommables : comptes 604 + 6063 = COUT_CONSO_N</t>
         </is>
       </c>
-      <c r="C65" s="52" t="n"/>
-      <c r="D65" s="51">
-        <f>'Le coût variable'!D74+'Le coût variable'!D75</f>
-        <v/>
-      </c>
-      <c r="E65" s="51">
+      <c r="C65" s="102" t="n"/>
+      <c r="D65" s="67">
+        <f>'Budget 2027'!D60+'Budget 2027'!D61</f>
+        <v/>
+      </c>
+      <c r="E65" s="67">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="F65" s="51">
+      <c r="F65" s="67">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="50">
+      <c r="G65" s="116">
         <f>IF(ABS(F65)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H65" s="80" t="inlineStr">
+      <c r="H65" s="138" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -9076,29 +11164,29 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
-      <c r="B66" s="49" t="inlineStr">
+      <c r="B66" s="61" t="inlineStr">
         <is>
           <t>Vacataires : compte 621 = COUT_VACAT_N</t>
         </is>
       </c>
-      <c r="C66" s="52" t="n"/>
-      <c r="D66" s="51">
-        <f>'Le coût variable'!D76</f>
-        <v/>
-      </c>
-      <c r="E66" s="51">
+      <c r="C66" s="102" t="n"/>
+      <c r="D66" s="67">
+        <f>'Budget 2027'!D63</f>
+        <v/>
+      </c>
+      <c r="E66" s="67">
         <f>'Le moteur'!S34</f>
         <v/>
       </c>
-      <c r="F66" s="51">
+      <c r="F66" s="67">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="50">
+      <c r="G66" s="116">
         <f>IF(ABS(F66)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H66" s="80" t="inlineStr">
+      <c r="H66" s="138" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -9110,29 +11198,29 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
-      <c r="B67" s="49" t="inlineStr">
+      <c r="B67" s="61" t="inlineStr">
         <is>
           <t>Permanents : compte 6411 = COUT_PERM_N</t>
         </is>
       </c>
-      <c r="C67" s="52" t="n"/>
-      <c r="D67" s="51">
-        <f>'Le coût variable'!D77</f>
-        <v/>
-      </c>
-      <c r="E67" s="51">
+      <c r="C67" s="102" t="n"/>
+      <c r="D67" s="67">
+        <f>'Budget 2027'!D65</f>
+        <v/>
+      </c>
+      <c r="E67" s="67">
         <f>'Le moteur'!T34</f>
         <v/>
       </c>
-      <c r="F67" s="51">
+      <c r="F67" s="67">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="50">
+      <c r="G67" s="116">
         <f>IF(ABS(F67)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H67" s="80" t="inlineStr">
+      <c r="H67" s="138" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -9144,29 +11232,29 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="49" t="inlineStr">
+      <c r="B68" s="61" t="inlineStr">
         <is>
           <t>Effectifs : grain programme = grain campus</t>
         </is>
       </c>
-      <c r="C68" s="52" t="n"/>
-      <c r="D68" s="59">
+      <c r="C68" s="102" t="n"/>
+      <c r="D68" s="58">
         <f>'Le coût variable'!C26</f>
         <v/>
       </c>
-      <c r="E68" s="59">
+      <c r="E68" s="58">
         <f>'Le moteur'!N34</f>
         <v/>
       </c>
-      <c r="F68" s="59">
+      <c r="F68" s="58">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="50">
+      <c r="G68" s="116">
         <f>IF(ABS(F68)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H68" s="80" t="inlineStr">
+      <c r="H68" s="138" t="inlineStr">
         <is>
           <t>cycle × modalité contre campus</t>
         </is>
@@ -9178,29 +11266,29 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
-      <c r="B69" s="49" t="inlineStr">
+      <c r="B69" s="61" t="inlineStr">
         <is>
           <t>Allocation : consommables alloués aux programmes = total réseau</t>
         </is>
       </c>
-      <c r="C69" s="52" t="n"/>
-      <c r="D69" s="51">
+      <c r="C69" s="102" t="n"/>
+      <c r="D69" s="67">
         <f>SUMPRODUCT('Le coût variable'!C22:C25,'Le coût variable'!G22:G25)</f>
         <v/>
       </c>
-      <c r="E69" s="51">
+      <c r="E69" s="67">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="F69" s="51">
+      <c r="F69" s="67">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="50">
+      <c r="G69" s="116">
         <f>IF(ABS(F69)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H69" s="80" t="inlineStr">
+      <c r="H69" s="138" t="inlineStr">
         <is>
           <t>la clé EFFECTIFS ne perd rien</t>
         </is>
@@ -9212,29 +11300,29 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="49" t="inlineStr">
+      <c r="B70" s="61" t="inlineStr">
         <is>
           <t>EBITDA gagné : CA gagné − Δ budget − coût de service</t>
         </is>
       </c>
-      <c r="C70" s="52" t="n"/>
-      <c r="D70" s="51">
+      <c r="C70" s="102" t="n"/>
+      <c r="D70" s="67">
         <f>'Le moteur'!J58-'Le moteur'!H58-'Le moteur'!I58*'Le moteur'!K58</f>
         <v/>
       </c>
-      <c r="E70" s="51">
+      <c r="E70" s="67">
         <f>'Le moteur'!L58</f>
         <v/>
       </c>
-      <c r="F70" s="51">
+      <c r="F70" s="67">
         <f>D70-E70</f>
         <v/>
       </c>
-      <c r="G70" s="50">
+      <c r="G70" s="116">
         <f>IF(ABS(F70)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H70" s="80" t="inlineStr">
+      <c r="H70" s="138" t="inlineStr">
         <is>
           <t>additivité de la ligne groupe</t>
         </is>
@@ -9246,29 +11334,29 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="49" t="inlineStr">
+      <c r="B71" s="61" t="inlineStr">
         <is>
           <t>Régime du coût marginal : inscrits gagnés ≤ places libres</t>
         </is>
       </c>
-      <c r="C71" s="52" t="n"/>
-      <c r="D71" s="59">
+      <c r="C71" s="102" t="n"/>
+      <c r="D71" s="58">
         <f>'Le moteur'!I58</f>
         <v/>
       </c>
-      <c r="E71" s="59">
+      <c r="E71" s="58">
         <f>'Le moteur'!G58</f>
         <v/>
       </c>
-      <c r="F71" s="59">
+      <c r="F71" s="58">
         <f>E71-D71</f>
         <v/>
       </c>
-      <c r="G71" s="50">
+      <c r="G71" s="116">
         <f>IF(F71&gt;0,"OK · marge","BASCULE")</f>
         <v/>
       </c>
-      <c r="H71" s="80" t="inlineStr">
+      <c r="H71" s="138" t="inlineStr">
         <is>
           <t>si dépassé, une classe ouvre</t>
         </is>
@@ -9308,39 +11396,39 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="109" t="inlineStr">
+      <c r="B74" s="157" t="inlineStr">
         <is>
           <t>Ce qu'il reste à faire côté Tagetik</t>
         </is>
       </c>
-      <c r="C74" s="110" t="n"/>
-      <c r="D74" s="110" t="n"/>
-      <c r="E74" s="110" t="n"/>
-      <c r="F74" s="110" t="n"/>
-      <c r="G74" s="110" t="n"/>
-      <c r="H74" s="110" t="n"/>
-      <c r="I74" s="110" t="n"/>
-      <c r="J74" s="110" t="n"/>
-      <c r="K74" s="110" t="n"/>
-      <c r="L74" s="110" t="n"/>
+      <c r="C74" s="112" t="n"/>
+      <c r="D74" s="112" t="n"/>
+      <c r="E74" s="112" t="n"/>
+      <c r="F74" s="112" t="n"/>
+      <c r="G74" s="112" t="n"/>
+      <c r="H74" s="112" t="n"/>
+      <c r="I74" s="112" t="n"/>
+      <c r="J74" s="112" t="n"/>
+      <c r="K74" s="112" t="n"/>
+      <c r="L74" s="112" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="111" t="inlineStr">
+      <c r="B75" s="114" t="inlineStr">
         <is>
           <t>① ajouter HEURES_N et COUT_PERM_N à V_MOTEUR_CAL (le .sql du dépôt les porte).  ② brancher le tableau ① sur la vue, une ligne par campus, hiérarchie MARQUE ▸ CAMPUS.  ③ le tableau ② est un masque de saisie : seule F4 est ouverte.  ④ l'onglet « Le coût variable » ne lit que le tableau ① et les paramètres ci-dessus.</t>
         </is>
       </c>
-      <c r="C75" s="112" t="n"/>
-      <c r="D75" s="112" t="n"/>
-      <c r="E75" s="112" t="n"/>
-      <c r="F75" s="112" t="n"/>
-      <c r="G75" s="112" t="n"/>
-      <c r="H75" s="112" t="n"/>
-      <c r="I75" s="112" t="n"/>
-      <c r="J75" s="112" t="n"/>
-      <c r="K75" s="112" t="n"/>
-      <c r="L75" s="112" t="n"/>
+      <c r="C75" s="115" t="n"/>
+      <c r="D75" s="115" t="n"/>
+      <c r="E75" s="115" t="n"/>
+      <c r="F75" s="115" t="n"/>
+      <c r="G75" s="115" t="n"/>
+      <c r="H75" s="115" t="n"/>
+      <c r="I75" s="115" t="n"/>
+      <c r="J75" s="115" t="n"/>
+      <c r="K75" s="115" t="n"/>
+      <c r="L75" s="115" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -9409,2609 +11497,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.4" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>EDUSERVICES · le moteur d'acquisition</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>PROJETER 2027  —  le CA en quatre lignes, les coûts en sept familles</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-    </row>
-    <row r="3" ht="3" customHeight="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="47" t="inlineStr">
-        <is>
-          <t>La croissance se défait en deux, et la seconde moitié, c'est le moteur.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>On sait séparer ce que porte le socle de ce qu'ajoute le budget d'acquisition : +181 élèves en 2026, dont 31,8 dus au +10 % d'acquisition et 149,2 au socle. Le socle se saisit ; le geste, lui, n'est pas saisi — il est LIÉ aux cellules du premier onglet. C'est ce qui fait que ce budget et le moteur disent le même chiffre.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>ⓐ  Les huit saisies  ·  et la neuvième, qui n'en est pas une</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Chacune est une décision, et chacune a un propriétaire. Le Δ budget d'acquisition ne se saisit pas ici : il vient du geste de l'onglet « Le moteur ».</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>Saisie</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>Valeur retenue</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="inlineStr">
-        <is>
-          <t>D'où elle vient</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="113" t="inlineStr">
-        <is>
-          <t>CE QUI FAIT LE CHIFFRE D'AFFAIRES</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="114" t="inlineStr">
-        <is>
-          <t>Croissance du socle, hors geste d'acquisition</t>
-        </is>
-      </c>
-      <c r="C13" s="115" t="n"/>
-      <c r="D13" s="115" t="n"/>
-      <c r="E13" s="116" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="F13" s="115" t="n"/>
-      <c r="G13" s="117" t="inlineStr">
-        <is>
-          <t>constatée 2026, geste défalqué</t>
-        </is>
-      </c>
-      <c r="H13" s="115" t="n"/>
-      <c r="I13" s="115" t="n"/>
-      <c r="J13" s="115" t="n"/>
-      <c r="K13" s="115" t="n"/>
-      <c r="L13" s="115" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="114" t="inlineStr">
-        <is>
-          <t>Hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="C14" s="115" t="n"/>
-      <c r="D14" s="115" t="n"/>
-      <c r="E14" s="116" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F14" s="115" t="n"/>
-      <c r="G14" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H14" s="115" t="n"/>
-      <c r="I14" s="115" t="n"/>
-      <c r="J14" s="115" t="n"/>
-      <c r="K14" s="115" t="n"/>
-      <c r="L14" s="115" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="114" t="inlineStr">
-        <is>
-          <t>Δ budget d'acquisition  (6231)</t>
-        </is>
-      </c>
-      <c r="C15" s="115" t="n"/>
-      <c r="D15" s="115" t="n"/>
-      <c r="E15" s="118">
-        <f>'Le moteur'!F4</f>
-        <v/>
-      </c>
-      <c r="F15" s="115" t="n"/>
-      <c r="G15" s="119" t="inlineStr">
-        <is>
-          <t>LIÉ au geste, onglet « Le moteur »</t>
-        </is>
-      </c>
-      <c r="H15" s="115" t="n"/>
-      <c r="I15" s="115" t="n"/>
-      <c r="J15" s="115" t="n"/>
-      <c r="K15" s="115" t="n"/>
-      <c r="L15" s="115" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="113" t="inlineStr">
-        <is>
-          <t>CE QUI FAIT LES COÛTS</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="114" t="inlineStr">
-        <is>
-          <t>Inflation des charges externes</t>
-        </is>
-      </c>
-      <c r="C17" s="115" t="n"/>
-      <c r="D17" s="115" t="n"/>
-      <c r="E17" s="116" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F17" s="115" t="n"/>
-      <c r="G17" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H17" s="115" t="n"/>
-      <c r="I17" s="115" t="n"/>
-      <c r="J17" s="115" t="n"/>
-      <c r="K17" s="115" t="n"/>
-      <c r="L17" s="115" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="114" t="inlineStr">
-        <is>
-          <t>Effort de productivité achats &amp; structure</t>
-        </is>
-      </c>
-      <c r="C18" s="115" t="n"/>
-      <c r="D18" s="115" t="n"/>
-      <c r="E18" s="116" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="F18" s="115" t="n"/>
-      <c r="G18" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H18" s="115" t="n"/>
-      <c r="I18" s="115" t="n"/>
-      <c r="J18" s="115" t="n"/>
-      <c r="K18" s="115" t="n"/>
-      <c r="L18" s="115" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="114" t="inlineStr">
-        <is>
-          <t>Politique salariale sur la masse permanente</t>
-        </is>
-      </c>
-      <c r="C19" s="115" t="n"/>
-      <c r="D19" s="115" t="n"/>
-      <c r="E19" s="116" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F19" s="115" t="n"/>
-      <c r="G19" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H19" s="115" t="n"/>
-      <c r="I19" s="115" t="n"/>
-      <c r="J19" s="115" t="n"/>
-      <c r="K19" s="115" t="n"/>
-      <c r="L19" s="115" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="114" t="inlineStr">
-        <is>
-          <t>Variation des effectifs permanents</t>
-        </is>
-      </c>
-      <c r="C20" s="115" t="n"/>
-      <c r="D20" s="115" t="n"/>
-      <c r="E20" s="116" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F20" s="115" t="n"/>
-      <c r="G20" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H20" s="115" t="n"/>
-      <c r="I20" s="115" t="n"/>
-      <c r="J20" s="115" t="n"/>
-      <c r="K20" s="115" t="n"/>
-      <c r="L20" s="115" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="114" t="inlineStr">
-        <is>
-          <t>Δ budget de marque  (6236)</t>
-        </is>
-      </c>
-      <c r="C21" s="115" t="n"/>
-      <c r="D21" s="115" t="n"/>
-      <c r="E21" s="116" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="115" t="n"/>
-      <c r="G21" s="117" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H21" s="115" t="n"/>
-      <c r="I21" s="115" t="n"/>
-      <c r="J21" s="115" t="n"/>
-      <c r="K21" s="115" t="n"/>
-      <c r="L21" s="115" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="114" t="inlineStr">
-        <is>
-          <t>Dotations aux amortissements</t>
-        </is>
-      </c>
-      <c r="C22" s="115" t="n"/>
-      <c r="D22" s="115" t="n"/>
-      <c r="E22" s="116" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F22" s="115" t="n"/>
-      <c r="G22" s="117" t="inlineStr">
-        <is>
-          <t>plan d'amortissement</t>
-        </is>
-      </c>
-      <c r="H22" s="115" t="n"/>
-      <c r="I22" s="115" t="n"/>
-      <c r="J22" s="115" t="n"/>
-      <c r="K22" s="115" t="n"/>
-      <c r="L22" s="115" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>ⓑ  Le volume 2027  ·  ce que porte le socle, ce qu'ajoute le geste</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>La ligne « ce que le geste ajoute » n'est pas calculée ici : c'est la cellule I58 de l'onglet « Le moteur ». Bouger F4 là-bas bouge ce budget-ci.</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>Grandeur</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F27" s="26" t="n"/>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="120" t="inlineStr">
-        <is>
-          <t>Effectifs 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="121" t="n"/>
-      <c r="D28" s="121" t="n"/>
-      <c r="E28" s="59">
-        <f>'Le moteur'!N34</f>
-        <v/>
-      </c>
-      <c r="F28" s="121" t="n"/>
-      <c r="G28" s="122" t="inlineStr">
-        <is>
-          <t>restitué</t>
-        </is>
-      </c>
-      <c r="H28" s="121" t="n"/>
-      <c r="I28" s="121" t="n"/>
-      <c r="J28" s="121" t="n"/>
-      <c r="K28" s="121" t="n"/>
-      <c r="L28" s="121" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="120" t="inlineStr">
-        <is>
-          <t>+ ce que porte le socle</t>
-        </is>
-      </c>
-      <c r="C29" s="121" t="n"/>
-      <c r="D29" s="121" t="n"/>
-      <c r="E29" s="123">
-        <f>E28*$E$13</f>
-        <v/>
-      </c>
-      <c r="F29" s="121" t="n"/>
-      <c r="G29" s="122" t="inlineStr">
-        <is>
-          <t>rétention, passage, notoriété</t>
-        </is>
-      </c>
-      <c r="H29" s="121" t="n"/>
-      <c r="I29" s="121" t="n"/>
-      <c r="J29" s="121" t="n"/>
-      <c r="K29" s="121" t="n"/>
-      <c r="L29" s="121" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="120" t="inlineStr">
-        <is>
-          <t>+ ce que le geste ajoute</t>
-        </is>
-      </c>
-      <c r="C30" s="121" t="n"/>
-      <c r="D30" s="121" t="n"/>
-      <c r="E30" s="123">
-        <f>'Le moteur'!I58</f>
-        <v/>
-      </c>
-      <c r="F30" s="121" t="n"/>
-      <c r="G30" s="122" t="inlineStr">
-        <is>
-          <t>LIÉ au moteur — les inscrits gagnés par le Δ budget</t>
-        </is>
-      </c>
-      <c r="H30" s="121" t="n"/>
-      <c r="I30" s="121" t="n"/>
-      <c r="J30" s="121" t="n"/>
-      <c r="K30" s="121" t="n"/>
-      <c r="L30" s="121" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="49">
-        <f> Effectifs 2027</f>
-        <v/>
-      </c>
-      <c r="C31" s="121" t="n"/>
-      <c r="D31" s="121" t="n"/>
-      <c r="E31" s="124">
-        <f>E28+E29+E30</f>
-        <v/>
-      </c>
-      <c r="F31" s="121" t="n"/>
-      <c r="G31" s="122" t="inlineStr"/>
-      <c r="H31" s="121" t="n"/>
-      <c r="I31" s="121" t="n"/>
-      <c r="J31" s="121" t="n"/>
-      <c r="K31" s="121" t="n"/>
-      <c r="L31" s="121" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="120" t="inlineStr">
-        <is>
-          <t>Croissance totale</t>
-        </is>
-      </c>
-      <c r="C32" s="121" t="n"/>
-      <c r="D32" s="121" t="n"/>
-      <c r="E32" s="125">
-        <f>IFERROR(E31/E28-1,0)</f>
-        <v/>
-      </c>
-      <c r="F32" s="121" t="n"/>
-      <c r="G32" s="122" t="inlineStr">
-        <is>
-          <t>elle n'est pas saisie : elle se déduit</t>
-        </is>
-      </c>
-      <c r="H32" s="121" t="n"/>
-      <c r="I32" s="121" t="n"/>
-      <c r="J32" s="121" t="n"/>
-      <c r="K32" s="121" t="n"/>
-      <c r="L32" s="121" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="120" t="inlineStr">
-        <is>
-          <t>Places du réseau</t>
-        </is>
-      </c>
-      <c r="C33" s="121" t="n"/>
-      <c r="D33" s="121" t="n"/>
-      <c r="E33" s="59">
-        <f>'Le moteur'!O34</f>
-        <v/>
-      </c>
-      <c r="F33" s="121" t="n"/>
-      <c r="G33" s="122" t="inlineStr">
-        <is>
-          <t>135 classes, inchangées depuis 2024</t>
-        </is>
-      </c>
-      <c r="H33" s="121" t="n"/>
-      <c r="I33" s="121" t="n"/>
-      <c r="J33" s="121" t="n"/>
-      <c r="K33" s="121" t="n"/>
-      <c r="L33" s="121" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="120" t="inlineStr">
-        <is>
-          <t>Classes 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="121" t="n"/>
-      <c r="D34" s="121" t="n"/>
-      <c r="E34" s="59">
-        <f>'Le moteur'!P34</f>
-        <v/>
-      </c>
-      <c r="F34" s="121" t="n"/>
-      <c r="G34" s="122" t="inlineStr"/>
-      <c r="H34" s="121" t="n"/>
-      <c r="I34" s="121" t="n"/>
-      <c r="J34" s="121" t="n"/>
-      <c r="K34" s="121" t="n"/>
-      <c r="L34" s="121" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="120" t="inlineStr">
-        <is>
-          <t>Capacité moyenne d'une classe</t>
-        </is>
-      </c>
-      <c r="C35" s="121" t="n"/>
-      <c r="D35" s="121" t="n"/>
-      <c r="E35" s="123">
-        <f>IFERROR(E33/E34,0)</f>
-        <v/>
-      </c>
-      <c r="F35" s="121" t="n"/>
-      <c r="G35" s="122" t="inlineStr"/>
-      <c r="H35" s="121" t="n"/>
-      <c r="I35" s="121" t="n"/>
-      <c r="J35" s="121" t="n"/>
-      <c r="K35" s="121" t="n"/>
-      <c r="L35" s="121" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="120" t="inlineStr">
-        <is>
-          <t>Croissance possible avant saturation</t>
-        </is>
-      </c>
-      <c r="C36" s="121" t="n"/>
-      <c r="D36" s="121" t="n"/>
-      <c r="E36" s="72">
-        <f>'Le coût variable'!L48</f>
-        <v/>
-      </c>
-      <c r="F36" s="121" t="n"/>
-      <c r="G36" s="122" t="inlineStr">
-        <is>
-          <t>le premier campus qui sature : MBway Paris</t>
-        </is>
-      </c>
-      <c r="H36" s="121" t="n"/>
-      <c r="I36" s="121" t="n"/>
-      <c r="J36" s="121" t="n"/>
-      <c r="K36" s="121" t="n"/>
-      <c r="L36" s="121" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>Classes à ouvrir en 2027</t>
-        </is>
-      </c>
-      <c r="C37" s="121" t="n"/>
-      <c r="D37" s="121" t="n"/>
-      <c r="E37" s="126">
-        <f>MAX(0,ROUNDUP((E31-E33)/E35,0))</f>
-        <v/>
-      </c>
-      <c r="F37" s="121" t="n"/>
-      <c r="G37" s="122" t="inlineStr">
-        <is>
-          <t>aucune — et c'est toute la démonstration</t>
-        </is>
-      </c>
-      <c r="H37" s="121" t="n"/>
-      <c r="I37" s="121" t="n"/>
-      <c r="J37" s="121" t="n"/>
-      <c r="K37" s="121" t="n"/>
-      <c r="L37" s="121" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="120" t="inlineStr">
-        <is>
-          <t>Classes 2027</t>
-        </is>
-      </c>
-      <c r="C38" s="121" t="n"/>
-      <c r="D38" s="121" t="n"/>
-      <c r="E38" s="59">
-        <f>E34+E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="121" t="n"/>
-      <c r="G38" s="122" t="inlineStr"/>
-      <c r="H38" s="121" t="n"/>
-      <c r="I38" s="121" t="n"/>
-      <c r="J38" s="121" t="n"/>
-      <c r="K38" s="121" t="n"/>
-      <c r="L38" s="121" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="120" t="inlineStr">
-        <is>
-          <t>Inducteur du compte 621</t>
-        </is>
-      </c>
-      <c r="C39" s="121" t="n"/>
-      <c r="D39" s="121" t="n"/>
-      <c r="E39" s="127">
-        <f>IFERROR(E38/E34,0)</f>
-        <v/>
-      </c>
-      <c r="F39" s="121" t="n"/>
-      <c r="G39" s="122" t="inlineStr">
-        <is>
-          <t>le ratio de CLASSES, jamais celui des effectifs</t>
-        </is>
-      </c>
-      <c r="H39" s="121" t="n"/>
-      <c r="I39" s="121" t="n"/>
-      <c r="J39" s="121" t="n"/>
-      <c r="K39" s="121" t="n"/>
-      <c r="L39" s="121" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>À +6 % l'an, MBway Paris tient jusqu'en 2029. Vérifiable ligne à ligne : onglet « Le coût variable », dernière colonne du tableau campus.</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>ⓒ  Le chiffre d'affaires 2027  ·  quatre lignes, et une seule est une décision</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>Le socle est déjà inscrit, le geste est celui du moteur, le prix est un arbitrage. Rien d'autre n'entre dans le CA.</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>Ligne</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="n"/>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="120" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires 2026</t>
-        </is>
-      </c>
-      <c r="C47" s="121" t="n"/>
-      <c r="D47" s="121" t="n"/>
-      <c r="E47" s="51">
-        <f>'Le coût variable'!D95</f>
-        <v/>
-      </c>
-      <c r="F47" s="121" t="n"/>
-      <c r="G47" s="122" t="inlineStr">
-        <is>
-          <t>restitué · 706 + 7062 + 708</t>
-        </is>
-      </c>
-      <c r="H47" s="121" t="n"/>
-      <c r="I47" s="121" t="n"/>
-      <c r="J47" s="121" t="n"/>
-      <c r="K47" s="121" t="n"/>
-      <c r="L47" s="121" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="120" t="inlineStr">
-        <is>
-          <t>+ ce que porte le socle</t>
-        </is>
-      </c>
-      <c r="C48" s="121" t="n"/>
-      <c r="D48" s="121" t="n"/>
-      <c r="E48" s="51">
-        <f>E47*$E$13</f>
-        <v/>
-      </c>
-      <c r="F48" s="121" t="n"/>
-      <c r="G48" s="122" t="inlineStr">
-        <is>
-          <t>la rentrée déjà engagée</t>
-        </is>
-      </c>
-      <c r="H48" s="121" t="n"/>
-      <c r="I48" s="121" t="n"/>
-      <c r="J48" s="121" t="n"/>
-      <c r="K48" s="121" t="n"/>
-      <c r="L48" s="121" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="120" t="inlineStr">
-        <is>
-          <t>+ ce que le geste ajoute</t>
-        </is>
-      </c>
-      <c r="C49" s="121" t="n"/>
-      <c r="D49" s="121" t="n"/>
-      <c r="E49" s="51">
-        <f>'Le moteur'!J58</f>
-        <v/>
-      </c>
-      <c r="F49" s="121" t="n"/>
-      <c r="G49" s="122" t="inlineStr">
-        <is>
-          <t>LIÉ au moteur — le CA gagné par le Δ budget</t>
-        </is>
-      </c>
-      <c r="H49" s="121" t="n"/>
-      <c r="I49" s="121" t="n"/>
-      <c r="J49" s="121" t="n"/>
-      <c r="K49" s="121" t="n"/>
-      <c r="L49" s="121" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n"/>
-      <c r="B50" s="120" t="inlineStr">
-        <is>
-          <t>+ effet prix</t>
-        </is>
-      </c>
-      <c r="C50" s="121" t="n"/>
-      <c r="D50" s="121" t="n"/>
-      <c r="E50" s="51">
-        <f>(E47+E48+E49)*$E$14</f>
-        <v/>
-      </c>
-      <c r="F50" s="121" t="n"/>
-      <c r="G50" s="122" t="inlineStr">
-        <is>
-          <t>la hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="H50" s="121" t="n"/>
-      <c r="I50" s="121" t="n"/>
-      <c r="J50" s="121" t="n"/>
-      <c r="K50" s="121" t="n"/>
-      <c r="L50" s="121" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n"/>
-      <c r="B51" s="49">
-        <f> Chiffre d'affaires 2027</f>
-        <v/>
-      </c>
-      <c r="C51" s="121" t="n"/>
-      <c r="D51" s="121" t="n"/>
-      <c r="E51" s="128">
-        <f>SUM(E47:E50)</f>
-        <v/>
-      </c>
-      <c r="F51" s="121" t="n"/>
-      <c r="G51" s="122" t="inlineStr"/>
-      <c r="H51" s="121" t="n"/>
-      <c r="I51" s="121" t="n"/>
-      <c r="J51" s="121" t="n"/>
-      <c r="K51" s="121" t="n"/>
-      <c r="L51" s="121" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="5" t="n"/>
-      <c r="K52" s="5" t="n"/>
-      <c r="L52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n"/>
-      <c r="B53" s="129">
-        <f>"Sur "&amp;TEXT(E51-E47,"#,##0 €")&amp;" de croissance, "&amp;TEXT(E48/(E51-E47),"0 %")&amp;" viennent du socle déjà inscrit, "&amp;TEXT(E49/(E51-E47),"0 %")&amp;" du geste d'acquisition et "&amp;TEXT(E50/(E51-E47),"0 %")&amp;" du prix. Le chiffre d'affaires ne se décrète pas."</f>
-        <v/>
-      </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="n"/>
-      <c r="B55" s="38" t="inlineStr">
-        <is>
-          <t>ⓓ  Les coûts 2027  ·  sept familles, sept règles</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="5" t="n"/>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>Un budget qui indexe tout au même taux ne dit rien. Celui-ci donne à chaque euro l'inducteur de son comportement — et c'est ce qui fait apparaître où est le levier, et surtout où il n'est pas.</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="n"/>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>Famille · compte</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2026</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
-        <is>
-          <t>Ce qui la fait bouger</t>
-        </is>
-      </c>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>Effet volume</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="inlineStr">
-        <is>
-          <t>Effet prix</t>
-        </is>
-      </c>
-      <c r="H58" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2027</t>
-        </is>
-      </c>
-      <c r="I58" s="26" t="inlineStr">
-        <is>
-          <t>Variation</t>
-        </is>
-      </c>
-      <c r="J58" s="26" t="inlineStr">
-        <is>
-          <t>Ce qui décide</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="n"/>
-      <c r="B59" s="64" t="inlineStr">
-        <is>
-          <t>①  Suit l'ÉLÈVE</t>
-        </is>
-      </c>
-      <c r="C59" s="64" t="n"/>
-      <c r="D59" s="68">
-        <f>SUM(D60:D61)</f>
-        <v/>
-      </c>
-      <c r="E59" s="130" t="inlineStr">
-        <is>
-          <t>effectifs × inflation</t>
-        </is>
-      </c>
-      <c r="F59" s="131" t="inlineStr"/>
-      <c r="G59" s="131" t="inlineStr"/>
-      <c r="H59" s="68">
-        <f>SUM(H60:H61)</f>
-        <v/>
-      </c>
-      <c r="I59" s="132">
-        <f>IFERROR(H59/D59-1,0)</f>
-        <v/>
-      </c>
-      <c r="J59" s="133" t="inlineStr">
-        <is>
-          <t>604 + 6063</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="5" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n"/>
-      <c r="B60" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      604 · Achats d'études et supports pédagogiques</t>
-        </is>
-      </c>
-      <c r="C60" s="107" t="n"/>
-      <c r="D60" s="135">
-        <f>'Le coût variable'!D74</f>
-        <v/>
-      </c>
-      <c r="E60" s="107" t="inlineStr"/>
-      <c r="F60" s="136">
-        <f>$E$31/$E$28</f>
-        <v/>
-      </c>
-      <c r="G60" s="136">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H60" s="135">
-        <f>D60*F60*G60</f>
-        <v/>
-      </c>
-      <c r="I60" s="137">
-        <f>IFERROR(H60/D60-1,0)</f>
-        <v/>
-      </c>
-      <c r="J60" s="107" t="inlineStr"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6063 · Fournitures pédagogiques et administratives</t>
-        </is>
-      </c>
-      <c r="C61" s="107" t="n"/>
-      <c r="D61" s="135">
-        <f>'Le coût variable'!D75</f>
-        <v/>
-      </c>
-      <c r="E61" s="107" t="inlineStr"/>
-      <c r="F61" s="136">
-        <f>$E$31/$E$28</f>
-        <v/>
-      </c>
-      <c r="G61" s="136">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H61" s="135">
-        <f>D61*F61*G61</f>
-        <v/>
-      </c>
-      <c r="I61" s="137">
-        <f>IFERROR(H61/D61-1,0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="107" t="inlineStr"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="64" t="inlineStr">
-        <is>
-          <t>②  Suit la CLASSE</t>
-        </is>
-      </c>
-      <c r="C62" s="64" t="n"/>
-      <c r="D62" s="68">
-        <f>SUM(D63:D63)</f>
-        <v/>
-      </c>
-      <c r="E62" s="138" t="inlineStr">
-        <is>
-          <t>classes × inflation</t>
-        </is>
-      </c>
-      <c r="F62" s="131" t="inlineStr"/>
-      <c r="G62" s="131" t="inlineStr"/>
-      <c r="H62" s="68">
-        <f>SUM(H63:H63)</f>
-        <v/>
-      </c>
-      <c r="I62" s="139">
-        <f>IFERROR(H62/D62-1,0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="133" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      621 · Personnel extérieur — enseignants vacataires</t>
-        </is>
-      </c>
-      <c r="C63" s="107" t="n"/>
-      <c r="D63" s="135">
-        <f>'Le coût variable'!D76</f>
-        <v/>
-      </c>
-      <c r="E63" s="107" t="inlineStr"/>
-      <c r="F63" s="136">
-        <f>$E$39</f>
-        <v/>
-      </c>
-      <c r="G63" s="136">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H63" s="135">
-        <f>D63*F63*G63</f>
-        <v/>
-      </c>
-      <c r="I63" s="137">
-        <f>IFERROR(H63/D63-1,0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="107" t="inlineStr"/>
-      <c r="K63" s="5" t="n"/>
-      <c r="L63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="64" t="inlineStr">
-        <is>
-          <t>③  Suit les POSTES</t>
-        </is>
-      </c>
-      <c r="C64" s="64" t="n"/>
-      <c r="D64" s="68">
-        <f>SUM(D65:D67)</f>
-        <v/>
-      </c>
-      <c r="E64" s="140" t="inlineStr">
-        <is>
-          <t>politique salariale, + les postes créés</t>
-        </is>
-      </c>
-      <c r="F64" s="131" t="inlineStr"/>
-      <c r="G64" s="131" t="inlineStr"/>
-      <c r="H64" s="68">
-        <f>SUM(H65:H67)</f>
-        <v/>
-      </c>
-      <c r="I64" s="141">
-        <f>IFERROR(H64/D64-1,0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="133" t="inlineStr">
-        <is>
-          <t>6411 + 6413 + 6414</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6411 · Salaires — enseignants permanents</t>
-        </is>
-      </c>
-      <c r="C65" s="107" t="n"/>
-      <c r="D65" s="135">
-        <f>'Le coût variable'!D77</f>
-        <v/>
-      </c>
-      <c r="E65" s="107" t="inlineStr"/>
-      <c r="F65" s="136">
-        <f>1+$E$20</f>
-        <v/>
-      </c>
-      <c r="G65" s="136">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H65" s="135">
-        <f>D65*F65*G65</f>
-        <v/>
-      </c>
-      <c r="I65" s="137">
-        <f>IFERROR(H65/D65-1,0)</f>
-        <v/>
-      </c>
-      <c r="J65" s="107" t="inlineStr"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="n"/>
-      <c r="B66" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6413 · Salaires — personnel administratif des campus</t>
-        </is>
-      </c>
-      <c r="C66" s="107" t="n"/>
-      <c r="D66" s="135">
-        <f>'Le coût variable'!D79</f>
-        <v/>
-      </c>
-      <c r="E66" s="107" t="inlineStr"/>
-      <c r="F66" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="136">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H66" s="135">
-        <f>D66*F66*G66</f>
-        <v/>
-      </c>
-      <c r="I66" s="137">
-        <f>IFERROR(H66/D66-1,0)</f>
-        <v/>
-      </c>
-      <c r="J66" s="107" t="inlineStr"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6414 · Salaires du siège</t>
-        </is>
-      </c>
-      <c r="C67" s="107" t="n"/>
-      <c r="D67" s="135">
-        <f>'Le coût variable'!D87</f>
-        <v/>
-      </c>
-      <c r="E67" s="107" t="inlineStr"/>
-      <c r="F67" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="136">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H67" s="135">
-        <f>D67*F67*G67</f>
-        <v/>
-      </c>
-      <c r="I67" s="137">
-        <f>IFERROR(H67/D67-1,0)</f>
-        <v/>
-      </c>
-      <c r="J67" s="107" t="inlineStr"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="n"/>
-      <c r="B68" s="64" t="inlineStr">
-        <is>
-          <t>④  Assis sur la MASSE</t>
-        </is>
-      </c>
-      <c r="C68" s="64" t="n"/>
-      <c r="D68" s="68">
-        <f>SUM(D69:D71)</f>
-        <v/>
-      </c>
-      <c r="E68" s="140" t="inlineStr">
-        <is>
-          <t>au prorata de la masse salariale</t>
-        </is>
-      </c>
-      <c r="F68" s="131" t="inlineStr"/>
-      <c r="G68" s="131" t="inlineStr"/>
-      <c r="H68" s="68">
-        <f>SUM(H69:H71)</f>
-        <v/>
-      </c>
-      <c r="I68" s="141">
-        <f>IFERROR(H68/D68-1,0)</f>
-        <v/>
-      </c>
-      <c r="J68" s="133" t="inlineStr">
-        <is>
-          <t>645 + 6331 + 6333</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      645 · Charges sociales sur les salaires</t>
-        </is>
-      </c>
-      <c r="C69" s="107" t="n"/>
-      <c r="D69" s="135">
-        <f>'Le coût variable'!D80</f>
-        <v/>
-      </c>
-      <c r="E69" s="107" t="inlineStr"/>
-      <c r="F69" s="136">
-        <f>(H65+H66+H67)/(D65+D66+D67)</f>
-        <v/>
-      </c>
-      <c r="G69" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="135">
-        <f>D69*F69*G69</f>
-        <v/>
-      </c>
-      <c r="I69" s="137">
-        <f>IFERROR(H69/D69-1,0)</f>
-        <v/>
-      </c>
-      <c r="J69" s="107" t="inlineStr"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6331 · Versement mobilité</t>
-        </is>
-      </c>
-      <c r="C70" s="107" t="n"/>
-      <c r="D70" s="135">
-        <f>'Le coût variable'!D91</f>
-        <v/>
-      </c>
-      <c r="E70" s="107" t="inlineStr"/>
-      <c r="F70" s="136">
-        <f>(H65+H66+H67)/(D65+D66+D67)</f>
-        <v/>
-      </c>
-      <c r="G70" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="135">
-        <f>D70*F70*G70</f>
-        <v/>
-      </c>
-      <c r="I70" s="137">
-        <f>IFERROR(H70/D70-1,0)</f>
-        <v/>
-      </c>
-      <c r="J70" s="107" t="inlineStr"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6333 · Participation à la formation professionnelle</t>
-        </is>
-      </c>
-      <c r="C71" s="107" t="n"/>
-      <c r="D71" s="135">
-        <f>'Le coût variable'!D92</f>
-        <v/>
-      </c>
-      <c r="E71" s="107" t="inlineStr"/>
-      <c r="F71" s="136">
-        <f>(H65+H66+H67)/(D65+D66+D67)</f>
-        <v/>
-      </c>
-      <c r="G71" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="135">
-        <f>D71*F71*G71</f>
-        <v/>
-      </c>
-      <c r="I71" s="137">
-        <f>IFERROR(H71/D71-1,0)</f>
-        <v/>
-      </c>
-      <c r="J71" s="107" t="inlineStr"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="64" t="inlineStr">
-        <is>
-          <t>⑤  INDEXÉ</t>
-        </is>
-      </c>
-      <c r="C72" s="64" t="n"/>
-      <c r="D72" s="68">
-        <f>SUM(D73:D80)</f>
-        <v/>
-      </c>
-      <c r="E72" s="142" t="inlineStr">
-        <is>
-          <t>inflation moins l'effort de productivité</t>
-        </is>
-      </c>
-      <c r="F72" s="131" t="inlineStr"/>
-      <c r="G72" s="131" t="inlineStr"/>
-      <c r="H72" s="68">
-        <f>SUM(H73:H80)</f>
-        <v/>
-      </c>
-      <c r="I72" s="143">
-        <f>IFERROR(H72/D72-1,0)</f>
-        <v/>
-      </c>
-      <c r="J72" s="133" t="inlineStr">
-        <is>
-          <t>613 · 615 · 616 · 625 · 63511 · 6226 · 626 · 6281</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="5" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      613 · Locations immobilières des campus</t>
-        </is>
-      </c>
-      <c r="C73" s="107" t="n"/>
-      <c r="D73" s="135">
-        <f>'Le coût variable'!D81</f>
-        <v/>
-      </c>
-      <c r="E73" s="107" t="inlineStr"/>
-      <c r="F73" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H73" s="135">
-        <f>D73*F73*G73</f>
-        <v/>
-      </c>
-      <c r="I73" s="137">
-        <f>IFERROR(H73/D73-1,0)</f>
-        <v/>
-      </c>
-      <c r="J73" s="107" t="inlineStr"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      615 · Entretien et réparations</t>
-        </is>
-      </c>
-      <c r="C74" s="107" t="n"/>
-      <c r="D74" s="135">
-        <f>'Le coût variable'!D82</f>
-        <v/>
-      </c>
-      <c r="E74" s="107" t="inlineStr"/>
-      <c r="F74" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H74" s="135">
-        <f>D74*F74*G74</f>
-        <v/>
-      </c>
-      <c r="I74" s="137">
-        <f>IFERROR(H74/D74-1,0)</f>
-        <v/>
-      </c>
-      <c r="J74" s="107" t="inlineStr"/>
-      <c r="K74" s="5" t="n"/>
-      <c r="L74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="n"/>
-      <c r="B75" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      616 · Primes d'assurance</t>
-        </is>
-      </c>
-      <c r="C75" s="107" t="n"/>
-      <c r="D75" s="135">
-        <f>'Le coût variable'!D83</f>
-        <v/>
-      </c>
-      <c r="E75" s="107" t="inlineStr"/>
-      <c r="F75" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H75" s="135">
-        <f>D75*F75*G75</f>
-        <v/>
-      </c>
-      <c r="I75" s="137">
-        <f>IFERROR(H75/D75-1,0)</f>
-        <v/>
-      </c>
-      <c r="J75" s="107" t="inlineStr"/>
-      <c r="K75" s="5" t="n"/>
-      <c r="L75" s="5" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      625 · Déplacements, missions et réceptions</t>
-        </is>
-      </c>
-      <c r="C76" s="107" t="n"/>
-      <c r="D76" s="135">
-        <f>'Le coût variable'!D84</f>
-        <v/>
-      </c>
-      <c r="E76" s="107" t="inlineStr"/>
-      <c r="F76" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H76" s="135">
-        <f>D76*F76*G76</f>
-        <v/>
-      </c>
-      <c r="I76" s="137">
-        <f>IFERROR(H76/D76-1,0)</f>
-        <v/>
-      </c>
-      <c r="J76" s="107" t="inlineStr"/>
-      <c r="K76" s="5" t="n"/>
-      <c r="L76" s="5" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      63511 · Contribution économique territoriale</t>
-        </is>
-      </c>
-      <c r="C77" s="107" t="n"/>
-      <c r="D77" s="135">
-        <f>'Le coût variable'!D85</f>
-        <v/>
-      </c>
-      <c r="E77" s="107" t="inlineStr"/>
-      <c r="F77" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H77" s="135">
-        <f>D77*F77*G77</f>
-        <v/>
-      </c>
-      <c r="I77" s="137">
-        <f>IFERROR(H77/D77-1,0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="107" t="inlineStr"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="n"/>
-      <c r="B78" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6226 · Honoraires</t>
-        </is>
-      </c>
-      <c r="C78" s="107" t="n"/>
-      <c r="D78" s="135">
-        <f>'Le coût variable'!D88</f>
-        <v/>
-      </c>
-      <c r="E78" s="107" t="inlineStr"/>
-      <c r="F78" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H78" s="135">
-        <f>D78*F78*G78</f>
-        <v/>
-      </c>
-      <c r="I78" s="137">
-        <f>IFERROR(H78/D78-1,0)</f>
-        <v/>
-      </c>
-      <c r="J78" s="107" t="inlineStr"/>
-      <c r="K78" s="5" t="n"/>
-      <c r="L78" s="5" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="n"/>
-      <c r="B79" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      626 · Frais postaux et de télécommunications</t>
-        </is>
-      </c>
-      <c r="C79" s="107" t="n"/>
-      <c r="D79" s="135">
-        <f>'Le coût variable'!D89</f>
-        <v/>
-      </c>
-      <c r="E79" s="107" t="inlineStr"/>
-      <c r="F79" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H79" s="135">
-        <f>D79*F79*G79</f>
-        <v/>
-      </c>
-      <c r="I79" s="137">
-        <f>IFERROR(H79/D79-1,0)</f>
-        <v/>
-      </c>
-      <c r="J79" s="107" t="inlineStr"/>
-      <c r="K79" s="5" t="n"/>
-      <c r="L79" s="5" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="n"/>
-      <c r="B80" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6281 · Cotisations et concours divers</t>
-        </is>
-      </c>
-      <c r="C80" s="107" t="n"/>
-      <c r="D80" s="135">
-        <f>'Le coût variable'!D90</f>
-        <v/>
-      </c>
-      <c r="E80" s="107" t="inlineStr"/>
-      <c r="F80" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="136">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H80" s="135">
-        <f>D80*F80*G80</f>
-        <v/>
-      </c>
-      <c r="I80" s="137">
-        <f>IFERROR(H80/D80-1,0)</f>
-        <v/>
-      </c>
-      <c r="J80" s="107" t="inlineStr"/>
-      <c r="K80" s="5" t="n"/>
-      <c r="L80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="n"/>
-      <c r="B81" s="64" t="inlineStr">
-        <is>
-          <t>⑥  DÉCIDÉ</t>
-        </is>
-      </c>
-      <c r="C81" s="64" t="n"/>
-      <c r="D81" s="68">
-        <f>SUM(D82:D83)</f>
-        <v/>
-      </c>
-      <c r="E81" s="144" t="inlineStr">
-        <is>
-          <t>le geste, et le budget de marque</t>
-        </is>
-      </c>
-      <c r="F81" s="131" t="inlineStr"/>
-      <c r="G81" s="131" t="inlineStr"/>
-      <c r="H81" s="68">
-        <f>SUM(H82:H83)</f>
-        <v/>
-      </c>
-      <c r="I81" s="145">
-        <f>IFERROR(H81/D81-1,0)</f>
-        <v/>
-      </c>
-      <c r="J81" s="133" t="inlineStr">
-        <is>
-          <t>6231 + 6236</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="n"/>
-      <c r="L81" s="5" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n"/>
-      <c r="B82" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6231 · Annonces et insertions — budget d'acquisition</t>
-        </is>
-      </c>
-      <c r="C82" s="107" t="n"/>
-      <c r="D82" s="135">
-        <f>'Le coût variable'!D78</f>
-        <v/>
-      </c>
-      <c r="E82" s="107" t="inlineStr"/>
-      <c r="F82" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="136">
-        <f>1+$E$15</f>
-        <v/>
-      </c>
-      <c r="H82" s="135">
-        <f>D82*F82*G82</f>
-        <v/>
-      </c>
-      <c r="I82" s="137">
-        <f>IFERROR(H82/D82-1,0)</f>
-        <v/>
-      </c>
-      <c r="J82" s="107" t="inlineStr"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="n"/>
-      <c r="B83" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6236 · Catalogues et imprimés — marketing de marque</t>
-        </is>
-      </c>
-      <c r="C83" s="107" t="n"/>
-      <c r="D83" s="135">
-        <f>'Le coût variable'!D86</f>
-        <v/>
-      </c>
-      <c r="E83" s="107" t="inlineStr"/>
-      <c r="F83" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="136">
-        <f>1+$E$21</f>
-        <v/>
-      </c>
-      <c r="H83" s="135">
-        <f>D83*F83*G83</f>
-        <v/>
-      </c>
-      <c r="I83" s="137">
-        <f>IFERROR(H83/D83-1,0)</f>
-        <v/>
-      </c>
-      <c r="J83" s="107" t="inlineStr"/>
-      <c r="K83" s="5" t="n"/>
-      <c r="L83" s="5" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="n"/>
-      <c r="B84" s="64" t="inlineStr">
-        <is>
-          <t>⑦  HORS EBITDA</t>
-        </is>
-      </c>
-      <c r="C84" s="64" t="n"/>
-      <c r="D84" s="68">
-        <f>SUM(D85:D85)</f>
-        <v/>
-      </c>
-      <c r="E84" s="142" t="inlineStr">
-        <is>
-          <t>le plan d'amortissement</t>
-        </is>
-      </c>
-      <c r="F84" s="131" t="inlineStr"/>
-      <c r="G84" s="131" t="inlineStr"/>
-      <c r="H84" s="68">
-        <f>SUM(H85:H85)</f>
-        <v/>
-      </c>
-      <c r="I84" s="143">
-        <f>IFERROR(H84/D84-1,0)</f>
-        <v/>
-      </c>
-      <c r="J84" s="133" t="inlineStr">
-        <is>
-          <t>6811</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="n"/>
-      <c r="L84" s="5" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="n"/>
-      <c r="B85" s="134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6811 · Dotations aux amortissements</t>
-        </is>
-      </c>
-      <c r="C85" s="107" t="n"/>
-      <c r="D85" s="135">
-        <f>'Le coût variable'!D93</f>
-        <v/>
-      </c>
-      <c r="E85" s="107" t="inlineStr"/>
-      <c r="F85" s="136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="136">
-        <f>1+$E$22</f>
-        <v/>
-      </c>
-      <c r="H85" s="135">
-        <f>D85*F85*G85</f>
-        <v/>
-      </c>
-      <c r="I85" s="137">
-        <f>IFERROR(H85/D85-1,0)</f>
-        <v/>
-      </c>
-      <c r="J85" s="107" t="inlineStr"/>
-      <c r="K85" s="5" t="n"/>
-      <c r="L85" s="5" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="n"/>
-      <c r="B86" s="64" t="inlineStr">
-        <is>
-          <t>TOTAL DES CHARGES  ·  dotations incluses</t>
-        </is>
-      </c>
-      <c r="C86" s="64" t="n"/>
-      <c r="D86" s="68">
-        <f>D59+D62+D64+D68+D72+D81+D84</f>
-        <v/>
-      </c>
-      <c r="E86" s="64" t="inlineStr"/>
-      <c r="F86" s="131" t="inlineStr"/>
-      <c r="G86" s="131" t="inlineStr"/>
-      <c r="H86" s="68">
-        <f>H59+H62+H64+H68+H72+H81+H84</f>
-        <v/>
-      </c>
-      <c r="I86" s="69">
-        <f>IFERROR(H86/D86-1,0)</f>
-        <v/>
-      </c>
-      <c r="J86" s="64" t="inlineStr"/>
-      <c r="K86" s="5" t="n"/>
-      <c r="L86" s="5" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="87" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires</t>
-        </is>
-      </c>
-      <c r="C87" s="87" t="n"/>
-      <c r="D87" s="88">
-        <f>'Le coût variable'!D95</f>
-        <v/>
-      </c>
-      <c r="E87" s="87" t="inlineStr"/>
-      <c r="F87" s="146" t="inlineStr"/>
-      <c r="G87" s="146" t="inlineStr"/>
-      <c r="H87" s="88">
-        <f>E51</f>
-        <v/>
-      </c>
-      <c r="I87" s="147">
-        <f>IFERROR(H87/D87-1,0)</f>
-        <v/>
-      </c>
-      <c r="J87" s="87" t="inlineStr">
-        <is>
-          <t>bloc ⓒ ci-dessus</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="n"/>
-      <c r="L87" s="5" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="n"/>
-      <c r="B88" s="64" t="inlineStr">
-        <is>
-          <t>EBITDA  ·  hors dotations</t>
-        </is>
-      </c>
-      <c r="C88" s="64" t="n"/>
-      <c r="D88" s="148">
-        <f>D87-D86+D85</f>
-        <v/>
-      </c>
-      <c r="E88" s="64" t="inlineStr"/>
-      <c r="F88" s="131" t="inlineStr"/>
-      <c r="G88" s="131" t="inlineStr"/>
-      <c r="H88" s="148">
-        <f>H87-H86+H85</f>
-        <v/>
-      </c>
-      <c r="I88" s="69">
-        <f>IFERROR(H88/D88-1,0)</f>
-        <v/>
-      </c>
-      <c r="J88" s="64" t="inlineStr"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="n"/>
-      <c r="B89" s="49" t="inlineStr">
-        <is>
-          <t>Marge d'EBITDA</t>
-        </is>
-      </c>
-      <c r="C89" s="49" t="n"/>
-      <c r="D89" s="149">
-        <f>IFERROR(D88/D87,0)</f>
-        <v/>
-      </c>
-      <c r="E89" s="49" t="inlineStr"/>
-      <c r="F89" s="150" t="inlineStr"/>
-      <c r="G89" s="150" t="inlineStr"/>
-      <c r="H89" s="149">
-        <f>IFERROR(H88/H87,0)</f>
-        <v/>
-      </c>
-      <c r="I89" s="151">
-        <f>H89-D89</f>
-        <v/>
-      </c>
-      <c r="J89" s="49" t="inlineStr"/>
-      <c r="K89" s="5" t="n"/>
-      <c r="L89" s="5" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
-      <c r="L90" s="5" t="n"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="5" t="n"/>
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>ⓔ  Est-ce qu'on retombe sur le moteur ?</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="5" t="n"/>
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>Le CA gagné est le même nombre — c'est le même lien. Le coût de service, lui, est calculé de deux façons différentes : le moteur pondère campus par campus, le budget applique un taux au réseau. L'écart qui en résulte est affiché, pas gommé.</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="n"/>
-      <c r="L93" s="5" t="n"/>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="5" t="n"/>
-      <c r="B94" s="25" t="inlineStr">
-        <is>
-          <t>Ce que le geste rapporte</t>
-        </is>
-      </c>
-      <c r="C94" s="26" t="n"/>
-      <c r="D94" s="26" t="inlineStr">
-        <is>
-          <t>Le moteur</t>
-        </is>
-      </c>
-      <c r="E94" s="26" t="n"/>
-      <c r="F94" s="26" t="inlineStr">
-        <is>
-          <t>Le budget 2027</t>
-        </is>
-      </c>
-      <c r="G94" s="26" t="n"/>
-      <c r="H94" s="26" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-      <c r="I94" s="26" t="n"/>
-      <c r="J94" s="26" t="inlineStr">
-        <is>
-          <t>Pourquoi</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="n"/>
-      <c r="L94" s="5" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="n"/>
-      <c r="B95" s="52" t="inlineStr">
-        <is>
-          <t>CA gagné par le geste</t>
-        </is>
-      </c>
-      <c r="C95" s="121" t="n"/>
-      <c r="D95" s="51">
-        <f>'Le moteur'!J58</f>
-        <v/>
-      </c>
-      <c r="E95" s="121" t="n"/>
-      <c r="F95" s="51">
-        <f>E49</f>
-        <v/>
-      </c>
-      <c r="G95" s="121" t="n"/>
-      <c r="H95" s="152">
-        <f>F95-D95</f>
-        <v/>
-      </c>
-      <c r="I95" s="121" t="n"/>
-      <c r="J95" s="122" t="inlineStr">
-        <is>
-          <t>le même lien — zéro par construction</t>
-        </is>
-      </c>
-      <c r="K95" s="121" t="n"/>
-      <c r="L95" s="121" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="n"/>
-      <c r="B96" s="52" t="inlineStr">
-        <is>
-          <t>Coût de servir ces élèves</t>
-        </is>
-      </c>
-      <c r="C96" s="121" t="n"/>
-      <c r="D96" s="51">
-        <f>'Le moteur'!I58*'Le moteur'!K58</f>
-        <v/>
-      </c>
-      <c r="E96" s="121" t="n"/>
-      <c r="F96" s="51">
-        <f>D59*'Le moteur'!I58/'Le moteur'!N34</f>
-        <v/>
-      </c>
-      <c r="G96" s="121" t="n"/>
-      <c r="H96" s="152">
-        <f>F96-D96</f>
-        <v/>
-      </c>
-      <c r="I96" s="121" t="n"/>
-      <c r="J96" s="122" t="inlineStr">
-        <is>
-          <t>consommables du réseau au prorata des inscrits gagnés</t>
-        </is>
-      </c>
-      <c r="K96" s="121" t="n"/>
-      <c r="L96" s="121" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="49" t="inlineStr">
-        <is>
-          <t>EBITDA gagné</t>
-        </is>
-      </c>
-      <c r="C97" s="121" t="n"/>
-      <c r="D97" s="153">
-        <f>'Le moteur'!L58</f>
-        <v/>
-      </c>
-      <c r="E97" s="121" t="n"/>
-      <c r="F97" s="153">
-        <f>F95-(H82-D82)-F96</f>
-        <v/>
-      </c>
-      <c r="G97" s="121" t="n"/>
-      <c r="H97" s="154">
-        <f>F97-D97</f>
-        <v/>
-      </c>
-      <c r="I97" s="121" t="n"/>
-      <c r="J97" s="122" t="inlineStr">
-        <is>
-          <t>CA gagné − Δ budget 6231 − coût de service</t>
-        </is>
-      </c>
-      <c r="K97" s="121" t="n"/>
-      <c r="L97" s="121" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="5" t="n"/>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="5" t="n"/>
-      <c r="K98" s="5" t="n"/>
-      <c r="L98" s="5" t="n"/>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="5" t="n"/>
-      <c r="B99" s="155">
-        <f>"Le budget 2027 retombe sur l'EBITDA gagné du moteur à "&amp;TEXT(ABS(H97),"#,##0 €")&amp;" près, soit "&amp;TEXT(ABS(H97/D97),"0.00 %")&amp;" — et l'écart a une cause nommée, pas une tolérance."</f>
-        <v/>
-      </c>
-      <c r="C99" s="110" t="n"/>
-      <c r="D99" s="110" t="n"/>
-      <c r="E99" s="110" t="n"/>
-      <c r="F99" s="110" t="n"/>
-      <c r="G99" s="110" t="n"/>
-      <c r="H99" s="110" t="n"/>
-      <c r="I99" s="110" t="n"/>
-      <c r="J99" s="110" t="n"/>
-      <c r="K99" s="110" t="n"/>
-      <c r="L99" s="110" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="n"/>
-      <c r="B100" s="156">
-        <f>"2027 : "&amp;TEXT(H88,"#,##0 €")&amp;" d'EBITDA, marge "&amp;TEXT(H89,"0.0 %")&amp;" contre "&amp;TEXT(D89,"0.0 %")&amp;" en 2026. Le gain ne vient d'aucune économie : il vient de "&amp;TEXT(E31-E28,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes — dont "&amp;TEXT(E30,"#,##0")&amp;" que le geste a payés."</f>
-        <v/>
-      </c>
-      <c r="C100" s="112" t="n"/>
-      <c r="D100" s="112" t="n"/>
-      <c r="E100" s="112" t="n"/>
-      <c r="F100" s="112" t="n"/>
-      <c r="G100" s="112" t="n"/>
-      <c r="H100" s="112" t="n"/>
-      <c r="I100" s="112" t="n"/>
-      <c r="J100" s="112" t="n"/>
-      <c r="K100" s="112" t="n"/>
-      <c r="L100" s="112" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
-      <c r="L101" s="5" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="5" t="n"/>
-      <c r="D102" s="5" t="n"/>
-      <c r="E102" s="5" t="n"/>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="5" t="n"/>
-      <c r="I102" s="5" t="n"/>
-      <c r="J102" s="5" t="n"/>
-      <c r="K102" s="5" t="n"/>
-      <c r="L102" s="5" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
-      <c r="L105" s="5" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="5" t="n"/>
-      <c r="K106" s="5" t="n"/>
-      <c r="L106" s="5" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="5" t="n"/>
-      <c r="G107" s="5" t="n"/>
-      <c r="H107" s="5" t="n"/>
-      <c r="I107" s="5" t="n"/>
-      <c r="J107" s="5" t="n"/>
-      <c r="K107" s="5" t="n"/>
-      <c r="L107" s="5" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="5" t="n"/>
-      <c r="K108" s="5" t="n"/>
-      <c r="L108" s="5" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="5" t="n"/>
-      <c r="K109" s="5" t="n"/>
-      <c r="L109" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I60 I61 I63 I65 I66 I67 I69 I70 I71 I73 I74 I75 I76 I77 I78 I79 I80 I82 I83 I85">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00DCEBC0"/>
-        <color rgb="00F7F7F5"/>
-        <color rgb="00F6C9CC"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="173" formatCode="+0.00%;-0.00%;&quot;—&quot;"/>
     <numFmt numFmtId="174" formatCode="+0.00%"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="49">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -222,6 +222,21 @@
       <b val="1"/>
       <color rgb="00007AC3"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00262626"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005F8A17"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C41822"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -449,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,6 +594,15 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -589,7 +613,7 @@
     <xf numFmtId="173" fontId="29" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="32" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -623,10 +647,10 @@
     <xf numFmtId="169" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="34" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="37" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -647,16 +671,16 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="35" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="38" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -668,7 +692,7 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,27 +701,27 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="38" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="41" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="40" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="172" fontId="43" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -707,7 +731,7 @@
     <xf numFmtId="172" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,19 +743,19 @@
     <xf numFmtId="165" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="37" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,13 +764,13 @@
     <xf numFmtId="172" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="45" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="48" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="15" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -758,7 +782,7 @@
     <xf numFmtId="165" fontId="29" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="35" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="38" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1291,8 +1315,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00007AC3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1349,7 +1374,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>CALIBRATION &amp; EFFET D'UN +Δ%  —  campus groupé par marque</t>
+          <t>LE MOTEUR D'ACQUISITION  —  l'effet d'un euro de plus, campus par campus</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1758,7 +1783,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>①  CE QUE LA VUE RESTITUE  ·  V_MOTEUR_CAL, une ligne par campus, aucun calcul</t>
+          <t>①  CE QUI VIENT DE LA BASE  ·  une ligne par campus, aucun calcul</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -2982,7 +3007,7 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t>②  CE QUE LE MASQUE CALCULE  ·  chaque formule pointe une cellule du tableau ①</t>
+          <t>②  CE QUE LE MOTEUR CALCULE  ·  chaque formule pointe une cellule du tableau ①</t>
         </is>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -4214,31 +4239,43 @@
       <formula>F44</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 EDUSERVICES · Le moteur&amp;R&amp;"Arial"&amp;8 page &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <tabColor rgb="00007AC3"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.4" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -4258,12 +4295,13 @@
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BUDGET 2027  —  le CA en quatre lignes, les coûts en six familles</t>
+          <t>BUDGET 2027  —  le chiffre d'affaires en quatre lignes, les coûts en six familles</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -4276,6 +4314,7 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -4290,6 +4329,7 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -4304,6 +4344,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="n"/>
@@ -4322,12 +4363,13 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>On sait séparer ce que porte le socle de ce qu'ajoute le budget d'acquisition : +181 élèves en 2026, dont 31,8 dus au +10 % d'acquisition et 149,2 au socle. Le socle se saisit ; le geste, lui, n'est pas saisi — il est LIÉ aux cellules du premier onglet. C'est ce qui fait que ce budget et le moteur disent le même chiffre.</t>
+          <t>On sait séparer ce que porte le socle de ce qu'ajoute le budget d'acquisition : +181 élèves en 2026, dont 31,8 dus au +10 % d'acquisition et 149,2 au socle. Le socle se saisit ; le geste, lui, ne se saisit pas — il vient de l'onglet précédent.</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -4340,6 +4382,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -4354,90 +4397,111 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+      <c r="M7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="3" customHeight="1">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>ⓐ  Les huit saisies  ·  et la neuvième, qui n'en est pas une</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="14" customHeight="1">
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="12" customHeight="1">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Chacune est une décision, et chacune a un propriétaire. Le Δ budget d'acquisition ne se saisit pas ici : il vient du geste de l'onglet « Le moteur ».</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-    </row>
-    <row r="10">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>CHIFFRE D'AFFAIRES</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>EBITDA PROPRE</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>QUOTE-PART DU SIÈGE</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>EBITDA NET</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+      <c r="B10" s="49">
+        <f>H84</f>
+        <v/>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="50">
+        <f>H85</f>
+        <v/>
+      </c>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="51">
+        <f>H95</f>
+        <v/>
+      </c>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="50">
+        <f>H97</f>
+        <v/>
+      </c>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>Saisie</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>Valeur retenue</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="inlineStr">
-        <is>
-          <t>D'où elle vient</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
+      <c r="B11" s="18">
+        <f>"contre "&amp;TEXT(D84,"#,##0 €")&amp;" en 2026"</f>
+        <v/>
+      </c>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="18">
+        <f>"ce que les campus produisent  ·  marge "&amp;TEXT(H85/H84,"0.0 %")</f>
+        <v/>
+      </c>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="18">
+        <f>"soit "&amp;TEXT(H95/H84,"0.0 %")&amp;" du chiffre d'affaires"</f>
+        <v/>
+      </c>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="18">
+        <f>"marge "&amp;TEXT(D97/D84,"0.0 %")&amp;" → "&amp;TEXT(H97/H84,"0.0 %")</f>
+        <v/>
+      </c>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="19" t="n"/>
+    </row>
+    <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="49" t="inlineStr">
-        <is>
-          <t>CE QUI FAIT LE CHIFFRE D'AFFAIRES</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -4448,87 +4512,64 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="50" t="inlineStr">
-        <is>
-          <t>Croissance du socle, hors geste d'acquisition</t>
-        </is>
-      </c>
-      <c r="C13" s="51" t="n"/>
-      <c r="D13" s="51" t="n"/>
-      <c r="E13" s="52" t="n">
-        <v>0.0509</v>
-      </c>
-      <c r="F13" s="51" t="n"/>
-      <c r="G13" s="53" t="inlineStr">
-        <is>
-          <t>constatée 2026, geste défalqué</t>
-        </is>
-      </c>
-      <c r="H13" s="51" t="n"/>
-      <c r="I13" s="51" t="n"/>
-      <c r="J13" s="51" t="n"/>
-      <c r="K13" s="51" t="n"/>
-      <c r="L13" s="51" t="n"/>
-    </row>
-    <row r="14">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="50" t="inlineStr">
-        <is>
-          <t>Hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="C14" s="51" t="n"/>
-      <c r="D14" s="51" t="n"/>
-      <c r="E14" s="52" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F14" s="51" t="n"/>
-      <c r="G14" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H14" s="51" t="n"/>
-      <c r="I14" s="51" t="n"/>
-      <c r="J14" s="51" t="n"/>
-      <c r="K14" s="51" t="n"/>
-      <c r="L14" s="51" t="n"/>
-    </row>
-    <row r="15">
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>ⓐ  Les huit hypothèses  ·  et la neuvième, qui n'en est pas une</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="50" t="inlineStr">
-        <is>
-          <t>Δ budget d'acquisition  (6231)</t>
-        </is>
-      </c>
-      <c r="C15" s="51" t="n"/>
-      <c r="D15" s="51" t="n"/>
-      <c r="E15" s="54">
-        <f>'Le moteur'!F4</f>
-        <v/>
-      </c>
-      <c r="F15" s="51" t="n"/>
-      <c r="G15" s="55" t="inlineStr">
-        <is>
-          <t>LIÉ au geste, onglet « Le moteur »</t>
-        </is>
-      </c>
-      <c r="H15" s="51" t="n"/>
-      <c r="I15" s="51" t="n"/>
-      <c r="J15" s="51" t="n"/>
-      <c r="K15" s="51" t="n"/>
-      <c r="L15" s="51" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Chacune est une décision, et chacune a un propriétaire. Le Δ budget d'acquisition ne se saisit pas ici : il vient du geste de l'onglet précédent. Fond sable = cellule à saisir.</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+    </row>
+    <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="49" t="inlineStr">
-        <is>
-          <t>CE QUI FAIT LES COÛTS</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
@@ -4539,1447 +4580,1475 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-    </row>
-    <row r="17">
+      <c r="M16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="50" t="inlineStr">
-        <is>
-          <t>Inflation des charges externes</t>
-        </is>
-      </c>
-      <c r="C17" s="51" t="n"/>
-      <c r="D17" s="51" t="n"/>
-      <c r="E17" s="52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F17" s="51" t="n"/>
-      <c r="G17" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H17" s="51" t="n"/>
-      <c r="I17" s="51" t="n"/>
-      <c r="J17" s="51" t="n"/>
-      <c r="K17" s="51" t="n"/>
-      <c r="L17" s="51" t="n"/>
-    </row>
-    <row r="18">
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Hypothèse</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>Valeur retenue</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="n"/>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>D'où elle vient</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="50" t="inlineStr">
-        <is>
-          <t>Effort de productivité achats &amp; structure</t>
-        </is>
-      </c>
-      <c r="C18" s="51" t="n"/>
-      <c r="D18" s="51" t="n"/>
-      <c r="E18" s="52" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="F18" s="51" t="n"/>
-      <c r="G18" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H18" s="51" t="n"/>
-      <c r="I18" s="51" t="n"/>
-      <c r="J18" s="51" t="n"/>
-      <c r="K18" s="51" t="n"/>
-      <c r="L18" s="51" t="n"/>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>CE QUI FAIT LE CHIFFRE D'AFFAIRES</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="50" t="inlineStr">
-        <is>
-          <t>Politique salariale sur la masse permanente</t>
-        </is>
-      </c>
-      <c r="C19" s="51" t="n"/>
-      <c r="D19" s="51" t="n"/>
-      <c r="E19" s="52" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F19" s="51" t="n"/>
-      <c r="G19" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H19" s="51" t="n"/>
-      <c r="I19" s="51" t="n"/>
-      <c r="J19" s="51" t="n"/>
-      <c r="K19" s="51" t="n"/>
-      <c r="L19" s="51" t="n"/>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>Croissance du socle, hors geste d'acquisition</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="55" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="F19" s="54" t="n"/>
+      <c r="G19" s="56" t="inlineStr">
+        <is>
+          <t>constatée 2026, geste défalqué</t>
+        </is>
+      </c>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="54" t="n"/>
+      <c r="L19" s="54" t="n"/>
+      <c r="M19" s="54" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="50" t="inlineStr">
-        <is>
-          <t>Variation des effectifs permanents</t>
-        </is>
-      </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="52" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · coûts</t>
-        </is>
-      </c>
-      <c r="H20" s="51" t="n"/>
-      <c r="I20" s="51" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="51" t="n"/>
-      <c r="L20" s="51" t="n"/>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>Hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="55" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="F20" s="54" t="n"/>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
+      <c r="J20" s="54" t="n"/>
+      <c r="K20" s="54" t="n"/>
+      <c r="L20" s="54" t="n"/>
+      <c r="M20" s="54" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="50" t="inlineStr">
-        <is>
-          <t>Δ budget de marque  (6236)</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="n"/>
-      <c r="D21" s="51" t="n"/>
-      <c r="E21" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="53" t="inlineStr">
-        <is>
-          <t>levier Cadrage · croissance</t>
-        </is>
-      </c>
-      <c r="H21" s="51" t="n"/>
-      <c r="I21" s="51" t="n"/>
-      <c r="J21" s="51" t="n"/>
-      <c r="K21" s="51" t="n"/>
-      <c r="L21" s="51" t="n"/>
-    </row>
-    <row r="22">
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>Δ budget d'acquisition  (6231)</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="57">
+        <f>'Le moteur'!F4</f>
+        <v/>
+      </c>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="58" t="inlineStr">
+        <is>
+          <t>LIÉ au geste, onglet précédent</t>
+        </is>
+      </c>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="50" t="inlineStr">
-        <is>
-          <t>Dotations aux amortissements</t>
-        </is>
-      </c>
-      <c r="C22" s="51" t="n"/>
-      <c r="D22" s="51" t="n"/>
-      <c r="E22" s="52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F22" s="51" t="n"/>
-      <c r="G22" s="53" t="inlineStr">
-        <is>
-          <t>plan d'amortissement</t>
-        </is>
-      </c>
-      <c r="H22" s="51" t="n"/>
-      <c r="I22" s="51" t="n"/>
-      <c r="J22" s="51" t="n"/>
-      <c r="K22" s="51" t="n"/>
-      <c r="L22" s="51" t="n"/>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>CE QUI FAIT LES COÛTS</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>Inflation des charges externes</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+    </row>
+    <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>ⓑ  Le volume 2027  ·  ce que porte le socle, ce qu'ajoute le geste</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>Effort de productivité achats &amp; structure</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="n"/>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="55" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="n"/>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="n"/>
+    </row>
+    <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>La ligne « ce que le geste ajoute » n'est pas calculée ici : c'est la cellule I58 de l'onglet « Le moteur ». Bouger F4 là-bas bouge ce budget-ci.</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>Politique salariale sur la masse permanente</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="n"/>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="55" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F25" s="54" t="n"/>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H25" s="54" t="n"/>
+      <c r="I25" s="54" t="n"/>
+      <c r="J25" s="54" t="n"/>
+      <c r="K25" s="54" t="n"/>
+      <c r="L25" s="54" t="n"/>
+      <c r="M25" s="54" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>Variation des effectifs permanents</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · coûts</t>
+        </is>
+      </c>
+      <c r="H26" s="54" t="n"/>
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="n"/>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n"/>
+    </row>
+    <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>Grandeur</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F27" s="26" t="n"/>
-      <c r="G27" s="26" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>Δ budget de marque  (6236)</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t>levier Cadrage · croissance</t>
+        </is>
+      </c>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
+      <c r="J27" s="54" t="n"/>
+      <c r="K27" s="54" t="n"/>
+      <c r="L27" s="54" t="n"/>
+      <c r="M27" s="54" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="56" t="inlineStr">
-        <is>
-          <t>Effectifs 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="57" t="n"/>
-      <c r="D28" s="57" t="n"/>
-      <c r="E28" s="58">
-        <f>'Le moteur'!N34</f>
-        <v/>
-      </c>
-      <c r="F28" s="57" t="n"/>
-      <c r="G28" s="59" t="inlineStr">
-        <is>
-          <t>restitué</t>
-        </is>
-      </c>
-      <c r="H28" s="57" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="57" t="n"/>
-      <c r="K28" s="57" t="n"/>
-      <c r="L28" s="57" t="n"/>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>Dotations aux amortissements</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="56" t="inlineStr">
+        <is>
+          <t>plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="H28" s="54" t="n"/>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="54" t="n"/>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="56" t="inlineStr">
-        <is>
-          <t>+ ce que porte le socle</t>
-        </is>
-      </c>
-      <c r="C29" s="57" t="n"/>
-      <c r="D29" s="57" t="n"/>
-      <c r="E29" s="60">
-        <f>E28*$E$13</f>
-        <v/>
-      </c>
-      <c r="F29" s="57" t="n"/>
-      <c r="G29" s="59" t="inlineStr">
-        <is>
-          <t>rétention, passage, notoriété</t>
-        </is>
-      </c>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="57" t="n"/>
-      <c r="K29" s="57" t="n"/>
-      <c r="L29" s="57" t="n"/>
-    </row>
-    <row r="30">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="56" t="inlineStr">
-        <is>
-          <t>+ ce que le geste ajoute</t>
-        </is>
-      </c>
-      <c r="C30" s="57" t="n"/>
-      <c r="D30" s="57" t="n"/>
-      <c r="E30" s="60">
-        <f>'Le moteur'!I58</f>
-        <v/>
-      </c>
-      <c r="F30" s="57" t="n"/>
-      <c r="G30" s="59" t="inlineStr">
-        <is>
-          <t>LIÉ au moteur — les inscrits gagnés par le Δ budget</t>
-        </is>
-      </c>
-      <c r="H30" s="57" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="57" t="n"/>
-      <c r="K30" s="57" t="n"/>
-      <c r="L30" s="57" t="n"/>
-    </row>
-    <row r="31">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>ⓑ  Combien d'élèves en 2027  ·  ce que porte le socle, ce qu'ajoute le geste</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="61">
-        <f> Effectifs 2027</f>
-        <v/>
-      </c>
-      <c r="C31" s="57" t="n"/>
-      <c r="D31" s="57" t="n"/>
-      <c r="E31" s="62">
-        <f>E28+E29+E30</f>
-        <v/>
-      </c>
-      <c r="F31" s="57" t="n"/>
-      <c r="G31" s="59" t="inlineStr"/>
-      <c r="H31" s="57" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="57" t="n"/>
-      <c r="K31" s="57" t="n"/>
-      <c r="L31" s="57" t="n"/>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>La ligne « ce que le geste ajoute » n'est pas calculée ici : elle vient du moteur d'acquisition. Bouger le Δ budget là-bas bouge ce budget-ci.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="56" t="inlineStr">
-        <is>
-          <t>Croissance totale</t>
-        </is>
-      </c>
-      <c r="C32" s="57" t="n"/>
-      <c r="D32" s="57" t="n"/>
-      <c r="E32" s="63">
-        <f>IFERROR(E31/E28-1,0)</f>
-        <v/>
-      </c>
-      <c r="F32" s="57" t="n"/>
-      <c r="G32" s="59" t="inlineStr">
-        <is>
-          <t>elle n'est pas saisie : elle se déduit</t>
-        </is>
-      </c>
-      <c r="H32" s="57" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="57" t="n"/>
-      <c r="K32" s="57" t="n"/>
-      <c r="L32" s="57" t="n"/>
-    </row>
-    <row r="33">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="5" t="n"/>
-      <c r="B33" s="56" t="inlineStr">
-        <is>
-          <t>Places du réseau</t>
-        </is>
-      </c>
-      <c r="C33" s="57" t="n"/>
-      <c r="D33" s="57" t="n"/>
-      <c r="E33" s="58">
-        <f>'Le moteur'!O34</f>
-        <v/>
-      </c>
-      <c r="F33" s="57" t="n"/>
-      <c r="G33" s="59" t="inlineStr">
-        <is>
-          <t>135 classes, inchangées depuis 2024</t>
-        </is>
-      </c>
-      <c r="H33" s="57" t="n"/>
-      <c r="I33" s="57" t="n"/>
-      <c r="J33" s="57" t="n"/>
-      <c r="K33" s="57" t="n"/>
-      <c r="L33" s="57" t="n"/>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Grandeur</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="56" t="inlineStr">
-        <is>
-          <t>Classes 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="57" t="n"/>
-      <c r="D34" s="57" t="n"/>
-      <c r="E34" s="58">
-        <f>'Le moteur'!P34</f>
-        <v/>
-      </c>
-      <c r="F34" s="57" t="n"/>
-      <c r="G34" s="59" t="inlineStr"/>
-      <c r="H34" s="57" t="n"/>
-      <c r="I34" s="57" t="n"/>
-      <c r="J34" s="57" t="n"/>
-      <c r="K34" s="57" t="n"/>
-      <c r="L34" s="57" t="n"/>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>Élèves 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="60" t="n"/>
+      <c r="D34" s="60" t="n"/>
+      <c r="E34" s="61">
+        <f>'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="F34" s="60" t="n"/>
+      <c r="G34" s="62" t="inlineStr">
+        <is>
+          <t>constaté</t>
+        </is>
+      </c>
+      <c r="H34" s="60" t="n"/>
+      <c r="I34" s="60" t="n"/>
+      <c r="J34" s="60" t="n"/>
+      <c r="K34" s="60" t="n"/>
+      <c r="L34" s="60" t="n"/>
+      <c r="M34" s="60" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="56" t="inlineStr">
-        <is>
-          <t>Capacité moyenne d'une classe</t>
-        </is>
-      </c>
-      <c r="C35" s="57" t="n"/>
-      <c r="D35" s="57" t="n"/>
-      <c r="E35" s="60">
-        <f>IFERROR(E33/E34,0)</f>
-        <v/>
-      </c>
-      <c r="F35" s="57" t="n"/>
-      <c r="G35" s="59" t="inlineStr"/>
-      <c r="H35" s="57" t="n"/>
-      <c r="I35" s="57" t="n"/>
-      <c r="J35" s="57" t="n"/>
-      <c r="K35" s="57" t="n"/>
-      <c r="L35" s="57" t="n"/>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="n"/>
+      <c r="D35" s="60" t="n"/>
+      <c r="E35" s="63">
+        <f>E34*$E$19</f>
+        <v/>
+      </c>
+      <c r="F35" s="60" t="n"/>
+      <c r="G35" s="62" t="inlineStr">
+        <is>
+          <t>rétention, passage, notoriété</t>
+        </is>
+      </c>
+      <c r="H35" s="60" t="n"/>
+      <c r="I35" s="60" t="n"/>
+      <c r="J35" s="60" t="n"/>
+      <c r="K35" s="60" t="n"/>
+      <c r="L35" s="60" t="n"/>
+      <c r="M35" s="60" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="56" t="inlineStr">
-        <is>
-          <t>Croissance possible avant saturation</t>
-        </is>
-      </c>
-      <c r="C36" s="57" t="n"/>
-      <c r="D36" s="57" t="n"/>
-      <c r="E36" s="64">
-        <f>'Le coût variable'!L48</f>
-        <v/>
-      </c>
-      <c r="F36" s="57" t="n"/>
-      <c r="G36" s="59" t="inlineStr">
-        <is>
-          <t>le premier campus qui sature : MBway Paris</t>
-        </is>
-      </c>
-      <c r="H36" s="57" t="n"/>
-      <c r="I36" s="57" t="n"/>
-      <c r="J36" s="57" t="n"/>
-      <c r="K36" s="57" t="n"/>
-      <c r="L36" s="57" t="n"/>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>+ ce que le geste d'acquisition ajoute</t>
+        </is>
+      </c>
+      <c r="C36" s="60" t="n"/>
+      <c r="D36" s="60" t="n"/>
+      <c r="E36" s="63">
+        <f>'Le moteur'!I58</f>
+        <v/>
+      </c>
+      <c r="F36" s="60" t="n"/>
+      <c r="G36" s="62" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — les inscrits gagnés</t>
+        </is>
+      </c>
+      <c r="H36" s="60" t="n"/>
+      <c r="I36" s="60" t="n"/>
+      <c r="J36" s="60" t="n"/>
+      <c r="K36" s="60" t="n"/>
+      <c r="L36" s="60" t="n"/>
+      <c r="M36" s="60" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="61" t="inlineStr">
-        <is>
-          <t>Classes à ouvrir en 2027</t>
-        </is>
-      </c>
-      <c r="C37" s="57" t="n"/>
-      <c r="D37" s="57" t="n"/>
+      <c r="B37" s="64">
+        <f> Élèves 2027</f>
+        <v/>
+      </c>
+      <c r="C37" s="60" t="n"/>
+      <c r="D37" s="60" t="n"/>
       <c r="E37" s="65">
-        <f>MAX(0,ROUNDUP((E31-E33)/E35,0))</f>
-        <v/>
-      </c>
-      <c r="F37" s="57" t="n"/>
-      <c r="G37" s="59" t="inlineStr">
-        <is>
-          <t>aucune — et c'est toute la démonstration</t>
-        </is>
-      </c>
-      <c r="H37" s="57" t="n"/>
-      <c r="I37" s="57" t="n"/>
-      <c r="J37" s="57" t="n"/>
-      <c r="K37" s="57" t="n"/>
-      <c r="L37" s="57" t="n"/>
+        <f>E34+E35+E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="60" t="n"/>
+      <c r="G37" s="62" t="inlineStr"/>
+      <c r="H37" s="60" t="n"/>
+      <c r="I37" s="60" t="n"/>
+      <c r="J37" s="60" t="n"/>
+      <c r="K37" s="60" t="n"/>
+      <c r="L37" s="60" t="n"/>
+      <c r="M37" s="60" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="56" t="inlineStr">
-        <is>
-          <t>Classes 2027</t>
-        </is>
-      </c>
-      <c r="C38" s="57" t="n"/>
-      <c r="D38" s="57" t="n"/>
-      <c r="E38" s="58">
-        <f>E34+E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="57" t="n"/>
-      <c r="G38" s="59" t="inlineStr"/>
-      <c r="H38" s="57" t="n"/>
-      <c r="I38" s="57" t="n"/>
-      <c r="J38" s="57" t="n"/>
-      <c r="K38" s="57" t="n"/>
-      <c r="L38" s="57" t="n"/>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>Croissance totale</t>
+        </is>
+      </c>
+      <c r="C38" s="60" t="n"/>
+      <c r="D38" s="60" t="n"/>
+      <c r="E38" s="66">
+        <f>IFERROR(E37/E34-1,0)</f>
+        <v/>
+      </c>
+      <c r="F38" s="60" t="n"/>
+      <c r="G38" s="62" t="inlineStr">
+        <is>
+          <t>elle ne se saisit pas : elle se déduit</t>
+        </is>
+      </c>
+      <c r="H38" s="60" t="n"/>
+      <c r="I38" s="60" t="n"/>
+      <c r="J38" s="60" t="n"/>
+      <c r="K38" s="60" t="n"/>
+      <c r="L38" s="60" t="n"/>
+      <c r="M38" s="60" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="56" t="inlineStr">
-        <is>
-          <t>Inducteur du compte 621</t>
-        </is>
-      </c>
-      <c r="C39" s="57" t="n"/>
-      <c r="D39" s="57" t="n"/>
-      <c r="E39" s="66">
-        <f>IFERROR(E38/E34,0)</f>
-        <v/>
-      </c>
-      <c r="F39" s="57" t="n"/>
-      <c r="G39" s="59" t="inlineStr">
-        <is>
-          <t>le ratio de CLASSES, jamais celui des effectifs</t>
-        </is>
-      </c>
-      <c r="H39" s="57" t="n"/>
-      <c r="I39" s="57" t="n"/>
-      <c r="J39" s="57" t="n"/>
-      <c r="K39" s="57" t="n"/>
-      <c r="L39" s="57" t="n"/>
+      <c r="B39" s="59" t="inlineStr">
+        <is>
+          <t>Places du réseau</t>
+        </is>
+      </c>
+      <c r="C39" s="60" t="n"/>
+      <c r="D39" s="60" t="n"/>
+      <c r="E39" s="61">
+        <f>'Le moteur'!O34</f>
+        <v/>
+      </c>
+      <c r="F39" s="60" t="n"/>
+      <c r="G39" s="62" t="inlineStr">
+        <is>
+          <t>135 classes, inchangées depuis 2024</t>
+        </is>
+      </c>
+      <c r="H39" s="60" t="n"/>
+      <c r="I39" s="60" t="n"/>
+      <c r="J39" s="60" t="n"/>
+      <c r="K39" s="60" t="n"/>
+      <c r="L39" s="60" t="n"/>
+      <c r="M39" s="60" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>Classes 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="60" t="n"/>
+      <c r="D40" s="60" t="n"/>
+      <c r="E40" s="61">
+        <f>'Le moteur'!P34</f>
+        <v/>
+      </c>
+      <c r="F40" s="60" t="n"/>
+      <c r="G40" s="62" t="inlineStr"/>
+      <c r="H40" s="60" t="n"/>
+      <c r="I40" s="60" t="n"/>
+      <c r="J40" s="60" t="n"/>
+      <c r="K40" s="60" t="n"/>
+      <c r="L40" s="60" t="n"/>
+      <c r="M40" s="60" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>À +6 % l'an, MBway Paris tient jusqu'en 2029. Vérifiable ligne à ligne : onglet « Le coût variable », dernière colonne du tableau campus.</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>Capacité moyenne d'une classe</t>
+        </is>
+      </c>
+      <c r="C41" s="60" t="n"/>
+      <c r="D41" s="60" t="n"/>
+      <c r="E41" s="63">
+        <f>IFERROR(E39/E40,0)</f>
+        <v/>
+      </c>
+      <c r="F41" s="60" t="n"/>
+      <c r="G41" s="62" t="inlineStr"/>
+      <c r="H41" s="60" t="n"/>
+      <c r="I41" s="60" t="n"/>
+      <c r="J41" s="60" t="n"/>
+      <c r="K41" s="60" t="n"/>
+      <c r="L41" s="60" t="n"/>
+      <c r="M41" s="60" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>Croissance possible avant saturation</t>
+        </is>
+      </c>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="67">
+        <f>'Le coût variable'!L48</f>
+        <v/>
+      </c>
+      <c r="F42" s="60" t="n"/>
+      <c r="G42" s="62" t="inlineStr">
+        <is>
+          <t>le premier campus qui sature : MBway Paris</t>
+        </is>
+      </c>
+      <c r="H42" s="60" t="n"/>
+      <c r="I42" s="60" t="n"/>
+      <c r="J42" s="60" t="n"/>
+      <c r="K42" s="60" t="n"/>
+      <c r="L42" s="60" t="n"/>
+      <c r="M42" s="60" t="n"/>
+    </row>
+    <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>ⓒ  Le chiffre d'affaires 2027  ·  quatre lignes, et une seule est une décision</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="14" customHeight="1">
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>Classes à ouvrir en 2027</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="n"/>
+      <c r="D43" s="60" t="n"/>
+      <c r="E43" s="68">
+        <f>MAX(0,ROUNDUP((E37-E39)/E41,0))</f>
+        <v/>
+      </c>
+      <c r="F43" s="60" t="n"/>
+      <c r="G43" s="62" t="inlineStr">
+        <is>
+          <t>aucune — et c'est toute la démonstration</t>
+        </is>
+      </c>
+      <c r="H43" s="60" t="n"/>
+      <c r="I43" s="60" t="n"/>
+      <c r="J43" s="60" t="n"/>
+      <c r="K43" s="60" t="n"/>
+      <c r="L43" s="60" t="n"/>
+      <c r="M43" s="60" t="n"/>
+    </row>
+    <row r="44">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>Le socle est déjà inscrit, le geste est celui du moteur, le prix est un arbitrage. Rien d'autre n'entre dans le CA.</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
+      <c r="B44" s="59" t="inlineStr">
+        <is>
+          <t>Classes 2027</t>
+        </is>
+      </c>
+      <c r="C44" s="60" t="n"/>
+      <c r="D44" s="60" t="n"/>
+      <c r="E44" s="61">
+        <f>E40+E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="60" t="n"/>
+      <c r="G44" s="62" t="inlineStr"/>
+      <c r="H44" s="60" t="n"/>
+      <c r="I44" s="60" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="60" t="n"/>
+      <c r="L44" s="60" t="n"/>
+      <c r="M44" s="60" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="B45" s="59" t="inlineStr">
+        <is>
+          <t>Effet volume du compte 621</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="n"/>
+      <c r="D45" s="60" t="n"/>
+      <c r="E45" s="69">
+        <f>IFERROR(E44/E40-1,0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="60" t="n"/>
+      <c r="G45" s="62" t="inlineStr">
+        <is>
+          <t>il suit les CLASSES, jamais les élèves</t>
+        </is>
+      </c>
+      <c r="H45" s="60" t="n"/>
+      <c r="I45" s="60" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="60" t="n"/>
+      <c r="L45" s="60" t="n"/>
+      <c r="M45" s="60" t="n"/>
+    </row>
+    <row r="46">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>Ligne</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="n"/>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>Montant</t>
-        </is>
-      </c>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="5" t="n"/>
       <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="56" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires 2026</t>
-        </is>
-      </c>
-      <c r="C47" s="57" t="n"/>
-      <c r="D47" s="57" t="n"/>
-      <c r="E47" s="67" t="n">
-        <v>23098985</v>
-      </c>
-      <c r="F47" s="57" t="n"/>
-      <c r="G47" s="59" t="inlineStr">
-        <is>
-          <t>restitué · 706 + 7062 + 708</t>
-        </is>
-      </c>
-      <c r="H47" s="57" t="n"/>
-      <c r="I47" s="57" t="n"/>
-      <c r="J47" s="57" t="n"/>
-      <c r="K47" s="57" t="n"/>
-      <c r="L47" s="57" t="n"/>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>À +6 % l'an, MBway Paris tient jusqu'en 2029 — c'est le premier campus qui butera sur ses murs, et le classeur dit lequel et quand.</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="56" t="inlineStr">
-        <is>
-          <t>+ ce que porte le socle</t>
-        </is>
-      </c>
-      <c r="C48" s="57" t="n"/>
-      <c r="D48" s="57" t="n"/>
-      <c r="E48" s="67">
-        <f>E47*$E$13</f>
-        <v/>
-      </c>
-      <c r="F48" s="57" t="n"/>
-      <c r="G48" s="59" t="inlineStr">
-        <is>
-          <t>la rentrée déjà engagée</t>
-        </is>
-      </c>
-      <c r="H48" s="57" t="n"/>
-      <c r="I48" s="57" t="n"/>
-      <c r="J48" s="57" t="n"/>
-      <c r="K48" s="57" t="n"/>
-      <c r="L48" s="57" t="n"/>
-    </row>
-    <row r="49">
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="56" t="inlineStr">
-        <is>
-          <t>+ ce que le geste ajoute</t>
-        </is>
-      </c>
-      <c r="C49" s="57" t="n"/>
-      <c r="D49" s="57" t="n"/>
-      <c r="E49" s="67">
-        <f>'Le moteur'!J58</f>
-        <v/>
-      </c>
-      <c r="F49" s="57" t="n"/>
-      <c r="G49" s="59" t="inlineStr">
-        <is>
-          <t>LIÉ au moteur — le CA gagné par le Δ budget</t>
-        </is>
-      </c>
-      <c r="H49" s="57" t="n"/>
-      <c r="I49" s="57" t="n"/>
-      <c r="J49" s="57" t="n"/>
-      <c r="K49" s="57" t="n"/>
-      <c r="L49" s="57" t="n"/>
-    </row>
-    <row r="50">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>ⓒ  Le chiffre d'affaires 2027  ·  quatre lignes, et une seule est une décision</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="56" t="inlineStr">
-        <is>
-          <t>+ effet prix</t>
-        </is>
-      </c>
-      <c r="C50" s="57" t="n"/>
-      <c r="D50" s="57" t="n"/>
-      <c r="E50" s="67">
-        <f>(E47+E48+E49)*$E$14</f>
-        <v/>
-      </c>
-      <c r="F50" s="57" t="n"/>
-      <c r="G50" s="59" t="inlineStr">
-        <is>
-          <t>la hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="H50" s="57" t="n"/>
-      <c r="I50" s="57" t="n"/>
-      <c r="J50" s="57" t="n"/>
-      <c r="K50" s="57" t="n"/>
-      <c r="L50" s="57" t="n"/>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Le socle est déjà inscrit, le geste vient du moteur, le prix est un arbitrage. Rien d'autre n'entre dans le chiffre d'affaires.</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="61">
-        <f> Chiffre d'affaires 2027</f>
-        <v/>
-      </c>
-      <c r="C51" s="57" t="n"/>
-      <c r="D51" s="57" t="n"/>
-      <c r="E51" s="68">
-        <f>SUM(E47:E50)</f>
-        <v/>
-      </c>
-      <c r="F51" s="57" t="n"/>
-      <c r="G51" s="59" t="inlineStr"/>
-      <c r="H51" s="57" t="n"/>
-      <c r="I51" s="57" t="n"/>
-      <c r="J51" s="57" t="n"/>
-      <c r="K51" s="57" t="n"/>
-      <c r="L51" s="57" t="n"/>
-    </row>
-    <row r="52">
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>Ligne</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="n"/>
+      <c r="D52" s="26" t="n"/>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="n"/>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="5" t="n"/>
       <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="69">
-        <f>"Sur "&amp;TEXT(E51-E47,"#,##0 €")&amp;" de croissance, "&amp;TEXT(E48/(E51-E47),"0 %")&amp;" viennent du socle déjà inscrit, "&amp;TEXT(E49/(E51-E47),"0 %")&amp;" du geste d'acquisition et "&amp;TEXT(E50/(E51-E47),"0 %")&amp;" du prix. Le chiffre d'affaires ne se décrète pas."</f>
-        <v/>
-      </c>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
+      <c r="B53" s="59" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="60" t="n"/>
+      <c r="D53" s="60" t="n"/>
+      <c r="E53" s="70" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="F53" s="60" t="n"/>
+      <c r="G53" s="62" t="inlineStr">
+        <is>
+          <t>constaté · 706 + 7062 + 708</t>
+        </is>
+      </c>
+      <c r="H53" s="60" t="n"/>
+      <c r="I53" s="60" t="n"/>
+      <c r="J53" s="60" t="n"/>
+      <c r="K53" s="60" t="n"/>
+      <c r="L53" s="60" t="n"/>
+      <c r="M53" s="60" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>+ ce que porte le socle</t>
+        </is>
+      </c>
+      <c r="C54" s="60" t="n"/>
+      <c r="D54" s="60" t="n"/>
+      <c r="E54" s="70">
+        <f>E53*$E$19</f>
+        <v/>
+      </c>
+      <c r="F54" s="60" t="n"/>
+      <c r="G54" s="62" t="inlineStr">
+        <is>
+          <t>la rentrée déjà engagée</t>
+        </is>
+      </c>
+      <c r="H54" s="60" t="n"/>
+      <c r="I54" s="60" t="n"/>
+      <c r="J54" s="60" t="n"/>
+      <c r="K54" s="60" t="n"/>
+      <c r="L54" s="60" t="n"/>
+      <c r="M54" s="60" t="n"/>
+    </row>
+    <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="38" t="inlineStr">
-        <is>
-          <t>ⓓ  Les coûts de CAMPUS  ·  six familles, six règles</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>+ ce que le geste ajoute</t>
+        </is>
+      </c>
+      <c r="C55" s="60" t="n"/>
+      <c r="D55" s="60" t="n"/>
+      <c r="E55" s="70">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="F55" s="60" t="n"/>
+      <c r="G55" s="62" t="inlineStr">
+        <is>
+          <t>LIÉ au moteur — le CA gagné par le Δ budget</t>
+        </is>
+      </c>
+      <c r="H55" s="60" t="n"/>
+      <c r="I55" s="60" t="n"/>
+      <c r="J55" s="60" t="n"/>
+      <c r="K55" s="60" t="n"/>
+      <c r="L55" s="60" t="n"/>
+      <c r="M55" s="60" t="n"/>
+    </row>
+    <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>Un budget qui indexe tout au même taux ne dit rien. Celui-ci donne à chaque euro l'inducteur de son comportement — et c'est ce qui fait apparaître où est le levier, et surtout où il n'est pas.</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
+      <c r="B56" s="59" t="inlineStr">
+        <is>
+          <t>+ effet prix</t>
+        </is>
+      </c>
+      <c r="C56" s="60" t="n"/>
+      <c r="D56" s="60" t="n"/>
+      <c r="E56" s="70">
+        <f>(E53+E54+E55)*$E$20</f>
+        <v/>
+      </c>
+      <c r="F56" s="60" t="n"/>
+      <c r="G56" s="62" t="inlineStr">
+        <is>
+          <t>la hausse tarifaire</t>
+        </is>
+      </c>
+      <c r="H56" s="60" t="n"/>
+      <c r="I56" s="60" t="n"/>
+      <c r="J56" s="60" t="n"/>
+      <c r="K56" s="60" t="n"/>
+      <c r="L56" s="60" t="n"/>
+      <c r="M56" s="60" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1">
+      <c r="B57" s="64">
+        <f> Chiffre d'affaires 2027</f>
+        <v/>
+      </c>
+      <c r="C57" s="60" t="n"/>
+      <c r="D57" s="60" t="n"/>
+      <c r="E57" s="71">
+        <f>SUM(E53:E56)</f>
+        <v/>
+      </c>
+      <c r="F57" s="60" t="n"/>
+      <c r="G57" s="62" t="inlineStr"/>
+      <c r="H57" s="60" t="n"/>
+      <c r="I57" s="60" t="n"/>
+      <c r="J57" s="60" t="n"/>
+      <c r="K57" s="60" t="n"/>
+      <c r="L57" s="60" t="n"/>
+      <c r="M57" s="60" t="n"/>
+    </row>
+    <row r="58">
       <c r="A58" s="5" t="n"/>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>Famille · compte</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2026</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
-        <is>
-          <t>Ce qui la fait bouger</t>
-        </is>
-      </c>
-      <c r="F58" s="26" t="inlineStr">
-        <is>
-          <t>Effet volume</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="inlineStr">
-        <is>
-          <t>Effet prix</t>
-        </is>
-      </c>
-      <c r="H58" s="26" t="inlineStr">
-        <is>
-          <t>Montant 2027</t>
-        </is>
-      </c>
-      <c r="I58" s="26" t="inlineStr">
-        <is>
-          <t>Variation</t>
-        </is>
-      </c>
-      <c r="J58" s="26" t="inlineStr">
-        <is>
-          <t>Bouge si un élève de plus arrive ?</t>
-        </is>
-      </c>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
-      <c r="B59" s="70" t="inlineStr">
-        <is>
-          <t>①  Suit l'ÉLÈVE</t>
-        </is>
-      </c>
-      <c r="C59" s="70" t="n"/>
-      <c r="D59" s="71">
-        <f>SUM(D60:D61)</f>
-        <v/>
-      </c>
-      <c r="E59" s="72" t="inlineStr">
-        <is>
-          <t>effectifs × inflation</t>
-        </is>
-      </c>
-      <c r="F59" s="73" t="inlineStr"/>
-      <c r="G59" s="73" t="inlineStr"/>
-      <c r="H59" s="71">
-        <f>SUM(H60:H61)</f>
-        <v/>
-      </c>
-      <c r="I59" s="74">
-        <f>IFERROR(H59/D59-1,0)</f>
-        <v/>
-      </c>
-      <c r="J59" s="75" t="inlineStr">
-        <is>
-          <t>OUI — le seul euro qui suive vraiment l'élève</t>
-        </is>
-      </c>
+      <c r="B59" s="72">
+        <f>"Sur "&amp;TEXT(E57-E53,"#,##0 €")&amp;" de croissance, "&amp;TEXT(E54/(E57-E53),"0 %")&amp;" viennent du socle déjà inscrit, "&amp;TEXT(E55/(E57-E53),"0 %")&amp;" du geste d'acquisition et "&amp;TEXT(E56/(E57-E53),"0 %")&amp;" du prix. Le chiffre d'affaires ne se décrète pas."</f>
+        <v/>
+      </c>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
-      <c r="B60" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      604 · Achats d'études et supports pédagogiques</t>
-        </is>
-      </c>
-      <c r="C60" s="77" t="n"/>
-      <c r="D60" s="78" t="n">
-        <v>677808</v>
-      </c>
-      <c r="E60" s="79" t="inlineStr"/>
-      <c r="F60" s="80">
-        <f>$E$31/$E$28</f>
-        <v/>
-      </c>
-      <c r="G60" s="80">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H60" s="78">
-        <f>D60*F60*G60</f>
-        <v/>
-      </c>
-      <c r="I60" s="81">
-        <f>IFERROR(H60/D60-1,0)</f>
-        <v/>
-      </c>
-      <c r="J60" s="77" t="inlineStr"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
-    </row>
-    <row r="61">
+      <c r="M60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
       <c r="A61" s="5" t="n"/>
-      <c r="B61" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6063 · Fournitures pédagogiques et administratives</t>
-        </is>
-      </c>
-      <c r="C61" s="77" t="n"/>
-      <c r="D61" s="78" t="n">
-        <v>451874</v>
-      </c>
-      <c r="E61" s="79" t="inlineStr"/>
-      <c r="F61" s="80">
-        <f>$E$31/$E$28</f>
-        <v/>
-      </c>
-      <c r="G61" s="80">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H61" s="78">
-        <f>D61*F61*G61</f>
-        <v/>
-      </c>
-      <c r="I61" s="81">
-        <f>IFERROR(H61/D61-1,0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="77" t="inlineStr"/>
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>ⓓ  Les coûts de CAMPUS  ·  six familles, six règles</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
       <c r="K61" s="5" t="n"/>
       <c r="L61" s="5" t="n"/>
-    </row>
-    <row r="62">
+      <c r="M61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
       <c r="A62" s="5" t="n"/>
-      <c r="B62" s="70" t="inlineStr">
-        <is>
-          <t>②  Suit la CLASSE</t>
-        </is>
-      </c>
-      <c r="C62" s="70" t="n"/>
-      <c r="D62" s="71">
-        <f>SUM(D63:D63)</f>
-        <v/>
-      </c>
-      <c r="E62" s="82" t="inlineStr">
-        <is>
-          <t>classes × inflation</t>
-        </is>
-      </c>
-      <c r="F62" s="73" t="inlineStr"/>
-      <c r="G62" s="73" t="inlineStr"/>
-      <c r="H62" s="71">
-        <f>SUM(H63:H63)</f>
-        <v/>
-      </c>
-      <c r="I62" s="83">
-        <f>IFERROR(H62/D62-1,0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="84" t="inlineStr">
-        <is>
-          <t>seulement si une classe doit ouvrir</t>
-        </is>
-      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>Un budget qui indexe tout au même taux ne dit rien. Celui-ci donne à chaque euro l'inducteur de son comportement — c'est ce qui fait apparaître où est le levier, et surtout où il n'est pas. Le détail des comptes est replié : cliquez le « + » dans la marge.</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
-      <c r="B63" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      621 · Personnel extérieur — enseignants vacataires</t>
-        </is>
-      </c>
-      <c r="C63" s="77" t="n"/>
-      <c r="D63" s="78" t="n">
-        <v>1581554</v>
-      </c>
-      <c r="E63" s="79" t="inlineStr"/>
-      <c r="F63" s="80">
-        <f>$E$39</f>
-        <v/>
-      </c>
-      <c r="G63" s="80">
-        <f>1+$E$17</f>
-        <v/>
-      </c>
-      <c r="H63" s="78">
-        <f>D63*F63*G63</f>
-        <v/>
-      </c>
-      <c r="I63" s="81">
-        <f>IFERROR(H63/D63-1,0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="77" t="inlineStr"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
-    </row>
-    <row r="64">
+      <c r="M63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="70" t="inlineStr">
-        <is>
-          <t>③  Suit les POSTES</t>
-        </is>
-      </c>
-      <c r="C64" s="70" t="n"/>
-      <c r="D64" s="71">
-        <f>SUM(D65:D66)</f>
-        <v/>
-      </c>
-      <c r="E64" s="85" t="inlineStr">
-        <is>
-          <t>politique salariale, + les postes créés</t>
-        </is>
-      </c>
-      <c r="F64" s="73" t="inlineStr"/>
-      <c r="G64" s="73" t="inlineStr"/>
-      <c r="H64" s="71">
-        <f>SUM(H65:H66)</f>
-        <v/>
-      </c>
-      <c r="I64" s="86">
-        <f>IFERROR(H64/D64-1,0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="87" t="inlineStr">
-        <is>
-          <t>NON — le poste est engagé à l'année</t>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>Famille · compte</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2026</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>Ce qui la fait bouger</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>Effet volume</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>Effet prix</t>
+        </is>
+      </c>
+      <c r="H64" s="26" t="inlineStr">
+        <is>
+          <t>Montant 2027</t>
+        </is>
+      </c>
+      <c r="I64" s="26" t="inlineStr">
+        <is>
+          <t>Variation</t>
+        </is>
+      </c>
+      <c r="J64" s="26" t="inlineStr">
+        <is>
+          <t>Bouge si un élève de plus arrive ?</t>
         </is>
       </c>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
-      <c r="B65" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6411 · Salaires — enseignants permanents</t>
-        </is>
-      </c>
-      <c r="C65" s="77" t="n"/>
-      <c r="D65" s="78" t="n">
-        <v>3841069.84</v>
-      </c>
-      <c r="E65" s="79" t="inlineStr"/>
-      <c r="F65" s="80">
-        <f>1+$E$20</f>
-        <v/>
-      </c>
-      <c r="G65" s="80">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H65" s="78">
-        <f>D65*F65*G65</f>
-        <v/>
-      </c>
-      <c r="I65" s="81">
+      <c r="B65" s="73" t="inlineStr">
+        <is>
+          <t>①  Suit l'ÉLÈVE</t>
+        </is>
+      </c>
+      <c r="C65" s="73" t="n"/>
+      <c r="D65" s="74">
+        <f>SUM(D66:D67)</f>
+        <v/>
+      </c>
+      <c r="E65" s="75" t="inlineStr">
+        <is>
+          <t>effectifs × inflation</t>
+        </is>
+      </c>
+      <c r="F65" s="76" t="inlineStr"/>
+      <c r="G65" s="76" t="inlineStr"/>
+      <c r="H65" s="74">
+        <f>SUM(H66:H67)</f>
+        <v/>
+      </c>
+      <c r="I65" s="77">
         <f>IFERROR(H65/D65-1,0)</f>
         <v/>
       </c>
-      <c r="J65" s="77" t="inlineStr"/>
+      <c r="J65" s="78" t="inlineStr">
+        <is>
+          <t>OUI — le seul euro qui suive vraiment l'élève</t>
+        </is>
+      </c>
       <c r="K65" s="5" t="n"/>
       <c r="L65" s="5" t="n"/>
-    </row>
-    <row r="66">
+      <c r="M65" s="5" t="n"/>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
       <c r="A66" s="5" t="n"/>
-      <c r="B66" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6413 · Salaires — personnel administratif des campus</t>
-        </is>
-      </c>
-      <c r="C66" s="77" t="n"/>
-      <c r="D66" s="78" t="n">
-        <v>2033330.6</v>
-      </c>
-      <c r="E66" s="79" t="inlineStr"/>
-      <c r="F66" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="80">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H66" s="78">
-        <f>D66*F66*G66</f>
-        <v/>
-      </c>
-      <c r="I66" s="81">
+      <c r="B66" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      604 · Achats d'études et supports pédagogiques</t>
+        </is>
+      </c>
+      <c r="C66" s="80" t="n"/>
+      <c r="D66" s="81" t="n">
+        <v>677808</v>
+      </c>
+      <c r="E66" s="82" t="inlineStr">
+        <is>
+          <t>les élèves</t>
+        </is>
+      </c>
+      <c r="F66" s="83">
+        <f>$E$37/$E$34-1</f>
+        <v/>
+      </c>
+      <c r="G66" s="83">
+        <f>$E$23</f>
+        <v/>
+      </c>
+      <c r="H66" s="81">
+        <f>D66*(1+F66)*(1+G66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="84">
         <f>IFERROR(H66/D66-1,0)</f>
         <v/>
       </c>
-      <c r="J66" s="77" t="inlineStr"/>
+      <c r="J66" s="80" t="inlineStr"/>
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="n"/>
-    </row>
-    <row r="67">
+      <c r="M66" s="5" t="n"/>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
       <c r="A67" s="5" t="n"/>
-      <c r="B67" s="70" t="inlineStr">
-        <is>
-          <t>④  Assis sur la MASSE</t>
-        </is>
-      </c>
-      <c r="C67" s="70" t="n"/>
-      <c r="D67" s="71">
-        <f>SUM(D68:D68)</f>
-        <v/>
-      </c>
-      <c r="E67" s="85" t="inlineStr">
-        <is>
-          <t>au prorata de la masse salariale des campus</t>
-        </is>
-      </c>
-      <c r="F67" s="73" t="inlineStr"/>
-      <c r="G67" s="73" t="inlineStr"/>
-      <c r="H67" s="71">
-        <f>SUM(H68:H68)</f>
-        <v/>
-      </c>
-      <c r="I67" s="86">
+      <c r="B67" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6063 · Fournitures pédagogiques et administratives</t>
+        </is>
+      </c>
+      <c r="C67" s="80" t="n"/>
+      <c r="D67" s="81" t="n">
+        <v>451874</v>
+      </c>
+      <c r="E67" s="82" t="inlineStr">
+        <is>
+          <t>les élèves</t>
+        </is>
+      </c>
+      <c r="F67" s="83">
+        <f>$E$37/$E$34-1</f>
+        <v/>
+      </c>
+      <c r="G67" s="83">
+        <f>$E$23</f>
+        <v/>
+      </c>
+      <c r="H67" s="81">
+        <f>D67*(1+F67)*(1+G67)</f>
+        <v/>
+      </c>
+      <c r="I67" s="84">
         <f>IFERROR(H67/D67-1,0)</f>
         <v/>
       </c>
-      <c r="J67" s="87" t="inlineStr">
-        <is>
-          <t>NON — elle suit la masse, pas l'élève</t>
-        </is>
-      </c>
+      <c r="J67" s="80" t="inlineStr"/>
       <c r="K67" s="5" t="n"/>
       <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      645 · Charges sociales sur les salaires</t>
-        </is>
-      </c>
-      <c r="C68" s="77" t="n"/>
-      <c r="D68" s="78" t="n">
-        <v>3162957.9</v>
-      </c>
-      <c r="E68" s="79" t="inlineStr"/>
-      <c r="F68" s="80">
-        <f>(H65+H66)/(D65+D66)</f>
-        <v/>
-      </c>
-      <c r="G68" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="78">
-        <f>D68*F68*G68</f>
-        <v/>
-      </c>
-      <c r="I68" s="81">
+      <c r="B68" s="73" t="inlineStr">
+        <is>
+          <t>②  Suit la CLASSE</t>
+        </is>
+      </c>
+      <c r="C68" s="73" t="n"/>
+      <c r="D68" s="74">
+        <f>SUM(D69:D69)</f>
+        <v/>
+      </c>
+      <c r="E68" s="85" t="inlineStr">
+        <is>
+          <t>classes × inflation</t>
+        </is>
+      </c>
+      <c r="F68" s="76" t="inlineStr"/>
+      <c r="G68" s="76" t="inlineStr"/>
+      <c r="H68" s="74">
+        <f>SUM(H69:H69)</f>
+        <v/>
+      </c>
+      <c r="I68" s="86">
         <f>IFERROR(H68/D68-1,0)</f>
         <v/>
       </c>
-      <c r="J68" s="77" t="inlineStr"/>
+      <c r="J68" s="87" t="inlineStr">
+        <is>
+          <t>seulement si une classe doit ouvrir</t>
+        </is>
+      </c>
       <c r="K68" s="5" t="n"/>
       <c r="L68" s="5" t="n"/>
-    </row>
-    <row r="69">
+      <c r="M68" s="5" t="n"/>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
       <c r="A69" s="5" t="n"/>
-      <c r="B69" s="70" t="inlineStr">
-        <is>
-          <t>⑤  INDEXÉ</t>
-        </is>
-      </c>
-      <c r="C69" s="70" t="n"/>
-      <c r="D69" s="71">
-        <f>SUM(D70:D74)</f>
-        <v/>
-      </c>
-      <c r="E69" s="88" t="inlineStr">
-        <is>
-          <t>inflation moins l'effort de productivité</t>
-        </is>
-      </c>
-      <c r="F69" s="73" t="inlineStr"/>
-      <c r="G69" s="73" t="inlineStr"/>
-      <c r="H69" s="71">
-        <f>SUM(H70:H74)</f>
-        <v/>
-      </c>
-      <c r="I69" s="89">
+      <c r="B69" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      621 · Personnel extérieur — enseignants vacataires</t>
+        </is>
+      </c>
+      <c r="C69" s="80" t="n"/>
+      <c r="D69" s="81" t="n">
+        <v>1581554</v>
+      </c>
+      <c r="E69" s="82" t="inlineStr">
+        <is>
+          <t>les classes</t>
+        </is>
+      </c>
+      <c r="F69" s="83">
+        <f>$E$45</f>
+        <v/>
+      </c>
+      <c r="G69" s="83">
+        <f>$E$23</f>
+        <v/>
+      </c>
+      <c r="H69" s="81">
+        <f>D69*(1+F69)*(1+G69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="84">
         <f>IFERROR(H69/D69-1,0)</f>
         <v/>
       </c>
-      <c r="J69" s="90" t="inlineStr">
-        <is>
-          <t>NON — c'est le mur qui coûte, pas l'élève</t>
-        </is>
-      </c>
+      <c r="J69" s="80" t="inlineStr"/>
       <c r="K69" s="5" t="n"/>
       <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      613 · Locations immobilières des campus</t>
-        </is>
-      </c>
-      <c r="C70" s="77" t="n"/>
-      <c r="D70" s="78" t="n">
-        <v>2372423.51</v>
-      </c>
-      <c r="E70" s="79" t="inlineStr"/>
-      <c r="F70" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="80">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H70" s="78">
-        <f>D70*F70*G70</f>
-        <v/>
-      </c>
-      <c r="I70" s="81">
+      <c r="B70" s="73" t="inlineStr">
+        <is>
+          <t>③  Suit les POSTES</t>
+        </is>
+      </c>
+      <c r="C70" s="73" t="n"/>
+      <c r="D70" s="74">
+        <f>SUM(D71:D72)</f>
+        <v/>
+      </c>
+      <c r="E70" s="88" t="inlineStr">
+        <is>
+          <t>politique salariale, + les postes créés</t>
+        </is>
+      </c>
+      <c r="F70" s="76" t="inlineStr"/>
+      <c r="G70" s="76" t="inlineStr"/>
+      <c r="H70" s="74">
+        <f>SUM(H71:H72)</f>
+        <v/>
+      </c>
+      <c r="I70" s="89">
         <f>IFERROR(H70/D70-1,0)</f>
         <v/>
       </c>
-      <c r="J70" s="77" t="inlineStr"/>
+      <c r="J70" s="90" t="inlineStr">
+        <is>
+          <t>NON — le poste est engagé à l'année</t>
+        </is>
+      </c>
       <c r="K70" s="5" t="n"/>
       <c r="L70" s="5" t="n"/>
-    </row>
-    <row r="71">
+      <c r="M70" s="5" t="n"/>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      615 · Entretien et réparations</t>
-        </is>
-      </c>
-      <c r="C71" s="77" t="n"/>
-      <c r="D71" s="78" t="n">
-        <v>338915.38</v>
-      </c>
-      <c r="E71" s="79" t="inlineStr"/>
-      <c r="F71" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="80">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H71" s="78">
-        <f>D71*F71*G71</f>
-        <v/>
-      </c>
-      <c r="I71" s="81">
+      <c r="B71" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6411 · Salaires — enseignants permanents</t>
+        </is>
+      </c>
+      <c r="C71" s="80" t="n"/>
+      <c r="D71" s="81" t="n">
+        <v>3841069.84</v>
+      </c>
+      <c r="E71" s="82" t="inlineStr">
+        <is>
+          <t>les postes</t>
+        </is>
+      </c>
+      <c r="F71" s="83">
+        <f>$E$26</f>
+        <v/>
+      </c>
+      <c r="G71" s="83">
+        <f>$E$25</f>
+        <v/>
+      </c>
+      <c r="H71" s="81">
+        <f>D71*(1+F71)*(1+G71)</f>
+        <v/>
+      </c>
+      <c r="I71" s="84">
         <f>IFERROR(H71/D71-1,0)</f>
         <v/>
       </c>
-      <c r="J71" s="77" t="inlineStr"/>
+      <c r="J71" s="80" t="inlineStr"/>
       <c r="K71" s="5" t="n"/>
       <c r="L71" s="5" t="n"/>
-    </row>
-    <row r="72">
+      <c r="M71" s="5" t="n"/>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
       <c r="A72" s="5" t="n"/>
-      <c r="B72" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      616 · Primes d'assurance</t>
-        </is>
-      </c>
-      <c r="C72" s="77" t="n"/>
-      <c r="D72" s="78" t="n">
-        <v>225926.43</v>
-      </c>
-      <c r="E72" s="79" t="inlineStr"/>
-      <c r="F72" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="80">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H72" s="78">
-        <f>D72*F72*G72</f>
-        <v/>
-      </c>
-      <c r="I72" s="81">
+      <c r="B72" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6413 · Salaires — personnel administratif des campus</t>
+        </is>
+      </c>
+      <c r="C72" s="80" t="n"/>
+      <c r="D72" s="81" t="n">
+        <v>2033330.6</v>
+      </c>
+      <c r="E72" s="82" t="inlineStr">
+        <is>
+          <t>la paie</t>
+        </is>
+      </c>
+      <c r="F72" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="83">
+        <f>$E$25</f>
+        <v/>
+      </c>
+      <c r="H72" s="81">
+        <f>D72*(1+F72)*(1+G72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="84">
         <f>IFERROR(H72/D72-1,0)</f>
         <v/>
       </c>
-      <c r="J72" s="77" t="inlineStr"/>
+      <c r="J72" s="80" t="inlineStr"/>
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
-      <c r="B73" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      625 · Déplacements, missions et réceptions</t>
-        </is>
-      </c>
-      <c r="C73" s="77" t="n"/>
-      <c r="D73" s="78" t="n">
-        <v>338890.38</v>
-      </c>
-      <c r="E73" s="79" t="inlineStr"/>
-      <c r="F73" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="80">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H73" s="78">
-        <f>D73*F73*G73</f>
-        <v/>
-      </c>
-      <c r="I73" s="81">
+      <c r="B73" s="73" t="inlineStr">
+        <is>
+          <t>④  Assis sur la MASSE</t>
+        </is>
+      </c>
+      <c r="C73" s="73" t="n"/>
+      <c r="D73" s="74">
+        <f>SUM(D74:D74)</f>
+        <v/>
+      </c>
+      <c r="E73" s="88" t="inlineStr">
+        <is>
+          <t>au prorata de la masse salariale des campus</t>
+        </is>
+      </c>
+      <c r="F73" s="76" t="inlineStr"/>
+      <c r="G73" s="76" t="inlineStr"/>
+      <c r="H73" s="74">
+        <f>SUM(H74:H74)</f>
+        <v/>
+      </c>
+      <c r="I73" s="89">
         <f>IFERROR(H73/D73-1,0)</f>
         <v/>
       </c>
-      <c r="J73" s="77" t="inlineStr"/>
+      <c r="J73" s="90" t="inlineStr">
+        <is>
+          <t>NON — elle suit la masse, pas l'élève</t>
+        </is>
+      </c>
       <c r="K73" s="5" t="n"/>
       <c r="L73" s="5" t="n"/>
-    </row>
-    <row r="74">
+      <c r="M73" s="5" t="n"/>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      63511 · Contribution économique territoriale</t>
-        </is>
-      </c>
-      <c r="C74" s="77" t="n"/>
-      <c r="D74" s="78" t="n">
-        <v>225943.95</v>
-      </c>
-      <c r="E74" s="79" t="inlineStr"/>
-      <c r="F74" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="80">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H74" s="78">
-        <f>D74*F74*G74</f>
-        <v/>
-      </c>
-      <c r="I74" s="81">
+      <c r="B74" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      645 · Charges sociales sur les salaires</t>
+        </is>
+      </c>
+      <c r="C74" s="80" t="n"/>
+      <c r="D74" s="81" t="n">
+        <v>3162957.9</v>
+      </c>
+      <c r="E74" s="82" t="inlineStr">
+        <is>
+          <t>la masse des campus</t>
+        </is>
+      </c>
+      <c r="F74" s="83">
+        <f>(H71+H72)/(D71+D72)-1</f>
+        <v/>
+      </c>
+      <c r="G74" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="81">
+        <f>D74*(1+F74)*(1+G74)</f>
+        <v/>
+      </c>
+      <c r="I74" s="84">
         <f>IFERROR(H74/D74-1,0)</f>
         <v/>
       </c>
-      <c r="J74" s="77" t="inlineStr"/>
+      <c r="J74" s="80" t="inlineStr"/>
       <c r="K74" s="5" t="n"/>
       <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="70" t="inlineStr">
-        <is>
-          <t>⑥  DÉCIDÉ</t>
-        </is>
-      </c>
-      <c r="C75" s="70" t="n"/>
-      <c r="D75" s="71">
-        <f>SUM(D76:D76)</f>
+      <c r="B75" s="73" t="inlineStr">
+        <is>
+          <t>⑤  INDEXÉ</t>
+        </is>
+      </c>
+      <c r="C75" s="73" t="n"/>
+      <c r="D75" s="74">
+        <f>SUM(D76:D80)</f>
         <v/>
       </c>
       <c r="E75" s="91" t="inlineStr">
         <is>
-          <t>le geste lui-même</t>
-        </is>
-      </c>
-      <c r="F75" s="73" t="inlineStr"/>
-      <c r="G75" s="73" t="inlineStr"/>
-      <c r="H75" s="71">
-        <f>SUM(H76:H76)</f>
+          <t>inflation moins l'effort de productivité</t>
+        </is>
+      </c>
+      <c r="F75" s="76" t="inlineStr"/>
+      <c r="G75" s="76" t="inlineStr"/>
+      <c r="H75" s="74">
+        <f>SUM(H76:H80)</f>
         <v/>
       </c>
       <c r="I75" s="92">
@@ -5988,561 +6057,673 @@
       </c>
       <c r="J75" s="93" t="inlineStr">
         <is>
-          <t>c'est la saisie elle-même</t>
+          <t>NON — c'est le mur qui coûte, pas l'élève</t>
         </is>
       </c>
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
-    </row>
-    <row r="76">
+      <c r="M75" s="5" t="n"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
       <c r="A76" s="5" t="n"/>
-      <c r="B76" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6231 · Annonces et insertions — budget d'acquisition</t>
-        </is>
-      </c>
-      <c r="C76" s="77" t="n"/>
-      <c r="D76" s="78" t="n">
-        <v>434174</v>
-      </c>
-      <c r="E76" s="79" t="inlineStr"/>
-      <c r="F76" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="80">
-        <f>1+$E$15</f>
-        <v/>
-      </c>
-      <c r="H76" s="78">
-        <f>D76*F76*G76</f>
-        <v/>
-      </c>
-      <c r="I76" s="81">
+      <c r="B76" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      613 · Locations immobilières des campus</t>
+        </is>
+      </c>
+      <c r="C76" s="80" t="n"/>
+      <c r="D76" s="81" t="n">
+        <v>2372423.51</v>
+      </c>
+      <c r="E76" s="82" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F76" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="83">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H76" s="81">
+        <f>D76*(1+F76)*(1+G76)</f>
+        <v/>
+      </c>
+      <c r="I76" s="84">
         <f>IFERROR(H76/D76-1,0)</f>
         <v/>
       </c>
-      <c r="J76" s="77" t="inlineStr"/>
+      <c r="J76" s="80" t="inlineStr"/>
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="5" t="n"/>
-    </row>
-    <row r="77">
+      <c r="M76" s="5" t="n"/>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
       <c r="A77" s="5" t="n"/>
-      <c r="B77" s="70" t="inlineStr">
-        <is>
-          <t>TOTAL DES CHARGES DE CAMPUS</t>
-        </is>
-      </c>
-      <c r="C77" s="70" t="n"/>
-      <c r="D77" s="71">
-        <f>D59+D62+D64+D67+D69+D75</f>
-        <v/>
-      </c>
-      <c r="E77" s="70" t="inlineStr"/>
-      <c r="F77" s="73" t="inlineStr"/>
-      <c r="G77" s="73" t="inlineStr"/>
-      <c r="H77" s="71">
-        <f>H59+H62+H64+H67+H69+H75</f>
-        <v/>
-      </c>
-      <c r="I77" s="94">
+      <c r="B77" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      615 · Entretien et réparations</t>
+        </is>
+      </c>
+      <c r="C77" s="80" t="n"/>
+      <c r="D77" s="81" t="n">
+        <v>338915.38</v>
+      </c>
+      <c r="E77" s="82" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F77" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="83">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H77" s="81">
+        <f>D77*(1+F77)*(1+G77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="84">
         <f>IFERROR(H77/D77-1,0)</f>
         <v/>
       </c>
-      <c r="J77" s="70" t="inlineStr"/>
+      <c r="J77" s="80" t="inlineStr"/>
       <c r="K77" s="5" t="n"/>
       <c r="L77" s="5" t="n"/>
-    </row>
-    <row r="78">
+      <c r="M77" s="5" t="n"/>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
       <c r="A78" s="5" t="n"/>
-      <c r="B78" s="95" t="inlineStr">
-        <is>
-          <t>Chiffre d'affaires</t>
-        </is>
-      </c>
-      <c r="C78" s="95" t="n"/>
-      <c r="D78" s="96" t="n">
-        <v>23098985</v>
-      </c>
-      <c r="E78" s="95" t="inlineStr"/>
-      <c r="F78" s="97" t="inlineStr"/>
-      <c r="G78" s="97" t="inlineStr"/>
-      <c r="H78" s="96">
-        <f>E51</f>
-        <v/>
-      </c>
-      <c r="I78" s="98">
+      <c r="B78" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      616 · Primes d'assurance</t>
+        </is>
+      </c>
+      <c r="C78" s="80" t="n"/>
+      <c r="D78" s="81" t="n">
+        <v>225926.43</v>
+      </c>
+      <c r="E78" s="82" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F78" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="83">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H78" s="81">
+        <f>D78*(1+F78)*(1+G78)</f>
+        <v/>
+      </c>
+      <c r="I78" s="84">
         <f>IFERROR(H78/D78-1,0)</f>
         <v/>
       </c>
-      <c r="J78" s="95" t="inlineStr">
-        <is>
-          <t>bloc ⓒ ci-dessus</t>
-        </is>
-      </c>
+      <c r="J78" s="80" t="inlineStr"/>
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
-    </row>
-    <row r="79">
+      <c r="M78" s="5" t="n"/>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
       <c r="A79" s="5" t="n"/>
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>EBITDA PROPRE  ·  avant quote-part du siège</t>
-        </is>
-      </c>
-      <c r="C79" s="70" t="n"/>
-      <c r="D79" s="99">
-        <f>D78-D77</f>
-        <v/>
-      </c>
-      <c r="E79" s="70" t="inlineStr"/>
-      <c r="F79" s="73" t="inlineStr"/>
-      <c r="G79" s="73" t="inlineStr"/>
-      <c r="H79" s="99">
-        <f>H78-H77</f>
-        <v/>
-      </c>
-      <c r="I79" s="94">
+      <c r="B79" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      625 · Déplacements, missions et réceptions</t>
+        </is>
+      </c>
+      <c r="C79" s="80" t="n"/>
+      <c r="D79" s="81" t="n">
+        <v>338890.38</v>
+      </c>
+      <c r="E79" s="82" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F79" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="83">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H79" s="81">
+        <f>D79*(1+F79)*(1+G79)</f>
+        <v/>
+      </c>
+      <c r="I79" s="84">
         <f>IFERROR(H79/D79-1,0)</f>
         <v/>
       </c>
-      <c r="J79" s="70" t="inlineStr">
-        <is>
-          <t>ce que les campus produisent</t>
-        </is>
-      </c>
+      <c r="J79" s="80" t="inlineStr"/>
       <c r="K79" s="5" t="n"/>
       <c r="L79" s="5" t="n"/>
-    </row>
-    <row r="80">
+      <c r="M79" s="5" t="n"/>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
       <c r="A80" s="5" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
-      <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
+      <c r="B80" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      63511 · Contribution économique territoriale</t>
+        </is>
+      </c>
+      <c r="C80" s="80" t="n"/>
+      <c r="D80" s="81" t="n">
+        <v>225943.95</v>
+      </c>
+      <c r="E80" s="82" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F80" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="83">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H80" s="81">
+        <f>D80*(1+F80)*(1+G80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="84">
+        <f>IFERROR(H80/D80-1,0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="80" t="inlineStr"/>
       <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n"/>
-    </row>
-    <row r="81" ht="20" customHeight="1">
+      <c r="M80" s="5" t="n"/>
+    </row>
+    <row r="81">
       <c r="A81" s="5" t="n"/>
-      <c r="B81" s="100" t="inlineStr">
-        <is>
-          <t>LE SIÈGE  ·  il ne suit aucun inducteur d'activité — il se décide, puis se cascade</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
-      <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
+      <c r="B81" s="73" t="inlineStr">
+        <is>
+          <t>⑥  DÉCIDÉ</t>
+        </is>
+      </c>
+      <c r="C81" s="73" t="n"/>
+      <c r="D81" s="74">
+        <f>SUM(D82:D82)</f>
+        <v/>
+      </c>
+      <c r="E81" s="94" t="inlineStr">
+        <is>
+          <t>le geste lui-même</t>
+        </is>
+      </c>
+      <c r="F81" s="76" t="inlineStr"/>
+      <c r="G81" s="76" t="inlineStr"/>
+      <c r="H81" s="74">
+        <f>SUM(H82:H82)</f>
+        <v/>
+      </c>
+      <c r="I81" s="95">
+        <f>IFERROR(H81/D81-1,0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="96" t="inlineStr">
+        <is>
+          <t>c'est la décision elle-même</t>
+        </is>
+      </c>
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="n"/>
-    </row>
-    <row r="82">
+      <c r="M81" s="5" t="n"/>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
       <c r="A82" s="5" t="n"/>
-      <c r="B82" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6236 · Catalogues et imprimés — marketing de marque</t>
-        </is>
-      </c>
-      <c r="C82" s="102" t="n"/>
-      <c r="D82" s="67" t="n">
-        <v>676344</v>
-      </c>
-      <c r="E82" s="59" t="inlineStr">
-        <is>
-          <t>décidé — cascade K4</t>
-        </is>
-      </c>
-      <c r="F82" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="66">
-        <f>1+$E$21</f>
-        <v/>
-      </c>
-      <c r="H82" s="67">
-        <f>D82*F82*G82</f>
-        <v/>
-      </c>
-      <c r="I82" s="103">
+      <c r="B82" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6231 · Annonces et insertions — budget d'acquisition</t>
+        </is>
+      </c>
+      <c r="C82" s="80" t="n"/>
+      <c r="D82" s="81" t="n">
+        <v>434174</v>
+      </c>
+      <c r="E82" s="82" t="inlineStr">
+        <is>
+          <t>le geste</t>
+        </is>
+      </c>
+      <c r="F82" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="83">
+        <f>$E$21</f>
+        <v/>
+      </c>
+      <c r="H82" s="81">
+        <f>D82*(1+F82)*(1+G82)</f>
+        <v/>
+      </c>
+      <c r="I82" s="84">
         <f>IFERROR(H82/D82-1,0)</f>
         <v/>
       </c>
-      <c r="J82" s="102" t="inlineStr"/>
+      <c r="J82" s="80" t="inlineStr"/>
       <c r="K82" s="5" t="n"/>
       <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
-      <c r="B83" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6414 · Salaires du siège</t>
-        </is>
-      </c>
-      <c r="C83" s="102" t="n"/>
-      <c r="D83" s="67" t="n">
-        <v>1242649</v>
-      </c>
-      <c r="E83" s="59" t="inlineStr">
-        <is>
-          <t>politique salariale</t>
-        </is>
-      </c>
-      <c r="F83" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="66">
-        <f>1+$E$19</f>
-        <v/>
-      </c>
-      <c r="H83" s="67">
-        <f>D83*F83*G83</f>
-        <v/>
-      </c>
-      <c r="I83" s="103">
+      <c r="B83" s="73" t="inlineStr">
+        <is>
+          <t>TOTAL DES CHARGES DE CAMPUS</t>
+        </is>
+      </c>
+      <c r="C83" s="73" t="n"/>
+      <c r="D83" s="74">
+        <f>D65+D68+D70+D73+D75+D81</f>
+        <v/>
+      </c>
+      <c r="E83" s="73" t="inlineStr"/>
+      <c r="F83" s="76" t="inlineStr"/>
+      <c r="G83" s="76" t="inlineStr"/>
+      <c r="H83" s="74">
+        <f>H65+H68+H70+H73+H75+H81</f>
+        <v/>
+      </c>
+      <c r="I83" s="97">
         <f>IFERROR(H83/D83-1,0)</f>
         <v/>
       </c>
-      <c r="J83" s="102" t="inlineStr"/>
+      <c r="J83" s="73" t="inlineStr"/>
       <c r="K83" s="5" t="n"/>
       <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
-      <c r="B84" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6226 · Honoraires</t>
-        </is>
-      </c>
-      <c r="C84" s="102" t="n"/>
-      <c r="D84" s="67" t="n">
-        <v>564841</v>
-      </c>
-      <c r="E84" s="59" t="inlineStr"/>
-      <c r="F84" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="66">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H84" s="67">
-        <f>D84*F84*G84</f>
-        <v/>
-      </c>
-      <c r="I84" s="103">
+      <c r="B84" s="98" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="C84" s="98" t="n"/>
+      <c r="D84" s="99" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="E84" s="98" t="inlineStr"/>
+      <c r="F84" s="100" t="inlineStr"/>
+      <c r="G84" s="100" t="inlineStr"/>
+      <c r="H84" s="99">
+        <f>E57</f>
+        <v/>
+      </c>
+      <c r="I84" s="101">
         <f>IFERROR(H84/D84-1,0)</f>
         <v/>
       </c>
-      <c r="J84" s="102" t="inlineStr"/>
+      <c r="J84" s="98" t="inlineStr">
+        <is>
+          <t>bloc ⓒ ci-dessus</t>
+        </is>
+      </c>
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
-      <c r="B85" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      626 · Frais postaux et de télécommunications</t>
-        </is>
-      </c>
-      <c r="C85" s="102" t="n"/>
-      <c r="D85" s="67" t="n">
-        <v>451872</v>
-      </c>
-      <c r="E85" s="59" t="inlineStr"/>
-      <c r="F85" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="66">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H85" s="67">
-        <f>D85*F85*G85</f>
-        <v/>
-      </c>
-      <c r="I85" s="103">
+      <c r="B85" s="73" t="inlineStr">
+        <is>
+          <t>EBITDA PROPRE  ·  avant quote-part du siège</t>
+        </is>
+      </c>
+      <c r="C85" s="73" t="n"/>
+      <c r="D85" s="102">
+        <f>D84-D83</f>
+        <v/>
+      </c>
+      <c r="E85" s="73" t="inlineStr"/>
+      <c r="F85" s="76" t="inlineStr"/>
+      <c r="G85" s="76" t="inlineStr"/>
+      <c r="H85" s="102">
+        <f>H84-H83</f>
+        <v/>
+      </c>
+      <c r="I85" s="97">
         <f>IFERROR(H85/D85-1,0)</f>
         <v/>
       </c>
-      <c r="J85" s="102" t="inlineStr"/>
+      <c r="J85" s="73" t="inlineStr">
+        <is>
+          <t>ce que les campus produisent</t>
+        </is>
+      </c>
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
-      <c r="B86" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6281 · Cotisations et concours divers</t>
-        </is>
-      </c>
-      <c r="C86" s="102" t="n"/>
-      <c r="D86" s="67" t="n">
-        <v>180749</v>
-      </c>
-      <c r="E86" s="59" t="inlineStr"/>
-      <c r="F86" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="66">
-        <f>1+$E$17-$E$18</f>
-        <v/>
-      </c>
-      <c r="H86" s="67">
-        <f>D86*F86*G86</f>
-        <v/>
-      </c>
-      <c r="I86" s="103">
-        <f>IFERROR(H86/D86-1,0)</f>
-        <v/>
-      </c>
-      <c r="J86" s="102" t="inlineStr"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="5" t="n"/>
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="n"/>
-    </row>
-    <row r="87">
+      <c r="M86" s="5" t="n"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
       <c r="A87" s="5" t="n"/>
-      <c r="B87" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6331 · Versement mobilité</t>
-        </is>
-      </c>
-      <c r="C87" s="102" t="n"/>
-      <c r="D87" s="67" t="n">
-        <v>338904</v>
-      </c>
-      <c r="E87" s="59" t="inlineStr">
-        <is>
-          <t>assis sur la masse</t>
-        </is>
-      </c>
-      <c r="F87" s="66">
-        <f>(H65+H66+H83)/(D65+D66+D83)</f>
-        <v/>
-      </c>
-      <c r="G87" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="67">
-        <f>D87*F87*G87</f>
-        <v/>
-      </c>
-      <c r="I87" s="103">
-        <f>IFERROR(H87/D87-1,0)</f>
-        <v/>
-      </c>
-      <c r="J87" s="102" t="inlineStr"/>
+      <c r="B87" s="103" t="inlineStr">
+        <is>
+          <t>LE SIÈGE  ·  il ne suit aucun inducteur d'activité — il se décide, puis se cascade</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="n"/>
-    </row>
-    <row r="88">
+      <c r="M87" s="5" t="n"/>
+    </row>
+    <row r="88" hidden="1" outlineLevel="1">
       <c r="A88" s="5" t="n"/>
-      <c r="B88" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6333 · Participation à la formation professionnelle</t>
-        </is>
-      </c>
-      <c r="C88" s="102" t="n"/>
-      <c r="D88" s="67" t="n">
-        <v>112968</v>
-      </c>
-      <c r="E88" s="59" t="inlineStr">
-        <is>
-          <t>assis sur la masse</t>
-        </is>
-      </c>
-      <c r="F88" s="66">
-        <f>(H65+H66+H83)/(D65+D66+D83)</f>
-        <v/>
-      </c>
-      <c r="G88" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="67">
-        <f>D88*F88*G88</f>
-        <v/>
-      </c>
-      <c r="I88" s="103">
+      <c r="B88" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6236 · Catalogues et imprimés — marketing de marque</t>
+        </is>
+      </c>
+      <c r="C88" s="105" t="n"/>
+      <c r="D88" s="70" t="n">
+        <v>676344</v>
+      </c>
+      <c r="E88" s="62" t="inlineStr">
+        <is>
+          <t>le budget de marque</t>
+        </is>
+      </c>
+      <c r="F88" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="69">
+        <f>$E$27</f>
+        <v/>
+      </c>
+      <c r="H88" s="70">
+        <f>D88*(1+F88)*(1+G88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="106">
         <f>IFERROR(H88/D88-1,0)</f>
         <v/>
       </c>
-      <c r="J88" s="102" t="inlineStr"/>
+      <c r="J88" s="105" t="inlineStr"/>
       <c r="K88" s="5" t="n"/>
       <c r="L88" s="5" t="n"/>
-    </row>
-    <row r="89">
+      <c r="M88" s="5" t="n"/>
+    </row>
+    <row r="89" hidden="1" outlineLevel="1">
       <c r="A89" s="5" t="n"/>
-      <c r="B89" s="70" t="inlineStr">
-        <is>
-          <t>QUOTE-PART DU SIÈGE  ·  6236 + 6414 + 6226 + 626 + 6281 + 6331 + 6333</t>
-        </is>
-      </c>
-      <c r="C89" s="70" t="n"/>
-      <c r="D89" s="71">
-        <f>D82+D83+D84+D85+D86+D87+D88</f>
-        <v/>
-      </c>
-      <c r="E89" s="70" t="inlineStr"/>
-      <c r="F89" s="73" t="inlineStr"/>
-      <c r="G89" s="73" t="inlineStr"/>
-      <c r="H89" s="71">
-        <f>H82+H83+H84+H85+H86+H87+H88</f>
-        <v/>
-      </c>
-      <c r="I89" s="94">
+      <c r="B89" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6414 · Salaires du siège</t>
+        </is>
+      </c>
+      <c r="C89" s="105" t="n"/>
+      <c r="D89" s="70" t="n">
+        <v>1242649</v>
+      </c>
+      <c r="E89" s="62" t="inlineStr">
+        <is>
+          <t>la paie</t>
+        </is>
+      </c>
+      <c r="F89" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="69">
+        <f>$E$25</f>
+        <v/>
+      </c>
+      <c r="H89" s="70">
+        <f>D89*(1+F89)*(1+G89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="106">
         <f>IFERROR(H89/D89-1,0)</f>
         <v/>
       </c>
-      <c r="J89" s="70" t="inlineStr">
-        <is>
-          <t>cascades K1 et K4</t>
-        </is>
-      </c>
+      <c r="J89" s="105" t="inlineStr"/>
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="n"/>
-    </row>
-    <row r="90">
+      <c r="M89" s="5" t="n"/>
+    </row>
+    <row r="90" hidden="1" outlineLevel="1">
       <c r="A90" s="5" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
+      <c r="B90" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6226 · Honoraires</t>
+        </is>
+      </c>
+      <c r="C90" s="105" t="n"/>
+      <c r="D90" s="70" t="n">
+        <v>564841</v>
+      </c>
+      <c r="E90" s="62" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F90" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="69">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H90" s="70">
+        <f>D90*(1+F90)*(1+G90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="106">
+        <f>IFERROR(H90/D90-1,0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="105" t="inlineStr"/>
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="5" t="n"/>
-    </row>
-    <row r="91">
+      <c r="M90" s="5" t="n"/>
+    </row>
+    <row r="91" hidden="1" outlineLevel="1">
       <c r="A91" s="5" t="n"/>
-      <c r="B91" s="70" t="inlineStr">
-        <is>
-          <t>EBITDA NET  ·  celui du groupe</t>
-        </is>
-      </c>
-      <c r="C91" s="70" t="n"/>
-      <c r="D91" s="104">
-        <f>D79-D89</f>
-        <v/>
-      </c>
-      <c r="E91" s="70" t="inlineStr"/>
-      <c r="F91" s="73" t="inlineStr"/>
-      <c r="G91" s="73" t="inlineStr"/>
-      <c r="H91" s="104">
-        <f>H79-H89</f>
-        <v/>
-      </c>
-      <c r="I91" s="94">
+      <c r="B91" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      626 · Frais postaux et de télécommunications</t>
+        </is>
+      </c>
+      <c r="C91" s="105" t="n"/>
+      <c r="D91" s="70" t="n">
+        <v>451872</v>
+      </c>
+      <c r="E91" s="62" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F91" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="69">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H91" s="70">
+        <f>D91*(1+F91)*(1+G91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="106">
         <f>IFERROR(H91/D91-1,0)</f>
         <v/>
       </c>
-      <c r="J91" s="70" t="inlineStr">
-        <is>
-          <t>dotations exclues</t>
-        </is>
-      </c>
+      <c r="J91" s="105" t="inlineStr"/>
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="5" t="n"/>
-    </row>
-    <row r="92">
+      <c r="M91" s="5" t="n"/>
+    </row>
+    <row r="92" hidden="1" outlineLevel="1">
       <c r="A92" s="5" t="n"/>
-      <c r="B92" s="61" t="inlineStr">
-        <is>
-          <t>Marge — propre  ·  nette</t>
-        </is>
-      </c>
-      <c r="C92" s="61" t="n"/>
-      <c r="D92" s="105">
-        <f>IFERROR(D79/D78,0)</f>
-        <v/>
-      </c>
-      <c r="E92" s="61" t="inlineStr"/>
-      <c r="F92" s="106" t="inlineStr"/>
-      <c r="G92" s="106" t="inlineStr"/>
-      <c r="H92" s="105">
-        <f>IFERROR(H79/H78,0)</f>
-        <v/>
-      </c>
-      <c r="I92" s="107" t="n"/>
-      <c r="J92" s="61">
-        <f>"nette : "&amp;TEXT(D91/D78,"0.0 %")&amp;"  →  "&amp;TEXT(H91/H78,"0.0 %")</f>
-        <v/>
-      </c>
+      <c r="B92" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6281 · Cotisations et concours divers</t>
+        </is>
+      </c>
+      <c r="C92" s="105" t="n"/>
+      <c r="D92" s="70" t="n">
+        <v>180749</v>
+      </c>
+      <c r="E92" s="62" t="inlineStr">
+        <is>
+          <t>l'indexation</t>
+        </is>
+      </c>
+      <c r="F92" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="69">
+        <f>$E$23-$E$24</f>
+        <v/>
+      </c>
+      <c r="H92" s="70">
+        <f>D92*(1+F92)*(1+G92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="106">
+        <f>IFERROR(H92/D92-1,0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="105" t="inlineStr"/>
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
-    </row>
-    <row r="93">
+      <c r="M92" s="5" t="n"/>
+    </row>
+    <row r="93" hidden="1" outlineLevel="1">
       <c r="A93" s="5" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
+      <c r="B93" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6331 · Versement mobilité</t>
+        </is>
+      </c>
+      <c r="C93" s="105" t="n"/>
+      <c r="D93" s="70" t="n">
+        <v>338904</v>
+      </c>
+      <c r="E93" s="62" t="inlineStr">
+        <is>
+          <t>la masse totale</t>
+        </is>
+      </c>
+      <c r="F93" s="69">
+        <f>(H71+H72+H89)/(D71+D72+D89)-1</f>
+        <v/>
+      </c>
+      <c r="G93" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="70">
+        <f>D93*(1+F93)*(1+G93)</f>
+        <v/>
+      </c>
+      <c r="I93" s="106">
+        <f>IFERROR(H93/D93-1,0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="105" t="inlineStr"/>
       <c r="K93" s="5" t="n"/>
       <c r="L93" s="5" t="n"/>
-    </row>
-    <row r="94">
+      <c r="M93" s="5" t="n"/>
+    </row>
+    <row r="94" hidden="1" outlineLevel="1">
       <c r="A94" s="5" t="n"/>
-      <c r="B94" s="101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      6811 · Dotations aux amortissements  ·  sous la ligne d'EBITDA</t>
-        </is>
-      </c>
-      <c r="C94" s="102" t="n"/>
-      <c r="D94" s="67" t="n">
-        <v>1352683</v>
-      </c>
-      <c r="E94" s="59" t="inlineStr">
-        <is>
-          <t>hors modèle</t>
-        </is>
-      </c>
-      <c r="F94" s="66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="66">
-        <f>1+$E$22</f>
-        <v/>
-      </c>
-      <c r="H94" s="67">
-        <f>D94*F94*G94</f>
-        <v/>
-      </c>
-      <c r="I94" s="103">
+      <c r="B94" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6333 · Participation à la formation professionnelle</t>
+        </is>
+      </c>
+      <c r="C94" s="105" t="n"/>
+      <c r="D94" s="70" t="n">
+        <v>112968</v>
+      </c>
+      <c r="E94" s="62" t="inlineStr">
+        <is>
+          <t>la masse totale</t>
+        </is>
+      </c>
+      <c r="F94" s="69">
+        <f>(H71+H72+H89)/(D71+D72+D89)-1</f>
+        <v/>
+      </c>
+      <c r="G94" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="70">
+        <f>D94*(1+F94)*(1+G94)</f>
+        <v/>
+      </c>
+      <c r="I94" s="106">
         <f>IFERROR(H94/D94-1,0)</f>
         <v/>
       </c>
-      <c r="J94" s="102" t="inlineStr"/>
+      <c r="J94" s="105" t="inlineStr"/>
       <c r="K94" s="5" t="n"/>
       <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
+      <c r="B95" s="73" t="inlineStr">
+        <is>
+          <t>QUOTE-PART DU SIÈGE</t>
+        </is>
+      </c>
+      <c r="C95" s="73" t="n"/>
+      <c r="D95" s="74">
+        <f>D88+D89+D90+D91+D92+D93+D94</f>
+        <v/>
+      </c>
+      <c r="E95" s="73" t="inlineStr"/>
+      <c r="F95" s="76" t="inlineStr"/>
+      <c r="G95" s="76" t="inlineStr"/>
+      <c r="H95" s="74">
+        <f>H88+H89+H90+H91+H92+H93+H94</f>
+        <v/>
+      </c>
+      <c r="I95" s="97">
+        <f>IFERROR(H95/D95-1,0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="73" t="inlineStr">
+        <is>
+          <t>marque, holding — cascades K1 et K4</t>
+        </is>
+      </c>
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -6557,42 +6738,67 @@
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="5" t="n"/>
-    </row>
-    <row r="97" ht="20" customHeight="1">
+      <c r="M96" s="5" t="n"/>
+    </row>
+    <row r="97">
       <c r="A97" s="5" t="n"/>
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>ⓔ  Est-ce qu'on retombe sur le moteur ?</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
-      <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
+      <c r="B97" s="73" t="inlineStr">
+        <is>
+          <t>EBITDA NET  ·  celui du groupe</t>
+        </is>
+      </c>
+      <c r="C97" s="73" t="n"/>
+      <c r="D97" s="107">
+        <f>D85-D95</f>
+        <v/>
+      </c>
+      <c r="E97" s="73" t="inlineStr"/>
+      <c r="F97" s="76" t="inlineStr"/>
+      <c r="G97" s="76" t="inlineStr"/>
+      <c r="H97" s="107">
+        <f>H85-H95</f>
+        <v/>
+      </c>
+      <c r="I97" s="97">
+        <f>IFERROR(H97/D97-1,0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="73" t="inlineStr">
+        <is>
+          <t>dotations exclues</t>
+        </is>
+      </c>
       <c r="K97" s="5" t="n"/>
       <c r="L97" s="5" t="n"/>
-    </row>
-    <row r="98" ht="14" customHeight="1">
+      <c r="M97" s="5" t="n"/>
+    </row>
+    <row r="98">
       <c r="A98" s="5" t="n"/>
-      <c r="B98" s="24" t="inlineStr">
-        <is>
-          <t>Le CA gagné est le même nombre — c'est le même lien. Le coût de service, lui, est calculé de deux façons : le moteur pondère campus par campus, le budget applique un taux au réseau. L'écart qui en résulte est affiché, pas gommé.</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="n"/>
-      <c r="D98" s="5" t="n"/>
-      <c r="E98" s="5" t="n"/>
-      <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="n"/>
-      <c r="H98" s="5" t="n"/>
-      <c r="I98" s="5" t="n"/>
-      <c r="J98" s="5" t="n"/>
+      <c r="B98" s="64" t="inlineStr">
+        <is>
+          <t>Marge d'EBITDA  —  propre</t>
+        </is>
+      </c>
+      <c r="C98" s="64" t="n"/>
+      <c r="D98" s="108">
+        <f>IFERROR(D85/D84,0)</f>
+        <v/>
+      </c>
+      <c r="E98" s="64" t="inlineStr"/>
+      <c r="F98" s="109" t="inlineStr"/>
+      <c r="G98" s="109" t="inlineStr"/>
+      <c r="H98" s="108">
+        <f>IFERROR(H85/H84,0)</f>
+        <v/>
+      </c>
+      <c r="I98" s="110" t="inlineStr"/>
+      <c r="J98" s="64">
+        <f>"et nette : "&amp;TEXT(D97/D84,"0.0 %")&amp;"  →  "&amp;TEXT(H97/H84,"0.0 %")</f>
+        <v/>
+      </c>
       <c r="K98" s="5" t="n"/>
       <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -6607,137 +6813,100 @@
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="5" t="n"/>
       <c r="L99" s="5" t="n"/>
-    </row>
-    <row r="100" ht="26" customHeight="1">
+      <c r="M99" s="5" t="n"/>
+    </row>
+    <row r="100">
       <c r="A100" s="5" t="n"/>
-      <c r="B100" s="25" t="inlineStr">
-        <is>
-          <t>Ce que le geste rapporte</t>
-        </is>
-      </c>
-      <c r="C100" s="26" t="n"/>
-      <c r="D100" s="26" t="inlineStr">
-        <is>
-          <t>Le moteur</t>
-        </is>
-      </c>
-      <c r="E100" s="26" t="n"/>
-      <c r="F100" s="26" t="inlineStr">
-        <is>
-          <t>Le budget 2027</t>
-        </is>
-      </c>
-      <c r="G100" s="26" t="n"/>
-      <c r="H100" s="26" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-      <c r="I100" s="26" t="n"/>
-      <c r="J100" s="26" t="inlineStr">
-        <is>
-          <t>Pourquoi</t>
-        </is>
-      </c>
+      <c r="B100" s="104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      6811 · Dotations aux amortissements  ·  sous la ligne d'EBITDA</t>
+        </is>
+      </c>
+      <c r="C100" s="105" t="n"/>
+      <c r="D100" s="70" t="n">
+        <v>1352683</v>
+      </c>
+      <c r="E100" s="62" t="inlineStr">
+        <is>
+          <t>le plan d'amortissement</t>
+        </is>
+      </c>
+      <c r="F100" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="69">
+        <f>$E$28</f>
+        <v/>
+      </c>
+      <c r="H100" s="70">
+        <f>D100*(1+F100)*(1+G100)</f>
+        <v/>
+      </c>
+      <c r="I100" s="106">
+        <f>IFERROR(H100/D100-1,0)</f>
+        <v/>
+      </c>
+      <c r="J100" s="105" t="inlineStr"/>
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
-      <c r="B101" s="102" t="inlineStr">
-        <is>
-          <t>CA gagné par le geste</t>
-        </is>
-      </c>
-      <c r="C101" s="57" t="n"/>
-      <c r="D101" s="67">
-        <f>'Le moteur'!J58</f>
-        <v/>
-      </c>
-      <c r="E101" s="57" t="n"/>
-      <c r="F101" s="67">
-        <f>E49</f>
-        <v/>
-      </c>
-      <c r="G101" s="57" t="n"/>
-      <c r="H101" s="108">
-        <f>F101-D101</f>
-        <v/>
-      </c>
-      <c r="I101" s="57" t="n"/>
-      <c r="J101" s="59" t="inlineStr">
-        <is>
-          <t>le même lien — zéro par construction</t>
-        </is>
-      </c>
-      <c r="K101" s="57" t="n"/>
-      <c r="L101" s="57" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
-      <c r="B102" s="102" t="inlineStr">
-        <is>
-          <t>Coût de servir ces élèves</t>
-        </is>
-      </c>
-      <c r="C102" s="57" t="n"/>
-      <c r="D102" s="67">
-        <f>'Le moteur'!I58*'Le moteur'!K58</f>
-        <v/>
-      </c>
-      <c r="E102" s="57" t="n"/>
-      <c r="F102" s="67">
-        <f>D59*'Le moteur'!I58/'Le moteur'!N34</f>
-        <v/>
-      </c>
-      <c r="G102" s="57" t="n"/>
-      <c r="H102" s="108">
-        <f>F102-D102</f>
-        <v/>
-      </c>
-      <c r="I102" s="57" t="n"/>
-      <c r="J102" s="59" t="inlineStr">
-        <is>
-          <t>consommables du réseau au prorata des inscrits gagnés</t>
-        </is>
-      </c>
-      <c r="K102" s="57" t="n"/>
-      <c r="L102" s="57" t="n"/>
-    </row>
-    <row r="103">
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="5" t="n"/>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
       <c r="A103" s="5" t="n"/>
-      <c r="B103" s="61" t="inlineStr">
-        <is>
-          <t>EBITDA gagné</t>
-        </is>
-      </c>
-      <c r="C103" s="57" t="n"/>
-      <c r="D103" s="109">
-        <f>'Le moteur'!L58</f>
-        <v/>
-      </c>
-      <c r="E103" s="57" t="n"/>
-      <c r="F103" s="109">
-        <f>F101-(H76-D76)-F102</f>
-        <v/>
-      </c>
-      <c r="G103" s="57" t="n"/>
-      <c r="H103" s="110">
-        <f>F103-D103</f>
-        <v/>
-      </c>
-      <c r="I103" s="57" t="n"/>
-      <c r="J103" s="59" t="inlineStr">
-        <is>
-          <t>CA gagné − Δ budget 6231 − coût de service</t>
-        </is>
-      </c>
-      <c r="K103" s="57" t="n"/>
-      <c r="L103" s="57" t="n"/>
-    </row>
-    <row r="104">
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>ⓔ  Est-ce que ce budget dit la même chose que le moteur ?</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
+      <c r="J103" s="5" t="n"/>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="5" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1">
       <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>Le CA gagné est le même nombre — c'est la même cellule. Le coût de service, lui, se calcule de deux façons : le moteur pondère campus par campus, le budget applique un taux au réseau. L'écart qui en résulte est affiché, pas gommé.</t>
+        </is>
+      </c>
       <c r="C104" s="5" t="n"/>
       <c r="D104" s="5" t="n"/>
       <c r="E104" s="5" t="n"/>
@@ -6748,74 +6917,240 @@
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n"/>
-    </row>
-    <row r="105" ht="18" customHeight="1">
+      <c r="M104" s="5" t="n"/>
+    </row>
+    <row r="105">
       <c r="A105" s="5" t="n"/>
-      <c r="B105" s="111">
-        <f>"Le budget 2027 retombe sur l'EBITDA gagné du moteur à "&amp;TEXT(ABS(H103),"#,##0 €")&amp;" près, soit "&amp;TEXT(ABS(H103/D103),"0.00 %")&amp;" — et l'écart a une cause nommée, pas une tolérance."</f>
-        <v/>
-      </c>
-      <c r="C105" s="112" t="n"/>
-      <c r="D105" s="112" t="n"/>
-      <c r="E105" s="112" t="n"/>
-      <c r="F105" s="112" t="n"/>
-      <c r="G105" s="112" t="n"/>
-      <c r="H105" s="112" t="n"/>
-      <c r="I105" s="112" t="n"/>
-      <c r="J105" s="112" t="n"/>
-      <c r="K105" s="112" t="n"/>
-      <c r="L105" s="112" t="n"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+    </row>
+    <row r="106" ht="26" customHeight="1">
       <c r="A106" s="5" t="n"/>
-      <c r="B106" s="113">
-        <f>"2027 : marge propre "&amp;TEXT(D79/D78,"0.0 %")&amp;" → "&amp;TEXT(H79/H78,"0.0 %")&amp;",  marge nette "&amp;TEXT(D91/D78,"0.0 %")&amp;" → "&amp;TEXT(H91/H78,"0.0 %")&amp;".  La nette gagne plus que la propre : ce n'est pas une performance de campus, c'est le siège qui se dilue — il croît de "&amp;TEXT(H89/D89-1,"0.0 %")&amp;" quand le CA croît de "&amp;TEXT(H78/D78-1,"0.0 %")&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C106" s="13" t="n"/>
-      <c r="D106" s="13" t="n"/>
-      <c r="E106" s="13" t="n"/>
-      <c r="F106" s="13" t="n"/>
-      <c r="G106" s="13" t="n"/>
-      <c r="H106" s="13" t="n"/>
-      <c r="I106" s="13" t="n"/>
-      <c r="J106" s="13" t="n"/>
-      <c r="K106" s="13" t="n"/>
-      <c r="L106" s="13" t="n"/>
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Ce que le geste rapporte</t>
+        </is>
+      </c>
+      <c r="C106" s="26" t="n"/>
+      <c r="D106" s="26" t="inlineStr">
+        <is>
+          <t>Le moteur</t>
+        </is>
+      </c>
+      <c r="E106" s="26" t="n"/>
+      <c r="F106" s="26" t="inlineStr">
+        <is>
+          <t>Le budget 2027</t>
+        </is>
+      </c>
+      <c r="G106" s="26" t="n"/>
+      <c r="H106" s="26" t="inlineStr">
+        <is>
+          <t>Écart</t>
+        </is>
+      </c>
+      <c r="I106" s="26" t="n"/>
+      <c r="J106" s="26" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
-      <c r="B107" s="114">
-        <f>"Le gain ne vient d'aucune économie : il vient de "&amp;TEXT(E31-E28,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes — dont "&amp;TEXT(E30,"#,##0")&amp;" que le geste a payés."</f>
-        <v/>
-      </c>
-      <c r="C107" s="115" t="n"/>
-      <c r="D107" s="115" t="n"/>
-      <c r="E107" s="115" t="n"/>
-      <c r="F107" s="115" t="n"/>
-      <c r="G107" s="115" t="n"/>
-      <c r="H107" s="115" t="n"/>
-      <c r="I107" s="115" t="n"/>
-      <c r="J107" s="115" t="n"/>
-      <c r="K107" s="115" t="n"/>
-      <c r="L107" s="115" t="n"/>
+      <c r="B107" s="105" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires gagné</t>
+        </is>
+      </c>
+      <c r="C107" s="60" t="n"/>
+      <c r="D107" s="70">
+        <f>'Le moteur'!J58</f>
+        <v/>
+      </c>
+      <c r="E107" s="60" t="n"/>
+      <c r="F107" s="70">
+        <f>E55</f>
+        <v/>
+      </c>
+      <c r="G107" s="60" t="n"/>
+      <c r="H107" s="111">
+        <f>F107-D107</f>
+        <v/>
+      </c>
+      <c r="I107" s="60" t="n"/>
+      <c r="J107" s="62" t="inlineStr">
+        <is>
+          <t>la même cellule — zéro par construction</t>
+        </is>
+      </c>
+      <c r="K107" s="60" t="n"/>
+      <c r="L107" s="60" t="n"/>
+      <c r="M107" s="60" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
-      <c r="G108" s="5" t="n"/>
-      <c r="H108" s="5" t="n"/>
-      <c r="I108" s="5" t="n"/>
-      <c r="J108" s="5" t="n"/>
-      <c r="K108" s="5" t="n"/>
-      <c r="L108" s="5" t="n"/>
+      <c r="B108" s="105" t="inlineStr">
+        <is>
+          <t>Coût de servir ces élèves</t>
+        </is>
+      </c>
+      <c r="C108" s="60" t="n"/>
+      <c r="D108" s="70">
+        <f>'Le moteur'!I58*'Le moteur'!K58</f>
+        <v/>
+      </c>
+      <c r="E108" s="60" t="n"/>
+      <c r="F108" s="70">
+        <f>D65*'Le moteur'!I58/'Le moteur'!N34</f>
+        <v/>
+      </c>
+      <c r="G108" s="60" t="n"/>
+      <c r="H108" s="111">
+        <f>F108-D108</f>
+        <v/>
+      </c>
+      <c r="I108" s="60" t="n"/>
+      <c r="J108" s="62" t="inlineStr">
+        <is>
+          <t>consommables du réseau au prorata des élèves gagnés</t>
+        </is>
+      </c>
+      <c r="K108" s="60" t="n"/>
+      <c r="L108" s="60" t="n"/>
+      <c r="M108" s="60" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="64" t="inlineStr">
+        <is>
+          <t>EBITDA gagné</t>
+        </is>
+      </c>
+      <c r="C109" s="60" t="n"/>
+      <c r="D109" s="112">
+        <f>'Le moteur'!L58</f>
+        <v/>
+      </c>
+      <c r="E109" s="60" t="n"/>
+      <c r="F109" s="112">
+        <f>F107-(H82-D82)-F108</f>
+        <v/>
+      </c>
+      <c r="G109" s="60" t="n"/>
+      <c r="H109" s="113">
+        <f>F109-D109</f>
+        <v/>
+      </c>
+      <c r="I109" s="60" t="n"/>
+      <c r="J109" s="62" t="inlineStr">
+        <is>
+          <t>CA gagné − Δ budget d'acquisition − coût de service</t>
+        </is>
+      </c>
+      <c r="K109" s="60" t="n"/>
+      <c r="L109" s="60" t="n"/>
+      <c r="M109" s="60" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="5" t="n"/>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="114">
+        <f>"Ce budget retombe sur l'EBITDA gagné du moteur à "&amp;TEXT(ABS(H109),"#,##0 €")&amp;" près, soit "&amp;TEXT(ABS(H109/D109),"0.00 %")&amp;" — et l'écart a une cause nommée, pas une tolérance."</f>
+        <v/>
+      </c>
+      <c r="C111" s="115" t="n"/>
+      <c r="D111" s="115" t="n"/>
+      <c r="E111" s="115" t="n"/>
+      <c r="F111" s="115" t="n"/>
+      <c r="G111" s="115" t="n"/>
+      <c r="H111" s="115" t="n"/>
+      <c r="I111" s="115" t="n"/>
+      <c r="J111" s="115" t="n"/>
+      <c r="K111" s="115" t="n"/>
+      <c r="L111" s="115" t="n"/>
+      <c r="M111" s="115" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="116">
+        <f>"La marge nette gagne "&amp;TEXT((H97/H84-D97/D84)*100,"0.0")&amp;" pt quand la marge propre n'en gagne que "&amp;TEXT((H85/H84-D85/D84)*100,"0.0")&amp;" : la différence ne vient pas des campus, elle vient du siège qui se dilue — il croît de "&amp;TEXT(H95/D95-1,"0.0 %")&amp;" quand le chiffre d'affaires croît de "&amp;TEXT(H84/D84-1,"0.0 %")&amp;"."</f>
+        <v/>
+      </c>
+      <c r="C112" s="13" t="n"/>
+      <c r="D112" s="13" t="n"/>
+      <c r="E112" s="13" t="n"/>
+      <c r="F112" s="13" t="n"/>
+      <c r="G112" s="13" t="n"/>
+      <c r="H112" s="13" t="n"/>
+      <c r="I112" s="13" t="n"/>
+      <c r="J112" s="13" t="n"/>
+      <c r="K112" s="13" t="n"/>
+      <c r="L112" s="13" t="n"/>
+      <c r="M112" s="13" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+      <c r="B113" s="117">
+        <f>"Et le gain ne vient d'aucune économie : il vient de "&amp;TEXT(E37-E34,"#,##0")&amp;" élèves de plus dans des classes déjà ouvertes — dont "&amp;TEXT(E36,"#,##0")&amp;" que le geste a payés."</f>
+        <v/>
+      </c>
+      <c r="C113" s="118" t="n"/>
+      <c r="D113" s="118" t="n"/>
+      <c r="E113" s="118" t="n"/>
+      <c r="F113" s="118" t="n"/>
+      <c r="G113" s="118" t="n"/>
+      <c r="H113" s="118" t="n"/>
+      <c r="I113" s="118" t="n"/>
+      <c r="J113" s="118" t="n"/>
+      <c r="K113" s="118" t="n"/>
+      <c r="L113" s="118" t="n"/>
+      <c r="M113" s="118" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="5" t="n"/>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I60 I61 I63 I65 I66 I68 I70 I71 I72 I73 I74 I76">
+  <conditionalFormatting sqref="I66 I67 I69 I71 I72 I74 I76 I77 I78 I79 I80 I82">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6827,15 +7162,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 EDUSERVICES · Budget 2027&amp;R&amp;"Arial"&amp;8 page &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00E7E6E6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6952,7 +7298,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>AW_002_000004_000001 est au grain CAMPUS × COMPTE. Un coût par élève et par programme ne se lit donc pas : il s'alloue. V_ALLOCATION le fait déjà, avec des clés différentes selon la nature de la charge — et c'est de là que vient tout le reste.</t>
+          <t>La comptabilité est tenue au grain CAMPUS × COMPTE. Un coût par élève et par programme ne se lit donc pas : il s'alloue. V_ALLOCATION le fait déjà, avec des clés différentes selon la nature de la charge — et c'est de là que vient tout le reste.</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -7086,36 +7432,36 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>Consommables</t>
         </is>
       </c>
-      <c r="C12" s="116" t="inlineStr">
+      <c r="C12" s="119" t="inlineStr">
         <is>
           <t>604 + 6063</t>
         </is>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="70">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="E12" s="102" t="inlineStr">
+      <c r="E12" s="105" t="inlineStr">
         <is>
           <t>EFFECTIFS</t>
         </is>
       </c>
-      <c r="F12" s="102" t="inlineStr">
+      <c r="F12" s="105" t="inlineStr">
         <is>
           <t>le campus</t>
         </is>
       </c>
-      <c r="G12" s="117" t="inlineStr">
+      <c r="G12" s="120" t="inlineStr">
         <is>
           <t>VARIABLE</t>
         </is>
       </c>
-      <c r="H12" s="118" t="inlineStr">
+      <c r="H12" s="121" t="inlineStr">
         <is>
           <t>OUI — c'est le seul euro qui suit vraiment l'élève</t>
         </is>
@@ -7129,36 +7475,36 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Vacataires</t>
         </is>
       </c>
-      <c r="C13" s="116" t="inlineStr">
+      <c r="C13" s="119" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D13" s="67">
+      <c r="D13" s="70">
         <f>'Le moteur'!S34</f>
         <v/>
       </c>
-      <c r="E13" s="102" t="inlineStr">
+      <c r="E13" s="105" t="inlineStr">
         <is>
           <t>HEURES</t>
         </is>
       </c>
-      <c r="F13" s="102" t="inlineStr">
+      <c r="F13" s="105" t="inlineStr">
         <is>
           <t>le programme</t>
         </is>
       </c>
-      <c r="G13" s="119" t="inlineStr">
+      <c r="G13" s="122" t="inlineStr">
         <is>
           <t>SEMI-VARIABLE</t>
         </is>
       </c>
-      <c r="H13" s="120" t="inlineStr">
+      <c r="H13" s="123" t="inlineStr">
         <is>
           <t>Seulement si la classe doit ouvrir</t>
         </is>
@@ -7172,36 +7518,36 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>Enseignants permanents</t>
         </is>
       </c>
-      <c r="C14" s="116" t="inlineStr">
+      <c r="C14" s="119" t="inlineStr">
         <is>
           <t>6411</t>
         </is>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="70">
         <f>'Le moteur'!T34</f>
         <v/>
       </c>
-      <c r="E14" s="102" t="inlineStr">
+      <c r="E14" s="105" t="inlineStr">
         <is>
           <t>HEURES</t>
         </is>
       </c>
-      <c r="F14" s="102" t="inlineStr">
+      <c r="F14" s="105" t="inlineStr">
         <is>
           <t>le nombre de postes</t>
         </is>
       </c>
-      <c r="G14" s="121" t="inlineStr">
+      <c r="G14" s="124" t="inlineStr">
         <is>
           <t>CAPACITÉ</t>
         </is>
       </c>
-      <c r="H14" s="122" t="inlineStr">
+      <c r="H14" s="125" t="inlineStr">
         <is>
           <t>NON — payé pareil pour 24 ou 32 élèves dans la salle</t>
         </is>
@@ -7371,33 +7717,33 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="64" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C22" s="58" t="n">
+      <c r="C22" s="61" t="n">
         <v>840</v>
       </c>
-      <c r="D22" s="123" t="n">
+      <c r="D22" s="126" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="124">
+      <c r="E22" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F22" s="125">
+      <c r="F22" s="128">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="G22" s="67" t="n">
+      <c r="G22" s="70" t="n">
         <v>372.0952843881691</v>
       </c>
-      <c r="H22" s="125">
+      <c r="H22" s="128">
         <f>F22+G22</f>
         <v/>
       </c>
-      <c r="I22" s="103">
+      <c r="I22" s="106">
         <f>IFERROR(H22/$H$26-1,0)</f>
         <v/>
       </c>
@@ -7409,33 +7755,33 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C23" s="58" t="n">
+      <c r="C23" s="61" t="n">
         <v>1688</v>
       </c>
-      <c r="D23" s="123" t="n">
+      <c r="D23" s="126" t="n">
         <v>21.04265402843602</v>
       </c>
-      <c r="E23" s="124">
+      <c r="E23" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F23" s="125">
+      <c r="F23" s="128">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="G23" s="67" t="n">
+      <c r="G23" s="70" t="n">
         <v>361.8303545853921</v>
       </c>
-      <c r="H23" s="125">
+      <c r="H23" s="128">
         <f>F23+G23</f>
         <v/>
       </c>
-      <c r="I23" s="103">
+      <c r="I23" s="106">
         <f>IFERROR(H23/$H$26-1,0)</f>
         <v/>
       </c>
@@ -7447,33 +7793,33 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="61" t="n">
         <v>424</v>
       </c>
-      <c r="D24" s="123" t="n">
+      <c r="D24" s="126" t="n">
         <v>24.05660377358491</v>
       </c>
-      <c r="E24" s="124">
+      <c r="E24" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F24" s="125">
+      <c r="F24" s="128">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="G24" s="67" t="n">
+      <c r="G24" s="70" t="n">
         <v>372.0952832735557</v>
       </c>
-      <c r="H24" s="125">
+      <c r="H24" s="128">
         <f>F24+G24</f>
         <v/>
       </c>
-      <c r="I24" s="103">
+      <c r="I24" s="106">
         <f>IFERROR(H24/$H$26-1,0)</f>
         <v/>
       </c>
@@ -7485,33 +7831,33 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="61" t="n">
         <v>162</v>
       </c>
-      <c r="D25" s="123" t="n">
+      <c r="D25" s="126" t="n">
         <v>34.5679012345679</v>
       </c>
-      <c r="E25" s="124">
+      <c r="E25" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="F25" s="125">
+      <c r="F25" s="128">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="G25" s="67" t="n">
+      <c r="G25" s="70" t="n">
         <v>299.900755961781</v>
       </c>
-      <c r="H25" s="125">
+      <c r="H25" s="128">
         <f>F25+G25</f>
         <v/>
       </c>
-      <c r="I25" s="103">
+      <c r="I25" s="106">
         <f>IFERROR(H25/$H$26-1,0)</f>
         <v/>
       </c>
@@ -7523,36 +7869,36 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="70" t="inlineStr">
+      <c r="B26" s="73" t="inlineStr">
         <is>
           <t>MOYENNE PONDÉRÉE</t>
         </is>
       </c>
-      <c r="C26" s="126">
+      <c r="C26" s="129">
         <f>SUM(C22:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="127">
+      <c r="D26" s="130">
         <f>IFERROR('Le moteur'!Q34/C26,0)</f>
         <v/>
       </c>
-      <c r="E26" s="128">
+      <c r="E26" s="131">
         <f>IFERROR('Le moteur'!S34/'Le moteur'!Q34,0)</f>
         <v/>
       </c>
-      <c r="F26" s="71">
+      <c r="F26" s="74">
         <f>D26*E26</f>
         <v/>
       </c>
-      <c r="G26" s="71">
+      <c r="G26" s="74">
         <f>IFERROR(SUMPRODUCT(C22:C25,G22:G25)/C26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="71">
+      <c r="H26" s="74">
         <f>F26+G26</f>
         <v/>
       </c>
-      <c r="I26" s="94" t="inlineStr">
+      <c r="I26" s="97" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7581,7 +7927,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="129">
+      <c r="B28" s="132">
         <f>"Un facteur "&amp;TEXT(MAX(H22:H25)/MIN(H22:H25),"0.00")&amp;" entre les extrêmes. Le coût variable « moyen » du réseau — "&amp;TEXT(H26,"#,##0 €")&amp;" — ne décrit aucun élève réel : il cadre, il ne décide pas."</f>
         <v/>
       </c>
@@ -7732,48 +8078,48 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="64" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Montpellier</t>
         </is>
       </c>
-      <c r="C34" s="58">
+      <c r="C34" s="61">
         <f>'Le moteur'!N20</f>
         <v/>
       </c>
-      <c r="D34" s="58">
+      <c r="D34" s="61">
         <f>'Le moteur'!G44</f>
         <v/>
       </c>
-      <c r="E34" s="67">
+      <c r="E34" s="70">
         <f>'Le moteur'!R20</f>
         <v/>
       </c>
-      <c r="F34" s="67">
+      <c r="F34" s="70">
         <f>IFERROR(E34/C34,0)</f>
         <v/>
       </c>
-      <c r="G34" s="130">
+      <c r="G34" s="133">
         <f>'Le moteur'!Q20</f>
         <v/>
       </c>
-      <c r="H34" s="67">
+      <c r="H34" s="70">
         <f>'Le moteur'!S20</f>
         <v/>
       </c>
-      <c r="I34" s="67">
+      <c r="I34" s="70">
         <f>IFERROR(H34/'Le moteur'!O20,0)</f>
         <v/>
       </c>
-      <c r="J34" s="67">
+      <c r="J34" s="70">
         <f>'Le moteur'!T20</f>
         <v/>
       </c>
-      <c r="K34" s="67">
+      <c r="K34" s="70">
         <f>IFERROR(J34/C34,0)</f>
         <v/>
       </c>
-      <c r="L34" s="64">
+      <c r="L34" s="67">
         <f>IFERROR(D34/C34,0)</f>
         <v/>
       </c>
@@ -7782,48 +8128,48 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="64" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Nantes</t>
         </is>
       </c>
-      <c r="C35" s="58">
+      <c r="C35" s="61">
         <f>'Le moteur'!N21</f>
         <v/>
       </c>
-      <c r="D35" s="58">
+      <c r="D35" s="61">
         <f>'Le moteur'!G45</f>
         <v/>
       </c>
-      <c r="E35" s="67">
+      <c r="E35" s="70">
         <f>'Le moteur'!R21</f>
         <v/>
       </c>
-      <c r="F35" s="67">
+      <c r="F35" s="70">
         <f>IFERROR(E35/C35,0)</f>
         <v/>
       </c>
-      <c r="G35" s="130">
+      <c r="G35" s="133">
         <f>'Le moteur'!Q21</f>
         <v/>
       </c>
-      <c r="H35" s="67">
+      <c r="H35" s="70">
         <f>'Le moteur'!S21</f>
         <v/>
       </c>
-      <c r="I35" s="67">
+      <c r="I35" s="70">
         <f>IFERROR(H35/'Le moteur'!O21,0)</f>
         <v/>
       </c>
-      <c r="J35" s="67">
+      <c r="J35" s="70">
         <f>'Le moteur'!T21</f>
         <v/>
       </c>
-      <c r="K35" s="67">
+      <c r="K35" s="70">
         <f>IFERROR(J35/C35,0)</f>
         <v/>
       </c>
-      <c r="L35" s="64">
+      <c r="L35" s="67">
         <f>IFERROR(D35/C35,0)</f>
         <v/>
       </c>
@@ -7832,48 +8178,48 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="B36" s="64" t="inlineStr">
         <is>
           <t>Ipac Bachelor Factory Rennes</t>
         </is>
       </c>
-      <c r="C36" s="58">
+      <c r="C36" s="61">
         <f>'Le moteur'!N22</f>
         <v/>
       </c>
-      <c r="D36" s="58">
+      <c r="D36" s="61">
         <f>'Le moteur'!G46</f>
         <v/>
       </c>
-      <c r="E36" s="67">
+      <c r="E36" s="70">
         <f>'Le moteur'!R22</f>
         <v/>
       </c>
-      <c r="F36" s="67">
+      <c r="F36" s="70">
         <f>IFERROR(E36/C36,0)</f>
         <v/>
       </c>
-      <c r="G36" s="130">
+      <c r="G36" s="133">
         <f>'Le moteur'!Q22</f>
         <v/>
       </c>
-      <c r="H36" s="67">
+      <c r="H36" s="70">
         <f>'Le moteur'!S22</f>
         <v/>
       </c>
-      <c r="I36" s="67">
+      <c r="I36" s="70">
         <f>IFERROR(H36/'Le moteur'!O22,0)</f>
         <v/>
       </c>
-      <c r="J36" s="67">
+      <c r="J36" s="70">
         <f>'Le moteur'!T22</f>
         <v/>
       </c>
-      <c r="K36" s="67">
+      <c r="K36" s="70">
         <f>IFERROR(J36/C36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="64">
+      <c r="L36" s="67">
         <f>IFERROR(D36/C36,0)</f>
         <v/>
       </c>
@@ -7882,48 +8228,48 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="64" t="inlineStr">
         <is>
           <t>ISCOM Lille</t>
         </is>
       </c>
-      <c r="C37" s="58">
+      <c r="C37" s="61">
         <f>'Le moteur'!N23</f>
         <v/>
       </c>
-      <c r="D37" s="58">
+      <c r="D37" s="61">
         <f>'Le moteur'!G47</f>
         <v/>
       </c>
-      <c r="E37" s="67">
+      <c r="E37" s="70">
         <f>'Le moteur'!R23</f>
         <v/>
       </c>
-      <c r="F37" s="67">
+      <c r="F37" s="70">
         <f>IFERROR(E37/C37,0)</f>
         <v/>
       </c>
-      <c r="G37" s="130">
+      <c r="G37" s="133">
         <f>'Le moteur'!Q23</f>
         <v/>
       </c>
-      <c r="H37" s="67">
+      <c r="H37" s="70">
         <f>'Le moteur'!S23</f>
         <v/>
       </c>
-      <c r="I37" s="67">
+      <c r="I37" s="70">
         <f>IFERROR(H37/'Le moteur'!O23,0)</f>
         <v/>
       </c>
-      <c r="J37" s="67">
+      <c r="J37" s="70">
         <f>'Le moteur'!T23</f>
         <v/>
       </c>
-      <c r="K37" s="67">
+      <c r="K37" s="70">
         <f>IFERROR(J37/C37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="64">
+      <c r="L37" s="67">
         <f>IFERROR(D37/C37,0)</f>
         <v/>
       </c>
@@ -7932,48 +8278,48 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="64" t="inlineStr">
         <is>
           <t>ISCOM Paris</t>
         </is>
       </c>
-      <c r="C38" s="58">
+      <c r="C38" s="61">
         <f>'Le moteur'!N24</f>
         <v/>
       </c>
-      <c r="D38" s="58">
+      <c r="D38" s="61">
         <f>'Le moteur'!G48</f>
         <v/>
       </c>
-      <c r="E38" s="67">
+      <c r="E38" s="70">
         <f>'Le moteur'!R24</f>
         <v/>
       </c>
-      <c r="F38" s="67">
+      <c r="F38" s="70">
         <f>IFERROR(E38/C38,0)</f>
         <v/>
       </c>
-      <c r="G38" s="130">
+      <c r="G38" s="133">
         <f>'Le moteur'!Q24</f>
         <v/>
       </c>
-      <c r="H38" s="67">
+      <c r="H38" s="70">
         <f>'Le moteur'!S24</f>
         <v/>
       </c>
-      <c r="I38" s="67">
+      <c r="I38" s="70">
         <f>IFERROR(H38/'Le moteur'!O24,0)</f>
         <v/>
       </c>
-      <c r="J38" s="67">
+      <c r="J38" s="70">
         <f>'Le moteur'!T24</f>
         <v/>
       </c>
-      <c r="K38" s="67">
+      <c r="K38" s="70">
         <f>IFERROR(J38/C38,0)</f>
         <v/>
       </c>
-      <c r="L38" s="64">
+      <c r="L38" s="67">
         <f>IFERROR(D38/C38,0)</f>
         <v/>
       </c>
@@ -7982,48 +8328,48 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B39" s="64" t="inlineStr">
         <is>
           <t>ISCOM Toulouse</t>
         </is>
       </c>
-      <c r="C39" s="58">
+      <c r="C39" s="61">
         <f>'Le moteur'!N25</f>
         <v/>
       </c>
-      <c r="D39" s="58">
+      <c r="D39" s="61">
         <f>'Le moteur'!G49</f>
         <v/>
       </c>
-      <c r="E39" s="67">
+      <c r="E39" s="70">
         <f>'Le moteur'!R25</f>
         <v/>
       </c>
-      <c r="F39" s="67">
+      <c r="F39" s="70">
         <f>IFERROR(E39/C39,0)</f>
         <v/>
       </c>
-      <c r="G39" s="130">
+      <c r="G39" s="133">
         <f>'Le moteur'!Q25</f>
         <v/>
       </c>
-      <c r="H39" s="67">
+      <c r="H39" s="70">
         <f>'Le moteur'!S25</f>
         <v/>
       </c>
-      <c r="I39" s="67">
+      <c r="I39" s="70">
         <f>IFERROR(H39/'Le moteur'!O25,0)</f>
         <v/>
       </c>
-      <c r="J39" s="67">
+      <c r="J39" s="70">
         <f>'Le moteur'!T25</f>
         <v/>
       </c>
-      <c r="K39" s="67">
+      <c r="K39" s="70">
         <f>IFERROR(J39/C39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="64">
+      <c r="L39" s="67">
         <f>IFERROR(D39/C39,0)</f>
         <v/>
       </c>
@@ -8032,48 +8378,48 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="64" t="inlineStr">
         <is>
           <t>MBway Bordeaux</t>
         </is>
       </c>
-      <c r="C40" s="58">
+      <c r="C40" s="61">
         <f>'Le moteur'!N26</f>
         <v/>
       </c>
-      <c r="D40" s="58">
+      <c r="D40" s="61">
         <f>'Le moteur'!G50</f>
         <v/>
       </c>
-      <c r="E40" s="67">
+      <c r="E40" s="70">
         <f>'Le moteur'!R26</f>
         <v/>
       </c>
-      <c r="F40" s="67">
+      <c r="F40" s="70">
         <f>IFERROR(E40/C40,0)</f>
         <v/>
       </c>
-      <c r="G40" s="130">
+      <c r="G40" s="133">
         <f>'Le moteur'!Q26</f>
         <v/>
       </c>
-      <c r="H40" s="67">
+      <c r="H40" s="70">
         <f>'Le moteur'!S26</f>
         <v/>
       </c>
-      <c r="I40" s="67">
+      <c r="I40" s="70">
         <f>IFERROR(H40/'Le moteur'!O26,0)</f>
         <v/>
       </c>
-      <c r="J40" s="67">
+      <c r="J40" s="70">
         <f>'Le moteur'!T26</f>
         <v/>
       </c>
-      <c r="K40" s="67">
+      <c r="K40" s="70">
         <f>IFERROR(J40/C40,0)</f>
         <v/>
       </c>
-      <c r="L40" s="64">
+      <c r="L40" s="67">
         <f>IFERROR(D40/C40,0)</f>
         <v/>
       </c>
@@ -8082,48 +8428,48 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="64" t="inlineStr">
         <is>
           <t>MBway Lyon</t>
         </is>
       </c>
-      <c r="C41" s="58">
+      <c r="C41" s="61">
         <f>'Le moteur'!N27</f>
         <v/>
       </c>
-      <c r="D41" s="58">
+      <c r="D41" s="61">
         <f>'Le moteur'!G51</f>
         <v/>
       </c>
-      <c r="E41" s="67">
+      <c r="E41" s="70">
         <f>'Le moteur'!R27</f>
         <v/>
       </c>
-      <c r="F41" s="67">
+      <c r="F41" s="70">
         <f>IFERROR(E41/C41,0)</f>
         <v/>
       </c>
-      <c r="G41" s="130">
+      <c r="G41" s="133">
         <f>'Le moteur'!Q27</f>
         <v/>
       </c>
-      <c r="H41" s="67">
+      <c r="H41" s="70">
         <f>'Le moteur'!S27</f>
         <v/>
       </c>
-      <c r="I41" s="67">
+      <c r="I41" s="70">
         <f>IFERROR(H41/'Le moteur'!O27,0)</f>
         <v/>
       </c>
-      <c r="J41" s="67">
+      <c r="J41" s="70">
         <f>'Le moteur'!T27</f>
         <v/>
       </c>
-      <c r="K41" s="67">
+      <c r="K41" s="70">
         <f>IFERROR(J41/C41,0)</f>
         <v/>
       </c>
-      <c r="L41" s="64">
+      <c r="L41" s="67">
         <f>IFERROR(D41/C41,0)</f>
         <v/>
       </c>
@@ -8132,48 +8478,48 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B42" s="64" t="inlineStr">
         <is>
           <t>MBway Nantes</t>
         </is>
       </c>
-      <c r="C42" s="58">
+      <c r="C42" s="61">
         <f>'Le moteur'!N28</f>
         <v/>
       </c>
-      <c r="D42" s="58">
+      <c r="D42" s="61">
         <f>'Le moteur'!G52</f>
         <v/>
       </c>
-      <c r="E42" s="67">
+      <c r="E42" s="70">
         <f>'Le moteur'!R28</f>
         <v/>
       </c>
-      <c r="F42" s="67">
+      <c r="F42" s="70">
         <f>IFERROR(E42/C42,0)</f>
         <v/>
       </c>
-      <c r="G42" s="130">
+      <c r="G42" s="133">
         <f>'Le moteur'!Q28</f>
         <v/>
       </c>
-      <c r="H42" s="67">
+      <c r="H42" s="70">
         <f>'Le moteur'!S28</f>
         <v/>
       </c>
-      <c r="I42" s="67">
+      <c r="I42" s="70">
         <f>IFERROR(H42/'Le moteur'!O28,0)</f>
         <v/>
       </c>
-      <c r="J42" s="67">
+      <c r="J42" s="70">
         <f>'Le moteur'!T28</f>
         <v/>
       </c>
-      <c r="K42" s="67">
+      <c r="K42" s="70">
         <f>IFERROR(J42/C42,0)</f>
         <v/>
       </c>
-      <c r="L42" s="64">
+      <c r="L42" s="67">
         <f>IFERROR(D42/C42,0)</f>
         <v/>
       </c>
@@ -8182,48 +8528,48 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="B43" s="64" t="inlineStr">
         <is>
           <t>MBway Paris</t>
         </is>
       </c>
-      <c r="C43" s="58">
+      <c r="C43" s="61">
         <f>'Le moteur'!N29</f>
         <v/>
       </c>
-      <c r="D43" s="58">
+      <c r="D43" s="61">
         <f>'Le moteur'!G53</f>
         <v/>
       </c>
-      <c r="E43" s="67">
+      <c r="E43" s="70">
         <f>'Le moteur'!R29</f>
         <v/>
       </c>
-      <c r="F43" s="67">
+      <c r="F43" s="70">
         <f>IFERROR(E43/C43,0)</f>
         <v/>
       </c>
-      <c r="G43" s="130">
+      <c r="G43" s="133">
         <f>'Le moteur'!Q29</f>
         <v/>
       </c>
-      <c r="H43" s="67">
+      <c r="H43" s="70">
         <f>'Le moteur'!S29</f>
         <v/>
       </c>
-      <c r="I43" s="67">
+      <c r="I43" s="70">
         <f>IFERROR(H43/'Le moteur'!O29,0)</f>
         <v/>
       </c>
-      <c r="J43" s="67">
+      <c r="J43" s="70">
         <f>'Le moteur'!T29</f>
         <v/>
       </c>
-      <c r="K43" s="67">
+      <c r="K43" s="70">
         <f>IFERROR(J43/C43,0)</f>
         <v/>
       </c>
-      <c r="L43" s="64">
+      <c r="L43" s="67">
         <f>IFERROR(D43/C43,0)</f>
         <v/>
       </c>
@@ -8232,48 +8578,48 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="B44" s="64" t="inlineStr">
         <is>
           <t>Pigier Bordeaux</t>
         </is>
       </c>
-      <c r="C44" s="58">
+      <c r="C44" s="61">
         <f>'Le moteur'!N30</f>
         <v/>
       </c>
-      <c r="D44" s="58">
+      <c r="D44" s="61">
         <f>'Le moteur'!G54</f>
         <v/>
       </c>
-      <c r="E44" s="67">
+      <c r="E44" s="70">
         <f>'Le moteur'!R30</f>
         <v/>
       </c>
-      <c r="F44" s="67">
+      <c r="F44" s="70">
         <f>IFERROR(E44/C44,0)</f>
         <v/>
       </c>
-      <c r="G44" s="130">
+      <c r="G44" s="133">
         <f>'Le moteur'!Q30</f>
         <v/>
       </c>
-      <c r="H44" s="67">
+      <c r="H44" s="70">
         <f>'Le moteur'!S30</f>
         <v/>
       </c>
-      <c r="I44" s="67">
+      <c r="I44" s="70">
         <f>IFERROR(H44/'Le moteur'!O30,0)</f>
         <v/>
       </c>
-      <c r="J44" s="67">
+      <c r="J44" s="70">
         <f>'Le moteur'!T30</f>
         <v/>
       </c>
-      <c r="K44" s="67">
+      <c r="K44" s="70">
         <f>IFERROR(J44/C44,0)</f>
         <v/>
       </c>
-      <c r="L44" s="64">
+      <c r="L44" s="67">
         <f>IFERROR(D44/C44,0)</f>
         <v/>
       </c>
@@ -8282,48 +8628,48 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
-      <c r="B45" s="61" t="inlineStr">
+      <c r="B45" s="64" t="inlineStr">
         <is>
           <t>Pigier Lyon</t>
         </is>
       </c>
-      <c r="C45" s="58">
+      <c r="C45" s="61">
         <f>'Le moteur'!N31</f>
         <v/>
       </c>
-      <c r="D45" s="58">
+      <c r="D45" s="61">
         <f>'Le moteur'!G55</f>
         <v/>
       </c>
-      <c r="E45" s="67">
+      <c r="E45" s="70">
         <f>'Le moteur'!R31</f>
         <v/>
       </c>
-      <c r="F45" s="67">
+      <c r="F45" s="70">
         <f>IFERROR(E45/C45,0)</f>
         <v/>
       </c>
-      <c r="G45" s="130">
+      <c r="G45" s="133">
         <f>'Le moteur'!Q31</f>
         <v/>
       </c>
-      <c r="H45" s="67">
+      <c r="H45" s="70">
         <f>'Le moteur'!S31</f>
         <v/>
       </c>
-      <c r="I45" s="67">
+      <c r="I45" s="70">
         <f>IFERROR(H45/'Le moteur'!O31,0)</f>
         <v/>
       </c>
-      <c r="J45" s="67">
+      <c r="J45" s="70">
         <f>'Le moteur'!T31</f>
         <v/>
       </c>
-      <c r="K45" s="67">
+      <c r="K45" s="70">
         <f>IFERROR(J45/C45,0)</f>
         <v/>
       </c>
-      <c r="L45" s="64">
+      <c r="L45" s="67">
         <f>IFERROR(D45/C45,0)</f>
         <v/>
       </c>
@@ -8332,48 +8678,48 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B46" s="64" t="inlineStr">
         <is>
           <t>Tunon Lyon</t>
         </is>
       </c>
-      <c r="C46" s="58">
+      <c r="C46" s="61">
         <f>'Le moteur'!N32</f>
         <v/>
       </c>
-      <c r="D46" s="58">
+      <c r="D46" s="61">
         <f>'Le moteur'!G56</f>
         <v/>
       </c>
-      <c r="E46" s="67">
+      <c r="E46" s="70">
         <f>'Le moteur'!R32</f>
         <v/>
       </c>
-      <c r="F46" s="67">
+      <c r="F46" s="70">
         <f>IFERROR(E46/C46,0)</f>
         <v/>
       </c>
-      <c r="G46" s="130">
+      <c r="G46" s="133">
         <f>'Le moteur'!Q32</f>
         <v/>
       </c>
-      <c r="H46" s="67">
+      <c r="H46" s="70">
         <f>'Le moteur'!S32</f>
         <v/>
       </c>
-      <c r="I46" s="67">
+      <c r="I46" s="70">
         <f>IFERROR(H46/'Le moteur'!O32,0)</f>
         <v/>
       </c>
-      <c r="J46" s="67">
+      <c r="J46" s="70">
         <f>'Le moteur'!T32</f>
         <v/>
       </c>
-      <c r="K46" s="67">
+      <c r="K46" s="70">
         <f>IFERROR(J46/C46,0)</f>
         <v/>
       </c>
-      <c r="L46" s="64">
+      <c r="L46" s="67">
         <f>IFERROR(D46/C46,0)</f>
         <v/>
       </c>
@@ -8382,48 +8728,48 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="61" t="inlineStr">
+      <c r="B47" s="64" t="inlineStr">
         <is>
           <t>Tunon Paris</t>
         </is>
       </c>
-      <c r="C47" s="58">
+      <c r="C47" s="61">
         <f>'Le moteur'!N33</f>
         <v/>
       </c>
-      <c r="D47" s="58">
+      <c r="D47" s="61">
         <f>'Le moteur'!G57</f>
         <v/>
       </c>
-      <c r="E47" s="67">
+      <c r="E47" s="70">
         <f>'Le moteur'!R33</f>
         <v/>
       </c>
-      <c r="F47" s="67">
+      <c r="F47" s="70">
         <f>IFERROR(E47/C47,0)</f>
         <v/>
       </c>
-      <c r="G47" s="130">
+      <c r="G47" s="133">
         <f>'Le moteur'!Q33</f>
         <v/>
       </c>
-      <c r="H47" s="67">
+      <c r="H47" s="70">
         <f>'Le moteur'!S33</f>
         <v/>
       </c>
-      <c r="I47" s="67">
+      <c r="I47" s="70">
         <f>IFERROR(H47/'Le moteur'!O33,0)</f>
         <v/>
       </c>
-      <c r="J47" s="67">
+      <c r="J47" s="70">
         <f>'Le moteur'!T33</f>
         <v/>
       </c>
-      <c r="K47" s="67">
+      <c r="K47" s="70">
         <f>IFERROR(J47/C47,0)</f>
         <v/>
       </c>
-      <c r="L47" s="64">
+      <c r="L47" s="67">
         <f>IFERROR(D47/C47,0)</f>
         <v/>
       </c>
@@ -8432,48 +8778,48 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="70" t="inlineStr">
+      <c r="B48" s="73" t="inlineStr">
         <is>
           <t>GROUPE · 14 campus</t>
         </is>
       </c>
-      <c r="C48" s="126">
+      <c r="C48" s="129">
         <f>SUM(C34:C47)</f>
         <v/>
       </c>
-      <c r="D48" s="126">
+      <c r="D48" s="129">
         <f>SUM(D34:D47)</f>
         <v/>
       </c>
-      <c r="E48" s="71">
+      <c r="E48" s="74">
         <f>SUM(E34:E47)</f>
         <v/>
       </c>
-      <c r="F48" s="71">
+      <c r="F48" s="74">
         <f>IFERROR(E48/C48,0)</f>
         <v/>
       </c>
-      <c r="G48" s="131">
+      <c r="G48" s="134">
         <f>SUM(G34:G47)</f>
         <v/>
       </c>
-      <c r="H48" s="71">
+      <c r="H48" s="74">
         <f>SUM(H34:H47)</f>
         <v/>
       </c>
-      <c r="I48" s="71">
+      <c r="I48" s="74">
         <f>IFERROR(H48/'Le moteur'!O34,0)</f>
         <v/>
       </c>
-      <c r="J48" s="71">
+      <c r="J48" s="74">
         <f>SUM(J34:J47)</f>
         <v/>
       </c>
-      <c r="K48" s="71">
+      <c r="K48" s="74">
         <f>IFERROR(J48/C48,0)</f>
         <v/>
       </c>
-      <c r="L48" s="132">
+      <c r="L48" s="135">
         <f>MIN(L34:L47)</f>
         <v/>
       </c>
@@ -8502,7 +8848,7 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="129">
+      <c r="B50" s="132">
         <f>"Les permanents pèsent "&amp;TEXT(J48/(E48+H48+J48),"0 %")&amp;" du coût d'enseignement du réseau, et pas un euro d'entre eux ne bouge quand un élève de plus s'assoit."</f>
         <v/>
       </c>
@@ -8593,13 +8939,13 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="133" t="inlineStr">
+      <c r="B55" s="136" t="inlineStr">
         <is>
           <t>TANT QU'IL RESTE UNE PLACE</t>
         </is>
       </c>
       <c r="C55" s="21" t="n"/>
-      <c r="D55" s="134">
+      <c r="D55" s="137">
         <f>"les consommables seuls  —  de "&amp;TEXT(MIN(F34:F47),"#,##0 €")&amp;" à "&amp;TEXT(MAX(F34:F47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -8616,13 +8962,13 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="135" t="inlineStr">
+      <c r="B56" s="138" t="inlineStr">
         <is>
           <t>QUAND LA CLASSE EST PLEINE</t>
         </is>
       </c>
       <c r="C56" s="13" t="n"/>
-      <c r="D56" s="136" t="inlineStr">
+      <c r="D56" s="139" t="inlineStr">
         <is>
           <t>+ la quote-part du vacataire d'une classe neuve  —  et là, le programme compte</t>
         </is>
@@ -8642,7 +8988,7 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="19" t="n"/>
       <c r="C57" s="19" t="n"/>
-      <c r="D57" s="137" t="inlineStr">
+      <c r="D57" s="140" t="inlineStr">
         <is>
           <t>Le masque bascule seul : IF(inscrits gagnés &lt;= places libres ; consommables ; consommables + vacataires du campus ÷ places du campus).</t>
         </is>
@@ -8736,32 +9082,32 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
-      <c r="B61" s="61" t="inlineStr">
+      <c r="B61" s="64" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C61" s="130">
+      <c r="C61" s="133">
         <f>'Intégration &amp; contrôles'!C9</f>
         <v/>
       </c>
-      <c r="D61" s="124">
+      <c r="D61" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E61" s="67">
+      <c r="E61" s="70">
         <f>C61*D61</f>
         <v/>
       </c>
-      <c r="F61" s="58">
+      <c r="F61" s="61">
         <f>'Intégration &amp; contrôles'!D9</f>
         <v/>
       </c>
-      <c r="G61" s="125">
+      <c r="G61" s="128">
         <f>E61/F61</f>
         <v/>
       </c>
-      <c r="H61" s="138">
+      <c r="H61" s="141">
         <f>"de "&amp;TEXT(G61+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G61+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -8774,32 +9120,32 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
-      <c r="B62" s="61" t="inlineStr">
+      <c r="B62" s="64" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C62" s="130">
+      <c r="C62" s="133">
         <f>'Intégration &amp; contrôles'!C13</f>
         <v/>
       </c>
-      <c r="D62" s="124">
+      <c r="D62" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E62" s="67">
+      <c r="E62" s="70">
         <f>C62*D62</f>
         <v/>
       </c>
-      <c r="F62" s="58">
+      <c r="F62" s="61">
         <f>'Intégration &amp; contrôles'!D13</f>
         <v/>
       </c>
-      <c r="G62" s="125">
+      <c r="G62" s="128">
         <f>E62/F62</f>
         <v/>
       </c>
-      <c r="H62" s="138">
+      <c r="H62" s="141">
         <f>"de "&amp;TEXT(G62+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G62+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -8812,32 +9158,32 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
-      <c r="B63" s="61" t="inlineStr">
+      <c r="B63" s="64" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C63" s="130">
+      <c r="C63" s="133">
         <f>'Intégration &amp; contrôles'!C10</f>
         <v/>
       </c>
-      <c r="D63" s="124">
+      <c r="D63" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E63" s="67">
+      <c r="E63" s="70">
         <f>C63*D63</f>
         <v/>
       </c>
-      <c r="F63" s="58">
+      <c r="F63" s="61">
         <f>'Intégration &amp; contrôles'!D10</f>
         <v/>
       </c>
-      <c r="G63" s="125">
+      <c r="G63" s="128">
         <f>E63/F63</f>
         <v/>
       </c>
-      <c r="H63" s="138">
+      <c r="H63" s="141">
         <f>"de "&amp;TEXT(G63+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G63+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -8850,32 +9196,32 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="61" t="inlineStr">
+      <c r="B64" s="64" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C64" s="130">
+      <c r="C64" s="133">
         <f>'Intégration &amp; contrôles'!C11</f>
         <v/>
       </c>
-      <c r="D64" s="124">
+      <c r="D64" s="127">
         <f>$E$26</f>
         <v/>
       </c>
-      <c r="E64" s="67">
+      <c r="E64" s="70">
         <f>C64*D64</f>
         <v/>
       </c>
-      <c r="F64" s="58">
+      <c r="F64" s="61">
         <f>'Intégration &amp; contrôles'!D11</f>
         <v/>
       </c>
-      <c r="G64" s="125">
+      <c r="G64" s="128">
         <f>E64/F64</f>
         <v/>
       </c>
-      <c r="H64" s="138">
+      <c r="H64" s="141">
         <f>"de "&amp;TEXT(G64+MIN($F$34:$F$47),"#,##0 €")&amp;" à "&amp;TEXT(G64+MAX($F$34:$F$47),"#,##0 €")&amp;" selon le campus"</f>
         <v/>
       </c>
@@ -8940,7 +9286,7 @@
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="139" t="inlineStr">
+      <c r="B68" s="142" t="inlineStr">
         <is>
           <t>⑤  Et les enseignants permanents, ils sont où ?</t>
         </is>
@@ -8980,7 +9326,7 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="134" t="inlineStr">
+      <c r="B70" s="137" t="inlineStr">
         <is>
           <t>Un professeur permanent est un ENGAGEMENT DE CAPACITÉ, pas un coût à l'élève : il est payé pareil que la salle contienne 24 ou 32 étudiants. Il varie avec le nombre de POSTES — donc par palier, et le palier suivant n'est pas une classe, c'est un campus.</t>
         </is>
@@ -9000,7 +9346,7 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="136" t="inlineStr">
+      <c r="B71" s="139" t="inlineStr">
         <is>
           <t>Le vacataire est la seule ressource enseignante qui s'achète à la classe. Et le 621 est du personnel EXTÉRIEUR : une facture, donc sans charges sociales 645 en plus, contrairement au 6411.</t>
         </is>
@@ -9020,8 +9366,8 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
-      <c r="B72" s="140">
-        <f>"Sur "&amp;TEXT('Budget 2027'!D77+'Budget 2027'!D89+'Budget 2027'!D94,"#,##0 €")&amp;" de charges, "&amp;TEXT('Budget 2027'!D59,"#,##0 €")&amp;" seulement bougent quand un élève de plus s'assoit — soit "&amp;TEXT('Budget 2027'!D59/('Budget 2027'!D77+'Budget 2027'!D89+'Budget 2027'!D94),"0.0 %")&amp;". Tout le reste est de la capacité déjà engagée : c'est ce qui rend le geste aussi rentable tant qu'il reste des places."</f>
+      <c r="B72" s="143">
+        <f>"Sur "&amp;TEXT('Budget 2027'!D83+'Budget 2027'!D95+'Budget 2027'!D100,"#,##0 €")&amp;" de charges, "&amp;TEXT('Budget 2027'!D65,"#,##0 €")&amp;" seulement bougent quand un élève de plus s'assoit — soit "&amp;TEXT('Budget 2027'!D65/('Budget 2027'!D83+'Budget 2027'!D95+'Budget 2027'!D100),"0.0 %")&amp;". Tout le reste est de la capacité déjà engagée : c'est ce qui rend le geste aussi rentable tant qu'il reste des places."</f>
         <v/>
       </c>
       <c r="C72" s="19" t="n"/>
@@ -9554,15 +9900,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 EDUSERVICES · Le coût variable&amp;R&amp;"Arial"&amp;8 page &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00E7E6E6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9727,18 +10084,18 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="141" t="inlineStr">
+      <c r="B9" s="144" t="inlineStr">
         <is>
           <t>Bachelor · alternance</t>
         </is>
       </c>
-      <c r="C9" s="142" t="n">
+      <c r="C9" s="145" t="n">
         <v>480</v>
       </c>
-      <c r="D9" s="143" t="n">
+      <c r="D9" s="146" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="144" t="inlineStr">
+      <c r="E9" s="147" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -9753,18 +10110,18 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="141" t="inlineStr">
+      <c r="B10" s="144" t="inlineStr">
         <is>
           <t>Bachelor · initial</t>
         </is>
       </c>
-      <c r="C10" s="142" t="n">
+      <c r="C10" s="145" t="n">
         <v>600</v>
       </c>
-      <c r="D10" s="143" t="n">
+      <c r="D10" s="146" t="n">
         <v>32</v>
       </c>
-      <c r="E10" s="144" t="inlineStr">
+      <c r="E10" s="147" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -9779,18 +10136,18 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="141" t="inlineStr">
+      <c r="B11" s="144" t="inlineStr">
         <is>
           <t>BTS · alternance</t>
         </is>
       </c>
-      <c r="C11" s="142" t="n">
+      <c r="C11" s="145" t="n">
         <v>700</v>
       </c>
-      <c r="D11" s="143" t="n">
+      <c r="D11" s="146" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="144" t="inlineStr">
+      <c r="E11" s="147" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -9805,18 +10162,18 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="145" t="inlineStr">
+      <c r="B12" s="148" t="inlineStr">
         <is>
           <t>BTS · initial</t>
         </is>
       </c>
-      <c r="C12" s="146" t="n">
+      <c r="C12" s="149" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="147" t="n">
+      <c r="D12" s="150" t="n">
         <v>30</v>
       </c>
-      <c r="E12" s="148" t="inlineStr">
+      <c r="E12" s="151" t="inlineStr">
         <is>
           <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
         </is>
@@ -9831,18 +10188,18 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="141" t="inlineStr">
+      <c r="B13" s="144" t="inlineStr">
         <is>
           <t>Mastère · alternance</t>
         </is>
       </c>
-      <c r="C13" s="142" t="n">
+      <c r="C13" s="145" t="n">
         <v>420</v>
       </c>
-      <c r="D13" s="143" t="n">
+      <c r="D13" s="146" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="144" t="inlineStr">
+      <c r="E13" s="147" t="inlineStr">
         <is>
           <t>maquette pédagogique</t>
         </is>
@@ -9857,18 +10214,18 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="145" t="inlineStr">
+      <c r="B14" s="148" t="inlineStr">
         <is>
           <t>Mastère · initial</t>
         </is>
       </c>
-      <c r="C14" s="146" t="n">
+      <c r="C14" s="149" t="n">
         <v>520</v>
       </c>
-      <c r="D14" s="147" t="n">
+      <c r="D14" s="150" t="n">
         <v>26</v>
       </c>
-      <c r="E14" s="148" t="inlineStr">
+      <c r="E14" s="151" t="inlineStr">
         <is>
           <t>maquette pédagogique  (programme absent du réseau en 2026)</t>
         </is>
@@ -10009,22 +10366,22 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="98" t="inlineStr">
         <is>
           <t>B  ·  Marque</t>
         </is>
       </c>
-      <c r="C22" s="149" t="inlineStr">
+      <c r="C22" s="152" t="inlineStr">
         <is>
           <t>MARQUE</t>
         </is>
       </c>
-      <c r="D22" s="149" t="inlineStr">
+      <c r="D22" s="152" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="E22" s="149" t="inlineStr">
+      <c r="E22" s="152" t="inlineStr">
         <is>
           <t>regroupement d'affichage</t>
         </is>
@@ -10039,22 +10396,22 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="95" t="inlineStr">
+      <c r="B23" s="98" t="inlineStr">
         <is>
           <t>C  ·  Campus</t>
         </is>
       </c>
-      <c r="C23" s="149" t="inlineStr">
+      <c r="C23" s="152" t="inlineStr">
         <is>
           <t>CAMPUS</t>
         </is>
       </c>
-      <c r="D23" s="149" t="inlineStr">
+      <c r="D23" s="152" t="inlineStr">
         <is>
           <t>dimension</t>
         </is>
       </c>
-      <c r="E23" s="149" t="inlineStr">
+      <c r="E23" s="152" t="inlineStr">
         <is>
           <t>libellé azienda</t>
         </is>
@@ -10069,22 +10426,22 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="95" t="inlineStr">
+      <c r="B24" s="98" t="inlineStr">
         <is>
           <t>D  ·  Leads payants 2024</t>
         </is>
       </c>
-      <c r="C24" s="149" t="inlineStr">
+      <c r="C24" s="152" t="inlineStr">
         <is>
           <t>LEAD_PAY_2024</t>
         </is>
       </c>
-      <c r="D24" s="149" t="inlineStr">
+      <c r="D24" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E24" s="149" t="inlineStr"/>
+      <c r="E24" s="152" t="inlineStr"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
@@ -10095,22 +10452,22 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="95" t="inlineStr">
+      <c r="B25" s="98" t="inlineStr">
         <is>
           <t>E  ·  Leads payants 2025</t>
         </is>
       </c>
-      <c r="C25" s="149" t="inlineStr">
+      <c r="C25" s="152" t="inlineStr">
         <is>
           <t>LEAD_PAY_2025</t>
         </is>
       </c>
-      <c r="D25" s="149" t="inlineStr">
+      <c r="D25" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E25" s="149" t="inlineStr"/>
+      <c r="E25" s="152" t="inlineStr"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -10121,22 +10478,22 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="95" t="inlineStr">
+      <c r="B26" s="98" t="inlineStr">
         <is>
           <t>F  ·  Leads payants 2026</t>
         </is>
       </c>
-      <c r="C26" s="149" t="inlineStr">
+      <c r="C26" s="152" t="inlineStr">
         <is>
           <t>LEAD_PAY_2026</t>
         </is>
       </c>
-      <c r="D26" s="149" t="inlineStr">
+      <c r="D26" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E26" s="149" t="inlineStr">
+      <c r="E26" s="152" t="inlineStr">
         <is>
           <t>base du geste</t>
         </is>
@@ -10151,22 +10508,22 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="95" t="inlineStr">
+      <c r="B27" s="98" t="inlineStr">
         <is>
           <t>G  ·  Budget acq. 2024</t>
         </is>
       </c>
-      <c r="C27" s="149" t="inlineStr">
+      <c r="C27" s="152" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2024</t>
         </is>
       </c>
-      <c r="D27" s="149" t="inlineStr">
+      <c r="D27" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E27" s="149" t="inlineStr"/>
+      <c r="E27" s="152" t="inlineStr"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
@@ -10177,22 +10534,22 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
-      <c r="B28" s="95" t="inlineStr">
+      <c r="B28" s="98" t="inlineStr">
         <is>
           <t>H  ·  Budget acq. 2025</t>
         </is>
       </c>
-      <c r="C28" s="149" t="inlineStr">
+      <c r="C28" s="152" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2025</t>
         </is>
       </c>
-      <c r="D28" s="149" t="inlineStr">
+      <c r="D28" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E28" s="149" t="inlineStr"/>
+      <c r="E28" s="152" t="inlineStr"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
@@ -10203,22 +10560,22 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="95" t="inlineStr">
+      <c r="B29" s="98" t="inlineStr">
         <is>
           <t>I  ·  Budget acq. 2026</t>
         </is>
       </c>
-      <c r="C29" s="149" t="inlineStr">
+      <c r="C29" s="152" t="inlineStr">
         <is>
           <t>SPEND_ACQ_2026</t>
         </is>
       </c>
-      <c r="D29" s="149" t="inlineStr">
+      <c r="D29" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E29" s="149">
+      <c r="E29" s="152">
         <f> compte 6231</f>
         <v/>
       </c>
@@ -10232,22 +10589,22 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
-      <c r="B30" s="95" t="inlineStr">
+      <c r="B30" s="98" t="inlineStr">
         <is>
           <t>J  ·  Élasticité</t>
         </is>
       </c>
-      <c r="C30" s="149" t="inlineStr">
+      <c r="C30" s="152" t="inlineStr">
         <is>
           <t>ELASTICITE</t>
         </is>
       </c>
-      <c r="D30" s="150" t="inlineStr">
+      <c r="D30" s="153" t="inlineStr">
         <is>
           <t>NON additive</t>
         </is>
       </c>
-      <c r="E30" s="149" t="inlineStr">
+      <c r="E30" s="152" t="inlineStr">
         <is>
           <t>régression log-log, reste au campus</t>
         </is>
@@ -10262,22 +10619,22 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
-      <c r="B31" s="95" t="inlineStr">
+      <c r="B31" s="98" t="inlineStr">
         <is>
           <t>K  ·  Leads totaux 2026</t>
         </is>
       </c>
-      <c r="C31" s="149" t="inlineStr">
+      <c r="C31" s="152" t="inlineStr">
         <is>
           <t>LEAD_TOT_N</t>
         </is>
       </c>
-      <c r="D31" s="149" t="inlineStr">
+      <c r="D31" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E31" s="149" t="inlineStr">
+      <c r="E31" s="152" t="inlineStr">
         <is>
           <t>dénominateur de la conversion</t>
         </is>
@@ -10292,22 +10649,22 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="95" t="inlineStr">
+      <c r="B32" s="98" t="inlineStr">
         <is>
           <t>L  ·  Inscrits 2026</t>
         </is>
       </c>
-      <c r="C32" s="149" t="inlineStr">
+      <c r="C32" s="152" t="inlineStr">
         <is>
           <t>INSCRITS_N</t>
         </is>
       </c>
-      <c r="D32" s="149" t="inlineStr">
+      <c r="D32" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E32" s="149" t="inlineStr">
+      <c r="E32" s="152" t="inlineStr">
         <is>
           <t>numérateur de la conversion</t>
         </is>
@@ -10322,22 +10679,22 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
-      <c r="B33" s="95" t="inlineStr">
+      <c r="B33" s="98" t="inlineStr">
         <is>
           <t>M  ·  CA nouveaux 2026</t>
         </is>
       </c>
-      <c r="C33" s="149" t="inlineStr">
+      <c r="C33" s="152" t="inlineStr">
         <is>
           <t>CA_NEW_N</t>
         </is>
       </c>
-      <c r="D33" s="149" t="inlineStr">
+      <c r="D33" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E33" s="149" t="inlineStr"/>
+      <c r="E33" s="152" t="inlineStr"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
@@ -10348,22 +10705,22 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
-      <c r="B34" s="95" t="inlineStr">
+      <c r="B34" s="98" t="inlineStr">
         <is>
           <t>N  ·  Effectifs 2026</t>
         </is>
       </c>
-      <c r="C34" s="149" t="inlineStr">
+      <c r="C34" s="152" t="inlineStr">
         <is>
           <t>EFFECTIFS_N</t>
         </is>
       </c>
-      <c r="D34" s="149" t="inlineStr">
+      <c r="D34" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E34" s="149" t="inlineStr"/>
+      <c r="E34" s="152" t="inlineStr"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
@@ -10374,22 +10731,22 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="95" t="inlineStr">
+      <c r="B35" s="98" t="inlineStr">
         <is>
           <t>O  ·  Places 2026</t>
         </is>
       </c>
-      <c r="C35" s="149" t="inlineStr">
+      <c r="C35" s="152" t="inlineStr">
         <is>
           <t>PLACES_N</t>
         </is>
       </c>
-      <c r="D35" s="149" t="inlineStr">
+      <c r="D35" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E35" s="149" t="inlineStr">
+      <c r="E35" s="152" t="inlineStr">
         <is>
           <t>classes × capacité</t>
         </is>
@@ -10404,22 +10761,22 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
-      <c r="B36" s="95" t="inlineStr">
+      <c r="B36" s="98" t="inlineStr">
         <is>
           <t>P  ·  Classes 2026</t>
         </is>
       </c>
-      <c r="C36" s="149" t="inlineStr">
+      <c r="C36" s="152" t="inlineStr">
         <is>
           <t>CLASSES_N</t>
         </is>
       </c>
-      <c r="D36" s="149" t="inlineStr">
+      <c r="D36" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E36" s="149" t="inlineStr"/>
+      <c r="E36" s="152" t="inlineStr"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
@@ -10430,22 +10787,22 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
-      <c r="B37" s="151" t="inlineStr">
+      <c r="B37" s="154" t="inlineStr">
         <is>
           <t>Q  ·  Heures d'enseignement 2026</t>
         </is>
       </c>
-      <c r="C37" s="152" t="inlineStr">
+      <c r="C37" s="155" t="inlineStr">
         <is>
           <t>HEURES_N</t>
         </is>
       </c>
-      <c r="D37" s="152" t="inlineStr">
+      <c r="D37" s="155" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E37" s="152" t="inlineStr">
+      <c r="E37" s="155" t="inlineStr">
         <is>
           <t>À AJOUTER À LA VUE</t>
         </is>
@@ -10460,22 +10817,22 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="95" t="inlineStr">
+      <c r="B38" s="98" t="inlineStr">
         <is>
           <t>R  ·  Consommables 604+6063</t>
         </is>
       </c>
-      <c r="C38" s="149" t="inlineStr">
+      <c r="C38" s="152" t="inlineStr">
         <is>
           <t>COUT_CONSO_N</t>
         </is>
       </c>
-      <c r="D38" s="149" t="inlineStr">
+      <c r="D38" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E38" s="149" t="inlineStr"/>
+      <c r="E38" s="152" t="inlineStr"/>
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
@@ -10486,22 +10843,22 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
-      <c r="B39" s="95" t="inlineStr">
+      <c r="B39" s="98" t="inlineStr">
         <is>
           <t>S  ·  Vacataires 621</t>
         </is>
       </c>
-      <c r="C39" s="149" t="inlineStr">
+      <c r="C39" s="152" t="inlineStr">
         <is>
           <t>COUT_VACAT_N</t>
         </is>
       </c>
-      <c r="D39" s="149" t="inlineStr">
+      <c r="D39" s="152" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E39" s="149" t="inlineStr"/>
+      <c r="E39" s="152" t="inlineStr"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
@@ -10512,22 +10869,22 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
-      <c r="B40" s="151" t="inlineStr">
+      <c r="B40" s="154" t="inlineStr">
         <is>
           <t>T  ·  Enseignants permanents 6411</t>
         </is>
       </c>
-      <c r="C40" s="152" t="inlineStr">
+      <c r="C40" s="155" t="inlineStr">
         <is>
           <t>COUT_PERM_N</t>
         </is>
       </c>
-      <c r="D40" s="152" t="inlineStr">
+      <c r="D40" s="155" t="inlineStr">
         <is>
           <t>mesure</t>
         </is>
       </c>
-      <c r="E40" s="152" t="inlineStr">
+      <c r="E40" s="155" t="inlineStr">
         <is>
           <t>À AJOUTER À LA VUE</t>
         </is>
@@ -10650,23 +11007,23 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
-      <c r="B47" s="153" t="inlineStr">
+      <c r="B47" s="156" t="inlineStr">
         <is>
           <t>Δ budget d'acquisition</t>
         </is>
       </c>
-      <c r="C47" s="153" t="inlineStr">
+      <c r="C47" s="156" t="inlineStr">
         <is>
           <t>F4</t>
         </is>
       </c>
-      <c r="D47" s="154" t="inlineStr">
+      <c r="D47" s="157" t="inlineStr">
         <is>
           <t>SAISIE</t>
         </is>
       </c>
-      <c r="E47" s="153" t="n"/>
-      <c r="F47" s="153" t="inlineStr">
+      <c r="E47" s="156" t="n"/>
+      <c r="F47" s="156" t="inlineStr">
         <is>
           <t>la seule cellule modifiable du classeur</t>
         </is>
@@ -10680,23 +11037,23 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
-      <c r="B48" s="155" t="inlineStr">
+      <c r="B48" s="158" t="inlineStr">
         <is>
           <t>Conversion lead → inscrit</t>
         </is>
       </c>
-      <c r="C48" s="77" t="inlineStr">
+      <c r="C48" s="80" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D48" s="156" t="inlineStr">
+      <c r="D48" s="159" t="inlineStr">
         <is>
           <t>=IFERROR(L20/K20,0)</t>
         </is>
       </c>
-      <c r="E48" s="77" t="n"/>
-      <c r="F48" s="77" t="inlineStr">
+      <c r="E48" s="80" t="n"/>
+      <c r="F48" s="80" t="inlineStr">
         <is>
           <t>INSCRITS_N ÷ LEAD_TOT_N — jamais pré-calculée, sinon la ligne groupe se trompe</t>
         </is>
@@ -10710,23 +11067,23 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
-      <c r="B49" s="155" t="inlineStr">
+      <c r="B49" s="158" t="inlineStr">
         <is>
           <t>CA par inscrit</t>
         </is>
       </c>
-      <c r="C49" s="77" t="inlineStr">
+      <c r="C49" s="80" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D49" s="156" t="inlineStr">
+      <c r="D49" s="159" t="inlineStr">
         <is>
           <t>=IFERROR(M20/L20,0)</t>
         </is>
       </c>
-      <c r="E49" s="77" t="n"/>
-      <c r="F49" s="77" t="inlineStr">
+      <c r="E49" s="80" t="n"/>
+      <c r="F49" s="80" t="inlineStr">
         <is>
           <t>CA_NEW_N ÷ INSCRITS_N</t>
         </is>
@@ -10740,23 +11097,23 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
-      <c r="B50" s="155" t="inlineStr">
+      <c r="B50" s="158" t="inlineStr">
         <is>
           <t>Consommables / élève</t>
         </is>
       </c>
-      <c r="C50" s="77" t="inlineStr">
+      <c r="C50" s="80" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D50" s="156" t="inlineStr">
+      <c r="D50" s="159" t="inlineStr">
         <is>
           <t>=IFERROR(R20/N20,0)</t>
         </is>
       </c>
-      <c r="E50" s="77" t="n"/>
-      <c r="F50" s="77" t="inlineStr">
+      <c r="E50" s="80" t="n"/>
+      <c r="F50" s="80" t="inlineStr">
         <is>
           <t>COUT_CONSO_N ÷ EFFECTIFS_N</t>
         </is>
@@ -10770,23 +11127,23 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
-      <c r="B51" s="155" t="inlineStr">
+      <c r="B51" s="158" t="inlineStr">
         <is>
           <t>Places libres</t>
         </is>
       </c>
-      <c r="C51" s="77" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="D51" s="156" t="inlineStr">
+      <c r="D51" s="159" t="inlineStr">
         <is>
           <t>=O20-N20</t>
         </is>
       </c>
-      <c r="E51" s="77" t="n"/>
-      <c r="F51" s="77" t="inlineStr">
+      <c r="E51" s="80" t="n"/>
+      <c r="F51" s="80" t="inlineStr">
         <is>
           <t>PLACES_N − EFFECTIFS_N : la borne physique du geste</t>
         </is>
@@ -10800,23 +11157,23 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
-      <c r="B52" s="155" t="inlineStr">
+      <c r="B52" s="158" t="inlineStr">
         <is>
           <t>Δ budget</t>
         </is>
       </c>
-      <c r="C52" s="77" t="inlineStr">
+      <c r="C52" s="80" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D52" s="156" t="inlineStr">
+      <c r="D52" s="159" t="inlineStr">
         <is>
           <t>=I20*$F$4</t>
         </is>
       </c>
-      <c r="E52" s="77" t="n"/>
-      <c r="F52" s="77" t="inlineStr">
+      <c r="E52" s="80" t="n"/>
+      <c r="F52" s="80" t="inlineStr">
         <is>
           <t>le geste, appliqué au budget 2026</t>
         </is>
@@ -10830,23 +11187,23 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
-      <c r="B53" s="155" t="inlineStr">
+      <c r="B53" s="158" t="inlineStr">
         <is>
           <t>Inscrits gagnés</t>
         </is>
       </c>
-      <c r="C53" s="77" t="inlineStr">
+      <c r="C53" s="80" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D53" s="156" t="inlineStr">
+      <c r="D53" s="159" t="inlineStr">
         <is>
           <t>=F20*((1+$F$4)^J20-1)*D44</t>
         </is>
       </c>
-      <c r="E53" s="77" t="n"/>
-      <c r="F53" s="77" t="inlineStr">
+      <c r="E53" s="80" t="n"/>
+      <c r="F53" s="80" t="inlineStr">
         <is>
           <t>leads payants × l'effet d'élasticité, converti au taux du campus</t>
         </is>
@@ -10860,23 +11217,23 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
-      <c r="B54" s="155" t="inlineStr">
+      <c r="B54" s="158" t="inlineStr">
         <is>
           <t>CA gagné</t>
         </is>
       </c>
-      <c r="C54" s="77" t="inlineStr">
+      <c r="C54" s="80" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="D54" s="156" t="inlineStr">
+      <c r="D54" s="159" t="inlineStr">
         <is>
           <t>=I44*E44</t>
         </is>
       </c>
-      <c r="E54" s="77" t="n"/>
-      <c r="F54" s="77" t="inlineStr">
+      <c r="E54" s="80" t="n"/>
+      <c r="F54" s="80" t="inlineStr">
         <is>
           <t>inscrits gagnés × CA par inscrit</t>
         </is>
@@ -10890,23 +11247,23 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
-      <c r="B55" s="155" t="inlineStr">
+      <c r="B55" s="158" t="inlineStr">
         <is>
           <t>Coût marginal / élève</t>
         </is>
       </c>
-      <c r="C55" s="77" t="inlineStr">
+      <c r="C55" s="80" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D55" s="156" t="inlineStr">
+      <c r="D55" s="159" t="inlineStr">
         <is>
           <t>=IF(I44&lt;=G44,F44,F44+S20/O20)</t>
         </is>
       </c>
-      <c r="E55" s="77" t="n"/>
-      <c r="F55" s="77" t="inlineStr">
+      <c r="E55" s="80" t="n"/>
+      <c r="F55" s="80" t="inlineStr">
         <is>
           <t>consommables seuls, + quote-part vacataire si la classe doit ouvrir</t>
         </is>
@@ -10920,23 +11277,23 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
-      <c r="B56" s="155" t="inlineStr">
+      <c r="B56" s="158" t="inlineStr">
         <is>
           <t>EBITDA gagné</t>
         </is>
       </c>
-      <c r="C56" s="77" t="inlineStr">
+      <c r="C56" s="80" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D56" s="156" t="inlineStr">
+      <c r="D56" s="159" t="inlineStr">
         <is>
           <t>=J44-H44-I44*K44</t>
         </is>
       </c>
-      <c r="E56" s="77" t="n"/>
-      <c r="F56" s="77" t="inlineStr">
+      <c r="E56" s="80" t="n"/>
+      <c r="F56" s="80" t="inlineStr">
         <is>
           <t>CA gagné − Δ budget − coût de service</t>
         </is>
@@ -10950,23 +11307,23 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
-      <c r="B57" s="155" t="inlineStr">
+      <c r="B57" s="158" t="inlineStr">
         <is>
           <t>CAC marginal</t>
         </is>
       </c>
-      <c r="C57" s="77" t="inlineStr">
+      <c r="C57" s="80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D57" s="156" t="inlineStr">
+      <c r="D57" s="159" t="inlineStr">
         <is>
           <t>=IFERROR(H44/I44,0)</t>
         </is>
       </c>
-      <c r="E57" s="77" t="n"/>
-      <c r="F57" s="77" t="inlineStr">
+      <c r="E57" s="80" t="n"/>
+      <c r="F57" s="80" t="inlineStr">
         <is>
           <t>Δ budget ÷ inscrits gagnés</t>
         </is>
@@ -11096,29 +11453,29 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
-      <c r="B64" s="61" t="inlineStr">
+      <c r="B64" s="64" t="inlineStr">
         <is>
           <t>Budget d'acquisition : dépense CRM 2026 = compte 6231</t>
         </is>
       </c>
-      <c r="C64" s="102" t="n"/>
-      <c r="D64" s="67">
+      <c r="C64" s="105" t="n"/>
+      <c r="D64" s="70">
         <f>'Le moteur'!I34</f>
         <v/>
       </c>
-      <c r="E64" s="67">
-        <f>'Budget 2027'!D76</f>
-        <v/>
-      </c>
-      <c r="F64" s="67">
+      <c r="E64" s="70">
+        <f>'Budget 2027'!D82</f>
+        <v/>
+      </c>
+      <c r="F64" s="70">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="116">
+      <c r="G64" s="119">
         <f>IF(ABS(F64)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H64" s="138" t="inlineStr">
+      <c r="H64" s="141" t="inlineStr">
         <is>
           <t>socle CRM contre comptabilité</t>
         </is>
@@ -11130,29 +11487,29 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
-      <c r="B65" s="61" t="inlineStr">
+      <c r="B65" s="64" t="inlineStr">
         <is>
           <t>Consommables : comptes 604 + 6063 = COUT_CONSO_N</t>
         </is>
       </c>
-      <c r="C65" s="102" t="n"/>
-      <c r="D65" s="67">
-        <f>'Budget 2027'!D60+'Budget 2027'!D61</f>
-        <v/>
-      </c>
-      <c r="E65" s="67">
+      <c r="C65" s="105" t="n"/>
+      <c r="D65" s="70">
+        <f>'Budget 2027'!D66+'Budget 2027'!D67</f>
+        <v/>
+      </c>
+      <c r="E65" s="70">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="F65" s="67">
+      <c r="F65" s="70">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="116">
+      <c r="G65" s="119">
         <f>IF(ABS(F65)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H65" s="138" t="inlineStr">
+      <c r="H65" s="141" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -11164,29 +11521,29 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
-      <c r="B66" s="61" t="inlineStr">
+      <c r="B66" s="64" t="inlineStr">
         <is>
           <t>Vacataires : compte 621 = COUT_VACAT_N</t>
         </is>
       </c>
-      <c r="C66" s="102" t="n"/>
-      <c r="D66" s="67">
-        <f>'Budget 2027'!D63</f>
-        <v/>
-      </c>
-      <c r="E66" s="67">
+      <c r="C66" s="105" t="n"/>
+      <c r="D66" s="70">
+        <f>'Budget 2027'!D69</f>
+        <v/>
+      </c>
+      <c r="E66" s="70">
         <f>'Le moteur'!S34</f>
         <v/>
       </c>
-      <c r="F66" s="67">
+      <c r="F66" s="70">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="116">
+      <c r="G66" s="119">
         <f>IF(ABS(F66)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H66" s="138" t="inlineStr">
+      <c r="H66" s="141" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -11198,29 +11555,29 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
-      <c r="B67" s="61" t="inlineStr">
+      <c r="B67" s="64" t="inlineStr">
         <is>
           <t>Permanents : compte 6411 = COUT_PERM_N</t>
         </is>
       </c>
-      <c r="C67" s="102" t="n"/>
-      <c r="D67" s="67">
-        <f>'Budget 2027'!D65</f>
-        <v/>
-      </c>
-      <c r="E67" s="67">
+      <c r="C67" s="105" t="n"/>
+      <c r="D67" s="70">
+        <f>'Budget 2027'!D71</f>
+        <v/>
+      </c>
+      <c r="E67" s="70">
         <f>'Le moteur'!T34</f>
         <v/>
       </c>
-      <c r="F67" s="67">
+      <c r="F67" s="70">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="116">
+      <c r="G67" s="119">
         <f>IF(ABS(F67)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H67" s="138" t="inlineStr">
+      <c r="H67" s="141" t="inlineStr">
         <is>
           <t>comptes contre agrégat de la vue</t>
         </is>
@@ -11232,29 +11589,29 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
-      <c r="B68" s="61" t="inlineStr">
+      <c r="B68" s="64" t="inlineStr">
         <is>
           <t>Effectifs : grain programme = grain campus</t>
         </is>
       </c>
-      <c r="C68" s="102" t="n"/>
-      <c r="D68" s="58">
+      <c r="C68" s="105" t="n"/>
+      <c r="D68" s="61">
         <f>'Le coût variable'!C26</f>
         <v/>
       </c>
-      <c r="E68" s="58">
+      <c r="E68" s="61">
         <f>'Le moteur'!N34</f>
         <v/>
       </c>
-      <c r="F68" s="58">
+      <c r="F68" s="61">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="116">
+      <c r="G68" s="119">
         <f>IF(ABS(F68)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H68" s="138" t="inlineStr">
+      <c r="H68" s="141" t="inlineStr">
         <is>
           <t>cycle × modalité contre campus</t>
         </is>
@@ -11266,29 +11623,29 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
-      <c r="B69" s="61" t="inlineStr">
+      <c r="B69" s="64" t="inlineStr">
         <is>
           <t>Allocation : consommables alloués aux programmes = total réseau</t>
         </is>
       </c>
-      <c r="C69" s="102" t="n"/>
-      <c r="D69" s="67">
+      <c r="C69" s="105" t="n"/>
+      <c r="D69" s="70">
         <f>SUMPRODUCT('Le coût variable'!C22:C25,'Le coût variable'!G22:G25)</f>
         <v/>
       </c>
-      <c r="E69" s="67">
+      <c r="E69" s="70">
         <f>'Le moteur'!R34</f>
         <v/>
       </c>
-      <c r="F69" s="67">
+      <c r="F69" s="70">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="116">
+      <c r="G69" s="119">
         <f>IF(ABS(F69)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H69" s="138" t="inlineStr">
+      <c r="H69" s="141" t="inlineStr">
         <is>
           <t>la clé EFFECTIFS ne perd rien</t>
         </is>
@@ -11300,29 +11657,29 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
-      <c r="B70" s="61" t="inlineStr">
+      <c r="B70" s="64" t="inlineStr">
         <is>
           <t>EBITDA gagné : CA gagné − Δ budget − coût de service</t>
         </is>
       </c>
-      <c r="C70" s="102" t="n"/>
-      <c r="D70" s="67">
+      <c r="C70" s="105" t="n"/>
+      <c r="D70" s="70">
         <f>'Le moteur'!J58-'Le moteur'!H58-'Le moteur'!I58*'Le moteur'!K58</f>
         <v/>
       </c>
-      <c r="E70" s="67">
+      <c r="E70" s="70">
         <f>'Le moteur'!L58</f>
         <v/>
       </c>
-      <c r="F70" s="67">
+      <c r="F70" s="70">
         <f>D70-E70</f>
         <v/>
       </c>
-      <c r="G70" s="116">
+      <c r="G70" s="119">
         <f>IF(ABS(F70)&lt;1,"OK","À VÉRIFIER")</f>
         <v/>
       </c>
-      <c r="H70" s="138" t="inlineStr">
+      <c r="H70" s="141" t="inlineStr">
         <is>
           <t>additivité de la ligne groupe</t>
         </is>
@@ -11334,29 +11691,29 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
-      <c r="B71" s="61" t="inlineStr">
+      <c r="B71" s="64" t="inlineStr">
         <is>
           <t>Régime du coût marginal : inscrits gagnés ≤ places libres</t>
         </is>
       </c>
-      <c r="C71" s="102" t="n"/>
-      <c r="D71" s="58">
+      <c r="C71" s="105" t="n"/>
+      <c r="D71" s="61">
         <f>'Le moteur'!I58</f>
         <v/>
       </c>
-      <c r="E71" s="58">
+      <c r="E71" s="61">
         <f>'Le moteur'!G58</f>
         <v/>
       </c>
-      <c r="F71" s="58">
+      <c r="F71" s="61">
         <f>E71-D71</f>
         <v/>
       </c>
-      <c r="G71" s="116">
+      <c r="G71" s="119">
         <f>IF(F71&gt;0,"OK · marge","BASCULE")</f>
         <v/>
       </c>
-      <c r="H71" s="138" t="inlineStr">
+      <c r="H71" s="141" t="inlineStr">
         <is>
           <t>si dépassé, une classe ouvre</t>
         </is>
@@ -11396,39 +11753,39 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="5" t="n"/>
-      <c r="B74" s="157" t="inlineStr">
+      <c r="B74" s="160" t="inlineStr">
         <is>
           <t>Ce qu'il reste à faire côté Tagetik</t>
         </is>
       </c>
-      <c r="C74" s="112" t="n"/>
-      <c r="D74" s="112" t="n"/>
-      <c r="E74" s="112" t="n"/>
-      <c r="F74" s="112" t="n"/>
-      <c r="G74" s="112" t="n"/>
-      <c r="H74" s="112" t="n"/>
-      <c r="I74" s="112" t="n"/>
-      <c r="J74" s="112" t="n"/>
-      <c r="K74" s="112" t="n"/>
-      <c r="L74" s="112" t="n"/>
+      <c r="C74" s="115" t="n"/>
+      <c r="D74" s="115" t="n"/>
+      <c r="E74" s="115" t="n"/>
+      <c r="F74" s="115" t="n"/>
+      <c r="G74" s="115" t="n"/>
+      <c r="H74" s="115" t="n"/>
+      <c r="I74" s="115" t="n"/>
+      <c r="J74" s="115" t="n"/>
+      <c r="K74" s="115" t="n"/>
+      <c r="L74" s="115" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
-      <c r="B75" s="114" t="inlineStr">
+      <c r="B75" s="117" t="inlineStr">
         <is>
           <t>① ajouter HEURES_N et COUT_PERM_N à V_MOTEUR_CAL (le .sql du dépôt les porte).  ② brancher le tableau ① sur la vue, une ligne par campus, hiérarchie MARQUE ▸ CAMPUS.  ③ le tableau ② est un masque de saisie : seule F4 est ouverte.  ④ l'onglet « Le coût variable » ne lit que le tableau ① et les paramètres ci-dessus.</t>
         </is>
       </c>
-      <c r="C75" s="115" t="n"/>
-      <c r="D75" s="115" t="n"/>
-      <c r="E75" s="115" t="n"/>
-      <c r="F75" s="115" t="n"/>
-      <c r="G75" s="115" t="n"/>
-      <c r="H75" s="115" t="n"/>
-      <c r="I75" s="115" t="n"/>
-      <c r="J75" s="115" t="n"/>
-      <c r="K75" s="115" t="n"/>
-      <c r="L75" s="115" t="n"/>
+      <c r="C75" s="118" t="n"/>
+      <c r="D75" s="118" t="n"/>
+      <c r="E75" s="118" t="n"/>
+      <c r="F75" s="118" t="n"/>
+      <c r="G75" s="118" t="n"/>
+      <c r="H75" s="118" t="n"/>
+      <c r="I75" s="118" t="n"/>
+      <c r="J75" s="118" t="n"/>
+      <c r="K75" s="118" t="n"/>
+      <c r="L75" s="118" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -11495,6 +11852,16 @@
       <formula>NOT(ISNUMBER(SEARCH("OK",$G64)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 EDUSERVICES · Intégration &amp; contrôles&amp;R&amp;"Arial"&amp;8 page &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/eduservices/MOTEUR_MASQUE.xlsx
+++ b/eduservices/MOTEUR_MASQUE.xlsx
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AF7" s="16" t="inlineStr">
         <is>
-          <t>HYP_CONV_LEAD</t>
+          <t>HYP_CNV_LEAD_CAND</t>
         </is>
       </c>
       <c r="AG7" s="16" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AF8" s="16" t="inlineStr">
         <is>
-          <t>HYP_CONV_ADM</t>
+          <t>HYP_CNV_ADM_INS</t>
         </is>
       </c>
       <c r="AG8" s="16" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AF9" s="16" t="inlineStr">
         <is>
-          <t>HYP_PASSAGE</t>
+          <t>HYP_PASS_RATE</t>
         </is>
       </c>
       <c r="AG9" s="16" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="AF15" s="16" t="inlineStr">
         <is>
-          <t>HYP_FEE</t>
+          <t>HYP_FILE_FEE</t>
         </is>
       </c>
       <c r="AG15" s="16" t="inlineStr">
